--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP3"/>
+  <dimension ref="A1:CX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,6 +757,176 @@
           <t>Sound_Loudspeaker</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Battery_Charging</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Body_Build</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Comms_NFC</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Display_Protection</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>EU LABEL_Battery</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>EU LABEL_Energy</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>EU LABEL_Free fall</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>EU LABEL_Repairability</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Main Camera_Dual</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Main Camera_Features</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Main Camera_Quad</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Main Camera_Triple</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Main Camera_Video</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>Misc_Models</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>Misc_SAR</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Network_2</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>Network_3</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>Network_4</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>Network_4G bands</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>Network_5G bands</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>Our Tests_Battery</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>Our Tests_Display</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>Our Tests_Loudspeaker</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>Our Tests_Performance</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>Platform_Chipset</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>Platform_GPU</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>Selfie camera_Dual</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>Selfie camera_Features</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>Selfie camera_Single</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>Selfie camera_Video</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -794,55 +964,37 @@
           <t>2006, February</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="H2" t="n">
+        <v>2006</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="J2" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="n">
+        <v>112</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>240</v>
+      </c>
+      <c r="P2" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>154</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -852,17 +1004,13 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
+      <c r="V2" t="n">
+        <v>900</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
+      <c r="Y2" t="n">
+        <v>1.16</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -934,10 +1082,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="AR2" t="n">
+        <v>2</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1055,6 +1201,40 @@
           <t>No</t>
         </is>
       </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1145,6 +1325,8696 @@
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A36</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a36-13497.php</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025, March 02</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>162.9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>12GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>190.94</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>239.00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>202.00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>27509</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>$ 190.94 / C$ 381.20 / £ 202.00 / € 239.00 / ₹ 27,509</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>162.9 x 78.2 x 7.4 mm (6.41 x 3.08 x 0.29 in)</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + eSIM · Nano-SIM + Nano-SIM + eSIM + eSIM (max 2 at a time)</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>195 g (6.88 oz)</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>5.4, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~86.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 120Hz, 1200 nits (HBM), 1900 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Virtual Proximity Sensing</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2025, March 02</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 10</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 6GB RAM, 256GB 8GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>Lavender, Black, White, Lime</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>$ 190.94 / C$ 381.20 / £ 202.00 / € 239.00 / ₹ 27,509</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.53 W/kg (head)     1.29 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.4 GHz Cortex-A78 &amp; 4x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>Android 15, up to 6 major Android upgrades, One UI 8.5</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>45W wired, 66% in 30 min, 100% in 68 min</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>IP67 dust/water resistant (up to 1m for 30 min)</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus+), plastic frame, glass back (Gorilla Glass Victus+)</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass Victus+, Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>41:28h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>Class C (90 falls)</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/1.96", 0.8µm, PDAF, OIS 8 MP, f/2.2, 123˚, (ultrawide), 1/4.0", 1.12µm 5 MP, f/2.4, (macro)</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>UFS 2.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>SM-A366E, SM-A366E/DS, SM-A366B, SM-A366B/DS, SM-A366U, SM-A366U1, SM-A366W</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>1.07 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 12, 13, 14, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>2, 5, 25, 41, 66, 71, 77, 78 SA/NSA/Sub6/mmWave - USA</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 25, 26, 28, 32, 38, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>Active use score 11:38h</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>1233 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>-26.2 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>AnTuTu: 613492 (v10) GeekBench: 2917 (v6) 3DMark: 912 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Qualcomm SM6475-AB Snapdragon 6 Gen 3 (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>Adreno 710</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.2, (wide)</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps, 10-bit HDR</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a26-13679.php</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025, March 02</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>163.77</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>193.00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>162.19</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>$ 163.77 / C$ 288.28 / £ 162.19 / € 193.00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>164 x 77.5 x 7.7 mm (6.46 x 3.05 x 0.30 in)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + eSIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>200 g (7.05 oz)</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~86.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 120Hz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Virtual proximity sensing</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>2025, March 02</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 19</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM, 256GB 6GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>Black, White, Mint, Peach Pink</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>$ 163.77 / C$ 288.28 / £ 162.19 / € 193.00</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.41 W/kg (head)     0.96 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.4 GHz Cortex-A78 &amp; 4x2.0 GHz Cortex-A55) - Global Octa-core (2x2.4 GHz Cortex-A78 &amp; 6x2.0 GHz Cortex-A55) - LATAM</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>Android 15, up to 6 major Android upgrades, One UI 8.5</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>IP67 dust/water resistant (up to 1m for 30 min)</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus+), plastic frame, glass back (Gorilla Glass Victus+)</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass Victus+, Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>37:05h endurance, 1200 cycles</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>Class B (269 falls)</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 27mm (wide), 1/2.76", 0.64µm, PDAF, OIS 8 MP, f/2.2, 120˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps, 720p@480fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>SM-A266E, SM-A266E/DS, SM-A266E/DSN, SM-A266B, SM-A266B/DS, SM-A266B/DSN, SM-A266U, SM-A266U1, SM-A266W</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>0.75 W/kg (head)     1.09 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 12, 13, 14, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>2, 5, 25, 41, 66, 71, 77, 78 SA/NSA/Sub6/mmWave - USA</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 26, 28, 32, 38, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>Active use score 10:44h</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>777 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>-27.1 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>AnTuTu: 579811 (v10) GeekBench: 2768 (v6) 3DMark: 794 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Exynos 1380 (5 nm) - Global Exynos 1280 (5 nm) - LATAM</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>Mali-G68 MP5 - Global Mali-G68 - LATAM</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, (wide), 1/3.06", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m16-13680.php</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025, February 27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 05</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>164.4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>15999</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>₹ 15,999</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>164.4 x 77.9 x 7.9 mm (6.47 x 3.07 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>191 g (6.74 oz)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~86.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 90Hz, 800 nits (HBM)</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>2025, February 27</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 05</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>Thunder Black, MInt Green, Blush Pink</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>₹ 15,999</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.99 W/kg (head)     1.19 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>Android 15, up to 6 major Android upgrades, One UI 7</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>IP54 dust protected and water resistant (water splashes)</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/2.76", 0.64µm, AF 5 MP, f/2.2, (ultrawide), 1/5.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>1080p@30fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>SM-M166P, SM-M166P/DS</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>1.08 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 26, 28, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 28, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 6300 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, (wide), 1/3.1", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m06-13681.php</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025, February 27</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 07</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>167.4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>12499</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>₹ 12,499</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Li-Ion 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>167.4 x 77.4 x 8 mm (6.59 x 3.05 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>191 g (6.74 oz)</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~260 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>6.74 inches, 109.7 cm 2 (~84.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>PLS LCD, 90Hz, 800 nits (HBM)</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>2025, February 27</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, March 07</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>Blazing Black, Sage Green</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>₹ 12,499</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1.30 W/kg (head)     1.30 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>Android 15, up to 4 major Android upgrades, One UI Core 7.0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>SM-M066B, SM-M066B/DS</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>1.05 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 26, 28, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 26, 28, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 6300 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A06 5G</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a06_5g-13662.php</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025, February 19</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>167.3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>169.99</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>12290</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>C$ 169.99 / ₹ 12,290</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Li-Ion 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>167.3 x 77.3 x 8 mm (6.59 x 3.04 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>191 g (6.74 oz)</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~262 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~83.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>PLS LCD, 90Hz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>2025, February 19</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 19</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>Black, Gray, Light Green</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>C$ 169.99 / ₹ 12,290</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>1.30 W/kg (head)     1.30 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>Android 15, up to 4 major Android upgrades, One UI 7</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>IP54 dust protected and water resistant (water splashes)</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 26mm (wide), 1/2.75", 0.64µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>SM-A066B, SM-A066B/DS</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>1.05 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 26, 28, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 26, 28, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 6300 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy F06 5G</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_f06_5g-13663.php</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025, February 12</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Available. Released February 20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>167.4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>12298</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>₹ 12,298</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Li-Ion 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>167.4 x 77.4 x 8 mm (6.59 x 3.05 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>191 g (6.74 oz)</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~262 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~83.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>PLS LCD, 800 nits (HBM)</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>2025, February 12</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Available. Released February 20</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Bahama Blue, Lit Violet</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>₹ 12,298</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>1.30 W/kg (head)     1.30 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>Android 15, up to 4 major Android upgrades, One UI Core 7.0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>SM-E066B, SM-E066B/DS</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>1.05 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>LTE</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 6300 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S25 Ultra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s25_ultra-13322.php</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>162.8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1TB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>12GB | 16GB</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>755.74</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>768.00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>634.25</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>93900</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>$ 755.74 / C$ 1,079.84 / £ 634.25 / € 768.00 / ₹ 93,900</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Li-Ion 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>162.8 x 77.6 x 8.2 mm (6.41 x 3.06 x 0.32 in)</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + Nano-SIM + eSIM + eSIM (max 2 at a time) - INT · Nano-SIM + eSIM + eSIM (max 2 at a time) - USA · Nano-SIM + Nano-SIM - CN</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>218 g (7.69 oz)</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>5.4, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, DisplayPort 1.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e/7, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>DX anti-reflective coating</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>1440 x 3120 pixels, 19.5:9 ratio (~498 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>6.9 inches, 116.9 cm 2 (~92.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Dynamic LTPO AMOLED 2X, 120Hz, HDR10+, 2600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samsung DeX, Samsung Wireless DeX (desktop experience support) Ultra Wideband (UWB) support</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>256GB 12GB RAM, 512GB 12GB RAM, 1TB 12GB RAM, 1TB 16GB RAM</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>Titanium Silver Blue, Titanium Black, Titanium White Silver, Titanium Gray, Titanium Jade Green, Titanium Jet Black, Titanium Pink Gold</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>$ 755.74 / C$ 1,079.84 / £ 634.25 / € 768.00 / ₹ 93,900</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>1.25 W/kg (head)     1.42 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>HSPA, LTE (CA), 5G</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>Octa-core (2x4.47 GHz Oryon V2 Phoenix L + 6x3.53 GHz Oryon V2 Phoenix M)</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>Android 15, up to 7 major Android upgrades, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>45W wired, PD3.0, 65% in 30 min 15W wireless (Qi2 Ready) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Stylus</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>Glass front (Corning Gorilla Armor 2), glass back (Gorilla Glass Victus 2), titanium frame (grade 5)</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Armor 2, Mohs level 6</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>44:54h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>Class A (270 falls)</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>Laser AF, Best Face, LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>200 MP, f/1.7, 24mm (wide), 1/1.3", 0.6µm, multi-directional PDAF, OIS 10 MP, f/2.4, 67mm (telephoto), 1/3.52", 1.12µm, PDAF, OIS, 3x optical zoom 50 MP, f/3.4, 111mm (periscope telephoto), 1/2.52", 0.7µm, PDAF, OIS, 5x optical zoom 50 MP, f/1.9, 120˚ (ultrawide), 1/2.5", 0.7µm, dual pixel PDAF, Super Steady video</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>8K@24/30fps, 4K@30/60/120fps, 1080p@30/60/120/240fps, 10-bit HDR, HDR10+, stereo sound rec., gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>UFS 4.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>SM-S938B, SM-S938B/DS, SM-S938U, SM-S938U1, SM-S938W, SM-S938N, SM-S9380, SM-S938E, SM-S938E/DS</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>1.26 W/kg (head)     0.64 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>1, 2, 5, 7, 25, 28, 41, 66, 71, 77, 78, 257, 258, 260, 261 SA/NSA/Sub6/mmWave - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 75, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>Active use score 14:49h</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>1417 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>-24.6 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>AnTuTu: 2207809 (v10) GeekBench: 9846 (v6) 3DMark: 6687 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8750-AC Snapdragon 8 Elite (3 nm)</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>Adreno 830 (1200 MHz)</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>HDR, HDR10+</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.2, 26mm (wide), 1/3.2", 1.12µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S25+</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s25+-13609.php</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>557.22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>735.00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>549.00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>$ 557.22 / C$ 869.99 / £ 549.00 / € 735.00</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Li-Ion 4900 mAh</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>158.4 x 75.8 x 7.3 mm (6.24 x 2.98 x 0.29 in)</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + Nano-SIM + eSIM + eSIM (max 2 at a time) - INT · Nano-SIM + eSIM + eSIM (max 2 at a time) - USA · Nano-SIM + Nano-SIM - CN</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>190 g (6.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>5.4, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, DisplayPort 1.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e/7, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>1440 x 3120 pixels, 19.5:9 ratio (~513 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~91.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Dynamic LTPO AMOLED 2X, 120Hz, HDR10+, 2600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samsung DeX, Samsung Wireless DeX (desktop experience support) Ultra Wideband (UWB) support</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>256GB 12GB RAM, 512GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>Icy Blue, Mint, Navy, Silver Shadow, Pink Gold, Coral Red, Blue Black</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>$ 557.22 / C$ 869.99 / £ 549.00 / € 735.00</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>1.26 W/kg (head)     1.26 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>HSPA, LTE (CA), 5G</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>Octa-core (2x4.47 GHz Oryon V2 Phoenix L + 6x3.53 GHz Oryon V2 Phoenix M)</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>Android 15, up to 7 major Android upgrades, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>45W wired, PD3.0, 65% in 30 min 15W wireless (Qi2 Ready) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Armor aluminum 2 frame</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus 2), glass back (Gorilla Glass Victus 2), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass Victus 2, Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>43:38h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>Class A (270 falls)</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>Best Face, LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 24mm (wide), 1/1.56", 1.0µm, dual pixel PDAF, OIS 10 MP, f/2.4, 67mm (telephoto), 1/3.94", 1.0µm, PDAF, OIS, 3x optical zoom 12 MP, f/2.2, 13mm, 120˚ (ultrawide), 1/2.55" 1.4µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>8K@24/30fps, 4K@30/60fps, 1080p@30/60/120/240fps, 10-bit HDR, HDR10+, stereo sound rec., gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>UFS 4.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>SM-S936B, SM-S936B/DS, SM-S936U, SM-S936U1, SM-S936W, SM-S936N, SM-S9360, SM-S936E, SM-S936E/DS</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>1.16 W/kg (head)     0.81 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>1, 2, 5, 7, 25, 28, 41, 66, 71, 77, 78, 257, 258, 260, 261 SA/NSA/Sub6/mmWave - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 75, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>Active use score 14:26h</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>1449 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>-25.1 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>AnTuTu: 2133477 (v10) GeekBench: 9669 (v6) 3DMark: 6601 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8750-AC Snapdragon 8 Elite (3 nm)</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>Adreno 830 (1200 MHz)</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>HDR, HDR10+</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.2, 26mm (wide), 1/3.2", 1.12µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s25-13610.php</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>146.9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>417.09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>449.99</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>420.96</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>74999</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>$ 417.09 / C$ 667.99 / £ 420.96 / € 449.99 / ₹ 74,999</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Li-Ion 4000 mAh</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>146.9 x 70.5 x 7.2 mm (5.78 x 2.78 x 0.28 in)</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + Nano-SIM + eSIM + eSIM (max 2 at a time) - INT · Nano-SIM + eSIM + eSIM (max 2 at a time) - USA · Nano-SIM + Nano-SIM - CN</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>162 g (5.71 oz)</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>5.4, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, DisplayPort 1.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e/7, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~416 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>6.2 inches, 94.4 cm 2 (~91.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Dynamic LTPO AMOLED 2X, 120Hz, HDR10+, 2600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samsung DeX, Samsung Wireless DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>2025, January 22</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, February 03</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>128GB 12GB RAM, 256GB 12GB RAM, 512GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>Icy Blue, Mint, Navy, Silver Shadow, Pink Gold, Coral Red, Blue Black</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>$ 417.09 / C$ 667.99 / £ 420.96 / € 449.99 / ₹ 74,999</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>1.29 W/kg (head)     1.36 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>HSPA, LTE (CA), 5G</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>Octa-core (2x4.47 GHz Oryon V2 Phoenix L + 6x3.53 GHz Oryon V2 Phoenix M)</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>Android 15, up to 7 major Android upgrades, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>25W wired, PD3.0, 50% in 30 min 15W wireless (Qi2 Ready) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Armor aluminum 2 frame</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus 2), glass back (Gorilla Glass Victus 2), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass Victus 2, Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>37:16h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>Class A (270 falls)</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>Best Face, LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 24mm (wide), 1/1.56", 1.0µm, dual pixel PDAF, OIS 10 MP, f/2.4, 67mm (telephoto), 1/3.94", 1.0µm, PDAF, OIS, 3x optical zoom 12 MP, f/2.2, 13mm, 120˚ (ultrawide), 1/2.55" 1.4µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>8K@24/30fps, 4K@30/60fps, 1080p@30/60/120/240fps, 10-bit HDR, HDR10+, stereo sound rec., gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>UFS 4.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>SM-S931B, SM-S931B/DS, SM-S931U, SM-S931U1, SM-S931W, SM-S931N, SM-S9310, SM-S931E, SM-S931E/DS</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>1.13 W/kg (head)     0.92 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>1, 2, 5, 7, 25, 28, 41, 66, 71, 77, 78, 257, 258, 260, 261 SA/NSA/Sub6/mmWave - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 75, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>Active use score 13:09h</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>1395 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>-26.1 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>AnTuTu: 2193701 (v10) GeekBench: 10050 (v6) 3DMark: 6755 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8750-AC Snapdragon 8 Elite (3 nm)</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
+          <t>Adreno 830 (1200 MHz)</t>
+        </is>
+      </c>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr">
+        <is>
+          <t>HDR, HDR10+</t>
+        </is>
+      </c>
+      <c r="CV12" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.2, 26mm (wide), 1/3.2", 1.12µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX12" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Z Fold Special</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Galaxy Z Fold SE, Samsung Galaxy Z Fold Special Edition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_z_fold_special-13452.php</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2024, October 21</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 24</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>157.9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>142.6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>About 1870 EUR</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Li-Po 4400 mAh</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Unfolded: 157.9 x 142.6 x 4.9 mm Folded: 157.9 x 72.8 x 10.6 mm</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Nano-SIM + eSIM + eSIM (max 2 at a time)</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>236 g (8.32 oz)</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e/7, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>Ultra Flexible Glass (UFG) Cover display: Dynamic LTPO AMOLED 2X, 120Hz, 2600 nits (peak), Corning Gorilla Glass Victus 2 6.5 inches, 1080 x 2520 pixels</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>1968 x 2184 pixels (~367 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>8.0 inches, 205.3 cm 2 (~91.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Foldable Dynamic LTPO AMOLED 2X, 120Hz, HDR10+, 2600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samsung DeX (desktop experience support) Ultra Wideband (UWB) support</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>2024, October 21</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 24</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>512GB 16GB RAM</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>About 1870 EUR</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>8-core (1x3.39GHz Cortex-X4 &amp; 3x3.1GHz Cortex-A720 &amp; 2x2.9GHz Cortex-A720 &amp; 2x2.2GHz Cortex-A520)</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>Android 14, up to 7 major Android upgrades, One UI 6.1.1</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>25W wired, QC2.0, 50% in 30 min 15W wireless 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>IP48 dust and water resistant (dust &gt; 1mm; immersible up to 1.5m for 30 min) Armor aluminum frame</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus 2) (folded), plastic front (unfolded), glass back (Gorilla Glass Victus 2), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>200 MP, f/1.8, (wide), PDAF, OIS 10 MP, f/2.4, 66mm (telephoto), 1.0µm, PDAF, OIS, 3x optical zoom 12 MP, f/2.2, 123˚, 12mm (ultrawide), 1.12µm, AF</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>8K@30fps, 4K@60fps, 1080p@60/120/240fps (gyro-EIS), 720p@960fps (gyro-EIS), HDR10+</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>UFS 4.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>SM-F958N</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>0.66 W/kg (head)     1.13 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8650-AC Snapdragon 8 Gen 3 (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>Adreno 750 (1 GHz)</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>4 MP, f/1.8, 26mm (wide), 2.0µm Cover camera: 10 MP, f/2.2, 24mm (wide), 1/3", 1.22µm</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX13" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a16-13383.php</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2024, October 15</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, November 20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>164.4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>114.00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>96.75</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>$ 101.00 / C$ 178.39 / £ 96.75 / € 114.00</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>164.4 x 77.9 x 7.9 mm (6.47 x 3.07 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>200 g (7.05 oz)</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>FM radio (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~86.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 90Hz</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Virtual proximity sensing</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, compass</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>2024, October 15</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, November 20</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM, 256GB 4GB RAM, 256GB 6GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Gray, water green, midnight blue</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>$ 101.00 / C$ 178.39 / £ 96.75 / € 114.00</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.31 W/kg (head)     1.08 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>Android 14, up to 6 major Android upgrades, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>IP54 dust protected and water resistant (water splashes)</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>45:10h endurance, 1200 cycles</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>Class B (180 falls)</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/2.76", 0.64µm, AF 5 MP, f/2.2, (ultrawide), 1/5.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>SM-A165F, SM-A165F/DS, SM-A165M, SM-A165M/DS, SM-A165F/DSB</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>Active use score 14:43h</t>
+        </is>
+      </c>
+      <c r="CO14" t="inlineStr">
+        <is>
+          <t>808 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>-25.2 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>AnTuTu: 387422 (v10) GeekBench: 1920 (v6) 3DMark: 345 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G99 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, (wide), 1/3.1", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A16 5G</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a16_5g-13346.php</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2024, October 07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>164.4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>81.99</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>169.00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>105.00</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>$ 81.99 / £ 105.00 / € 169.00</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>164.4 x 77.9 x 7.9 mm (6.47 x 3.07 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + eSIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>200 g (7.05 oz)</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~86.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 90Hz, 800 nits (HBM)</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Virtual proximity sensing</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>2024, October 07</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 25</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM, 256GB 6GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Blue Black, Light Gray, Gold, Light Green</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>$ 81.99 / £ 105.00 / € 169.00</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.38 W/kg (head)     0.94 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A78 &amp; 6x2.0 GHz Cortex-A55) or Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>Android 14, up to 6 major Android upgrades, One UI 8.5</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>IP54 dust protected and water resistant (water splashes)</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>43:30h endurance, 1200 cycles</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>Class B (180 falls)</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/2.76", 0.64µm, AF 5 MP, f/2.2, (ultrawide), 1/5.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>1080p@30fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>SM-A166B, SM-A166B/DS, SM-A166P, SM-A166P/DS, SM-A166E, SM-A166E/DS, SM-A166W, SM-A166U, SM-A166U1</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 12, 13, 14, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>2, 5, 25, 41, 66, 71, 77, 78 SA/NSA/Sub6/mmWave - USA unlocked</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 28, 38, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>1, 3, 7, 8, 20, 28, 38, 40, 41, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>Active use score 12:08h</t>
+        </is>
+      </c>
+      <c r="CO15" t="inlineStr">
+        <is>
+          <t>824 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>-25.7 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>AnTuTu: 368854 (v9), 435895 (v10) GeekBench: 2090 (v5), 2042 (v6) 3DMark: 360 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>Exynos 1330 (5 nm) or Mediatek Dimensity 6300 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>Mali-G68 MP2 or Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, (wide), 1/3.1", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S24 FE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s24_fe-13262.php</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>225.11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>363.13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>298.99</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>39999</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>$ 225.11 / C$ 443.99 / £ 298.99 / € 363.13 / ₹ 39,999</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>4700 mAh</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>162 x 77.3 x 8 mm (6.38 x 3.04 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM · Nano-SIM + eSIM · eSIM + eSIM</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>213 g (7.51 oz)</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e, dual-band or tri-band (market/region dependent), Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~385 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>6.7 inches, 110.2 cm 2 (~88.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED 2X, 120Hz, HDR10+, 1900 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Virtual proximity sensing Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM, 512GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Blue, Graphite, Gray, Mint, Yellow</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>$ 225.11 / C$ 443.99 / £ 298.99 / € 363.13 / ₹ 39,999</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.86 W/kg (head)     1.29 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>10-core (1x3.1 GHz + 2x2.9 GHz + 3x2.6 GHz + 4x1.95 GHz)</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>Android 14, up to 7 major Android upgrades, One UI 8.5</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>25W wired, PD, QC2, 50% in 30 min 15W wireless Reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min)</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus+), glass back (Gorilla Glass Victus+), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass Victus+, Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>42:00h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>Class A (270 falls)</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 24mm (wide), 1/1.57", 1.0µm, dual pixel PDAF, OIS 8 MP, f/2.4, 75mm (telephoto), 1/4.4", 1.0µm, PDAF, OIS, 3x optical zoom 12 MP, f/2.2, 13mm, 123˚ (ultrawide), 1/3.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>8K@30fps, 4K@30/60/120fps, 1080p@30/60/120/240fps</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>SM-S721B, SM-S721B/DS, SM-S721U1, SM-S721U, SM-S721W, SM-S7210, SM-S721N</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>0.94 W/kg (head)     0.71 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 18, 19, 20, 25, 26, 28, 32, 38, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 75, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>Active use score 11:48h</t>
+        </is>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>1372 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP16" t="inlineStr">
+        <is>
+          <t>-24.6 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>AnTuTu: 1548896 (v10) GeekBench: 6299 (v6) 3DMark: 3889 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>Exynos 2400e (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>Xclipse 940</t>
+        </is>
+      </c>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr">
+        <is>
+          <t>10 MP, f/2.4, 26mm (wide), 1/3.0", 1.22µm</t>
+        </is>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Tab S10 Ultra</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Versions: Galaxy Tab S10 Ultra Wi-Fi SM-X920; Galaxy Tab S10 Ultra 5G SM-X926BAlso known as Samsung Galaxy Tab S10 Ultra (14.6-inch)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_tab_s10_ultra-13362.php</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>326.4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>208.6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2960</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1TB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>12GB | 16GB</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>11200</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>About 1620 EUR</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Li-Po 11200 mAh</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>326.4 x 208.6 x 5.4 mm (12.85 x 8.21 x 0.21 in)</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Nano-SIM + eSIM (cellular model only)</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>718 g (Wi-Fi), 723 g (5G) (1.58 lb)</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO - cellular model only</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, magnetic connector</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e/7, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>1848 x 2960 pixels, 16:10 ratio (~239 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>14.6 inches, 617.8 cm 2 (~90.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED 2X, 120Hz, HDR10+</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Wireless Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>256GB 12GB RAM, 512GB 12GB RAM, 1TB 12GB RAM, 1TB 16GB RAM</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>Moonstone Gray, Platinum Silver</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>About 1620 EUR</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.94 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G - cellular model only</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>Octa-core (1x3.4 GHz Cortex-X4 &amp; 3x2.8 GHz Cortex-X4 &amp; 4x2.0 GHz Cortex-A720)</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>Android 14, One UI 6.1</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers (4 speakers)</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>45W wired</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Stylus, 2.8ms latency (Bluetooth integration, accelerometer, gyro) Enhanced Armor aluminum</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>Glass front, aluminum frame, aluminum back</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>85:18h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>Class G</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>Class E</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, 26mm (wide), 1/3.4", 1.0µm, AF 8 MP, f/2.2, (ultrawide)</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>UFS</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>SM-X920, SM-X926B, SM-X926N, SM-X920N</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM17" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 9300+ (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>Immortalis-G720 MC12</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.2, 26mm (wide) 12 MP, f/2.4, 120˚ (ultrawide)</t>
+        </is>
+      </c>
+      <c r="CU17" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Tab S10+</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Versions: Galaxy Tab S10+ Wi-Fi SM-X820; Galaxy Tab S10+ 5G SM-X826BAlso known as Samsung Galaxy Tab S10+ (12.4-inch)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_tab_s10+-13363.php</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>285.4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>185.4</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>10090</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>About 1150 EUR</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Li-Po 10090 mAh</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>285.4 x 185.4 x 5.6 mm (11.24 x 7.30 x 0.22 in)</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Nano-SIM + eSIM (cellular model only)</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>571 g (Wi-Fi), 576 g (5G) (1.26 lb)</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO - cellular model only</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, magnetic connector</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>1752 x 2800 pixels, 16:10 ratio (~266 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>12.4 inches, 446.1 cm 2 (~84.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED 2X, 120Hz, HDR10+</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Wireless Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>2024, September 26</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, October 03</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>256GB 12GB RAM, 512GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Moonstone Gray, Platinum Silver</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>About 1150 EUR</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>0.80 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G - cellular model only</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>Octa-core (1x3.4 GHz Cortex-X4 &amp; 3x2.8 GHz Cortex-X4 &amp; 4x2.0 GHz Cortex-A720)</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>Android 14, One UI 6.1</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers (4 speakers)</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>45W wired</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Stylus, 2.8ms latency (Bluetooth integration, accelerometer, gyro) Enhanced Armor aluminum</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>Glass front, aluminum frame, aluminum back</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>Mohs level 5</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>73:44h endurance, 2000 cycles</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>Class G</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>Class E</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>Class C</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, 26mm (wide), 1/3.4", 1.0µm, AF 8 MP, f/2.2, (ultrawide)</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>UFS</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>SM-X820, SM-X826B, SM-X820N, SM-X826N</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>SA/NSA/Sub6/mmWave</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="inlineStr"/>
+      <c r="CK18" t="inlineStr"/>
+      <c r="CL18" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM18" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 9300+ (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>Immortalis-G720 MC12</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV18" t="inlineStr">
+        <is>
+          <t>12 MP, f/2.4, 120˚ (ultrawide)</t>
+        </is>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M55s</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m55s-13354.php</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2024, September 24</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 26</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>163.9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>24999</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>₹ 24,999</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>163.9 x 76.5 x 7.8 mm (6.45 x 3.01 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>180 g (6.35 oz)</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>5.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~393 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~86.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Super AMOLED+, 120Hz, 1000 nits (HBM)</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>2024, September 24</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 26</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Thunder Black, Coral Green</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>₹ 24,999</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.4 GHz Cortex-A710 &amp; 3x2.36 GHz Cortex-A710 &amp; 4x1.8 GHz Cortex-A510)</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>Android 14, up to 4 major Android upgrades, upgradable to Android 16, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>45W wired</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/1.56", 1.0µm, PDAF, OIS 8 MP, f/2.2, 123˚ (ultrawide) 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps, gyro-EIS, OIS</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>SM-M558B, SM-M558B/DS</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>0.93 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 25, 26, 28, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41, 66, 77, 78 SA/NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7450-AB Snapdragon 7 Gen 1 (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>Adreno 644</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr">
+        <is>
+          <t>50 MP, f/2.4, (wide)</t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy F05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_f05-13345.php</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2024, September 17</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>168.8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>168.8 x 78.2 x 8.8 mm (6.65 x 3.08 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>195 g (6.88 oz)</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~262 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~82.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>2024, September 17</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 20</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Twilight Blue</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>Android 14, up to 2 major Android upgrades, One UI Core 6.0</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, silicone polymer (eco leather) back</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), AF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>SM-E055F, SM-E055F/DS</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>0.46 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr"/>
+      <c r="CI20" t="inlineStr"/>
+      <c r="CJ20" t="inlineStr"/>
+      <c r="CK20" t="inlineStr"/>
+      <c r="CL20" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G85 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0</t>
+        </is>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m05-13327.php</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024, September 10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>168.8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>168.8 x 78.2 x 8.8 mm (6.65 x 3.08 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>195 g (6.88 oz)</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~262 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~82.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>2024, September 10</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 10</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Mint Green</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>Android 14, up to 2 major Android upgrades, One UI Core 6.0</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), AF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>SM-M055F, SM-M055F/DS</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>0.46 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr"/>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="inlineStr"/>
+      <c r="CK21" t="inlineStr"/>
+      <c r="CL21" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G85 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0</t>
+        </is>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a06-13265.php</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2024, August 16</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, August 22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>167.3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>136.72</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>88.59</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>10299</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>$ 94.00 / C$ 118.00 / £ 88.59 / € 136.72 / ₹ 10,299</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>167.3 x 77.3 x 8 mm (6.59 x 3.04 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>189 g (6.67 oz)</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~262 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~83.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>2024, August 16</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, August 22</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Blue, Gold, White</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>$ 94.00 / C$ 118.00 / £ 88.59 / € 136.72 / ₹ 10,299</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>0.44 W/kg (head)     1.08 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>Android 14, up to 2 major Android upgrades, One UI 8</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/2.76", 0.64µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>SM-A065F, SM-A065F/DS, SM-A065M, SM-A065M/DS</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr">
+        <is>
+          <t>Active use score 13:50h</t>
+        </is>
+      </c>
+      <c r="CO22" t="inlineStr">
+        <is>
+          <t>1484:1 contrast ratio, 564 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>-27.7 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>AnTuTu: 182064 (v9), 247675 (v10) GeekBench: 1273 (v5), 1276 (v6) 3DMark: 188 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G85 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CX22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy F14 4G</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_f14_4g-13247.php</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024, August 02</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 05</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>168 x 77.8 x 8.8 mm (6.61 x 3.06 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>194 g (6.84 oz)</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~393 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>6.7 inches, 108.4 cm 2 (~82.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>PLS LCD, 90Hz</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>2024, August 02</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, September 05</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>Moonlight Silver, Peppermint Green</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.4 GHz Kryo 265 Gold &amp; 4x1.9 GHz Kryo 265 Silver)</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>Android 14, up to 2 major Android upgrades, One UI 6.1</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>25W wired</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>SM-E145F, SM-E145F/DS</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>0.56 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>Qualcomm SM6225 Snapdragon 680 4G (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>Adreno 610</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, (wide)</t>
+        </is>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Z Fold6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_z_fold6-13147.php</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2024, July 10</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, July 24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>153.5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>132.6</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1TB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>647.49</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>834.05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>573.40</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>$ 647.49 / C$ 1,379.99 / £ 573.40 / € 834.05</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Li-Po 4400 mAh</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Unfolded: 153.5 x 132.6 x 5.6 mm Folded: 153.5 x 68.1 x 12.1 mm</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>· Nano-SIM + eSIM · eSIM + eSIM · Nano-SIM + Nano-SIM (SM-F9560)</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>239 g (8.43 oz)</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>5.3, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.2, OTG</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6e, tri-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>Cover display: Dynamic LTPO AMOLED 2X, 120Hz, 2600 nits (peak), Corning Gorilla Glass Victus 2 6.3 inches, 968 x 2376 pixels, 410 ppi</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>1856 x 2160 pixels (~374 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>7.6 inches, 185.2 cm 2 (~91.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Foldable Dynamic LTPO AMOLED 2X, 120Hz, HDR10+, 2600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samsung DeX (desktop experience support) Ultra Wideband (UWB) support</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>2024, July 10</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>Available. Released 2024, July 24</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>256GB 12GB RAM, 512GB 12GB RAM, 1TB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Navy, Silver Shadow, Pink, Black, White</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>$ 647.49 / C$ 1,379.99 / £ 573.40 / € 834.05</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>1.24 W/kg (head)     1.39 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>8-core (1x3.39GHz Cortex-X4 &amp; 3x3.1GHz Cortex-A720 &amp; 2x2.9GHz Cortex-A720 &amp; 2x2.2GHz Cortex-A520)</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>Android 14, up to 7 major Android upgrades, One UI 6.1.1</t>
+        </is>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>25W wired, QC2.0, 50% in 30 min 15W wireless 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>IP48 dust and water resistant (dust &gt; 1mm; immersible up to 1.5m for 30 min) Armor aluminum frame Stylus support</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass Victus 2) (folded), plastic front (unfolded), glass back (Gorilla Glass Victus 2), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, 23mm (wide), 1/1.57", 1.0µm, dual pixel PDAF, OIS 10 MP, f/2.4, 66mm (telephoto), 1/3.94", 1.0µm, PDAF, OIS, 3x optical zoom 12 MP, f/2.2, 123˚, 12mm (ultrawide), 1/3.2", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>8K@30fps, 4K@60fps, 1080p@60/120/240fps (gyro-EIS), HDR10+</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>UFS 4.0</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>SM-F956B, SM-F956B/DS, SM-F956U, SM-F956U1, SM-F956N, SM-F956W, SM-F9560</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 48, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>1, 2, 5, 7, 25, 28, 41, 66, 71, 77, 78, 257, 258, 260, 261 SA/NSA/Sub6/mmWave - USA</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 20, 25, 26, 28, 38, 40, 41, 66, 75, 77, 78 SA/NSA/Sub6 - International</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>Active use score 11:31h</t>
+        </is>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>1630 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>-26.5 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>AnTuTu: 1608744 (v10) GeekBench: 6757 (v6) 3DMark: 4644 (Wild Life Extreme)</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8650-AC Snapdragon 8 Gen 3 (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>Adreno 750 (1 GHz)</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>4 MP, f/1.8, 26mm (wide), 1/3.0", 2.0µm, under display Cover camera: 10 MP, f/2.2, 24mm (wide), 1/3.0", 1.22µm</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Galaxy Z Flip6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_z_flip6-13192.php</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX25"/>
+  <dimension ref="A1:DI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,61 @@
       <c r="CX1" t="inlineStr">
         <is>
           <t>Sound</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>Features_Alarm</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>Features_Clock</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>Features_Games</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>Features_Java</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>Features_Messaging</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>Main Camera_Single</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>Memory_Call records</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>Memory_Phonebook</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>Network_EDGE</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>Network_GPRS</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>Selfie camera</t>
         </is>
       </c>
     </row>
@@ -1082,8 +1137,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AR2" t="n">
-        <v>2</v>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1235,6 +1292,17 @@
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr"/>
       <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1359,6 +1427,17 @@
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="inlineStr"/>
       <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1392,55 +1471,37 @@
           <t>2025, March 02</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H4" t="n">
+        <v>2025</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Available. Released 2025, March 10</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>162.9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J4" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>195</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>385</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1452,56 +1513,36 @@
           <t>12GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
+      <c r="T4" t="n">
+        <v>50</v>
+      </c>
+      <c r="U4" t="n">
+        <v>12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>190.94</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>239.00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>202.00</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
+      <c r="Y4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>190.94</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>239</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>202</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27509</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1803,6 +1844,17 @@
         </is>
       </c>
       <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1836,55 +1888,37 @@
           <t>2025, March 02</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H5" t="n">
+        <v>2025</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Available. Released 2025, March 19</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J5" t="n">
+        <v>164</v>
+      </c>
+      <c r="K5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>200</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>385</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1896,55 +1930,35 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>163.77</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>193.00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>162.19</t>
-        </is>
+      <c r="T5" t="n">
+        <v>50</v>
+      </c>
+      <c r="U5" t="n">
+        <v>13</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>163.77</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>193</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>162.19</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
@@ -2243,6 +2257,17 @@
         </is>
       </c>
       <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2276,55 +2301,37 @@
           <t>2025, February 27</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H6" t="n">
+        <v>2025</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Available. Released 2025, March 05</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J6" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>191</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>385</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2336,44 +2343,30 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
+      <c r="T6" t="n">
+        <v>50</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="Y6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.19</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>15999</t>
-        </is>
+      <c r="AD6" t="n">
+        <v>15999</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -2623,6 +2616,17 @@
         </is>
       </c>
       <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2656,55 +2660,37 @@
           <t>2025, February 27</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H7" t="n">
+        <v>2025</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Available. Released 2025, March 07</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>167.4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+      <c r="J7" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>191</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="O7" t="n">
+        <v>720</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>260</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2716,44 +2702,30 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="T7" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>12499</t>
-        </is>
+      <c r="AD7" t="n">
+        <v>12499</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -2999,6 +2971,17 @@
         </is>
       </c>
       <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3032,55 +3015,37 @@
           <t>2025, February 19</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H8" t="n">
+        <v>2025</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Available. Released 2025, February 19</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>167.3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="J8" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>191</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>720</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>262</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3092,48 +3057,32 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="T8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
       </c>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>169.99</t>
-        </is>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>169.99</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>12290</t>
-        </is>
+      <c r="AD8" t="n">
+        <v>12290</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -3383,6 +3332,17 @@
         </is>
       </c>
       <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3416,55 +3376,37 @@
           <t>2025, February 12</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H9" t="n">
+        <v>2025</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Available. Released February 20</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>167.4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="J9" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>191</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>720</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>262</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3476,44 +3418,30 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="T9" t="n">
+        <v>50</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>12298</t>
-        </is>
+      <c r="AD9" t="n">
+        <v>12298</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -3759,6 +3687,17 @@
         </is>
       </c>
       <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3792,55 +3731,37 @@
           <t>2025, January 22</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H10" t="n">
+        <v>2025</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Available. Released 2025, February 03</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>162.8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
+      <c r="J10" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>218</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3120</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>498</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3852,60 +3773,38 @@
           <t>12GB | 16GB</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>755.74</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>768.00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>634.25</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>93900</t>
-        </is>
+      <c r="T10" t="n">
+        <v>200</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>755.74</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>768</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>634.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>93900</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -4227,6 +4126,17 @@
           <t>High-bitrate audio support</t>
         </is>
       </c>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4260,55 +4170,37 @@
           <t>2025, January 22</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H11" t="n">
+        <v>2025</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Available. Released 2025, February 03</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>158.4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
+      <c r="J11" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>190</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>513</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -4320,55 +4212,35 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>557.22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>735.00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>549.00</t>
-        </is>
+      <c r="T11" t="n">
+        <v>50</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4900</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>557.22</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>735</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>549</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
@@ -4687,6 +4559,17 @@
           <t>High-bitrate audio support</t>
         </is>
       </c>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4720,55 +4603,37 @@
           <t>2025, January 22</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H12" t="n">
+        <v>2025</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Available. Released 2025, February 03</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>146.9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>70.5</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
+      <c r="J12" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>162</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>416</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -4780,60 +4645,38 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>417.09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>449.99</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>420.96</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>74999</t>
-        </is>
+      <c r="T12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>417.09</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>449.99</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>420.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>74999</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -5151,6 +4994,17 @@
           <t>High-bitrate audio support</t>
         </is>
       </c>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5188,55 +5042,37 @@
           <t>2024, October 21</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H13" t="n">
+        <v>2024</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Available. Released 2024, October 24</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>157.9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>142.6</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="J13" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>236</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1968</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2184</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>367</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5248,30 +5084,20 @@
           <t>16GB</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
+      <c r="T13" t="n">
+        <v>200</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4400</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.13</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
@@ -5543,6 +5369,17 @@
           <t>High-bitrate audio support</t>
         </is>
       </c>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5576,55 +5413,37 @@
           <t>2024, October 15</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H14" t="n">
+        <v>2024</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Available. Released 2024, November 20</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J14" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>200</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>385</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -5636,47 +5455,31 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T14" t="n">
+        <v>50</v>
+      </c>
+      <c r="U14" t="n">
+        <v>13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5000</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>96.75</t>
-        </is>
+      <c r="Y14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>101</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>114</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>96.75</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
@@ -5959,6 +5762,17 @@
         </is>
       </c>
       <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5992,55 +5806,37 @@
           <t>2024, October 07</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H15" t="n">
+        <v>2024</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Available. Released 2024, October 25</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J15" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>200</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>385</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -6052,47 +5848,31 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T15" t="n">
+        <v>50</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5000</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>81.99</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>169.00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>105.00</t>
-        </is>
+      <c r="Y15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>169</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>105</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
@@ -6387,6 +6167,17 @@
         </is>
       </c>
       <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6420,55 +6211,37 @@
           <t>2024, September 26</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H16" t="n">
+        <v>2024</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Available. Released 2024, October 03</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="J16" t="n">
+        <v>162</v>
+      </c>
+      <c r="K16" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>213</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>385</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -6480,60 +6253,38 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>4700</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>225.11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>363.13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>298.99</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>39999</t>
-        </is>
+      <c r="T16" t="n">
+        <v>50</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4700</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>225.11</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>298.99</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>39999</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -6823,6 +6574,17 @@
         </is>
       </c>
       <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6860,55 +6622,37 @@
           <t>2024, September 26</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H17" t="n">
+        <v>2024</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Available. Released 2024, October 03</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>326.4</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>208.6</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+      <c r="J17" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>718</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1848</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2960</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>239</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -6920,28 +6664,20 @@
           <t>12GB | 16GB</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>11200</t>
-        </is>
+      <c r="T17" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>11200</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
+      <c r="Z17" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
@@ -7223,6 +6959,17 @@
         </is>
       </c>
       <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
+      <c r="DH17" t="inlineStr"/>
+      <c r="DI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7260,55 +7007,37 @@
           <t>2024, September 26</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H18" t="n">
+        <v>2024</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Available. Released 2024, October 03</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>285.4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>185.4</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="J18" t="n">
+        <v>285.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>571</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1752</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>266</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -7320,28 +7049,20 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>10090</t>
-        </is>
+      <c r="T18" t="n">
+        <v>13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>12</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10090</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
+      <c r="Z18" t="n">
+        <v>0.8</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
@@ -7627,6 +7348,17 @@
         </is>
       </c>
       <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7660,55 +7392,37 @@
           <t>2024, September 24</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H19" t="n">
+        <v>2024</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Available. Released 2024, September 26</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>163.9</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="J19" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>180</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>393</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -7720,25 +7434,17 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="T19" t="n">
+        <v>50</v>
+      </c>
+      <c r="U19" t="n">
+        <v>50</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.93</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -7746,10 +7452,8 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>24999</t>
-        </is>
+      <c r="AD19" t="n">
+        <v>24999</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -7987,6 +7691,17 @@
         </is>
       </c>
       <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8020,55 +7735,37 @@
           <t>2024, September 17</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H20" t="n">
+        <v>2024</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Available. Released 2024, September 20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>168.8</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="J20" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>195</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>720</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>262</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -8080,25 +7777,17 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+      <c r="T20" t="n">
+        <v>50</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.46</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -8347,6 +8036,17 @@
         </is>
       </c>
       <c r="CX20" t="inlineStr"/>
+      <c r="CY20" t="inlineStr"/>
+      <c r="CZ20" t="inlineStr"/>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="inlineStr"/>
+      <c r="DD20" t="inlineStr"/>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="inlineStr"/>
+      <c r="DG20" t="inlineStr"/>
+      <c r="DH20" t="inlineStr"/>
+      <c r="DI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8380,55 +8080,37 @@
           <t>2024, September 10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H21" t="n">
+        <v>2024</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Available. Released 2024, September 10</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>168.8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="J21" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>195</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>720</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>262</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -8440,25 +8122,17 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+      <c r="T21" t="n">
+        <v>50</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.46</v>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -8707,6 +8381,17 @@
         </is>
       </c>
       <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8740,55 +8425,37 @@
           <t>2024, August 16</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H22" t="n">
+        <v>2024</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Available. Released 2024, August 22</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>167.3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="J22" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>189</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>720</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>262</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -8800,52 +8467,34 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T22" t="n">
+        <v>50</v>
+      </c>
+      <c r="U22" t="n">
+        <v>8</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5000</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>136.72</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>10299</t>
-        </is>
+      <c r="Y22" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>94</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>136.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10299</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -9103,6 +8752,17 @@
         </is>
       </c>
       <c r="CX22" t="inlineStr"/>
+      <c r="CY22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="inlineStr"/>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="inlineStr"/>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr"/>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9136,55 +8796,37 @@
           <t>2024, August 02</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H23" t="n">
+        <v>2024</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Available. Released 2024, September 05</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="J23" t="n">
+        <v>168</v>
+      </c>
+      <c r="K23" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>393</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -9196,25 +8838,17 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+      <c r="T23" t="n">
+        <v>50</v>
+      </c>
+      <c r="U23" t="n">
+        <v>13</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -9459,6 +9093,17 @@
         </is>
       </c>
       <c r="CX23" t="inlineStr"/>
+      <c r="CY23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr"/>
+      <c r="DC23" t="inlineStr"/>
+      <c r="DD23" t="inlineStr"/>
+      <c r="DE23" t="inlineStr"/>
+      <c r="DF23" t="inlineStr"/>
+      <c r="DG23" t="inlineStr"/>
+      <c r="DH23" t="inlineStr"/>
+      <c r="DI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9492,55 +9137,37 @@
           <t>2024, July 10</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H24" t="n">
+        <v>2024</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Available. Released 2024, July 24</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>153.5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>132.6</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2160</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
+      <c r="J24" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>239</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1856</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2160</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>374</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -9552,47 +9179,31 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
+      <c r="T24" t="n">
+        <v>50</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4400</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>647.49</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>834.05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>573.40</t>
-        </is>
+      <c r="Y24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>647.49</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>834.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>573.4</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
@@ -9891,6 +9502,17 @@
           <t>High-bitrate audio support</t>
         </is>
       </c>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr"/>
+      <c r="DI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10015,6 +9637,6368 @@
       <c r="CV25" t="inlineStr"/>
       <c r="CW25" t="inlineStr"/>
       <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+      <c r="DA25" t="inlineStr"/>
+      <c r="DB25" t="inlineStr"/>
+      <c r="DC25" t="inlineStr"/>
+      <c r="DD25" t="inlineStr"/>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
+      <c r="DI25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Telit t180</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t180-1661.php</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2006, Q2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2MB</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 650 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>100 x 45 x 18 mm (3.94 x 1.77 x 0.71 in)</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>76 g (2.68 oz)</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>128 x 128 pixels, 1:1 ratio</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>CSTN, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Voice memo eZi text input Unit Converter World Clock</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>2006, Q2</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2MB</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>Navy Blue, Lacquered White</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MIDI ringtones</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr"/>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="inlineStr"/>
+      <c r="CI26" t="inlineStr"/>
+      <c r="CJ26" t="inlineStr"/>
+      <c r="CK26" t="inlineStr"/>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr"/>
+      <c r="CY26" t="inlineStr"/>
+      <c r="CZ26" t="inlineStr"/>
+      <c r="DA26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB26" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 1.0</t>
+        </is>
+      </c>
+      <c r="DC26" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD26" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE26" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF26" t="inlineStr">
+        <is>
+          <t>300 entries</t>
+        </is>
+      </c>
+      <c r="DG26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH26" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Telit t410</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t410-1536.php</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Up to 100 h</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Up to 2 h</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 650 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>52 x 57 x 23 mm (2.05 x 2.24 x 0.91 in)</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>76 g (2.68 oz)</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>Second OLED display, 256 colors, 96 x 64 pixels Downloadable animation</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Video player Photo editor Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+      <c r="CG27" t="inlineStr"/>
+      <c r="CH27" t="inlineStr"/>
+      <c r="CI27" t="inlineStr"/>
+      <c r="CJ27" t="inlineStr"/>
+      <c r="CK27" t="inlineStr"/>
+      <c r="CL27" t="inlineStr"/>
+      <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr"/>
+      <c r="CW27" t="inlineStr"/>
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr"/>
+      <c r="CZ27" t="inlineStr"/>
+      <c r="DA27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC27" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD27" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE27" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF27" t="inlineStr">
+        <is>
+          <t>300 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH27" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Telit t130</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t130-1581.php</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2006, Q2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 800 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>101 x 44 x 16.5 mm (3.98 x 1.73 x 0.65 in)</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>75 g (2.65 oz)</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>miniUSB</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>96 x 64 pixels, 3:2 ratio (~84 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>1.37 inches, 5.6 cm 2 (~12.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Monochrome graphics</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>eZi text input Calculator Watch Speed dial</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>2006, Q2</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable monophonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr"/>
+      <c r="CH28" t="inlineStr"/>
+      <c r="CI28" t="inlineStr"/>
+      <c r="CJ28" t="inlineStr"/>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
+      <c r="CT28" t="inlineStr"/>
+      <c r="CU28" t="inlineStr"/>
+      <c r="CV28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr"/>
+      <c r="CX28" t="inlineStr"/>
+      <c r="CY28" t="inlineStr"/>
+      <c r="CZ28" t="inlineStr"/>
+      <c r="DA28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC28" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD28" t="inlineStr"/>
+      <c r="DE28" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF28" t="inlineStr">
+        <is>
+          <t>SIM based only</t>
+        </is>
+      </c>
+      <c r="DG28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Telit t110</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t110-1535.php</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2MB</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Up to 110 h</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>90 x 41 x 20 mm (3.54 x 1.61 x 0.79 in)</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>75 g (2.65 oz)</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>Second CSTN display, 4096 colors, 96 x 64 pixels Downloadable animation</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels (~114 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>1.8 inches, 29 x 35 mm, 10.2 cm 2 (~27.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>CSTN, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Video player Predictive text input Organizer Voice memo</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>WAP 1.2</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2MB</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO29" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr"/>
+      <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr"/>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr"/>
+      <c r="CF29" t="inlineStr"/>
+      <c r="CG29" t="inlineStr"/>
+      <c r="CH29" t="inlineStr"/>
+      <c r="CI29" t="inlineStr"/>
+      <c r="CJ29" t="inlineStr"/>
+      <c r="CK29" t="inlineStr"/>
+      <c r="CL29" t="inlineStr"/>
+      <c r="CM29" t="inlineStr"/>
+      <c r="CN29" t="inlineStr"/>
+      <c r="CO29" t="inlineStr"/>
+      <c r="CP29" t="inlineStr"/>
+      <c r="CQ29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="inlineStr"/>
+      <c r="CT29" t="inlineStr"/>
+      <c r="CU29" t="inlineStr"/>
+      <c r="CV29" t="inlineStr"/>
+      <c r="CW29" t="inlineStr"/>
+      <c r="CX29" t="inlineStr"/>
+      <c r="CY29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr"/>
+      <c r="DA29" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB29" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 1.0</t>
+        </is>
+      </c>
+      <c r="DC29" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD29" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE29" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF29" t="inlineStr">
+        <is>
+          <t>500 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH29" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Telit t210</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t210-1534.php</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Up to 100 h</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>93 x 45 x 24 mm (3.66 x 1.77 x 0.94 in)</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>85 g (3.00 oz)</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>Second CSTN display, 4096 colors, 96 x 64 pixels Downloadable animation</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels (~114 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>1.8 inches, 29 x 35 mm, 10.2 cm 2 (~24.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer Voice memo</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>WAP 1.2</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO30" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr"/>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr"/>
+      <c r="CF30" t="inlineStr"/>
+      <c r="CG30" t="inlineStr"/>
+      <c r="CH30" t="inlineStr"/>
+      <c r="CI30" t="inlineStr"/>
+      <c r="CJ30" t="inlineStr"/>
+      <c r="CK30" t="inlineStr"/>
+      <c r="CL30" t="inlineStr"/>
+      <c r="CM30" t="inlineStr"/>
+      <c r="CN30" t="inlineStr"/>
+      <c r="CO30" t="inlineStr"/>
+      <c r="CP30" t="inlineStr"/>
+      <c r="CQ30" t="inlineStr"/>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="inlineStr"/>
+      <c r="CT30" t="inlineStr"/>
+      <c r="CU30" t="inlineStr"/>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
+      <c r="CX30" t="inlineStr"/>
+      <c r="CY30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr"/>
+      <c r="DA30" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB30" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 1.0</t>
+        </is>
+      </c>
+      <c r="DC30" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD30" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE30" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF30" t="inlineStr">
+        <is>
+          <t>500 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH30" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Telit T510</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t510-1244.php</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>32MB</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Up to 100 h</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Up to 2 h</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 650 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>90 x 40 x 18 mm (3.54 x 1.57 x 0.71 in)</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>87 g (3.07 oz)</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>Downloadable animation</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels (~114 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>1.8 inches, 29 x 35 mm, 10.2 cm 2 (~28.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Predictive text input MP3 player Organizer Voice memo</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>miniSD</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>32MB</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>Silver, Blue</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO31" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP31" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr"/>
+      <c r="CC31" t="inlineStr"/>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr"/>
+      <c r="CG31" t="inlineStr"/>
+      <c r="CH31" t="inlineStr"/>
+      <c r="CI31" t="inlineStr"/>
+      <c r="CJ31" t="inlineStr"/>
+      <c r="CK31" t="inlineStr"/>
+      <c r="CL31" t="inlineStr"/>
+      <c r="CM31" t="inlineStr"/>
+      <c r="CN31" t="inlineStr"/>
+      <c r="CO31" t="inlineStr"/>
+      <c r="CP31" t="inlineStr"/>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr"/>
+      <c r="CT31" t="inlineStr"/>
+      <c r="CU31" t="inlineStr"/>
+      <c r="CV31" t="inlineStr"/>
+      <c r="CW31" t="inlineStr"/>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>Dual speaker</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr"/>
+      <c r="CZ31" t="inlineStr"/>
+      <c r="DA31" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DC31" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD31" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE31" t="inlineStr">
+        <is>
+          <t>10 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF31" t="inlineStr">
+        <is>
+          <t>250 entries</t>
+        </is>
+      </c>
+      <c r="DG31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH31" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Telit C1000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_c1000-1243.php</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Up to 100 h</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Up to 2 h</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>86 x 48 x 15.6 mm (3.39 x 1.89 x 0.61 in)</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>74.5 g (2.61 oz)</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>Handwriting recognition Downloadable animation</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Predictive text input Photo editor Organizer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>2005, Q1</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>5.5MB</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO32" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+      <c r="BU32" t="inlineStr"/>
+      <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB32" t="inlineStr"/>
+      <c r="CC32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr"/>
+      <c r="CF32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
+      <c r="CH32" t="inlineStr"/>
+      <c r="CI32" t="inlineStr"/>
+      <c r="CJ32" t="inlineStr"/>
+      <c r="CK32" t="inlineStr"/>
+      <c r="CL32" t="inlineStr"/>
+      <c r="CM32" t="inlineStr"/>
+      <c r="CN32" t="inlineStr"/>
+      <c r="CO32" t="inlineStr"/>
+      <c r="CP32" t="inlineStr"/>
+      <c r="CQ32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr"/>
+      <c r="CS32" t="inlineStr"/>
+      <c r="CT32" t="inlineStr"/>
+      <c r="CU32" t="inlineStr"/>
+      <c r="CV32" t="inlineStr"/>
+      <c r="CW32" t="inlineStr"/>
+      <c r="CX32" t="inlineStr"/>
+      <c r="CY32" t="inlineStr"/>
+      <c r="CZ32" t="inlineStr"/>
+      <c r="DA32" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC32" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD32" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE32" t="inlineStr"/>
+      <c r="DF32" t="inlineStr">
+        <is>
+          <t>300 entries</t>
+        </is>
+      </c>
+      <c r="DG32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH32" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Telit T91</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t91-863.php</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2004, Q3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Up to 120 h</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 720 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>85 x 43.5 x 21.9 mm (3.35 x 1.71 x 0.86 in)</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>85 g (3.00 oz)</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>Rotating screen Downloadable pictures</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>2004, Q3</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO33" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr"/>
+      <c r="CB33" t="inlineStr"/>
+      <c r="CC33" t="inlineStr"/>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE33" t="inlineStr"/>
+      <c r="CF33" t="inlineStr"/>
+      <c r="CG33" t="inlineStr"/>
+      <c r="CH33" t="inlineStr"/>
+      <c r="CI33" t="inlineStr"/>
+      <c r="CJ33" t="inlineStr"/>
+      <c r="CK33" t="inlineStr"/>
+      <c r="CL33" t="inlineStr"/>
+      <c r="CM33" t="inlineStr"/>
+      <c r="CN33" t="inlineStr"/>
+      <c r="CO33" t="inlineStr"/>
+      <c r="CP33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr"/>
+      <c r="CR33" t="inlineStr"/>
+      <c r="CS33" t="inlineStr"/>
+      <c r="CT33" t="inlineStr"/>
+      <c r="CU33" t="inlineStr"/>
+      <c r="CV33" t="inlineStr"/>
+      <c r="CW33" t="inlineStr"/>
+      <c r="CX33" t="inlineStr"/>
+      <c r="CY33" t="inlineStr"/>
+      <c r="CZ33" t="inlineStr"/>
+      <c r="DA33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC33" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD33" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE33" t="inlineStr"/>
+      <c r="DF33" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="DG33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH33" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Telit T90</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_t90-862.php</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2004, Q3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Up to 120 h</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 720 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>85 x 43.5 x 21.9 mm (3.35 x 1.71 x 0.86 in)</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>85 g (3.00 oz)</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>Second OLED LCD (96 x 64 pixels) with 4 color Downloadable pictures</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>2004, Q3</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO34" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="inlineStr"/>
+      <c r="CD34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE34" t="inlineStr"/>
+      <c r="CF34" t="inlineStr"/>
+      <c r="CG34" t="inlineStr"/>
+      <c r="CH34" t="inlineStr"/>
+      <c r="CI34" t="inlineStr"/>
+      <c r="CJ34" t="inlineStr"/>
+      <c r="CK34" t="inlineStr"/>
+      <c r="CL34" t="inlineStr"/>
+      <c r="CM34" t="inlineStr"/>
+      <c r="CN34" t="inlineStr"/>
+      <c r="CO34" t="inlineStr"/>
+      <c r="CP34" t="inlineStr"/>
+      <c r="CQ34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr"/>
+      <c r="CT34" t="inlineStr"/>
+      <c r="CU34" t="inlineStr"/>
+      <c r="CV34" t="inlineStr"/>
+      <c r="CW34" t="inlineStr"/>
+      <c r="CX34" t="inlineStr"/>
+      <c r="CY34" t="inlineStr"/>
+      <c r="CZ34" t="inlineStr"/>
+      <c r="DA34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC34" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD34" t="inlineStr">
+        <is>
+          <t>VGA, 180 deg. rotating lens</t>
+        </is>
+      </c>
+      <c r="DE34" t="inlineStr"/>
+      <c r="DF34" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="DG34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH34" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Telit NEO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_neo-793.php</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2004, Q2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>99 x 44 x 18 mm (3.90 x 1.73 x 0.71 in)</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>65 g (2.29 oz)</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>7-color flashing LED</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>128 x 128 pixels, 1:1 ratio</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Predictive text input - Organizer - Stopwatch - Voice memo</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>2004, Q2</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4MB</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO35" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr"/>
+      <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="inlineStr"/>
+      <c r="CA35" t="inlineStr"/>
+      <c r="CB35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr"/>
+      <c r="CD35" t="inlineStr"/>
+      <c r="CE35" t="inlineStr"/>
+      <c r="CF35" t="inlineStr"/>
+      <c r="CG35" t="inlineStr"/>
+      <c r="CH35" t="inlineStr"/>
+      <c r="CI35" t="inlineStr"/>
+      <c r="CJ35" t="inlineStr"/>
+      <c r="CK35" t="inlineStr"/>
+      <c r="CL35" t="inlineStr"/>
+      <c r="CM35" t="inlineStr"/>
+      <c r="CN35" t="inlineStr"/>
+      <c r="CO35" t="inlineStr"/>
+      <c r="CP35" t="inlineStr"/>
+      <c r="CQ35" t="inlineStr"/>
+      <c r="CR35" t="inlineStr"/>
+      <c r="CS35" t="inlineStr"/>
+      <c r="CT35" t="inlineStr"/>
+      <c r="CU35" t="inlineStr"/>
+      <c r="CV35" t="inlineStr"/>
+      <c r="CW35" t="inlineStr"/>
+      <c r="CX35" t="inlineStr"/>
+      <c r="CY35" t="inlineStr"/>
+      <c r="CZ35" t="inlineStr"/>
+      <c r="DA35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC35" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD35" t="inlineStr"/>
+      <c r="DE35" t="inlineStr"/>
+      <c r="DF35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DG35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH35" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Telit X60i</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_x60i-792.php</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2004, Q2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Up to 3 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 720 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>72 x 41 x 22 mm (2.83 x 1.61 x 0.87 in)</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>65 g (2.29 oz)</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>Second external mono display (80 x 48 pixels)</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>128 x 128 pixels, 1:1 ratio</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>CSTN, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer Voice memo</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>2004, Q2</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>Silver, Blue</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO36" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr"/>
+      <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="inlineStr"/>
+      <c r="CA36" t="inlineStr"/>
+      <c r="CB36" t="inlineStr"/>
+      <c r="CC36" t="inlineStr"/>
+      <c r="CD36" t="inlineStr"/>
+      <c r="CE36" t="inlineStr"/>
+      <c r="CF36" t="inlineStr"/>
+      <c r="CG36" t="inlineStr"/>
+      <c r="CH36" t="inlineStr"/>
+      <c r="CI36" t="inlineStr"/>
+      <c r="CJ36" t="inlineStr"/>
+      <c r="CK36" t="inlineStr"/>
+      <c r="CL36" t="inlineStr"/>
+      <c r="CM36" t="inlineStr"/>
+      <c r="CN36" t="inlineStr"/>
+      <c r="CO36" t="inlineStr"/>
+      <c r="CP36" t="inlineStr"/>
+      <c r="CQ36" t="inlineStr"/>
+      <c r="CR36" t="inlineStr"/>
+      <c r="CS36" t="inlineStr"/>
+      <c r="CT36" t="inlineStr"/>
+      <c r="CU36" t="inlineStr"/>
+      <c r="CV36" t="inlineStr"/>
+      <c r="CW36" t="inlineStr"/>
+      <c r="CX36" t="inlineStr"/>
+      <c r="CY36" t="inlineStr"/>
+      <c r="CZ36" t="inlineStr"/>
+      <c r="DA36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC36" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD36" t="inlineStr"/>
+      <c r="DE36" t="inlineStr"/>
+      <c r="DF36" t="inlineStr">
+        <is>
+          <t>100 fields</t>
+        </is>
+      </c>
+      <c r="DG36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH36" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Telit G90</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_g90-578.php</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2003, Q4</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>16MB | 32MB</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Up to 100 h</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Up to 2 h</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Removable Li-Po 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>97 x 52 x 28 mm (3.82 x 2.05 x 1.10 in)</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>135 g (4.76 oz)</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>Second external display (64 x 48 pixels)</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels (~128 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>2.2 inches, 35 x 44 mm, 15.2 cm 2 (~30.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>MP3/AAC/AAC+/WMA/OGG/AMR player WMV/MP4 player Predictive text input Voice memo (3 min.) Organizer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>2003, Q4</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>16MB RAM, 32MB ROM</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>Intel XScale 200 MHz</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>Microsoft Smartphone 2002</t>
+        </is>
+      </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO37" t="inlineStr">
+        <is>
+          <t>Vibration; Polyphonic(40) ringtones</t>
+        </is>
+      </c>
+      <c r="BP37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
+      <c r="BU37" t="inlineStr"/>
+      <c r="BV37" t="inlineStr"/>
+      <c r="BW37" t="inlineStr"/>
+      <c r="BX37" t="inlineStr"/>
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="inlineStr"/>
+      <c r="CA37" t="inlineStr"/>
+      <c r="CB37" t="inlineStr"/>
+      <c r="CC37" t="inlineStr"/>
+      <c r="CD37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE37" t="inlineStr">
+        <is>
+          <t>Intel Xscale 200 MHz</t>
+        </is>
+      </c>
+      <c r="CF37" t="inlineStr"/>
+      <c r="CG37" t="inlineStr"/>
+      <c r="CH37" t="inlineStr"/>
+      <c r="CI37" t="inlineStr"/>
+      <c r="CJ37" t="inlineStr"/>
+      <c r="CK37" t="inlineStr"/>
+      <c r="CL37" t="inlineStr"/>
+      <c r="CM37" t="inlineStr"/>
+      <c r="CN37" t="inlineStr"/>
+      <c r="CO37" t="inlineStr"/>
+      <c r="CP37" t="inlineStr"/>
+      <c r="CQ37" t="inlineStr"/>
+      <c r="CR37" t="inlineStr"/>
+      <c r="CS37" t="inlineStr"/>
+      <c r="CT37" t="inlineStr"/>
+      <c r="CU37" t="inlineStr"/>
+      <c r="CV37" t="inlineStr"/>
+      <c r="CW37" t="inlineStr"/>
+      <c r="CX37" t="inlineStr"/>
+      <c r="CY37" t="inlineStr"/>
+      <c r="CZ37" t="inlineStr"/>
+      <c r="DA37" t="inlineStr"/>
+      <c r="DB37" t="inlineStr"/>
+      <c r="DC37" t="inlineStr"/>
+      <c r="DD37" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="DE37" t="inlineStr"/>
+      <c r="DF37" t="inlineStr"/>
+      <c r="DG37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH37" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Telit G83</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_g83-577.php</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2003, Q4</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 780 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>108 x 45 x 20 mm (4.25 x 1.77 x 0.79 in)</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>90 g (3.17 oz)</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer Voice dial/memo Photo editor</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>2003, Q4</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO38" t="inlineStr">
+        <is>
+          <t>Vibration; Polyphonic(16) ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
+      <c r="CA38" t="inlineStr"/>
+      <c r="CB38" t="inlineStr"/>
+      <c r="CC38" t="inlineStr"/>
+      <c r="CD38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE38" t="inlineStr"/>
+      <c r="CF38" t="inlineStr"/>
+      <c r="CG38" t="inlineStr"/>
+      <c r="CH38" t="inlineStr"/>
+      <c r="CI38" t="inlineStr"/>
+      <c r="CJ38" t="inlineStr"/>
+      <c r="CK38" t="inlineStr"/>
+      <c r="CL38" t="inlineStr"/>
+      <c r="CM38" t="inlineStr"/>
+      <c r="CN38" t="inlineStr"/>
+      <c r="CO38" t="inlineStr"/>
+      <c r="CP38" t="inlineStr"/>
+      <c r="CQ38" t="inlineStr"/>
+      <c r="CR38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr"/>
+      <c r="CT38" t="inlineStr"/>
+      <c r="CU38" t="inlineStr"/>
+      <c r="CV38" t="inlineStr"/>
+      <c r="CW38" t="inlineStr"/>
+      <c r="CX38" t="inlineStr"/>
+      <c r="CY38" t="inlineStr"/>
+      <c r="CZ38" t="inlineStr"/>
+      <c r="DA38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="DB38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DC38" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD38" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE38" t="inlineStr"/>
+      <c r="DF38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DG38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH38" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Telit G80</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Giugiaro Design</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_g80-362.php</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2002, Nov</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Up to 160 h</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Up to 6 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 600 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>105 x 60 x 23 mm (4.13 x 2.36 x 0.91 in)</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>96 g (3.39 oz)</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>3 fonts</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>160 x 120 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>CSTN, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>Barometer, altimeter</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>2002, Nov</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO39" t="inlineStr">
+        <is>
+          <t>Vibration; Polyphonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ39" t="inlineStr"/>
+      <c r="BR39" t="inlineStr"/>
+      <c r="BS39" t="inlineStr"/>
+      <c r="BT39" t="inlineStr"/>
+      <c r="BU39" t="inlineStr"/>
+      <c r="BV39" t="inlineStr"/>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
+      <c r="BY39" t="inlineStr"/>
+      <c r="BZ39" t="inlineStr"/>
+      <c r="CA39" t="inlineStr"/>
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
+      <c r="CH39" t="inlineStr"/>
+      <c r="CI39" t="inlineStr"/>
+      <c r="CJ39" t="inlineStr"/>
+      <c r="CK39" t="inlineStr"/>
+      <c r="CL39" t="inlineStr"/>
+      <c r="CM39" t="inlineStr"/>
+      <c r="CN39" t="inlineStr"/>
+      <c r="CO39" t="inlineStr"/>
+      <c r="CP39" t="inlineStr"/>
+      <c r="CQ39" t="inlineStr"/>
+      <c r="CR39" t="inlineStr"/>
+      <c r="CS39" t="inlineStr"/>
+      <c r="CT39" t="inlineStr"/>
+      <c r="CU39" t="inlineStr"/>
+      <c r="CV39" t="inlineStr"/>
+      <c r="CW39" t="inlineStr"/>
+      <c r="CX39" t="inlineStr"/>
+      <c r="CY39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC39" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD39" t="inlineStr">
+        <is>
+          <t>QVGA</t>
+        </is>
+      </c>
+      <c r="DE39" t="inlineStr"/>
+      <c r="DF39" t="inlineStr">
+        <is>
+          <t>Contact groups</t>
+        </is>
+      </c>
+      <c r="DG39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH39" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Telit G82</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Giugiaro Design</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_g82-361.php</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Up to 6 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 550 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>114 x 53 x 27 mm (4.49 x 2.09 x 1.06 in)</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>90 g (3.17 oz)</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>3 fonts</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>128 x 96 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>CSTN, 4096 colors</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO40" t="inlineStr">
+        <is>
+          <t>Vibration; Monophonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ40" t="inlineStr"/>
+      <c r="BR40" t="inlineStr"/>
+      <c r="BS40" t="inlineStr"/>
+      <c r="BT40" t="inlineStr"/>
+      <c r="BU40" t="inlineStr"/>
+      <c r="BV40" t="inlineStr"/>
+      <c r="BW40" t="inlineStr"/>
+      <c r="BX40" t="inlineStr"/>
+      <c r="BY40" t="inlineStr"/>
+      <c r="BZ40" t="inlineStr"/>
+      <c r="CA40" t="inlineStr"/>
+      <c r="CB40" t="inlineStr"/>
+      <c r="CC40" t="inlineStr"/>
+      <c r="CD40" t="inlineStr"/>
+      <c r="CE40" t="inlineStr"/>
+      <c r="CF40" t="inlineStr"/>
+      <c r="CG40" t="inlineStr"/>
+      <c r="CH40" t="inlineStr"/>
+      <c r="CI40" t="inlineStr"/>
+      <c r="CJ40" t="inlineStr"/>
+      <c r="CK40" t="inlineStr"/>
+      <c r="CL40" t="inlineStr"/>
+      <c r="CM40" t="inlineStr"/>
+      <c r="CN40" t="inlineStr"/>
+      <c r="CO40" t="inlineStr"/>
+      <c r="CP40" t="inlineStr"/>
+      <c r="CQ40" t="inlineStr"/>
+      <c r="CR40" t="inlineStr"/>
+      <c r="CS40" t="inlineStr"/>
+      <c r="CT40" t="inlineStr"/>
+      <c r="CU40" t="inlineStr"/>
+      <c r="CV40" t="inlineStr"/>
+      <c r="CW40" t="inlineStr"/>
+      <c r="CX40" t="inlineStr"/>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC40" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD40" t="inlineStr"/>
+      <c r="DE40" t="inlineStr"/>
+      <c r="DF40" t="inlineStr">
+        <is>
+          <t>Contact groups</t>
+        </is>
+      </c>
+      <c r="DG40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH40" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Telit G40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_g40-442.php</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2003, Q2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Up to 240 h</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Up to 2 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 610 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>105 x 46 x 18.5 mm (4.13 x 1.81 x 0.73 in)</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>75 g (2.65 oz)</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>Downloadable logos and backgrounds</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>101 x 80 pixels</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Predictive text input Chronometer Organizer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>2003, Q2</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO41" t="inlineStr">
+        <is>
+          <t>Vibration; Polyphonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ41" t="inlineStr"/>
+      <c r="BR41" t="inlineStr"/>
+      <c r="BS41" t="inlineStr"/>
+      <c r="BT41" t="inlineStr"/>
+      <c r="BU41" t="inlineStr"/>
+      <c r="BV41" t="inlineStr"/>
+      <c r="BW41" t="inlineStr"/>
+      <c r="BX41" t="inlineStr"/>
+      <c r="BY41" t="inlineStr"/>
+      <c r="BZ41" t="inlineStr"/>
+      <c r="CA41" t="inlineStr"/>
+      <c r="CB41" t="inlineStr"/>
+      <c r="CC41" t="inlineStr"/>
+      <c r="CD41" t="inlineStr"/>
+      <c r="CE41" t="inlineStr"/>
+      <c r="CF41" t="inlineStr"/>
+      <c r="CG41" t="inlineStr"/>
+      <c r="CH41" t="inlineStr"/>
+      <c r="CI41" t="inlineStr"/>
+      <c r="CJ41" t="inlineStr"/>
+      <c r="CK41" t="inlineStr"/>
+      <c r="CL41" t="inlineStr"/>
+      <c r="CM41" t="inlineStr"/>
+      <c r="CN41" t="inlineStr"/>
+      <c r="CO41" t="inlineStr"/>
+      <c r="CP41" t="inlineStr"/>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
+      <c r="CS41" t="inlineStr"/>
+      <c r="CT41" t="inlineStr"/>
+      <c r="CU41" t="inlineStr"/>
+      <c r="CV41" t="inlineStr"/>
+      <c r="CW41" t="inlineStr"/>
+      <c r="CX41" t="inlineStr"/>
+      <c r="CY41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA41" t="inlineStr">
+        <is>
+          <t>4 - Maze box, Failing, GridGuest, Dengo</t>
+        </is>
+      </c>
+      <c r="DB41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC41" t="inlineStr">
+        <is>
+          <t>SMS, EMS</t>
+        </is>
+      </c>
+      <c r="DD41" t="inlineStr"/>
+      <c r="DE41" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="DF41" t="inlineStr">
+        <is>
+          <t>Contact groups</t>
+        </is>
+      </c>
+      <c r="DG41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH41" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="DI41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Telit GM 882</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_gm_882-360.php</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Up to 6 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Removable NiMH 550 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>107 x 54 x 22 mm (4.21 x 2.13 x 0.87 in)</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>100 g (3.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>Blue backlight 3 fonts Fixed icons Softkeys</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>132 x 65 pixels, 18.5:9 ratio</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Predictive text input Organizer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>WAP 1.2.1</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO42" t="inlineStr">
+        <is>
+          <t>Vibration; Monophonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ42" t="inlineStr"/>
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="inlineStr"/>
+      <c r="BT42" t="inlineStr"/>
+      <c r="BU42" t="inlineStr"/>
+      <c r="BV42" t="inlineStr"/>
+      <c r="BW42" t="inlineStr"/>
+      <c r="BX42" t="inlineStr"/>
+      <c r="BY42" t="inlineStr"/>
+      <c r="BZ42" t="inlineStr"/>
+      <c r="CA42" t="inlineStr"/>
+      <c r="CB42" t="inlineStr"/>
+      <c r="CC42" t="inlineStr"/>
+      <c r="CD42" t="inlineStr"/>
+      <c r="CE42" t="inlineStr">
+        <is>
+          <t>11 predefined messages</t>
+        </is>
+      </c>
+      <c r="CF42" t="inlineStr"/>
+      <c r="CG42" t="inlineStr"/>
+      <c r="CH42" t="inlineStr"/>
+      <c r="CI42" t="inlineStr"/>
+      <c r="CJ42" t="inlineStr"/>
+      <c r="CK42" t="inlineStr"/>
+      <c r="CL42" t="inlineStr"/>
+      <c r="CM42" t="inlineStr"/>
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="inlineStr"/>
+      <c r="CP42" t="inlineStr"/>
+      <c r="CQ42" t="inlineStr"/>
+      <c r="CR42" t="inlineStr"/>
+      <c r="CS42" t="inlineStr"/>
+      <c r="CT42" t="inlineStr"/>
+      <c r="CU42" t="inlineStr"/>
+      <c r="CV42" t="inlineStr"/>
+      <c r="CW42" t="inlineStr"/>
+      <c r="CX42" t="inlineStr"/>
+      <c r="CY42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="DB42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC42" t="inlineStr">
+        <is>
+          <t>SMS, EMS, Email</t>
+        </is>
+      </c>
+      <c r="DD42" t="inlineStr"/>
+      <c r="DE42" t="inlineStr"/>
+      <c r="DF42" t="inlineStr">
+        <is>
+          <t>150 entries, contact groups</t>
+        </is>
+      </c>
+      <c r="DG42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH42" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="DI42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Telit GM 830</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_gm_830-189.php</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>52 h</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>4 h</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 650 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>117 x 51 x 20 mm (4.61 x 2.01 x 0.79 in)</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>105 g (3.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>Dynamic font size Fixed icons Softkeys</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>4 lines</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO43" t="inlineStr">
+        <is>
+          <t>Vibration; Monophonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ43" t="inlineStr"/>
+      <c r="BR43" t="inlineStr"/>
+      <c r="BS43" t="inlineStr"/>
+      <c r="BT43" t="inlineStr"/>
+      <c r="BU43" t="inlineStr"/>
+      <c r="BV43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr"/>
+      <c r="BZ43" t="inlineStr"/>
+      <c r="CA43" t="inlineStr"/>
+      <c r="CB43" t="inlineStr"/>
+      <c r="CC43" t="inlineStr"/>
+      <c r="CD43" t="inlineStr"/>
+      <c r="CE43" t="inlineStr"/>
+      <c r="CF43" t="inlineStr"/>
+      <c r="CG43" t="inlineStr"/>
+      <c r="CH43" t="inlineStr"/>
+      <c r="CI43" t="inlineStr"/>
+      <c r="CJ43" t="inlineStr"/>
+      <c r="CK43" t="inlineStr"/>
+      <c r="CL43" t="inlineStr"/>
+      <c r="CM43" t="inlineStr"/>
+      <c r="CN43" t="inlineStr"/>
+      <c r="CO43" t="inlineStr"/>
+      <c r="CP43" t="inlineStr"/>
+      <c r="CQ43" t="inlineStr"/>
+      <c r="CR43" t="inlineStr"/>
+      <c r="CS43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr"/>
+      <c r="CU43" t="inlineStr"/>
+      <c r="CV43" t="inlineStr"/>
+      <c r="CW43" t="inlineStr"/>
+      <c r="CX43" t="inlineStr"/>
+      <c r="CY43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC43" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD43" t="inlineStr"/>
+      <c r="DE43" t="inlineStr">
+        <is>
+          <t>10 dialed, 10 received, 10 missed calls</t>
+        </is>
+      </c>
+      <c r="DF43" t="inlineStr"/>
+      <c r="DG43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Telit GM 810</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_gm_810-188.php</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>52 h</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>4 h</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 650 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>117 x 51 x 18 mm (4.61 x 2.01 x 0.71 in)</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>105 g (3.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>Dynamic font size Fixed icons Softkeys</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>4 lines</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO44" t="inlineStr">
+        <is>
+          <t>Vibration; Monophonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ44" t="inlineStr"/>
+      <c r="BR44" t="inlineStr"/>
+      <c r="BS44" t="inlineStr"/>
+      <c r="BT44" t="inlineStr"/>
+      <c r="BU44" t="inlineStr"/>
+      <c r="BV44" t="inlineStr"/>
+      <c r="BW44" t="inlineStr"/>
+      <c r="BX44" t="inlineStr"/>
+      <c r="BY44" t="inlineStr"/>
+      <c r="BZ44" t="inlineStr"/>
+      <c r="CA44" t="inlineStr"/>
+      <c r="CB44" t="inlineStr"/>
+      <c r="CC44" t="inlineStr"/>
+      <c r="CD44" t="inlineStr"/>
+      <c r="CE44" t="inlineStr"/>
+      <c r="CF44" t="inlineStr"/>
+      <c r="CG44" t="inlineStr"/>
+      <c r="CH44" t="inlineStr"/>
+      <c r="CI44" t="inlineStr"/>
+      <c r="CJ44" t="inlineStr"/>
+      <c r="CK44" t="inlineStr"/>
+      <c r="CL44" t="inlineStr"/>
+      <c r="CM44" t="inlineStr"/>
+      <c r="CN44" t="inlineStr"/>
+      <c r="CO44" t="inlineStr"/>
+      <c r="CP44" t="inlineStr"/>
+      <c r="CQ44" t="inlineStr"/>
+      <c r="CR44" t="inlineStr"/>
+      <c r="CS44" t="inlineStr"/>
+      <c r="CT44" t="inlineStr"/>
+      <c r="CU44" t="inlineStr"/>
+      <c r="CV44" t="inlineStr"/>
+      <c r="CW44" t="inlineStr"/>
+      <c r="CX44" t="inlineStr"/>
+      <c r="CY44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC44" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD44" t="inlineStr"/>
+      <c r="DE44" t="inlineStr"/>
+      <c r="DF44" t="inlineStr"/>
+      <c r="DG44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Telit Estremo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_estremo-187.php</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>70 h</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>5 h</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>134 x 53 x 24 mm (5.28 x 2.09 x 0.94 in)</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>176 g (6.21 oz)</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>Dynamic font size Fixed icons Softkeys</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>4 lines</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>GSM 900</t>
+        </is>
+      </c>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO45" t="inlineStr">
+        <is>
+          <t>Monophonic ringtones, composer</t>
+        </is>
+      </c>
+      <c r="BP45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr">
+        <is>
+          <t>Water and shock resistant</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
+      <c r="BU45" t="inlineStr"/>
+      <c r="BV45" t="inlineStr"/>
+      <c r="BW45" t="inlineStr"/>
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="inlineStr"/>
+      <c r="BZ45" t="inlineStr"/>
+      <c r="CA45" t="inlineStr"/>
+      <c r="CB45" t="inlineStr"/>
+      <c r="CC45" t="inlineStr"/>
+      <c r="CD45" t="inlineStr"/>
+      <c r="CE45" t="inlineStr"/>
+      <c r="CF45" t="inlineStr"/>
+      <c r="CG45" t="inlineStr"/>
+      <c r="CH45" t="inlineStr"/>
+      <c r="CI45" t="inlineStr"/>
+      <c r="CJ45" t="inlineStr"/>
+      <c r="CK45" t="inlineStr"/>
+      <c r="CL45" t="inlineStr"/>
+      <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr"/>
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="inlineStr"/>
+      <c r="CQ45" t="inlineStr"/>
+      <c r="CR45" t="inlineStr"/>
+      <c r="CS45" t="inlineStr"/>
+      <c r="CT45" t="inlineStr"/>
+      <c r="CU45" t="inlineStr"/>
+      <c r="CV45" t="inlineStr"/>
+      <c r="CW45" t="inlineStr"/>
+      <c r="CX45" t="inlineStr"/>
+      <c r="CY45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC45" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD45" t="inlineStr"/>
+      <c r="DE45" t="inlineStr"/>
+      <c r="DF45" t="inlineStr"/>
+      <c r="DG45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GM 710</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_gm_710-186.php</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:59 UTC</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="inlineStr"/>
+      <c r="BR46" t="inlineStr"/>
+      <c r="BS46" t="inlineStr"/>
+      <c r="BT46" t="inlineStr"/>
+      <c r="BU46" t="inlineStr"/>
+      <c r="BV46" t="inlineStr"/>
+      <c r="BW46" t="inlineStr"/>
+      <c r="BX46" t="inlineStr"/>
+      <c r="BY46" t="inlineStr"/>
+      <c r="BZ46" t="inlineStr"/>
+      <c r="CA46" t="inlineStr"/>
+      <c r="CB46" t="inlineStr"/>
+      <c r="CC46" t="inlineStr"/>
+      <c r="CD46" t="inlineStr"/>
+      <c r="CE46" t="inlineStr"/>
+      <c r="CF46" t="inlineStr"/>
+      <c r="CG46" t="inlineStr"/>
+      <c r="CH46" t="inlineStr"/>
+      <c r="CI46" t="inlineStr"/>
+      <c r="CJ46" t="inlineStr"/>
+      <c r="CK46" t="inlineStr"/>
+      <c r="CL46" t="inlineStr"/>
+      <c r="CM46" t="inlineStr"/>
+      <c r="CN46" t="inlineStr"/>
+      <c r="CO46" t="inlineStr"/>
+      <c r="CP46" t="inlineStr"/>
+      <c r="CQ46" t="inlineStr"/>
+      <c r="CR46" t="inlineStr"/>
+      <c r="CS46" t="inlineStr"/>
+      <c r="CT46" t="inlineStr"/>
+      <c r="CU46" t="inlineStr"/>
+      <c r="CV46" t="inlineStr"/>
+      <c r="CW46" t="inlineStr"/>
+      <c r="CX46" t="inlineStr"/>
+      <c r="CY46" t="inlineStr"/>
+      <c r="CZ46" t="inlineStr"/>
+      <c r="DA46" t="inlineStr"/>
+      <c r="DB46" t="inlineStr"/>
+      <c r="DC46" t="inlineStr"/>
+      <c r="DD46" t="inlineStr"/>
+      <c r="DE46" t="inlineStr"/>
+      <c r="DF46" t="inlineStr"/>
+      <c r="DG46" t="inlineStr"/>
+      <c r="DH46" t="inlineStr"/>
+      <c r="DI46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI46"/>
+  <dimension ref="A1:DK69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,6 +980,16 @@
       <c r="DI1" t="inlineStr">
         <is>
           <t>Selfie camera</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>Our Tests_Audio quality</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>Our Tests_Camera</t>
         </is>
       </c>
     </row>
@@ -1303,6 +1313,8 @@
       <c r="DG2" t="inlineStr"/>
       <c r="DH2" t="inlineStr"/>
       <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1438,6 +1450,8 @@
       <c r="DG3" t="inlineStr"/>
       <c r="DH3" t="inlineStr"/>
       <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1855,6 +1869,8 @@
       <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="inlineStr"/>
       <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2268,6 +2284,8 @@
       <c r="DG5" t="inlineStr"/>
       <c r="DH5" t="inlineStr"/>
       <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2627,6 +2645,8 @@
       <c r="DG6" t="inlineStr"/>
       <c r="DH6" t="inlineStr"/>
       <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2982,6 +3002,8 @@
       <c r="DG7" t="inlineStr"/>
       <c r="DH7" t="inlineStr"/>
       <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3343,6 +3365,8 @@
       <c r="DG8" t="inlineStr"/>
       <c r="DH8" t="inlineStr"/>
       <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3698,6 +3722,8 @@
       <c r="DG9" t="inlineStr"/>
       <c r="DH9" t="inlineStr"/>
       <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4137,6 +4163,8 @@
       <c r="DG10" t="inlineStr"/>
       <c r="DH10" t="inlineStr"/>
       <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4570,6 +4598,8 @@
       <c r="DG11" t="inlineStr"/>
       <c r="DH11" t="inlineStr"/>
       <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5005,6 +5035,8 @@
       <c r="DG12" t="inlineStr"/>
       <c r="DH12" t="inlineStr"/>
       <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5380,6 +5412,8 @@
       <c r="DG13" t="inlineStr"/>
       <c r="DH13" t="inlineStr"/>
       <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5773,6 +5807,8 @@
       <c r="DG14" t="inlineStr"/>
       <c r="DH14" t="inlineStr"/>
       <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="inlineStr"/>
+      <c r="DK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6178,6 +6214,8 @@
       <c r="DG15" t="inlineStr"/>
       <c r="DH15" t="inlineStr"/>
       <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6585,6 +6623,8 @@
       <c r="DG16" t="inlineStr"/>
       <c r="DH16" t="inlineStr"/>
       <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6970,6 +7010,8 @@
       <c r="DG17" t="inlineStr"/>
       <c r="DH17" t="inlineStr"/>
       <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="inlineStr"/>
+      <c r="DK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7359,6 +7401,8 @@
       <c r="DG18" t="inlineStr"/>
       <c r="DH18" t="inlineStr"/>
       <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="inlineStr"/>
+      <c r="DK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7702,6 +7746,8 @@
       <c r="DG19" t="inlineStr"/>
       <c r="DH19" t="inlineStr"/>
       <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="inlineStr"/>
+      <c r="DK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8047,6 +8093,8 @@
       <c r="DG20" t="inlineStr"/>
       <c r="DH20" t="inlineStr"/>
       <c r="DI20" t="inlineStr"/>
+      <c r="DJ20" t="inlineStr"/>
+      <c r="DK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8392,6 +8440,8 @@
       <c r="DG21" t="inlineStr"/>
       <c r="DH21" t="inlineStr"/>
       <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="inlineStr"/>
+      <c r="DK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8763,6 +8813,8 @@
       <c r="DG22" t="inlineStr"/>
       <c r="DH22" t="inlineStr"/>
       <c r="DI22" t="inlineStr"/>
+      <c r="DJ22" t="inlineStr"/>
+      <c r="DK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9104,6 +9156,8 @@
       <c r="DG23" t="inlineStr"/>
       <c r="DH23" t="inlineStr"/>
       <c r="DI23" t="inlineStr"/>
+      <c r="DJ23" t="inlineStr"/>
+      <c r="DK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9513,6 +9567,8 @@
       <c r="DG24" t="inlineStr"/>
       <c r="DH24" t="inlineStr"/>
       <c r="DI24" t="inlineStr"/>
+      <c r="DJ24" t="inlineStr"/>
+      <c r="DK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9648,6 +9704,8 @@
       <c r="DG25" t="inlineStr"/>
       <c r="DH25" t="inlineStr"/>
       <c r="DI25" t="inlineStr"/>
+      <c r="DJ25" t="inlineStr"/>
+      <c r="DK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9681,46 +9739,32 @@
           <t>2006, Q2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="H26" t="n">
+        <v>2006</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="J26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" t="n">
+        <v>45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18</v>
+      </c>
+      <c r="M26" t="n">
+        <v>76</v>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="O26" t="n">
+        <v>128</v>
+      </c>
+      <c r="P26" t="n">
+        <v>128</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -9731,10 +9775,8 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="V26" t="n">
+        <v>650</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -9967,6 +10009,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ26" t="inlineStr"/>
+      <c r="DK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10000,56 +10044,40 @@
           <t>2005, Q1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="H27" t="n">
+        <v>2005</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="J27" t="n">
+        <v>52</v>
+      </c>
+      <c r="K27" t="n">
+        <v>57</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23</v>
+      </c>
+      <c r="M27" t="n">
+        <v>76</v>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="O27" t="n">
+        <v>128</v>
+      </c>
+      <c r="P27" t="n">
+        <v>160</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="V27" t="n">
+        <v>650</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -10282,6 +10310,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ27" t="inlineStr"/>
+      <c r="DK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10315,55 +10345,37 @@
           <t>2006, Q2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="H28" t="n">
+        <v>2006</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="J28" t="n">
+        <v>101</v>
+      </c>
+      <c r="K28" t="n">
+        <v>44</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>75</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O28" t="n">
+        <v>96</v>
+      </c>
+      <c r="P28" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>84</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -10373,10 +10385,8 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="V28" t="n">
+        <v>800</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -10597,6 +10607,8 @@
         </is>
       </c>
       <c r="DI28" t="inlineStr"/>
+      <c r="DJ28" t="inlineStr"/>
+      <c r="DK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10630,55 +10642,37 @@
           <t>2005, Q1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="H29" t="n">
+        <v>2005</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="J29" t="n">
+        <v>90</v>
+      </c>
+      <c r="K29" t="n">
+        <v>41</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20</v>
+      </c>
+      <c r="M29" t="n">
+        <v>75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>128</v>
+      </c>
+      <c r="P29" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>114</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -10928,6 +10922,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ29" t="inlineStr"/>
+      <c r="DK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10961,55 +10957,37 @@
           <t>2005, Q1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="H30" t="n">
+        <v>2005</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="J30" t="n">
+        <v>93</v>
+      </c>
+      <c r="K30" t="n">
+        <v>45</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>128</v>
+      </c>
+      <c r="P30" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>114</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -11017,10 +10995,8 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="T30" t="n">
+        <v>3</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -11263,6 +11239,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ30" t="inlineStr"/>
+      <c r="DK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11296,55 +11274,37 @@
           <t>2005, Q1</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="H31" t="n">
+        <v>2005</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="J31" t="n">
+        <v>90</v>
+      </c>
+      <c r="K31" t="n">
+        <v>40</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>128</v>
+      </c>
+      <c r="P31" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>114</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -11354,10 +11314,8 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="V31" t="n">
+        <v>650</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -11606,6 +11564,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ31" t="inlineStr"/>
+      <c r="DK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11639,46 +11599,32 @@
           <t>2005, Q1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="H32" t="n">
+        <v>2005</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
+      <c r="J32" t="n">
+        <v>86</v>
+      </c>
+      <c r="K32" t="n">
+        <v>48</v>
+      </c>
+      <c r="L32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>74.5</v>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="O32" t="n">
+        <v>128</v>
+      </c>
+      <c r="P32" t="n">
+        <v>160</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -11917,6 +11863,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ32" t="inlineStr"/>
+      <c r="DK32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11950,46 +11898,32 @@
           <t>2004, Q3</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="H33" t="n">
+        <v>2004</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="J33" t="n">
+        <v>85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85</v>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="O33" t="n">
+        <v>128</v>
+      </c>
+      <c r="P33" t="n">
+        <v>160</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -12000,10 +11934,8 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="V33" t="n">
+        <v>720</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -12228,6 +12160,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ33" t="inlineStr"/>
+      <c r="DK33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12261,46 +12195,32 @@
           <t>2004, Q3</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="H34" t="n">
+        <v>2004</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="J34" t="n">
+        <v>85</v>
+      </c>
+      <c r="K34" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85</v>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="O34" t="n">
+        <v>128</v>
+      </c>
+      <c r="P34" t="n">
+        <v>160</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -12311,10 +12231,8 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="V34" t="n">
+        <v>720</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -12539,6 +12457,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ34" t="inlineStr"/>
+      <c r="DK34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12572,46 +12492,32 @@
           <t>2004, Q2</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="H35" t="n">
+        <v>2004</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="J35" t="n">
+        <v>99</v>
+      </c>
+      <c r="K35" t="n">
+        <v>44</v>
+      </c>
+      <c r="L35" t="n">
+        <v>18</v>
+      </c>
+      <c r="M35" t="n">
+        <v>65</v>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="O35" t="n">
+        <v>128</v>
+      </c>
+      <c r="P35" t="n">
+        <v>128</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -12838,6 +12744,8 @@
         </is>
       </c>
       <c r="DI35" t="inlineStr"/>
+      <c r="DJ35" t="inlineStr"/>
+      <c r="DK35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12871,56 +12779,40 @@
           <t>2004, Q2</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="H36" t="n">
+        <v>2004</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="J36" t="n">
+        <v>72</v>
+      </c>
+      <c r="K36" t="n">
+        <v>41</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22</v>
+      </c>
+      <c r="M36" t="n">
+        <v>65</v>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="O36" t="n">
+        <v>128</v>
+      </c>
+      <c r="P36" t="n">
+        <v>128</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
+      <c r="V36" t="n">
+        <v>720</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -13137,6 +13029,8 @@
         </is>
       </c>
       <c r="DI36" t="inlineStr"/>
+      <c r="DJ36" t="inlineStr"/>
+      <c r="DK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13170,55 +13064,37 @@
           <t>2003, Q4</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="H37" t="n">
+        <v>2003</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="J37" t="n">
+        <v>97</v>
+      </c>
+      <c r="K37" t="n">
+        <v>52</v>
+      </c>
+      <c r="L37" t="n">
+        <v>28</v>
+      </c>
+      <c r="M37" t="n">
+        <v>135</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>176</v>
+      </c>
+      <c r="P37" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>128</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -13232,10 +13108,8 @@
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="V37" t="n">
+        <v>1000</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -13472,6 +13346,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ37" t="inlineStr"/>
+      <c r="DK37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13505,56 +13381,40 @@
           <t>2003, Q4</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="H38" t="n">
+        <v>2003</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="J38" t="n">
+        <v>108</v>
+      </c>
+      <c r="K38" t="n">
+        <v>45</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="n">
+        <v>90</v>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="O38" t="n">
+        <v>128</v>
+      </c>
+      <c r="P38" t="n">
+        <v>160</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
+      <c r="V38" t="n">
+        <v>780</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
@@ -13767,6 +13627,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ38" t="inlineStr"/>
+      <c r="DK38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13804,56 +13666,40 @@
           <t>2002, Nov</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="H39" t="n">
+        <v>2002</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="J39" t="n">
+        <v>105</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23</v>
+      </c>
+      <c r="M39" t="n">
+        <v>96</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="O39" t="n">
+        <v>160</v>
+      </c>
+      <c r="P39" t="n">
+        <v>120</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="V39" t="n">
+        <v>600</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -14086,6 +13932,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DJ39" t="inlineStr"/>
+      <c r="DK39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14123,56 +13971,40 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="H40" t="n">
+        <v>2002</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="J40" t="n">
+        <v>114</v>
+      </c>
+      <c r="K40" t="n">
+        <v>53</v>
+      </c>
+      <c r="L40" t="n">
+        <v>27</v>
+      </c>
+      <c r="M40" t="n">
+        <v>90</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="O40" t="n">
+        <v>128</v>
+      </c>
+      <c r="P40" t="n">
+        <v>96</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="V40" t="n">
+        <v>550</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -14393,6 +14225,8 @@
         </is>
       </c>
       <c r="DI40" t="inlineStr"/>
+      <c r="DJ40" t="inlineStr"/>
+      <c r="DK40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14426,56 +14260,40 @@
           <t>2003, Q2</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="H41" t="n">
+        <v>2003</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="J41" t="n">
+        <v>105</v>
+      </c>
+      <c r="K41" t="n">
+        <v>46</v>
+      </c>
+      <c r="L41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>75</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="O41" t="n">
+        <v>101</v>
+      </c>
+      <c r="P41" t="n">
+        <v>80</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
+      <c r="V41" t="n">
+        <v>610</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -14700,6 +14518,8 @@
         </is>
       </c>
       <c r="DI41" t="inlineStr"/>
+      <c r="DJ41" t="inlineStr"/>
+      <c r="DK41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14733,56 +14553,40 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="H42" t="n">
+        <v>2002</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="J42" t="n">
+        <v>107</v>
+      </c>
+      <c r="K42" t="n">
+        <v>54</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22</v>
+      </c>
+      <c r="M42" t="n">
+        <v>100</v>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="O42" t="n">
+        <v>132</v>
+      </c>
+      <c r="P42" t="n">
+        <v>65</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="V42" t="n">
+        <v>550</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -15007,6 +14811,8 @@
         </is>
       </c>
       <c r="DI42" t="inlineStr"/>
+      <c r="DJ42" t="inlineStr"/>
+      <c r="DK42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15046,25 +14852,17 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="J43" t="n">
+        <v>117</v>
+      </c>
+      <c r="K43" t="n">
+        <v>51</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20</v>
+      </c>
+      <c r="M43" t="n">
+        <v>105</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -15074,10 +14872,8 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="V43" t="n">
+        <v>650</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -15294,6 +15090,8 @@
         </is>
       </c>
       <c r="DI43" t="inlineStr"/>
+      <c r="DJ43" t="inlineStr"/>
+      <c r="DK43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15333,25 +15131,17 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="J44" t="n">
+        <v>117</v>
+      </c>
+      <c r="K44" t="n">
+        <v>51</v>
+      </c>
+      <c r="L44" t="n">
+        <v>18</v>
+      </c>
+      <c r="M44" t="n">
+        <v>105</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -15361,10 +15151,8 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="V44" t="n">
+        <v>650</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -15577,6 +15365,8 @@
         </is>
       </c>
       <c r="DI44" t="inlineStr"/>
+      <c r="DJ44" t="inlineStr"/>
+      <c r="DK44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15616,25 +15406,17 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="J45" t="n">
+        <v>134</v>
+      </c>
+      <c r="K45" t="n">
+        <v>53</v>
+      </c>
+      <c r="L45" t="n">
+        <v>24</v>
+      </c>
+      <c r="M45" t="n">
+        <v>176</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -15644,10 +15426,8 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="V45" t="n">
+        <v>1000</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -15864,6 +15644,8 @@
         </is>
       </c>
       <c r="DI45" t="inlineStr"/>
+      <c r="DJ45" t="inlineStr"/>
+      <c r="DK45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15999,6 +15781,7999 @@
       <c r="DG46" t="inlineStr"/>
       <c r="DH46" t="inlineStr"/>
       <c r="DI46" t="inlineStr"/>
+      <c r="DJ46" t="inlineStr"/>
+      <c r="DK46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Samsung R360 Messenger Touch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>For U.S. Cellular</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_r360_messenger_touch-3435.php</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Up to 288 h</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>105 x 54 x 15 mm (4.13 x 2.13 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>108 g (3.81 oz)</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~154 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>2.6 inches, 20.9 cm 2 (~36.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>TFT,  256K colors</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>MP4/H.263 player MP3/AAC+ player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
+      <c r="BU47" t="inlineStr"/>
+      <c r="BV47" t="inlineStr"/>
+      <c r="BW47" t="inlineStr"/>
+      <c r="BX47" t="inlineStr"/>
+      <c r="BY47" t="inlineStr"/>
+      <c r="BZ47" t="inlineStr"/>
+      <c r="CA47" t="inlineStr"/>
+      <c r="CB47" t="inlineStr"/>
+      <c r="CC47" t="inlineStr"/>
+      <c r="CD47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE47" t="inlineStr"/>
+      <c r="CF47" t="inlineStr"/>
+      <c r="CG47" t="inlineStr">
+        <is>
+          <t>0.95 W/kg (head)     1.02 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH47" t="inlineStr"/>
+      <c r="CI47" t="inlineStr"/>
+      <c r="CJ47" t="inlineStr"/>
+      <c r="CK47" t="inlineStr"/>
+      <c r="CL47" t="inlineStr"/>
+      <c r="CM47" t="inlineStr"/>
+      <c r="CN47" t="inlineStr"/>
+      <c r="CO47" t="inlineStr"/>
+      <c r="CP47" t="inlineStr"/>
+      <c r="CQ47" t="inlineStr"/>
+      <c r="CR47" t="inlineStr"/>
+      <c r="CS47" t="inlineStr"/>
+      <c r="CT47" t="inlineStr"/>
+      <c r="CU47" t="inlineStr"/>
+      <c r="CV47" t="inlineStr"/>
+      <c r="CW47" t="inlineStr"/>
+      <c r="CX47" t="inlineStr"/>
+      <c r="CY47" t="inlineStr"/>
+      <c r="CZ47" t="inlineStr"/>
+      <c r="DA47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB47" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC47" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="DD47" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF47" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG47" t="inlineStr"/>
+      <c r="DH47" t="inlineStr"/>
+      <c r="DI47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ47" t="inlineStr"/>
+      <c r="DK47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Samsung i225 Exec</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>For U.S. Cellular</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i225_exec-3436.php</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>123MB</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Up to 450 h</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Up to 8 h</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>117 x 60 x 11 mm (4.61 x 2.36 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>105 g (3.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>320 x 240 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~25.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>MP4/H.264/WMV player MP3/AAC+ player Organizer Document viewer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>123MB</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="BK48" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL48" t="inlineStr">
+        <is>
+          <t>667 MHz</t>
+        </is>
+      </c>
+      <c r="BM48" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.5 Standard</t>
+        </is>
+      </c>
+      <c r="BN48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO48" t="inlineStr"/>
+      <c r="BP48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ48" t="inlineStr"/>
+      <c r="BR48" t="inlineStr"/>
+      <c r="BS48" t="inlineStr"/>
+      <c r="BT48" t="inlineStr"/>
+      <c r="BU48" t="inlineStr"/>
+      <c r="BV48" t="inlineStr"/>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="inlineStr"/>
+      <c r="CB48" t="inlineStr"/>
+      <c r="CC48" t="inlineStr"/>
+      <c r="CD48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE48" t="inlineStr"/>
+      <c r="CF48" t="inlineStr"/>
+      <c r="CG48" t="inlineStr">
+        <is>
+          <t>1.03 W/kg (head)     0.53 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH48" t="inlineStr"/>
+      <c r="CI48" t="inlineStr"/>
+      <c r="CJ48" t="inlineStr"/>
+      <c r="CK48" t="inlineStr"/>
+      <c r="CL48" t="inlineStr"/>
+      <c r="CM48" t="inlineStr"/>
+      <c r="CN48" t="inlineStr"/>
+      <c r="CO48" t="inlineStr"/>
+      <c r="CP48" t="inlineStr"/>
+      <c r="CQ48" t="inlineStr"/>
+      <c r="CR48" t="inlineStr"/>
+      <c r="CS48" t="inlineStr"/>
+      <c r="CT48" t="inlineStr"/>
+      <c r="CU48" t="inlineStr"/>
+      <c r="CV48" t="inlineStr"/>
+      <c r="CW48" t="inlineStr"/>
+      <c r="CX48" t="inlineStr"/>
+      <c r="CY48" t="inlineStr"/>
+      <c r="CZ48" t="inlineStr"/>
+      <c r="DA48" t="inlineStr"/>
+      <c r="DB48" t="inlineStr"/>
+      <c r="DC48" t="inlineStr"/>
+      <c r="DD48" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE48" t="inlineStr"/>
+      <c r="DF48" t="inlineStr"/>
+      <c r="DG48" t="inlineStr"/>
+      <c r="DH48" t="inlineStr"/>
+      <c r="DI48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ48" t="inlineStr"/>
+      <c r="DK48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Samsung M570 Restore</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>For Sprint</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_m570_restore-3438.php</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Up to 400 h</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1160 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>117 x 53 x 15 mm (4.61 x 2.09 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>122 g (4.30 oz)</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~150 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>2.66 inches, 21.9 cm 2 (~35.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>SNS integration MP4/H.264 player MP3/eAAC+/WAV player Organizer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>Black, Green</t>
+        </is>
+      </c>
+      <c r="BF49" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO49" t="inlineStr"/>
+      <c r="BP49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ49" t="inlineStr"/>
+      <c r="BR49" t="inlineStr">
+        <is>
+          <t>Optical trackpad</t>
+        </is>
+      </c>
+      <c r="BS49" t="inlineStr"/>
+      <c r="BT49" t="inlineStr"/>
+      <c r="BU49" t="inlineStr"/>
+      <c r="BV49" t="inlineStr"/>
+      <c r="BW49" t="inlineStr"/>
+      <c r="BX49" t="inlineStr"/>
+      <c r="BY49" t="inlineStr"/>
+      <c r="BZ49" t="inlineStr"/>
+      <c r="CA49" t="inlineStr"/>
+      <c r="CB49" t="inlineStr"/>
+      <c r="CC49" t="inlineStr"/>
+      <c r="CD49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE49" t="inlineStr"/>
+      <c r="CF49" t="inlineStr"/>
+      <c r="CG49" t="inlineStr">
+        <is>
+          <t>0.99 W/kg (head)     0.56 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH49" t="inlineStr"/>
+      <c r="CI49" t="inlineStr"/>
+      <c r="CJ49" t="inlineStr"/>
+      <c r="CK49" t="inlineStr"/>
+      <c r="CL49" t="inlineStr"/>
+      <c r="CM49" t="inlineStr"/>
+      <c r="CN49" t="inlineStr"/>
+      <c r="CO49" t="inlineStr"/>
+      <c r="CP49" t="inlineStr"/>
+      <c r="CQ49" t="inlineStr"/>
+      <c r="CR49" t="inlineStr"/>
+      <c r="CS49" t="inlineStr"/>
+      <c r="CT49" t="inlineStr"/>
+      <c r="CU49" t="inlineStr"/>
+      <c r="CV49" t="inlineStr"/>
+      <c r="CW49" t="inlineStr"/>
+      <c r="CX49" t="inlineStr">
+        <is>
+          <t>2.5 mm audio jack</t>
+        </is>
+      </c>
+      <c r="CY49" t="inlineStr"/>
+      <c r="CZ49" t="inlineStr"/>
+      <c r="DA49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB49" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC49" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="DD49" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF49" t="inlineStr">
+        <is>
+          <t>Yes, Photocall</t>
+        </is>
+      </c>
+      <c r="DG49" t="inlineStr"/>
+      <c r="DH49" t="inlineStr"/>
+      <c r="DI49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ49" t="inlineStr"/>
+      <c r="DK49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Samsung R351 Freeform</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>For U.S. CellularAlso known as Samsung LINK, Samsung R350 Freeform</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_r351_freeform-3439.php</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2009, August. Released 2009, August</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>55MB</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>112 x 61 x 13 mm (4.41 x 2.40 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>103 g (3.63 oz)</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>220 x 176 pixels (~128 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.2 cm 2 (~22.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>MP4/H.263 player MP3/AAC+ player Organizer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>2009, August. Released 2009, August</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>55MB</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>Black, Red</t>
+        </is>
+      </c>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>CDMA / CDMA2000</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO50" t="inlineStr"/>
+      <c r="BP50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ50" t="inlineStr"/>
+      <c r="BR50" t="inlineStr"/>
+      <c r="BS50" t="inlineStr"/>
+      <c r="BT50" t="inlineStr"/>
+      <c r="BU50" t="inlineStr"/>
+      <c r="BV50" t="inlineStr"/>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
+      <c r="BY50" t="inlineStr"/>
+      <c r="BZ50" t="inlineStr"/>
+      <c r="CA50" t="inlineStr"/>
+      <c r="CB50" t="inlineStr"/>
+      <c r="CC50" t="inlineStr"/>
+      <c r="CD50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE50" t="inlineStr"/>
+      <c r="CF50" t="inlineStr"/>
+      <c r="CG50" t="inlineStr">
+        <is>
+          <t>1.01 W/kg (head)     0.53 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH50" t="inlineStr"/>
+      <c r="CI50" t="inlineStr"/>
+      <c r="CJ50" t="inlineStr"/>
+      <c r="CK50" t="inlineStr"/>
+      <c r="CL50" t="inlineStr"/>
+      <c r="CM50" t="inlineStr"/>
+      <c r="CN50" t="inlineStr"/>
+      <c r="CO50" t="inlineStr"/>
+      <c r="CP50" t="inlineStr"/>
+      <c r="CQ50" t="inlineStr"/>
+      <c r="CR50" t="inlineStr"/>
+      <c r="CS50" t="inlineStr"/>
+      <c r="CT50" t="inlineStr"/>
+      <c r="CU50" t="inlineStr"/>
+      <c r="CV50" t="inlineStr"/>
+      <c r="CW50" t="inlineStr"/>
+      <c r="CX50" t="inlineStr">
+        <is>
+          <t>2.5 mm audio jack</t>
+        </is>
+      </c>
+      <c r="CY50" t="inlineStr"/>
+      <c r="CZ50" t="inlineStr"/>
+      <c r="DA50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB50" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC50" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD50" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF50" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG50" t="inlineStr"/>
+      <c r="DH50" t="inlineStr"/>
+      <c r="DI50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ50" t="inlineStr"/>
+      <c r="DK50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Samsung T369</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>For T-mobileAlso known as Samsung Linx for US</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_t369-3928.php</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Up to 300 h</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Up to 5 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>114 x 53 x 15 mm (4.49 x 2.09 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>112 g (3.95 oz)</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>2.0, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~160 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>2.5 inches, 19.4 cm 2 (~32.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>MP3/AAC+ player MP4/H.263 player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO51" t="inlineStr"/>
+      <c r="BP51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ51" t="inlineStr"/>
+      <c r="BR51" t="inlineStr"/>
+      <c r="BS51" t="inlineStr"/>
+      <c r="BT51" t="inlineStr"/>
+      <c r="BU51" t="inlineStr"/>
+      <c r="BV51" t="inlineStr"/>
+      <c r="BW51" t="inlineStr"/>
+      <c r="BX51" t="inlineStr"/>
+      <c r="BY51" t="inlineStr"/>
+      <c r="BZ51" t="inlineStr"/>
+      <c r="CA51" t="inlineStr"/>
+      <c r="CB51" t="inlineStr"/>
+      <c r="CC51" t="inlineStr"/>
+      <c r="CD51" t="inlineStr">
+        <is>
+          <t>QCIF</t>
+        </is>
+      </c>
+      <c r="CE51" t="inlineStr"/>
+      <c r="CF51" t="inlineStr"/>
+      <c r="CG51" t="inlineStr">
+        <is>
+          <t>0.52 W/kg (head)     1.11 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH51" t="inlineStr"/>
+      <c r="CI51" t="inlineStr"/>
+      <c r="CJ51" t="inlineStr"/>
+      <c r="CK51" t="inlineStr"/>
+      <c r="CL51" t="inlineStr"/>
+      <c r="CM51" t="inlineStr"/>
+      <c r="CN51" t="inlineStr"/>
+      <c r="CO51" t="inlineStr"/>
+      <c r="CP51" t="inlineStr"/>
+      <c r="CQ51" t="inlineStr"/>
+      <c r="CR51" t="inlineStr"/>
+      <c r="CS51" t="inlineStr"/>
+      <c r="CT51" t="inlineStr"/>
+      <c r="CU51" t="inlineStr"/>
+      <c r="CV51" t="inlineStr"/>
+      <c r="CW51" t="inlineStr"/>
+      <c r="CX51" t="inlineStr"/>
+      <c r="CY51" t="inlineStr"/>
+      <c r="CZ51" t="inlineStr"/>
+      <c r="DA51" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB51" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC51" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD51" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF51" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG51" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DH51" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ51" t="inlineStr"/>
+      <c r="DK51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Samsung S5330 Wave533</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Previously known as Samsung Wave 2 Pro</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_s5330_wave533-3399.php</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Up to 1090 h</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Up to 14 h</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>109.5 x 55 x 15.2 mm (4.31 x 2.17 x 0.60 in)</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>118 g (4.16 oz)</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>TouchWiz UI 3.0</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~48.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>TFT,  256K colors</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>MP3/WAV/eAAC+ player MP4/H.264 player Organizer Music Recognition Photo editor Voice memo Predictive text input (T9 Trace)</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>0.32 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr">
+        <is>
+          <t>bada OS</t>
+        </is>
+      </c>
+      <c r="BN52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO52" t="inlineStr"/>
+      <c r="BP52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ52" t="inlineStr"/>
+      <c r="BR52" t="inlineStr"/>
+      <c r="BS52" t="inlineStr"/>
+      <c r="BT52" t="inlineStr"/>
+      <c r="BU52" t="inlineStr"/>
+      <c r="BV52" t="inlineStr"/>
+      <c r="BW52" t="inlineStr"/>
+      <c r="BX52" t="inlineStr"/>
+      <c r="BY52" t="inlineStr"/>
+      <c r="BZ52" t="inlineStr"/>
+      <c r="CA52" t="inlineStr"/>
+      <c r="CB52" t="inlineStr"/>
+      <c r="CC52" t="inlineStr"/>
+      <c r="CD52" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="CE52" t="inlineStr"/>
+      <c r="CF52" t="inlineStr"/>
+      <c r="CG52" t="inlineStr">
+        <is>
+          <t>0.35 W/kg (head)     0.65 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH52" t="inlineStr"/>
+      <c r="CI52" t="inlineStr"/>
+      <c r="CJ52" t="inlineStr"/>
+      <c r="CK52" t="inlineStr"/>
+      <c r="CL52" t="inlineStr"/>
+      <c r="CM52" t="inlineStr"/>
+      <c r="CN52" t="inlineStr"/>
+      <c r="CO52" t="inlineStr"/>
+      <c r="CP52" t="inlineStr"/>
+      <c r="CQ52" t="inlineStr"/>
+      <c r="CR52" t="inlineStr"/>
+      <c r="CS52" t="inlineStr"/>
+      <c r="CT52" t="inlineStr"/>
+      <c r="CU52" t="inlineStr"/>
+      <c r="CV52" t="inlineStr"/>
+      <c r="CW52" t="inlineStr"/>
+      <c r="CX52" t="inlineStr"/>
+      <c r="CY52" t="inlineStr"/>
+      <c r="CZ52" t="inlineStr"/>
+      <c r="DA52" t="inlineStr"/>
+      <c r="DB52" t="inlineStr"/>
+      <c r="DC52" t="inlineStr"/>
+      <c r="DD52" t="inlineStr">
+        <is>
+          <t>3.15 MP</t>
+        </is>
+      </c>
+      <c r="DE52" t="inlineStr"/>
+      <c r="DF52" t="inlineStr"/>
+      <c r="DG52" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DH52" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DI52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ52" t="inlineStr"/>
+      <c r="DK52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Samsung S5250 Wave525</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Previously known as Samsung Wave 2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_s5250_wave525-3400.php</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Up to 1200 h</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Up to 14 h</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>109.5 x 55 x 11.9 mm (4.31 x 2.17 x 0.47 in)</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>100 g (3.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>TouchWiz UI 3.0</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~48.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>TFT,  256K colors</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>MP3/WAV/eAAC+ player MP4/H.264 player Organizer Music Recognition Photo editor Voice memo Predictive text input (T9 Trace)</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>100MB</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>Black, White/La Fleur edition</t>
+        </is>
+      </c>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>0.69 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr">
+        <is>
+          <t>bada OS</t>
+        </is>
+      </c>
+      <c r="BN53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO53" t="inlineStr"/>
+      <c r="BP53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ53" t="inlineStr"/>
+      <c r="BR53" t="inlineStr"/>
+      <c r="BS53" t="inlineStr"/>
+      <c r="BT53" t="inlineStr"/>
+      <c r="BU53" t="inlineStr"/>
+      <c r="BV53" t="inlineStr"/>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
+      <c r="BY53" t="inlineStr"/>
+      <c r="BZ53" t="inlineStr"/>
+      <c r="CA53" t="inlineStr"/>
+      <c r="CB53" t="inlineStr"/>
+      <c r="CC53" t="inlineStr"/>
+      <c r="CD53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE53" t="inlineStr"/>
+      <c r="CF53" t="inlineStr"/>
+      <c r="CG53" t="inlineStr">
+        <is>
+          <t>0.63 W/kg (head)     0.52 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH53" t="inlineStr"/>
+      <c r="CI53" t="inlineStr"/>
+      <c r="CJ53" t="inlineStr"/>
+      <c r="CK53" t="inlineStr"/>
+      <c r="CL53" t="inlineStr"/>
+      <c r="CM53" t="inlineStr"/>
+      <c r="CN53" t="inlineStr"/>
+      <c r="CO53" t="inlineStr"/>
+      <c r="CP53" t="inlineStr"/>
+      <c r="CQ53" t="inlineStr"/>
+      <c r="CR53" t="inlineStr"/>
+      <c r="CS53" t="inlineStr"/>
+      <c r="CT53" t="inlineStr"/>
+      <c r="CU53" t="inlineStr"/>
+      <c r="CV53" t="inlineStr"/>
+      <c r="CW53" t="inlineStr"/>
+      <c r="CX53" t="inlineStr"/>
+      <c r="CY53" t="inlineStr"/>
+      <c r="CZ53" t="inlineStr"/>
+      <c r="DA53" t="inlineStr"/>
+      <c r="DB53" t="inlineStr"/>
+      <c r="DC53" t="inlineStr"/>
+      <c r="DD53" t="inlineStr">
+        <is>
+          <t>3.15 MP</t>
+        </is>
+      </c>
+      <c r="DE53" t="inlineStr"/>
+      <c r="DF53" t="inlineStr"/>
+      <c r="DG53" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DH53" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DI53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ53" t="inlineStr"/>
+      <c r="DK53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Samsung I5500 Galaxy 5</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Also known as Samsung i5500 Corby Smartphone, Samsung Galaxy Europa, Samsung Galaxy 550</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i5500_galaxy_5-3371.php</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, August</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>170MB</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Up to 521 h (2G) / Up to 375 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Up to 9 h 30 min (2G) / Up to 6 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>108 x 56 x 12.3 mm (4.25 x 2.20 x 0.48 in)</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>102 g (3.60 oz)</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, DLNA, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>TouchWiz v3.0</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~143 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>2.8 inches, 24.3 cm 2 (~40.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>MP4/H.264 player MP3/WAV/eAAC+ player</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, August</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 1 GB included</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>170MB</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>0.65 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ54" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL54" t="inlineStr">
+        <is>
+          <t>600 MHz</t>
+        </is>
+      </c>
+      <c r="BM54" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="BN54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO54" t="inlineStr"/>
+      <c r="BP54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ54" t="inlineStr"/>
+      <c r="BR54" t="inlineStr"/>
+      <c r="BS54" t="inlineStr"/>
+      <c r="BT54" t="inlineStr"/>
+      <c r="BU54" t="inlineStr"/>
+      <c r="BV54" t="inlineStr"/>
+      <c r="BW54" t="inlineStr"/>
+      <c r="BX54" t="inlineStr"/>
+      <c r="BY54" t="inlineStr"/>
+      <c r="BZ54" t="inlineStr"/>
+      <c r="CA54" t="inlineStr"/>
+      <c r="CB54" t="inlineStr"/>
+      <c r="CC54" t="inlineStr"/>
+      <c r="CD54" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="CE54" t="inlineStr"/>
+      <c r="CF54" t="inlineStr"/>
+      <c r="CG54" t="inlineStr"/>
+      <c r="CH54" t="inlineStr"/>
+      <c r="CI54" t="inlineStr"/>
+      <c r="CJ54" t="inlineStr"/>
+      <c r="CK54" t="inlineStr"/>
+      <c r="CL54" t="inlineStr"/>
+      <c r="CM54" t="inlineStr"/>
+      <c r="CN54" t="inlineStr"/>
+      <c r="CO54" t="inlineStr"/>
+      <c r="CP54" t="inlineStr">
+        <is>
+          <t>Voice 73dB / Noise 66dB / Ring 76dB</t>
+        </is>
+      </c>
+      <c r="CQ54" t="inlineStr"/>
+      <c r="CR54" t="inlineStr"/>
+      <c r="CS54" t="inlineStr"/>
+      <c r="CT54" t="inlineStr"/>
+      <c r="CU54" t="inlineStr"/>
+      <c r="CV54" t="inlineStr"/>
+      <c r="CW54" t="inlineStr"/>
+      <c r="CX54" t="inlineStr"/>
+      <c r="CY54" t="inlineStr"/>
+      <c r="CZ54" t="inlineStr"/>
+      <c r="DA54" t="inlineStr"/>
+      <c r="DB54" t="inlineStr"/>
+      <c r="DC54" t="inlineStr"/>
+      <c r="DD54" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE54" t="inlineStr"/>
+      <c r="DF54" t="inlineStr"/>
+      <c r="DG54" t="inlineStr"/>
+      <c r="DH54" t="inlineStr"/>
+      <c r="DI54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ54" t="inlineStr">
+        <is>
+          <t>Noise -79.7dB / Crosstalk -75.1dB</t>
+        </is>
+      </c>
+      <c r="DK54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Samsung I5801 Galaxy Apollo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>For OrangeAlso known as Samsung Galaxy Naos, Samsung Galaxy Leo</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i5801_galaxy_apollo-3432.php</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>113.5</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Up to 620 h (2G) / Up to 480 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Up to 15 h 30 min (2G) / Up to 7 h 15 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>113.5 x 55 x 12.6 mm (4.47 x 2.17 x 0.50 in)</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>113 g (3.99 oz)</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>Touch Wiz 3.0</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~46.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>MP4/DivX/XviD/WMV/H.264 player MP3/WAV/eAAC+ player Document editor</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 1 GB included</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>512MB 256MB RAM</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>0.57 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ55" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK55" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL55" t="inlineStr">
+        <is>
+          <t>Samsung S5P6422 667 MHz</t>
+        </is>
+      </c>
+      <c r="BM55" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="BN55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ55" t="inlineStr"/>
+      <c r="BR55" t="inlineStr"/>
+      <c r="BS55" t="inlineStr"/>
+      <c r="BT55" t="inlineStr"/>
+      <c r="BU55" t="inlineStr"/>
+      <c r="BV55" t="inlineStr"/>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="inlineStr"/>
+      <c r="CB55" t="inlineStr"/>
+      <c r="CC55" t="inlineStr"/>
+      <c r="CD55" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="CE55" t="inlineStr"/>
+      <c r="CF55" t="inlineStr"/>
+      <c r="CG55" t="inlineStr"/>
+      <c r="CH55" t="inlineStr"/>
+      <c r="CI55" t="inlineStr"/>
+      <c r="CJ55" t="inlineStr"/>
+      <c r="CK55" t="inlineStr"/>
+      <c r="CL55" t="inlineStr"/>
+      <c r="CM55" t="inlineStr"/>
+      <c r="CN55" t="inlineStr"/>
+      <c r="CO55" t="inlineStr"/>
+      <c r="CP55" t="inlineStr">
+        <is>
+          <t>Voice 71dB / Noise 66dB / Ring 71dB</t>
+        </is>
+      </c>
+      <c r="CQ55" t="inlineStr"/>
+      <c r="CR55" t="inlineStr"/>
+      <c r="CS55" t="inlineStr"/>
+      <c r="CT55" t="inlineStr"/>
+      <c r="CU55" t="inlineStr"/>
+      <c r="CV55" t="inlineStr"/>
+      <c r="CW55" t="inlineStr"/>
+      <c r="CX55" t="inlineStr"/>
+      <c r="CY55" t="inlineStr"/>
+      <c r="CZ55" t="inlineStr"/>
+      <c r="DA55" t="inlineStr"/>
+      <c r="DB55" t="inlineStr"/>
+      <c r="DC55" t="inlineStr"/>
+      <c r="DD55" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE55" t="inlineStr"/>
+      <c r="DF55" t="inlineStr"/>
+      <c r="DG55" t="inlineStr"/>
+      <c r="DH55" t="inlineStr"/>
+      <c r="DI55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ55" t="inlineStr">
+        <is>
+          <t>Noise -91.0dB / Crosstalk -89.9dB</t>
+        </is>
+      </c>
+      <c r="DK55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Samsung I5800 Galaxy 3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i5800_galaxy_3-3395.php</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>113.5</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Up to 620 h (2G) / Up to 510 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Up to 15 h 30 min (2G) / Up to 7 h 15 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>113.5 x 55 x 12.9 mm (4.47 x 2.17 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>109 g (3.84 oz)</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>Touch Wiz 3.0</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~46.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>MP4/DivX/XviD/WMV/H.264 player MP3/WAV/eAAC+ player Document editor</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 1 GB included</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>512MB 256MB RAM</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>0.57 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK56" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL56" t="inlineStr">
+        <is>
+          <t>Samsung S5P6422 667 MHz</t>
+        </is>
+      </c>
+      <c r="BM56" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="BN56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ56" t="inlineStr"/>
+      <c r="BR56" t="inlineStr"/>
+      <c r="BS56" t="inlineStr"/>
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="inlineStr"/>
+      <c r="BV56" t="inlineStr"/>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="inlineStr"/>
+      <c r="CB56" t="inlineStr"/>
+      <c r="CC56" t="inlineStr"/>
+      <c r="CD56" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="CE56" t="inlineStr"/>
+      <c r="CF56" t="inlineStr"/>
+      <c r="CG56" t="inlineStr"/>
+      <c r="CH56" t="inlineStr"/>
+      <c r="CI56" t="inlineStr"/>
+      <c r="CJ56" t="inlineStr"/>
+      <c r="CK56" t="inlineStr"/>
+      <c r="CL56" t="inlineStr"/>
+      <c r="CM56" t="inlineStr"/>
+      <c r="CN56" t="inlineStr"/>
+      <c r="CO56" t="inlineStr"/>
+      <c r="CP56" t="inlineStr">
+        <is>
+          <t>Voice 71dB / Noise 66dB / Ring 71dB</t>
+        </is>
+      </c>
+      <c r="CQ56" t="inlineStr"/>
+      <c r="CR56" t="inlineStr"/>
+      <c r="CS56" t="inlineStr"/>
+      <c r="CT56" t="inlineStr"/>
+      <c r="CU56" t="inlineStr"/>
+      <c r="CV56" t="inlineStr"/>
+      <c r="CW56" t="inlineStr"/>
+      <c r="CX56" t="inlineStr"/>
+      <c r="CY56" t="inlineStr"/>
+      <c r="CZ56" t="inlineStr"/>
+      <c r="DA56" t="inlineStr"/>
+      <c r="DB56" t="inlineStr"/>
+      <c r="DC56" t="inlineStr"/>
+      <c r="DD56" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE56" t="inlineStr"/>
+      <c r="DF56" t="inlineStr"/>
+      <c r="DG56" t="inlineStr"/>
+      <c r="DH56" t="inlineStr"/>
+      <c r="DI56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ56" t="inlineStr">
+        <is>
+          <t>Noise -91.2dB / Crosstalk -89.9dB</t>
+        </is>
+      </c>
+      <c r="DK56" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Samsung B7722</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Dual SIM Star Duos in India</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_b7722-3362.php</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>113.5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>270MB</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Up to 420 h (2G) / Up to 330 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Up to 12 h 50 min (2G) / Up to 5 h 40 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>113.5 x 55.5 x 14.3 mm (4.47 x 2.19 x 0.56 in)</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM, dual stand-by)</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>112 g (3.95 oz)</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~46.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>MP3/WAV/WMA/eAAC+ player MP4/H.264 player Organizer Document viewer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr"/>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>270MB</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>0.69 W/kg (head)     0.70 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1</t>
+        </is>
+      </c>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>HSDPA 2100 - SIM 1 only</t>
+        </is>
+      </c>
+      <c r="BJ57" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK57" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO57" t="inlineStr"/>
+      <c r="BP57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ57" t="inlineStr"/>
+      <c r="BR57" t="inlineStr"/>
+      <c r="BS57" t="inlineStr"/>
+      <c r="BT57" t="inlineStr"/>
+      <c r="BU57" t="inlineStr"/>
+      <c r="BV57" t="inlineStr"/>
+      <c r="BW57" t="inlineStr"/>
+      <c r="BX57" t="inlineStr"/>
+      <c r="BY57" t="inlineStr"/>
+      <c r="BZ57" t="inlineStr"/>
+      <c r="CA57" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB57" t="inlineStr"/>
+      <c r="CC57" t="inlineStr"/>
+      <c r="CD57" t="inlineStr">
+        <is>
+          <t>320p@30fps</t>
+        </is>
+      </c>
+      <c r="CE57" t="inlineStr"/>
+      <c r="CF57" t="inlineStr"/>
+      <c r="CG57" t="inlineStr"/>
+      <c r="CH57" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 - SIM 2</t>
+        </is>
+      </c>
+      <c r="CI57" t="inlineStr"/>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="inlineStr"/>
+      <c r="CL57" t="inlineStr"/>
+      <c r="CM57" t="inlineStr"/>
+      <c r="CN57" t="inlineStr"/>
+      <c r="CO57" t="inlineStr"/>
+      <c r="CP57" t="inlineStr">
+        <is>
+          <t>Voice 74dB / Noise 67dB / Ring 76dB</t>
+        </is>
+      </c>
+      <c r="CQ57" t="inlineStr"/>
+      <c r="CR57" t="inlineStr"/>
+      <c r="CS57" t="inlineStr"/>
+      <c r="CT57" t="inlineStr"/>
+      <c r="CU57" t="inlineStr"/>
+      <c r="CV57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW57" t="inlineStr"/>
+      <c r="CX57" t="inlineStr"/>
+      <c r="CY57" t="inlineStr"/>
+      <c r="CZ57" t="inlineStr"/>
+      <c r="DA57" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB57" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.1</t>
+        </is>
+      </c>
+      <c r="DC57" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, Push Email, IM, RSS</t>
+        </is>
+      </c>
+      <c r="DD57" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE57" t="inlineStr">
+        <is>
+          <t>30 dialed, 30 received, 30 missed calls</t>
+        </is>
+      </c>
+      <c r="DF57" t="inlineStr">
+        <is>
+          <t>2000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG57" t="inlineStr"/>
+      <c r="DH57" t="inlineStr"/>
+      <c r="DI57" t="inlineStr"/>
+      <c r="DJ57" t="inlineStr">
+        <is>
+          <t>Noise -83.9dB / Crosstalk -82.9dB</t>
+        </is>
+      </c>
+      <c r="DK57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Samsung A847 Rugby II</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>For AT&amp;T</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_a847_rugby_ii-3355.php</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>70MB</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1300 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>102 x 52 x 22 mm (4.02 x 2.05 x 0.87 in)</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>100 g (3.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>A-GPS only; AT&amp;T Navigator</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>External 1.3" monochrome display (CSTN, 128x128 pixels)</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~182 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.0 cm 2 (~28.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>MP3/WAV/AAC+ player MP4/H.263 player Organizer Push to Talk Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr"/>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>70MB</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF58" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>0.51 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI58" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ58" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK58" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO58" t="inlineStr"/>
+      <c r="BP58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ58" t="inlineStr"/>
+      <c r="BR58" t="inlineStr">
+        <is>
+          <t>MIL-STD-810G compliant salt, dust, humidity, rain, vibration, solar radiation, transport and thermal shock resistant</t>
+        </is>
+      </c>
+      <c r="BS58" t="inlineStr"/>
+      <c r="BT58" t="inlineStr"/>
+      <c r="BU58" t="inlineStr"/>
+      <c r="BV58" t="inlineStr"/>
+      <c r="BW58" t="inlineStr"/>
+      <c r="BX58" t="inlineStr"/>
+      <c r="BY58" t="inlineStr"/>
+      <c r="BZ58" t="inlineStr"/>
+      <c r="CA58" t="inlineStr"/>
+      <c r="CB58" t="inlineStr"/>
+      <c r="CC58" t="inlineStr"/>
+      <c r="CD58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE58" t="inlineStr"/>
+      <c r="CF58" t="inlineStr"/>
+      <c r="CG58" t="inlineStr"/>
+      <c r="CH58" t="inlineStr"/>
+      <c r="CI58" t="inlineStr"/>
+      <c r="CJ58" t="inlineStr"/>
+      <c r="CK58" t="inlineStr"/>
+      <c r="CL58" t="inlineStr"/>
+      <c r="CM58" t="inlineStr"/>
+      <c r="CN58" t="inlineStr"/>
+      <c r="CO58" t="inlineStr"/>
+      <c r="CP58" t="inlineStr"/>
+      <c r="CQ58" t="inlineStr"/>
+      <c r="CR58" t="inlineStr"/>
+      <c r="CS58" t="inlineStr"/>
+      <c r="CT58" t="inlineStr"/>
+      <c r="CU58" t="inlineStr"/>
+      <c r="CV58" t="inlineStr"/>
+      <c r="CW58" t="inlineStr"/>
+      <c r="CX58" t="inlineStr"/>
+      <c r="CY58" t="inlineStr"/>
+      <c r="CZ58" t="inlineStr"/>
+      <c r="DA58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB58" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC58" t="inlineStr">
+        <is>
+          <t>SMS, AMS, MMS, Email, Push Email, IM</t>
+        </is>
+      </c>
+      <c r="DD58" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE58" t="inlineStr">
+        <is>
+          <t>30 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="DF58" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG58" t="inlineStr"/>
+      <c r="DH58" t="inlineStr"/>
+      <c r="DI58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ58" t="inlineStr"/>
+      <c r="DK58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Samsung C3300K Champ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Libre, Samsung C3303 Champ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_c3300k_champ-3346.php</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>30MB</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Up to 666 h</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Up to 12 h</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>96.3 x 53.8 x 13 mm (3.79 x 2.12 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>80 g (2.82 oz)</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>Stereo FM radio; built-in antenna</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~34.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>SNS integration MP3/WMA/eAAC+ player MP4/H.263 player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr"/>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>30MB</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>Deep black, Espresso brown, Sweet pink, Chic white</t>
+        </is>
+      </c>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>0.90 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="inlineStr">
+        <is>
+          <t>TouchWiz Lite UI</t>
+        </is>
+      </c>
+      <c r="BN59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO59" t="inlineStr"/>
+      <c r="BP59" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ59" t="inlineStr"/>
+      <c r="BR59" t="inlineStr"/>
+      <c r="BS59" t="inlineStr"/>
+      <c r="BT59" t="inlineStr"/>
+      <c r="BU59" t="inlineStr"/>
+      <c r="BV59" t="inlineStr"/>
+      <c r="BW59" t="inlineStr"/>
+      <c r="BX59" t="inlineStr"/>
+      <c r="BY59" t="inlineStr"/>
+      <c r="BZ59" t="inlineStr"/>
+      <c r="CA59" t="inlineStr"/>
+      <c r="CB59" t="inlineStr"/>
+      <c r="CC59" t="inlineStr"/>
+      <c r="CD59" t="inlineStr">
+        <is>
+          <t>QCIF@15fps</t>
+        </is>
+      </c>
+      <c r="CE59" t="inlineStr"/>
+      <c r="CF59" t="inlineStr"/>
+      <c r="CG59" t="inlineStr"/>
+      <c r="CH59" t="inlineStr"/>
+      <c r="CI59" t="inlineStr"/>
+      <c r="CJ59" t="inlineStr"/>
+      <c r="CK59" t="inlineStr"/>
+      <c r="CL59" t="inlineStr"/>
+      <c r="CM59" t="inlineStr"/>
+      <c r="CN59" t="inlineStr"/>
+      <c r="CO59" t="inlineStr"/>
+      <c r="CP59" t="inlineStr">
+        <is>
+          <t>Voice 75dB / Noise 68dB / Ring 70dB</t>
+        </is>
+      </c>
+      <c r="CQ59" t="inlineStr"/>
+      <c r="CR59" t="inlineStr"/>
+      <c r="CS59" t="inlineStr"/>
+      <c r="CT59" t="inlineStr"/>
+      <c r="CU59" t="inlineStr"/>
+      <c r="CV59" t="inlineStr"/>
+      <c r="CW59" t="inlineStr"/>
+      <c r="CX59" t="inlineStr"/>
+      <c r="CY59" t="inlineStr"/>
+      <c r="CZ59" t="inlineStr"/>
+      <c r="DA59" t="inlineStr"/>
+      <c r="DB59" t="inlineStr"/>
+      <c r="DC59" t="inlineStr"/>
+      <c r="DD59" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE59" t="inlineStr"/>
+      <c r="DF59" t="inlineStr"/>
+      <c r="DG59" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DH59" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ59" t="inlineStr">
+        <is>
+          <t>Noise -89.1dB / Crosstalk -70.7dB</t>
+        </is>
+      </c>
+      <c r="DK59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Samsung W960 AMOLED 3D</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>For South Korea</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_w960_amoled_3d-3319.php</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>113.9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>120.6</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Up to 425 h (2G) / Up to 460 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Up to 6 h (2G) / Up to 10 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1150 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>113.9 x 53.9 x 13.9 mm (4.48 x 2.12 x 0.55 in)</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>120.6 g (4.23 oz)</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>Gesture control Touch Wiz 2.0 UI</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~47.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>AMOLED 3D</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>DMB TV MP4/H.264 player MP3/WAV/eAAC+ player Organizer Document viewer (Word, Excel, PowerPoint, PDF) Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>0.36 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI60" t="inlineStr">
+        <is>
+          <t>HSDPA</t>
+        </is>
+      </c>
+      <c r="BJ60" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="BK60" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL60" t="inlineStr"/>
+      <c r="BM60" t="inlineStr"/>
+      <c r="BN60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO60" t="inlineStr"/>
+      <c r="BP60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ60" t="inlineStr"/>
+      <c r="BR60" t="inlineStr"/>
+      <c r="BS60" t="inlineStr"/>
+      <c r="BT60" t="inlineStr"/>
+      <c r="BU60" t="inlineStr"/>
+      <c r="BV60" t="inlineStr"/>
+      <c r="BW60" t="inlineStr"/>
+      <c r="BX60" t="inlineStr"/>
+      <c r="BY60" t="inlineStr"/>
+      <c r="BZ60" t="inlineStr"/>
+      <c r="CA60" t="inlineStr"/>
+      <c r="CB60" t="inlineStr"/>
+      <c r="CC60" t="inlineStr"/>
+      <c r="CD60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE60" t="inlineStr"/>
+      <c r="CF60" t="inlineStr"/>
+      <c r="CG60" t="inlineStr"/>
+      <c r="CH60" t="inlineStr"/>
+      <c r="CI60" t="inlineStr"/>
+      <c r="CJ60" t="inlineStr"/>
+      <c r="CK60" t="inlineStr"/>
+      <c r="CL60" t="inlineStr"/>
+      <c r="CM60" t="inlineStr"/>
+      <c r="CN60" t="inlineStr"/>
+      <c r="CO60" t="inlineStr"/>
+      <c r="CP60" t="inlineStr"/>
+      <c r="CQ60" t="inlineStr"/>
+      <c r="CR60" t="inlineStr"/>
+      <c r="CS60" t="inlineStr"/>
+      <c r="CT60" t="inlineStr"/>
+      <c r="CU60" t="inlineStr"/>
+      <c r="CV60" t="inlineStr"/>
+      <c r="CW60" t="inlineStr"/>
+      <c r="CX60" t="inlineStr"/>
+      <c r="CY60" t="inlineStr"/>
+      <c r="CZ60" t="inlineStr"/>
+      <c r="DA60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB60" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="DC60" t="inlineStr">
+        <is>
+          <t>SMS(threaded view), MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD60" t="inlineStr">
+        <is>
+          <t>3.2 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF60" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG60" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DH60" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ60" t="inlineStr"/>
+      <c r="DK60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Samsung M110S Galaxy S</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>For South Korea</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_m110s_galaxy_s-3418.php</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>122.4</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Up to 590 h (2G) / Up to 490 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Up to 15 h 30 min (2G) / Up to 7 h 50 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Removable Li-Po 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>122.4 x 64.2 x 9.9 mm (4.82 x 2.53 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>121 g (4.27 oz)</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>TouchWiz 3.0 UI</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~58.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>DMB TV MP4/DivX/WMV/H.264 player MP3/WAV/eAAC+/FLAC player Photo/video editor Document editor</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>HTML, Adobe Flash Lite</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>16GB (14GB user available)</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>Snow White, Black</t>
+        </is>
+      </c>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="BG61" t="inlineStr">
+        <is>
+          <t>0.63 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>HSDPA</t>
+        </is>
+      </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="BK61" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL61" t="inlineStr">
+        <is>
+          <t>1.0 GHz Cortex-A8</t>
+        </is>
+      </c>
+      <c r="BM61" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.3 (Gingerbread)</t>
+        </is>
+      </c>
+      <c r="BN61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO61" t="inlineStr"/>
+      <c r="BP61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ61" t="inlineStr"/>
+      <c r="BR61" t="inlineStr"/>
+      <c r="BS61" t="inlineStr"/>
+      <c r="BT61" t="inlineStr"/>
+      <c r="BU61" t="inlineStr"/>
+      <c r="BV61" t="inlineStr"/>
+      <c r="BW61" t="inlineStr"/>
+      <c r="BX61" t="inlineStr"/>
+      <c r="BY61" t="inlineStr"/>
+      <c r="BZ61" t="inlineStr"/>
+      <c r="CA61" t="inlineStr"/>
+      <c r="CB61" t="inlineStr"/>
+      <c r="CC61" t="inlineStr"/>
+      <c r="CD61" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE61" t="inlineStr"/>
+      <c r="CF61" t="inlineStr">
+        <is>
+          <t>SHW-M110S</t>
+        </is>
+      </c>
+      <c r="CG61" t="inlineStr"/>
+      <c r="CH61" t="inlineStr"/>
+      <c r="CI61" t="inlineStr"/>
+      <c r="CJ61" t="inlineStr"/>
+      <c r="CK61" t="inlineStr"/>
+      <c r="CL61" t="inlineStr"/>
+      <c r="CM61" t="inlineStr"/>
+      <c r="CN61" t="inlineStr"/>
+      <c r="CO61" t="inlineStr"/>
+      <c r="CP61" t="inlineStr"/>
+      <c r="CQ61" t="inlineStr"/>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>Hummingbird</t>
+        </is>
+      </c>
+      <c r="CS61" t="inlineStr">
+        <is>
+          <t>PowerVR SGX540</t>
+        </is>
+      </c>
+      <c r="CT61" t="inlineStr"/>
+      <c r="CU61" t="inlineStr"/>
+      <c r="CV61" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CW61" t="inlineStr"/>
+      <c r="CX61" t="inlineStr"/>
+      <c r="CY61" t="inlineStr"/>
+      <c r="CZ61" t="inlineStr"/>
+      <c r="DA61" t="inlineStr"/>
+      <c r="DB61" t="inlineStr"/>
+      <c r="DC61" t="inlineStr"/>
+      <c r="DD61" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE61" t="inlineStr"/>
+      <c r="DF61" t="inlineStr"/>
+      <c r="DG61" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DH61" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="DI61" t="inlineStr"/>
+      <c r="DJ61" t="inlineStr"/>
+      <c r="DK61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>For South Korea</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a-3294.php</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>384MB</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Up to 560 h (2G) / Up to 450 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Up to 13 h 20 min (2G) / Up to 7 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>119.5 x 59.8 x 12.5 mm (4.70 x 2.35 x 0.49 in)</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>128 g (4.52 oz)</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~252 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>3.7 inches, 39.0 cm 2 (~54.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>DMB TV MP4/DivX/WMV/H.264 player MP3/WAV/eAAC+ player Document viewer</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 8 GB included</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1GB 384MB RAM</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>Deep Black, Cream White</t>
+        </is>
+      </c>
+      <c r="BF62" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>0.48 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK62" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL62" t="inlineStr">
+        <is>
+          <t>720 MHz Cortex-A8</t>
+        </is>
+      </c>
+      <c r="BM62" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair)</t>
+        </is>
+      </c>
+      <c r="BN62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO62" t="inlineStr"/>
+      <c r="BP62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ62" t="inlineStr"/>
+      <c r="BR62" t="inlineStr"/>
+      <c r="BS62" t="inlineStr"/>
+      <c r="BT62" t="inlineStr"/>
+      <c r="BU62" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV62" t="inlineStr"/>
+      <c r="BW62" t="inlineStr"/>
+      <c r="BX62" t="inlineStr"/>
+      <c r="BY62" t="inlineStr"/>
+      <c r="BZ62" t="inlineStr"/>
+      <c r="CA62" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB62" t="inlineStr"/>
+      <c r="CC62" t="inlineStr"/>
+      <c r="CD62" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE62" t="inlineStr"/>
+      <c r="CF62" t="inlineStr"/>
+      <c r="CG62" t="inlineStr"/>
+      <c r="CH62" t="inlineStr"/>
+      <c r="CI62" t="inlineStr"/>
+      <c r="CJ62" t="inlineStr"/>
+      <c r="CK62" t="inlineStr"/>
+      <c r="CL62" t="inlineStr"/>
+      <c r="CM62" t="inlineStr"/>
+      <c r="CN62" t="inlineStr"/>
+      <c r="CO62" t="inlineStr"/>
+      <c r="CP62" t="inlineStr"/>
+      <c r="CQ62" t="inlineStr"/>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>TI OMAP 3430</t>
+        </is>
+      </c>
+      <c r="CS62" t="inlineStr">
+        <is>
+          <t>PowerVR SGX530</t>
+        </is>
+      </c>
+      <c r="CT62" t="inlineStr"/>
+      <c r="CU62" t="inlineStr"/>
+      <c r="CV62" t="inlineStr">
+        <is>
+          <t>VGA videocall camera</t>
+        </is>
+      </c>
+      <c r="CW62" t="inlineStr"/>
+      <c r="CX62" t="inlineStr"/>
+      <c r="CY62" t="inlineStr"/>
+      <c r="CZ62" t="inlineStr"/>
+      <c r="DA62" t="inlineStr"/>
+      <c r="DB62" t="inlineStr"/>
+      <c r="DC62" t="inlineStr"/>
+      <c r="DD62" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE62" t="inlineStr"/>
+      <c r="DF62" t="inlineStr"/>
+      <c r="DG62" t="inlineStr"/>
+      <c r="DH62" t="inlineStr"/>
+      <c r="DI62" t="inlineStr"/>
+      <c r="DJ62" t="inlineStr"/>
+      <c r="DK62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Samsung I9000 Galaxy S</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Also known as Samsung I9008 Galaxy S in China</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i9000_galaxy_s-3115.php</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2010, March. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>122.4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>16GB | 8GB</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Up to 750 h (2G) / Up to 576 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Up to 13 h 30 min (2G) / Up to 6 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>122.4 x 64.2 x 9.9 mm (4.82 x 2.53 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>119 g (4.20 oz)</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>3.0, A2DP, aptX</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, DLNA, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~58.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>ISDB-Tb Digital TV tuner (only available for Brazilian market)</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML, Adobe Flash</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>2010, March. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>8GB 512MB RAM, 16GB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>0.27 W/kg (head)     0.51 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ63" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="BK63" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL63" t="inlineStr">
+        <is>
+          <t>1.0 GHz Cortex-A8</t>
+        </is>
+      </c>
+      <c r="BM63" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.3 (Gingerbread), TouchWiz UI 3</t>
+        </is>
+      </c>
+      <c r="BN63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO63" t="inlineStr"/>
+      <c r="BP63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ63" t="inlineStr"/>
+      <c r="BR63" t="inlineStr"/>
+      <c r="BS63" t="inlineStr"/>
+      <c r="BT63" t="inlineStr"/>
+      <c r="BU63" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV63" t="inlineStr"/>
+      <c r="BW63" t="inlineStr"/>
+      <c r="BX63" t="inlineStr"/>
+      <c r="BY63" t="inlineStr"/>
+      <c r="BZ63" t="inlineStr"/>
+      <c r="CA63" t="inlineStr"/>
+      <c r="CB63" t="inlineStr"/>
+      <c r="CC63" t="inlineStr"/>
+      <c r="CD63" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="CE63" t="inlineStr"/>
+      <c r="CF63" t="inlineStr">
+        <is>
+          <t>GT-I9000</t>
+        </is>
+      </c>
+      <c r="CG63" t="inlineStr"/>
+      <c r="CH63" t="inlineStr"/>
+      <c r="CI63" t="inlineStr"/>
+      <c r="CJ63" t="inlineStr"/>
+      <c r="CK63" t="inlineStr"/>
+      <c r="CL63" t="inlineStr"/>
+      <c r="CM63" t="inlineStr"/>
+      <c r="CN63" t="inlineStr"/>
+      <c r="CO63" t="inlineStr">
+        <is>
+          <t>Contrast ratio: Infinite (nominal) / 3.155:1 (sunlight)</t>
+        </is>
+      </c>
+      <c r="CP63" t="inlineStr">
+        <is>
+          <t>Voice 66dB / Noise 65dB / Ring 66dB</t>
+        </is>
+      </c>
+      <c r="CQ63" t="inlineStr"/>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>Hummingbird</t>
+        </is>
+      </c>
+      <c r="CS63" t="inlineStr">
+        <is>
+          <t>PowerVR SGX540</t>
+        </is>
+      </c>
+      <c r="CT63" t="inlineStr"/>
+      <c r="CU63" t="inlineStr"/>
+      <c r="CV63" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CW63" t="inlineStr"/>
+      <c r="CX63" t="inlineStr"/>
+      <c r="CY63" t="inlineStr"/>
+      <c r="CZ63" t="inlineStr"/>
+      <c r="DA63" t="inlineStr"/>
+      <c r="DB63" t="inlineStr"/>
+      <c r="DC63" t="inlineStr"/>
+      <c r="DD63" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE63" t="inlineStr"/>
+      <c r="DF63" t="inlineStr"/>
+      <c r="DG63" t="inlineStr"/>
+      <c r="DH63" t="inlineStr"/>
+      <c r="DI63" t="inlineStr"/>
+      <c r="DJ63" t="inlineStr">
+        <is>
+          <t>Noise -90.7dB / Crosstalk -90.6dB</t>
+        </is>
+      </c>
+      <c r="DK63" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Samsung S3370</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Corby 3G, Samsung Acton, Samsung Pocket3G, Samsung Star Nano 3G</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_s3370-3234.php</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>99.9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Up to 500 h (2G) / Up to 450 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Up to 10 h 30 min (2G) / Up to 4 h 40 min (3G)</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>99.9 x 53 x 12.9 mm (3.93 x 2.09 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>86 g (3.03 oz)</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>TouchWiz UI 2.0</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~154 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>2.6 inches, 20.9 cm 2 (~39.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>MP3/eAAC+ player MP4/H.263 player Facebook, MySpace apps Music ID recognition Document viewer Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr"/>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF64" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>0.97 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>UMTS 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ64" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="BK64" t="inlineStr">
+        <is>
+          <t>GSM / UMTS</t>
+        </is>
+      </c>
+      <c r="BL64" t="inlineStr"/>
+      <c r="BM64" t="inlineStr"/>
+      <c r="BN64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO64" t="inlineStr"/>
+      <c r="BP64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ64" t="inlineStr"/>
+      <c r="BR64" t="inlineStr"/>
+      <c r="BS64" t="inlineStr"/>
+      <c r="BT64" t="inlineStr"/>
+      <c r="BU64" t="inlineStr"/>
+      <c r="BV64" t="inlineStr"/>
+      <c r="BW64" t="inlineStr"/>
+      <c r="BX64" t="inlineStr"/>
+      <c r="BY64" t="inlineStr"/>
+      <c r="BZ64" t="inlineStr"/>
+      <c r="CA64" t="inlineStr"/>
+      <c r="CB64" t="inlineStr"/>
+      <c r="CC64" t="inlineStr"/>
+      <c r="CD64" t="inlineStr">
+        <is>
+          <t>QCIF</t>
+        </is>
+      </c>
+      <c r="CE64" t="inlineStr"/>
+      <c r="CF64" t="inlineStr"/>
+      <c r="CG64" t="inlineStr"/>
+      <c r="CH64" t="inlineStr"/>
+      <c r="CI64" t="inlineStr"/>
+      <c r="CJ64" t="inlineStr"/>
+      <c r="CK64" t="inlineStr"/>
+      <c r="CL64" t="inlineStr"/>
+      <c r="CM64" t="inlineStr"/>
+      <c r="CN64" t="inlineStr"/>
+      <c r="CO64" t="inlineStr"/>
+      <c r="CP64" t="inlineStr"/>
+      <c r="CQ64" t="inlineStr"/>
+      <c r="CR64" t="inlineStr"/>
+      <c r="CS64" t="inlineStr"/>
+      <c r="CT64" t="inlineStr"/>
+      <c r="CU64" t="inlineStr"/>
+      <c r="CV64" t="inlineStr"/>
+      <c r="CW64" t="inlineStr"/>
+      <c r="CX64" t="inlineStr"/>
+      <c r="CY64" t="inlineStr"/>
+      <c r="CZ64" t="inlineStr"/>
+      <c r="DA64" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB64" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.1</t>
+        </is>
+      </c>
+      <c r="DC64" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="DD64" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF64" t="inlineStr">
+        <is>
+          <t>2000 contacts, Photocall</t>
+        </is>
+      </c>
+      <c r="DG64" t="inlineStr"/>
+      <c r="DH64" t="inlineStr"/>
+      <c r="DI64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ64" t="inlineStr"/>
+      <c r="DK64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Samsung I6500U Galaxy</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Also known as Samsung I6500 SaturnFor China</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i6500u_galaxy-3002.php</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2010, March. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>180MB</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>About 310 EUR</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>117 x 59 x 13.3 mm (4.61 x 2.32 x 0.52 in)</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>126 g (4.44 oz)</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>320 x 480 pixels, 3:2 ratio (~180 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>3.2 inches, 30.5 cm 2 (~44.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>MP4/H.264/WMV player MP3/WAV/eAAC+/WMA player Document viewer</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>Accelerometer, compass</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>2010, March. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>180MB</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>About 310 EUR</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>0.36 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ65" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="BK65" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL65" t="inlineStr">
+        <is>
+          <t>800 MHz</t>
+        </is>
+      </c>
+      <c r="BM65" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair)</t>
+        </is>
+      </c>
+      <c r="BN65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO65" t="inlineStr"/>
+      <c r="BP65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ65" t="inlineStr"/>
+      <c r="BR65" t="inlineStr"/>
+      <c r="BS65" t="inlineStr"/>
+      <c r="BT65" t="inlineStr"/>
+      <c r="BU65" t="inlineStr"/>
+      <c r="BV65" t="inlineStr"/>
+      <c r="BW65" t="inlineStr"/>
+      <c r="BX65" t="inlineStr"/>
+      <c r="BY65" t="inlineStr"/>
+      <c r="BZ65" t="inlineStr"/>
+      <c r="CA65" t="inlineStr"/>
+      <c r="CB65" t="inlineStr"/>
+      <c r="CC65" t="inlineStr"/>
+      <c r="CD65" t="inlineStr">
+        <is>
+          <t>480p@30fps</t>
+        </is>
+      </c>
+      <c r="CE65" t="inlineStr"/>
+      <c r="CF65" t="inlineStr"/>
+      <c r="CG65" t="inlineStr"/>
+      <c r="CH65" t="inlineStr"/>
+      <c r="CI65" t="inlineStr"/>
+      <c r="CJ65" t="inlineStr"/>
+      <c r="CK65" t="inlineStr"/>
+      <c r="CL65" t="inlineStr"/>
+      <c r="CM65" t="inlineStr"/>
+      <c r="CN65" t="inlineStr"/>
+      <c r="CO65" t="inlineStr"/>
+      <c r="CP65" t="inlineStr"/>
+      <c r="CQ65" t="inlineStr"/>
+      <c r="CR65" t="inlineStr"/>
+      <c r="CS65" t="inlineStr"/>
+      <c r="CT65" t="inlineStr"/>
+      <c r="CU65" t="inlineStr"/>
+      <c r="CV65" t="inlineStr"/>
+      <c r="CW65" t="inlineStr"/>
+      <c r="CX65" t="inlineStr"/>
+      <c r="CY65" t="inlineStr"/>
+      <c r="CZ65" t="inlineStr"/>
+      <c r="DA65" t="inlineStr"/>
+      <c r="DB65" t="inlineStr"/>
+      <c r="DC65" t="inlineStr"/>
+      <c r="DD65" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE65" t="inlineStr"/>
+      <c r="DF65" t="inlineStr"/>
+      <c r="DG65" t="inlineStr"/>
+      <c r="DH65" t="inlineStr"/>
+      <c r="DI65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ65" t="inlineStr"/>
+      <c r="DK65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Samsung E1170</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_e1170-3332.php</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>108.7</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>About 30 EUR</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Up to 830 h</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Up to 10 h 30 min</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>108.7 x 46.1 x 14.1 mm (4.28 x 1.81 x 0.56 in)</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>72 g (2.54 oz)</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>128 x 128 pixels, 1:1 ratio (~119 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>1.52 inches, 7.5 cm 2 (~14.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>CSTN, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Organizer Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF66" t="inlineStr">
+        <is>
+          <t>About 30 EUR</t>
+        </is>
+      </c>
+      <c r="BG66" t="inlineStr">
+        <is>
+          <t>0.57 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="BH66" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL66" t="inlineStr"/>
+      <c r="BM66" t="inlineStr"/>
+      <c r="BN66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO66" t="inlineStr"/>
+      <c r="BP66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ66" t="inlineStr"/>
+      <c r="BR66" t="inlineStr"/>
+      <c r="BS66" t="inlineStr"/>
+      <c r="BT66" t="inlineStr"/>
+      <c r="BU66" t="inlineStr"/>
+      <c r="BV66" t="inlineStr"/>
+      <c r="BW66" t="inlineStr"/>
+      <c r="BX66" t="inlineStr"/>
+      <c r="BY66" t="inlineStr"/>
+      <c r="BZ66" t="inlineStr"/>
+      <c r="CA66" t="inlineStr"/>
+      <c r="CB66" t="inlineStr"/>
+      <c r="CC66" t="inlineStr"/>
+      <c r="CD66" t="inlineStr"/>
+      <c r="CE66" t="inlineStr"/>
+      <c r="CF66" t="inlineStr"/>
+      <c r="CG66" t="inlineStr"/>
+      <c r="CH66" t="inlineStr"/>
+      <c r="CI66" t="inlineStr"/>
+      <c r="CJ66" t="inlineStr"/>
+      <c r="CK66" t="inlineStr"/>
+      <c r="CL66" t="inlineStr"/>
+      <c r="CM66" t="inlineStr"/>
+      <c r="CN66" t="inlineStr"/>
+      <c r="CO66" t="inlineStr"/>
+      <c r="CP66" t="inlineStr"/>
+      <c r="CQ66" t="inlineStr"/>
+      <c r="CR66" t="inlineStr"/>
+      <c r="CS66" t="inlineStr"/>
+      <c r="CT66" t="inlineStr"/>
+      <c r="CU66" t="inlineStr"/>
+      <c r="CV66" t="inlineStr"/>
+      <c r="CW66" t="inlineStr"/>
+      <c r="CX66" t="inlineStr"/>
+      <c r="CY66" t="inlineStr"/>
+      <c r="CZ66" t="inlineStr"/>
+      <c r="DA66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DB66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC66" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD66" t="inlineStr"/>
+      <c r="DE66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF66" t="inlineStr">
+        <is>
+          <t>Yes, up to 200 entries</t>
+        </is>
+      </c>
+      <c r="DG66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI66" t="inlineStr"/>
+      <c r="DJ66" t="inlineStr"/>
+      <c r="DK66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Samsung Metro TV</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_metro_tv-3273.php</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>2.2, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~200 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.4 cm 2</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>MimobiTV Mobile TV SNS integration MP3/WAV/eAAC+/WMA player MP4/H.263/WMV player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr"/>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF67" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ67" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="BK67" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL67" t="inlineStr"/>
+      <c r="BM67" t="inlineStr"/>
+      <c r="BN67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO67" t="inlineStr"/>
+      <c r="BP67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ67" t="inlineStr"/>
+      <c r="BR67" t="inlineStr"/>
+      <c r="BS67" t="inlineStr"/>
+      <c r="BT67" t="inlineStr"/>
+      <c r="BU67" t="inlineStr"/>
+      <c r="BV67" t="inlineStr"/>
+      <c r="BW67" t="inlineStr"/>
+      <c r="BX67" t="inlineStr"/>
+      <c r="BY67" t="inlineStr"/>
+      <c r="BZ67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr"/>
+      <c r="CB67" t="inlineStr"/>
+      <c r="CC67" t="inlineStr"/>
+      <c r="CD67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE67" t="inlineStr"/>
+      <c r="CF67" t="inlineStr"/>
+      <c r="CG67" t="inlineStr"/>
+      <c r="CH67" t="inlineStr"/>
+      <c r="CI67" t="inlineStr"/>
+      <c r="CJ67" t="inlineStr"/>
+      <c r="CK67" t="inlineStr"/>
+      <c r="CL67" t="inlineStr"/>
+      <c r="CM67" t="inlineStr"/>
+      <c r="CN67" t="inlineStr"/>
+      <c r="CO67" t="inlineStr"/>
+      <c r="CP67" t="inlineStr"/>
+      <c r="CQ67" t="inlineStr"/>
+      <c r="CR67" t="inlineStr"/>
+      <c r="CS67" t="inlineStr"/>
+      <c r="CT67" t="inlineStr"/>
+      <c r="CU67" t="inlineStr"/>
+      <c r="CV67" t="inlineStr"/>
+      <c r="CW67" t="inlineStr"/>
+      <c r="CX67" t="inlineStr"/>
+      <c r="CY67" t="inlineStr"/>
+      <c r="CZ67" t="inlineStr"/>
+      <c r="DA67" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC67" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD67" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DF67" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="DG67" t="inlineStr"/>
+      <c r="DH67" t="inlineStr"/>
+      <c r="DI67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ67" t="inlineStr"/>
+      <c r="DK67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Samsung Corby TV F339</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_corby_tv_f339-3272.php</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>79MB</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Up to 3 h 20 min</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 960 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>103 x 56.5 x 12.2 mm (4.06 x 2.22 x 0.48 in)</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>92 g (3.25 oz)</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>Smart unlock Cartoon UI</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~143 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>2.8 inches, 24.3 cm 2 (~41.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mobile TV SNS integration MP3/WMA/eAAC+ player Find Music recognition service H.264/MP4/WMV player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>2010, April. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>79MB</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>Jamaican Yellow, Cupid Pink, Minimal White, and Festival Orange; 2 Fashion Jackets</t>
+        </is>
+      </c>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="BK68" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL68" t="inlineStr"/>
+      <c r="BM68" t="inlineStr"/>
+      <c r="BN68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO68" t="inlineStr"/>
+      <c r="BP68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ68" t="inlineStr"/>
+      <c r="BR68" t="inlineStr"/>
+      <c r="BS68" t="inlineStr"/>
+      <c r="BT68" t="inlineStr"/>
+      <c r="BU68" t="inlineStr"/>
+      <c r="BV68" t="inlineStr"/>
+      <c r="BW68" t="inlineStr"/>
+      <c r="BX68" t="inlineStr"/>
+      <c r="BY68" t="inlineStr"/>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr"/>
+      <c r="CB68" t="inlineStr"/>
+      <c r="CC68" t="inlineStr"/>
+      <c r="CD68" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="CE68" t="inlineStr"/>
+      <c r="CF68" t="inlineStr"/>
+      <c r="CG68" t="inlineStr">
+        <is>
+          <t>1.08 W/kg (head)     1.01 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH68" t="inlineStr"/>
+      <c r="CI68" t="inlineStr"/>
+      <c r="CJ68" t="inlineStr"/>
+      <c r="CK68" t="inlineStr"/>
+      <c r="CL68" t="inlineStr"/>
+      <c r="CM68" t="inlineStr"/>
+      <c r="CN68" t="inlineStr"/>
+      <c r="CO68" t="inlineStr"/>
+      <c r="CP68" t="inlineStr"/>
+      <c r="CQ68" t="inlineStr"/>
+      <c r="CR68" t="inlineStr"/>
+      <c r="CS68" t="inlineStr"/>
+      <c r="CT68" t="inlineStr"/>
+      <c r="CU68" t="inlineStr"/>
+      <c r="CV68" t="inlineStr"/>
+      <c r="CW68" t="inlineStr"/>
+      <c r="CX68" t="inlineStr"/>
+      <c r="CY68" t="inlineStr"/>
+      <c r="CZ68" t="inlineStr"/>
+      <c r="DA68" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="DB68" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.1</t>
+        </is>
+      </c>
+      <c r="DC68" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="DD68" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE68" t="inlineStr">
+        <is>
+          <t>200 received, 200 dialed, 200 missed calls</t>
+        </is>
+      </c>
+      <c r="DF68" t="inlineStr">
+        <is>
+          <t>2000 contacts, Photocall</t>
+        </is>
+      </c>
+      <c r="DG68" t="inlineStr"/>
+      <c r="DH68" t="inlineStr"/>
+      <c r="DI68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ68" t="inlineStr"/>
+      <c r="DK68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S3650W Corby</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_s3650w_corby-3047.php</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
+      <c r="BA69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
+      <c r="BJ69" t="inlineStr"/>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr"/>
+      <c r="BM69" t="inlineStr"/>
+      <c r="BN69" t="inlineStr"/>
+      <c r="BO69" t="inlineStr"/>
+      <c r="BP69" t="inlineStr"/>
+      <c r="BQ69" t="inlineStr"/>
+      <c r="BR69" t="inlineStr"/>
+      <c r="BS69" t="inlineStr"/>
+      <c r="BT69" t="inlineStr"/>
+      <c r="BU69" t="inlineStr"/>
+      <c r="BV69" t="inlineStr"/>
+      <c r="BW69" t="inlineStr"/>
+      <c r="BX69" t="inlineStr"/>
+      <c r="BY69" t="inlineStr"/>
+      <c r="BZ69" t="inlineStr"/>
+      <c r="CA69" t="inlineStr"/>
+      <c r="CB69" t="inlineStr"/>
+      <c r="CC69" t="inlineStr"/>
+      <c r="CD69" t="inlineStr"/>
+      <c r="CE69" t="inlineStr"/>
+      <c r="CF69" t="inlineStr"/>
+      <c r="CG69" t="inlineStr"/>
+      <c r="CH69" t="inlineStr"/>
+      <c r="CI69" t="inlineStr"/>
+      <c r="CJ69" t="inlineStr"/>
+      <c r="CK69" t="inlineStr"/>
+      <c r="CL69" t="inlineStr"/>
+      <c r="CM69" t="inlineStr"/>
+      <c r="CN69" t="inlineStr"/>
+      <c r="CO69" t="inlineStr"/>
+      <c r="CP69" t="inlineStr"/>
+      <c r="CQ69" t="inlineStr"/>
+      <c r="CR69" t="inlineStr"/>
+      <c r="CS69" t="inlineStr"/>
+      <c r="CT69" t="inlineStr"/>
+      <c r="CU69" t="inlineStr"/>
+      <c r="CV69" t="inlineStr"/>
+      <c r="CW69" t="inlineStr"/>
+      <c r="CX69" t="inlineStr"/>
+      <c r="CY69" t="inlineStr"/>
+      <c r="CZ69" t="inlineStr"/>
+      <c r="DA69" t="inlineStr"/>
+      <c r="DB69" t="inlineStr"/>
+      <c r="DC69" t="inlineStr"/>
+      <c r="DD69" t="inlineStr"/>
+      <c r="DE69" t="inlineStr"/>
+      <c r="DF69" t="inlineStr"/>
+      <c r="DG69" t="inlineStr"/>
+      <c r="DH69" t="inlineStr"/>
+      <c r="DI69" t="inlineStr"/>
+      <c r="DJ69" t="inlineStr"/>
+      <c r="DK69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM133"/>
+  <dimension ref="A1:DM140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38886,55 +38886,37 @@
           <t>2024, July 10</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H113" t="n">
+        <v>2024</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>Available. Released 2024, July 24</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
+      <c r="J113" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="K113" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L113" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O113" t="n">
+        <v>480</v>
+      </c>
+      <c r="P113" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>327</v>
       </c>
       <c r="R113" t="inlineStr">
         <is>
@@ -38948,28 +38930,20 @@
       </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
+      <c r="V113" t="n">
+        <v>590</v>
       </c>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
+      <c r="Y113" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA113" t="inlineStr"/>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>369.99</t>
-        </is>
+      <c r="AB113" t="n">
+        <v>369.99</v>
       </c>
       <c r="AC113" t="inlineStr"/>
       <c r="AD113" t="inlineStr"/>
@@ -39253,55 +39227,37 @@
           <t>2024, July 10</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H114" t="n">
+        <v>2024</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>Available. Released 2024, July 24</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
+      <c r="J114" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K114" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L114" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M114" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O114" t="n">
+        <v>480</v>
+      </c>
+      <c r="P114" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>327</v>
       </c>
       <c r="R114" t="inlineStr">
         <is>
@@ -39315,32 +39271,22 @@
       </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
+      <c r="V114" t="n">
+        <v>425</v>
       </c>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>204.89</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>158.50</t>
-        </is>
+      <c r="Y114" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>204.89</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>158.5</v>
       </c>
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr"/>
@@ -39624,55 +39570,37 @@
           <t>2024, June 13</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H115" t="n">
+        <v>2024</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>Available. Released 2024, June 24</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>26.6</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
+      <c r="J115" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K115" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M115" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O115" t="n">
+        <v>396</v>
+      </c>
+      <c r="P115" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>330</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>
@@ -39686,28 +39614,20 @@
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
+      <c r="V115" t="n">
+        <v>247</v>
       </c>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
+      <c r="Y115" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0.17</v>
       </c>
       <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>99.62</t>
-        </is>
+      <c r="AB115" t="n">
+        <v>99.62</v>
       </c>
       <c r="AC115" t="inlineStr"/>
       <c r="AD115" t="inlineStr"/>
@@ -39987,55 +39907,37 @@
           <t>2024, May 24</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H116" t="n">
+        <v>2024</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>Available. Released 2024, May 24</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>162.3</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>78.6</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J116" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="K116" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="L116" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>222</v>
+      </c>
+      <c r="N116" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P116" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>390</v>
       </c>
       <c r="R116" t="inlineStr">
         <is>
@@ -40047,48 +39949,32 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+      <c r="T116" t="n">
+        <v>50</v>
+      </c>
+      <c r="U116" t="n">
+        <v>13</v>
+      </c>
+      <c r="V116" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0.53</v>
       </c>
       <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="Y116" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
+      <c r="AB116" t="n">
+        <v>198</v>
       </c>
       <c r="AC116" t="inlineStr"/>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>24999</t>
-        </is>
+      <c r="AD116" t="n">
+        <v>24999</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -40390,55 +40276,37 @@
           <t>2024, May 17</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H117" t="n">
+        <v>2024</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>Available. Released 2024, May 27</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>163.9</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="J117" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="K117" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M117" t="n">
+        <v>180</v>
+      </c>
+      <c r="N117" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P117" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>393</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
@@ -40450,34 +40318,24 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="T117" t="n">
+        <v>50</v>
+      </c>
+      <c r="U117" t="n">
+        <v>50</v>
+      </c>
+      <c r="V117" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.93</v>
       </c>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>50.02</t>
-        </is>
+      <c r="AB117" t="n">
+        <v>50.02</v>
       </c>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr"/>
@@ -40769,55 +40627,37 @@
           <t>2024, April 22</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H118" t="n">
+        <v>2024</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>Available. Released 2024, April 22</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>163.9</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="J118" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="K118" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L118" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M118" t="n">
+        <v>180</v>
+      </c>
+      <c r="N118" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P118" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>393</v>
       </c>
       <c r="R118" t="inlineStr">
         <is>
@@ -40829,20 +40669,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T118" t="n">
+        <v>50</v>
+      </c>
+      <c r="U118" t="n">
+        <v>50</v>
+      </c>
+      <c r="V118" t="n">
+        <v>5000</v>
       </c>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr"/>
@@ -41128,55 +40962,37 @@
           <t>2024, March 28</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H119" t="n">
+        <v>2024</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 28</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>163.9</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="J119" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="K119" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M119" t="n">
+        <v>180</v>
+      </c>
+      <c r="N119" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P119" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>393</v>
       </c>
       <c r="R119" t="inlineStr">
         <is>
@@ -41188,52 +41004,34 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="T119" t="n">
+        <v>50</v>
+      </c>
+      <c r="U119" t="n">
+        <v>50</v>
+      </c>
+      <c r="V119" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.93</v>
       </c>
       <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>273.00</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>279.00</t>
-        </is>
+      <c r="Y119" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>273</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>279</v>
       </c>
       <c r="AC119" t="inlineStr"/>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>28999</t>
-        </is>
+      <c r="AD119" t="n">
+        <v>28999</v>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
@@ -41527,55 +41325,37 @@
           <t>2024, March 26</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H120" t="n">
+        <v>2024</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 28</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>244.5</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>154.3</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="J120" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="L120" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" t="n">
+        <v>467</v>
+      </c>
+      <c r="N120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>224</v>
       </c>
       <c r="R120" t="inlineStr">
         <is>
@@ -41587,26 +41367,18 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
+      <c r="T120" t="n">
+        <v>8</v>
+      </c>
+      <c r="U120" t="n">
+        <v>5</v>
+      </c>
+      <c r="V120" t="n">
+        <v>7040</v>
       </c>
       <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="X120" t="n">
+        <v>0.95</v>
       </c>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
@@ -41906,55 +41678,37 @@
           <t>2024, March 11</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H121" t="n">
+        <v>2024</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 15</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>161.1</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J121" t="n">
+        <v>161.1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M121" t="n">
+        <v>213</v>
+      </c>
+      <c r="N121" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P121" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>390</v>
       </c>
       <c r="R121" t="inlineStr">
         <is>
@@ -41966,43 +41720,29 @@
           <t>12GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T121" t="n">
+        <v>50</v>
+      </c>
+      <c r="U121" t="n">
+        <v>32</v>
+      </c>
+      <c r="V121" t="n">
+        <v>5000</v>
       </c>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr"/>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="Y121" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1.04</v>
       </c>
       <c r="AA121" t="inlineStr"/>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>239.89</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>295.00</t>
-        </is>
+      <c r="AB121" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>295</v>
       </c>
       <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr">
@@ -42321,55 +42061,37 @@
           <t>2024, March 11</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H122" t="n">
+        <v>2024</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 15</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>161.7</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J122" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="K122" t="n">
+        <v>78</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>209</v>
+      </c>
+      <c r="N122" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>390</v>
       </c>
       <c r="R122" t="inlineStr">
         <is>
@@ -42381,56 +42103,36 @@
           <t>12GB | 4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
+      <c r="T122" t="n">
+        <v>50</v>
+      </c>
+      <c r="U122" t="n">
+        <v>13</v>
+      </c>
+      <c r="V122" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="X122" t="inlineStr"/>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>161.99</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>230.00</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>168.99</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>21990</t>
-        </is>
+      <c r="Y122" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>161.99</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>230</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>21990</v>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
@@ -42752,55 +42454,37 @@
           <t>2024, March 09</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H123" t="n">
+        <v>2024</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>Available. Released 2024, April 05</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>160.1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="J123" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="L123" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>217</v>
+      </c>
+      <c r="N123" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>396</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
@@ -42812,44 +42496,30 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
+      <c r="T123" t="n">
+        <v>50</v>
+      </c>
+      <c r="U123" t="n">
+        <v>13</v>
+      </c>
+      <c r="V123" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.71</v>
       </c>
       <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="Y123" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>1.19</v>
       </c>
       <c r="AA123" t="inlineStr"/>
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>15999</t>
-        </is>
+      <c r="AD123" t="n">
+        <v>15999</v>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
@@ -43147,55 +42817,37 @@
           <t>2024, March 07</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H124" t="n">
+        <v>2024</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 07</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
+      <c r="J124" t="n">
+        <v>168</v>
+      </c>
+      <c r="K124" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="L124" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>194</v>
+      </c>
+      <c r="N124" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>394</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
@@ -43207,25 +42859,17 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+      <c r="T124" t="n">
+        <v>50</v>
+      </c>
+      <c r="U124" t="n">
+        <v>13</v>
+      </c>
+      <c r="V124" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
@@ -43514,55 +43158,37 @@
           <t>2024, March 04</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H125" t="n">
+        <v>2024</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>Available. Released 2024, March 11</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>160.1</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J125" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="L125" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>217</v>
+      </c>
+      <c r="N125" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>390</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
@@ -43574,25 +43200,17 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
+      <c r="T125" t="n">
+        <v>50</v>
+      </c>
+      <c r="U125" t="n">
+        <v>13</v>
+      </c>
+      <c r="V125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.71</v>
       </c>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
@@ -43893,55 +43511,37 @@
           <t>2024, January 17</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H126" t="n">
+        <v>2024</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>Available. Released 2024, January 24</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>162.3</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
+      <c r="J126" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="K126" t="n">
+        <v>79</v>
+      </c>
+      <c r="L126" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M126" t="n">
+        <v>232</v>
+      </c>
+      <c r="N126" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3120</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>505</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
@@ -43953,55 +43553,35 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>527.98</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>559.44</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>460.96</t>
-        </is>
+      <c r="T126" t="n">
+        <v>200</v>
+      </c>
+      <c r="U126" t="n">
+        <v>12</v>
+      </c>
+      <c r="V126" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W126" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>527.98</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>559.4400000000001</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>460.96</v>
       </c>
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr">
@@ -44360,55 +43940,37 @@
           <t>2024, January 17</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H127" t="n">
+        <v>2024</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>Available. Released 2024, January 24</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
+      <c r="J127" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L127" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M127" t="n">
+        <v>196</v>
+      </c>
+      <c r="N127" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P127" t="n">
+        <v>3120</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>513</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
@@ -44420,55 +43982,35 @@
           <t>12GB</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>402.99</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>471.32</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>399.99</t>
-        </is>
+      <c r="T127" t="n">
+        <v>50</v>
+      </c>
+      <c r="U127" t="n">
+        <v>12</v>
+      </c>
+      <c r="V127" t="n">
+        <v>4900</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>471.32</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>399.99</v>
       </c>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
@@ -44823,55 +44365,37 @@
           <t>2024, January 17</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H128" t="n">
+        <v>2024</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>Available. Released 2024, January 24</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
+      <c r="J128" t="n">
+        <v>147</v>
+      </c>
+      <c r="K128" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M128" t="n">
+        <v>167</v>
+      </c>
+      <c r="N128" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>416</v>
       </c>
       <c r="R128" t="inlineStr">
         <is>
@@ -44883,60 +44407,38 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>279.95</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>432.39</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>303.86</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>45000</t>
-        </is>
+      <c r="T128" t="n">
+        <v>50</v>
+      </c>
+      <c r="U128" t="n">
+        <v>12</v>
+      </c>
+      <c r="V128" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>279.95</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>432.39</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>303.86</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>45000</v>
       </c>
       <c r="AE128" t="inlineStr">
         <is>
@@ -45290,55 +44792,37 @@
           <t>2024, January 10</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H129" t="n">
+        <v>2024</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>Available. Released 2024, January 23</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="J129" t="n">
+        <v>169</v>
+      </c>
+      <c r="K129" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="L129" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M129" t="n">
+        <v>240</v>
+      </c>
+      <c r="N129" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P129" t="n">
+        <v>2408</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>400</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
@@ -45350,42 +44834,28 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>4050</t>
-        </is>
+      <c r="T129" t="n">
+        <v>50</v>
+      </c>
+      <c r="U129" t="n">
+        <v>5</v>
+      </c>
+      <c r="V129" t="n">
+        <v>4050</v>
       </c>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>329.99</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>229.00</t>
-        </is>
+      <c r="Y129" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>329.99</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>229</v>
       </c>
       <c r="AC129" t="inlineStr"/>
       <c r="AD129" t="inlineStr"/>
@@ -45685,55 +45155,37 @@
           <t>2024, January 10</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H130" t="n">
+        <v>2024</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>Available. Released 2024, January 23</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>213.8</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>126.8</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
+      <c r="J130" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="K130" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>433</v>
+      </c>
+      <c r="N130" t="n">
+        <v>8</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1920</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>283</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
@@ -45745,32 +45197,22 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
+      <c r="T130" t="n">
+        <v>13</v>
+      </c>
+      <c r="U130" t="n">
+        <v>5</v>
+      </c>
+      <c r="V130" t="n">
+        <v>5050</v>
       </c>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
+      <c r="Y130" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr"/>
@@ -46068,55 +45510,37 @@
           <t>2023, December 11</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H131" t="n">
+        <v>2023</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>Available. Released 2023, December 16</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="J131" t="n">
+        <v>161</v>
+      </c>
+      <c r="K131" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M131" t="n">
+        <v>197</v>
+      </c>
+      <c r="N131" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P131" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>396</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
@@ -46128,47 +45552,31 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T131" t="n">
+        <v>50</v>
+      </c>
+      <c r="U131" t="n">
+        <v>13</v>
+      </c>
+      <c r="V131" t="n">
+        <v>5000</v>
       </c>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>182.84</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>139.00</t>
-        </is>
+      <c r="Y131" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>129</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>182.84</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>139</v>
       </c>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="inlineStr">
@@ -46483,55 +45891,37 @@
           <t>2023, December 11</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H132" t="n">
+        <v>2023</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>Available. Released 2023, December 16</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>160.1</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="J132" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M132" t="n">
+        <v>200</v>
+      </c>
+      <c r="N132" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P132" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>396</v>
       </c>
       <c r="R132" t="inlineStr">
         <is>
@@ -46543,47 +45933,31 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T132" t="n">
+        <v>50</v>
+      </c>
+      <c r="U132" t="n">
+        <v>13</v>
+      </c>
+      <c r="V132" t="n">
+        <v>5000</v>
       </c>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>81.99</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>164.00</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>144.99</t>
-        </is>
+      <c r="Y132" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>164</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>144.99</v>
       </c>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
@@ -47001,6 +46375,2291 @@
       <c r="DL133" t="inlineStr"/>
       <c r="DM133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Umidigi A11S</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_a11s-13084.php</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>162.2</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>5150 mAh</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>162.2 x 75 x 9.2 mm (6.39 x 2.95 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr"/>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>225 g (7.94 oz)</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr"/>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~84.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>32GB 4GB RAM, 64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE134" t="inlineStr">
+        <is>
+          <t>Mist Blue, Frost Grey</t>
+        </is>
+      </c>
+      <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI134" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ134" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK134" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL134" t="inlineStr">
+        <is>
+          <t>Quad-core (1x2.0 GHz Cortex-A75 &amp; 3x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM134" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO134" t="inlineStr"/>
+      <c r="BP134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ134" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR134" t="inlineStr"/>
+      <c r="BS134" t="inlineStr"/>
+      <c r="BT134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU134" t="inlineStr"/>
+      <c r="BV134" t="inlineStr"/>
+      <c r="BW134" t="inlineStr"/>
+      <c r="BX134" t="inlineStr"/>
+      <c r="BY134" t="inlineStr"/>
+      <c r="BZ134" t="inlineStr"/>
+      <c r="CA134" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB134" t="inlineStr"/>
+      <c r="CC134" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, (wide), AF 8 MP, 120˚ (ultrawide) 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD134" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE134" t="inlineStr"/>
+      <c r="CF134" t="inlineStr"/>
+      <c r="CG134" t="inlineStr"/>
+      <c r="CH134" t="inlineStr"/>
+      <c r="CI134" t="inlineStr"/>
+      <c r="CJ134" t="inlineStr"/>
+      <c r="CK134" t="inlineStr"/>
+      <c r="CL134" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM134" t="inlineStr"/>
+      <c r="CN134" t="inlineStr"/>
+      <c r="CO134" t="inlineStr"/>
+      <c r="CP134" t="inlineStr"/>
+      <c r="CQ134" t="inlineStr"/>
+      <c r="CR134" t="inlineStr">
+        <is>
+          <t>Unisoc Tiger T310 (12nm)</t>
+        </is>
+      </c>
+      <c r="CS134" t="inlineStr">
+        <is>
+          <t>PowerVR GE8300</t>
+        </is>
+      </c>
+      <c r="CT134" t="inlineStr"/>
+      <c r="CU134" t="inlineStr"/>
+      <c r="CV134" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.2, (wide)</t>
+        </is>
+      </c>
+      <c r="CW134" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX134" t="inlineStr"/>
+      <c r="CY134" t="inlineStr"/>
+      <c r="CZ134" t="inlineStr"/>
+      <c r="DA134" t="inlineStr"/>
+      <c r="DB134" t="inlineStr"/>
+      <c r="DC134" t="inlineStr"/>
+      <c r="DD134" t="inlineStr"/>
+      <c r="DE134" t="inlineStr"/>
+      <c r="DF134" t="inlineStr"/>
+      <c r="DG134" t="inlineStr"/>
+      <c r="DH134" t="inlineStr"/>
+      <c r="DI134" t="inlineStr"/>
+      <c r="DJ134" t="inlineStr"/>
+      <c r="DK134" t="inlineStr"/>
+      <c r="DL134" t="inlineStr"/>
+      <c r="DM134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Umidigi Bison X10 Pro</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_bison_x10_pro-13097.php</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>169.7</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>6150 mAh</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>169.7 x 82.1 x 12.9 mm (6.68 x 3.23 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr"/>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>285 g (10.05 oz)</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr"/>
+      <c r="AN135" t="inlineStr">
+        <is>
+          <t>4.2, A2DP</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr"/>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>Wireless FM radio</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~73.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, barometer, thermometer (skin temperature)</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE135" t="inlineStr">
+        <is>
+          <t>Storm Gray, Supersonic Yellow, Hack Black</t>
+        </is>
+      </c>
+      <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI135" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ135" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK135" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="BL135" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A73 &amp; 4x2.0 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM135" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO135" t="inlineStr"/>
+      <c r="BP135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ135" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR135" t="inlineStr">
+        <is>
+          <t>IP68/IP69K dust tight and water resistant (high pressure water jets; immersible up to 1.5m for 30 min) MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="BS135" t="inlineStr"/>
+      <c r="BT135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU135" t="inlineStr"/>
+      <c r="BV135" t="inlineStr"/>
+      <c r="BW135" t="inlineStr"/>
+      <c r="BX135" t="inlineStr"/>
+      <c r="BY135" t="inlineStr"/>
+      <c r="BZ135" t="inlineStr"/>
+      <c r="CA135" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB135" t="inlineStr"/>
+      <c r="CC135" t="inlineStr">
+        <is>
+          <t>20 MP, f/1.8, (wide), AF 8 MP, 120˚ (ultrawide) 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD135" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE135" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF135" t="inlineStr"/>
+      <c r="CG135" t="inlineStr"/>
+      <c r="CH135" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI135" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ135" t="inlineStr"/>
+      <c r="CK135" t="inlineStr"/>
+      <c r="CL135" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM135" t="inlineStr"/>
+      <c r="CN135" t="inlineStr"/>
+      <c r="CO135" t="inlineStr"/>
+      <c r="CP135" t="inlineStr"/>
+      <c r="CQ135" t="inlineStr"/>
+      <c r="CR135" t="inlineStr">
+        <is>
+          <t>Mediatek Helio P60 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS135" t="inlineStr">
+        <is>
+          <t>Mali-G72 MP3</t>
+        </is>
+      </c>
+      <c r="CT135" t="inlineStr"/>
+      <c r="CU135" t="inlineStr"/>
+      <c r="CV135" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.2, (wide)</t>
+        </is>
+      </c>
+      <c r="CW135" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX135" t="inlineStr"/>
+      <c r="CY135" t="inlineStr"/>
+      <c r="CZ135" t="inlineStr"/>
+      <c r="DA135" t="inlineStr"/>
+      <c r="DB135" t="inlineStr"/>
+      <c r="DC135" t="inlineStr"/>
+      <c r="DD135" t="inlineStr"/>
+      <c r="DE135" t="inlineStr"/>
+      <c r="DF135" t="inlineStr"/>
+      <c r="DG135" t="inlineStr"/>
+      <c r="DH135" t="inlineStr"/>
+      <c r="DI135" t="inlineStr"/>
+      <c r="DJ135" t="inlineStr"/>
+      <c r="DK135" t="inlineStr"/>
+      <c r="DL135" t="inlineStr"/>
+      <c r="DM135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Umidigi Bison X10</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_bison_x10-13098.php</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>169.7</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>6150 mAh</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>169.7 x 82.1 x 12.9 mm (6.68 x 3.23 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr"/>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>282 g (9.95 oz)</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr"/>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t>4.2, A2DP</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr"/>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>Wireless FM radio</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~73.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr"/>
+      <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>Storm Gray, Supersonic Yellow, Hack Black</t>
+        </is>
+      </c>
+      <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI136" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ136" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK136" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="BL136" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A73 &amp; 4x2.0 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM136" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO136" t="inlineStr"/>
+      <c r="BP136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ136" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR136" t="inlineStr">
+        <is>
+          <t>IP68/IP69K dust tight and water resistant (high pressure water jets; immersible up to 1.5m for 30 min) MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="BS136" t="inlineStr"/>
+      <c r="BT136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU136" t="inlineStr"/>
+      <c r="BV136" t="inlineStr"/>
+      <c r="BW136" t="inlineStr"/>
+      <c r="BX136" t="inlineStr"/>
+      <c r="BY136" t="inlineStr"/>
+      <c r="BZ136" t="inlineStr"/>
+      <c r="CA136" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB136" t="inlineStr"/>
+      <c r="CC136" t="inlineStr">
+        <is>
+          <t>20 MP, f/1.8, (wide), AF 8 MP, 120˚ (ultrawide) 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD136" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE136" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF136" t="inlineStr"/>
+      <c r="CG136" t="inlineStr"/>
+      <c r="CH136" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI136" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ136" t="inlineStr"/>
+      <c r="CK136" t="inlineStr"/>
+      <c r="CL136" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM136" t="inlineStr"/>
+      <c r="CN136" t="inlineStr"/>
+      <c r="CO136" t="inlineStr"/>
+      <c r="CP136" t="inlineStr"/>
+      <c r="CQ136" t="inlineStr"/>
+      <c r="CR136" t="inlineStr">
+        <is>
+          <t>Mediatek Helio P60 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS136" t="inlineStr">
+        <is>
+          <t>Mali-G72 MP3</t>
+        </is>
+      </c>
+      <c r="CT136" t="inlineStr"/>
+      <c r="CU136" t="inlineStr"/>
+      <c r="CV136" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.2, (wide)</t>
+        </is>
+      </c>
+      <c r="CW136" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX136" t="inlineStr"/>
+      <c r="CY136" t="inlineStr"/>
+      <c r="CZ136" t="inlineStr"/>
+      <c r="DA136" t="inlineStr"/>
+      <c r="DB136" t="inlineStr"/>
+      <c r="DC136" t="inlineStr"/>
+      <c r="DD136" t="inlineStr"/>
+      <c r="DE136" t="inlineStr"/>
+      <c r="DF136" t="inlineStr"/>
+      <c r="DG136" t="inlineStr"/>
+      <c r="DH136" t="inlineStr"/>
+      <c r="DI136" t="inlineStr"/>
+      <c r="DJ136" t="inlineStr"/>
+      <c r="DK136" t="inlineStr"/>
+      <c r="DL136" t="inlineStr"/>
+      <c r="DM136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Umidigi A11 Pro Max</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_a11_pro_max-13100.php</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>167.8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>4GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>5150 mAh</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>167.8 x 75.6 x 8.6 mm (6.61 x 2.98 x 0.34 in)</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr"/>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>225 g (7.94 oz)</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr"/>
+      <c r="AN137" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr"/>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>1080 x 2460 pixels (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>6.8 inches, 109.8 cm 2 (~86.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, thermometer (skin temperature)</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>Mist Blue, Frost Grey</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI137" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ137" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK137" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / CDMA2000 / LTE</t>
+        </is>
+      </c>
+      <c r="BL137" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM137" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO137" t="inlineStr"/>
+      <c r="BP137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ137" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR137" t="inlineStr"/>
+      <c r="BS137" t="inlineStr">
+        <is>
+          <t>Aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU137" t="inlineStr"/>
+      <c r="BV137" t="inlineStr"/>
+      <c r="BW137" t="inlineStr"/>
+      <c r="BX137" t="inlineStr"/>
+      <c r="BY137" t="inlineStr"/>
+      <c r="BZ137" t="inlineStr"/>
+      <c r="CA137" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB137" t="inlineStr"/>
+      <c r="CC137" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, (wide), 1/2.0", AF 16 MP, f/2.2, 120˚ (ultrawide) 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD137" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE137" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF137" t="inlineStr"/>
+      <c r="CG137" t="inlineStr"/>
+      <c r="CH137" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI137" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CJ137" t="inlineStr"/>
+      <c r="CK137" t="inlineStr"/>
+      <c r="CL137" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM137" t="inlineStr"/>
+      <c r="CN137" t="inlineStr"/>
+      <c r="CO137" t="inlineStr"/>
+      <c r="CP137" t="inlineStr"/>
+      <c r="CQ137" t="inlineStr"/>
+      <c r="CR137" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G80 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS137" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT137" t="inlineStr"/>
+      <c r="CU137" t="inlineStr"/>
+      <c r="CV137" t="inlineStr">
+        <is>
+          <t>24 MP, f/1.8, (wide)</t>
+        </is>
+      </c>
+      <c r="CW137" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX137" t="inlineStr"/>
+      <c r="CY137" t="inlineStr"/>
+      <c r="CZ137" t="inlineStr"/>
+      <c r="DA137" t="inlineStr"/>
+      <c r="DB137" t="inlineStr"/>
+      <c r="DC137" t="inlineStr"/>
+      <c r="DD137" t="inlineStr"/>
+      <c r="DE137" t="inlineStr"/>
+      <c r="DF137" t="inlineStr"/>
+      <c r="DG137" t="inlineStr"/>
+      <c r="DH137" t="inlineStr"/>
+      <c r="DI137" t="inlineStr"/>
+      <c r="DJ137" t="inlineStr"/>
+      <c r="DK137" t="inlineStr"/>
+      <c r="DL137" t="inlineStr"/>
+      <c r="DM137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Umidigi Bison Pro</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_bison_pro-13099.php</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>4GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>164 x 79.6 x 12.7 mm (6.46 x 3.13 x 0.5 in)</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr"/>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>265 g (9.35 oz)</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr"/>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>4.2, A2DP</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr"/>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>6.3 inches, 97.4 cm 2 (~74.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr"/>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, barometer, thermometer (skin temperature)</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE138" t="inlineStr">
+        <is>
+          <t>Storm Gray, Hack Black</t>
+        </is>
+      </c>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI138" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ138" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK138" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / CDMA2000 / LTE</t>
+        </is>
+      </c>
+      <c r="BL138" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM138" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO138" t="inlineStr"/>
+      <c r="BP138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ138" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR138" t="inlineStr">
+        <is>
+          <t>IP68/IP69K dust tight and water resistant (high pressure water jets; immersible up to 1.5m for 30 min) MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="BS138" t="inlineStr"/>
+      <c r="BT138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU138" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV138" t="inlineStr"/>
+      <c r="BW138" t="inlineStr"/>
+      <c r="BX138" t="inlineStr"/>
+      <c r="BY138" t="inlineStr"/>
+      <c r="BZ138" t="inlineStr"/>
+      <c r="CA138" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB138" t="inlineStr"/>
+      <c r="CC138" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, (wide), 1/2.0", AF 16 MP, 117˚ (ultrawide) 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD138" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE138" t="inlineStr"/>
+      <c r="CF138" t="inlineStr"/>
+      <c r="CG138" t="inlineStr"/>
+      <c r="CH138" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI138" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CJ138" t="inlineStr"/>
+      <c r="CK138" t="inlineStr"/>
+      <c r="CL138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM138" t="inlineStr"/>
+      <c r="CN138" t="inlineStr"/>
+      <c r="CO138" t="inlineStr"/>
+      <c r="CP138" t="inlineStr"/>
+      <c r="CQ138" t="inlineStr"/>
+      <c r="CR138" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G80 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS138" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT138" t="inlineStr"/>
+      <c r="CU138" t="inlineStr"/>
+      <c r="CV138" t="inlineStr">
+        <is>
+          <t>24 MP, f/2.0, (wide)</t>
+        </is>
+      </c>
+      <c r="CW138" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX138" t="inlineStr"/>
+      <c r="CY138" t="inlineStr"/>
+      <c r="CZ138" t="inlineStr"/>
+      <c r="DA138" t="inlineStr"/>
+      <c r="DB138" t="inlineStr"/>
+      <c r="DC138" t="inlineStr"/>
+      <c r="DD138" t="inlineStr"/>
+      <c r="DE138" t="inlineStr"/>
+      <c r="DF138" t="inlineStr"/>
+      <c r="DG138" t="inlineStr"/>
+      <c r="DH138" t="inlineStr"/>
+      <c r="DI138" t="inlineStr"/>
+      <c r="DJ138" t="inlineStr"/>
+      <c r="DK138" t="inlineStr"/>
+      <c r="DL138" t="inlineStr"/>
+      <c r="DM138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Umidigi Power 5</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_power_5-13105.php</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>164.8</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>6150 mAh</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>164.8 x 76.9 x 9.9 mm (6.49 x 3.03 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr"/>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>211 g (7.44 oz)</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr"/>
+      <c r="AN139" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr"/>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>USB Type-C, OTG</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr"/>
+      <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, thermometer (skin temperature)</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>2021. Released 2021</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>64GB 3GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>Carbon Grey, Jade Green, Sapphire Blue</t>
+        </is>
+      </c>
+      <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI139" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ139" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK139" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL139" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A53 &amp; 4x1.5 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM139" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="BN139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO139" t="inlineStr"/>
+      <c r="BP139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ139" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR139" t="inlineStr"/>
+      <c r="BS139" t="inlineStr"/>
+      <c r="BT139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU139" t="inlineStr"/>
+      <c r="BV139" t="inlineStr"/>
+      <c r="BW139" t="inlineStr"/>
+      <c r="BX139" t="inlineStr"/>
+      <c r="BY139" t="inlineStr"/>
+      <c r="BZ139" t="inlineStr"/>
+      <c r="CA139" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB139" t="inlineStr"/>
+      <c r="CC139" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, (wide), AF 8 MP, 120˚ (ultrawide) 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD139" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE139" t="inlineStr"/>
+      <c r="CF139" t="inlineStr"/>
+      <c r="CG139" t="inlineStr"/>
+      <c r="CH139" t="inlineStr"/>
+      <c r="CI139" t="inlineStr"/>
+      <c r="CJ139" t="inlineStr"/>
+      <c r="CK139" t="inlineStr"/>
+      <c r="CL139" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CM139" t="inlineStr"/>
+      <c r="CN139" t="inlineStr"/>
+      <c r="CO139" t="inlineStr"/>
+      <c r="CP139" t="inlineStr"/>
+      <c r="CQ139" t="inlineStr"/>
+      <c r="CR139" t="inlineStr">
+        <is>
+          <t>Mediatek Helio G25 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS139" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT139" t="inlineStr"/>
+      <c r="CU139" t="inlineStr"/>
+      <c r="CV139" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.2, (wide)</t>
+        </is>
+      </c>
+      <c r="CW139" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX139" t="inlineStr"/>
+      <c r="CY139" t="inlineStr"/>
+      <c r="CZ139" t="inlineStr"/>
+      <c r="DA139" t="inlineStr"/>
+      <c r="DB139" t="inlineStr"/>
+      <c r="DC139" t="inlineStr"/>
+      <c r="DD139" t="inlineStr"/>
+      <c r="DE139" t="inlineStr"/>
+      <c r="DF139" t="inlineStr"/>
+      <c r="DG139" t="inlineStr"/>
+      <c r="DH139" t="inlineStr"/>
+      <c r="DI139" t="inlineStr"/>
+      <c r="DJ139" t="inlineStr"/>
+      <c r="DK139" t="inlineStr"/>
+      <c r="DL139" t="inlineStr"/>
+      <c r="DM139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/umidigi_a11-13106.php</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:04 UTC</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr"/>
+      <c r="AJ140" t="inlineStr"/>
+      <c r="AK140" t="inlineStr"/>
+      <c r="AL140" t="inlineStr"/>
+      <c r="AM140" t="inlineStr"/>
+      <c r="AN140" t="inlineStr"/>
+      <c r="AO140" t="inlineStr"/>
+      <c r="AP140" t="inlineStr"/>
+      <c r="AQ140" t="inlineStr"/>
+      <c r="AR140" t="inlineStr"/>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AU140" t="inlineStr"/>
+      <c r="AV140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr"/>
+      <c r="AX140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr"/>
+      <c r="BA140" t="inlineStr"/>
+      <c r="BB140" t="inlineStr"/>
+      <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
+      <c r="BG140" t="inlineStr"/>
+      <c r="BH140" t="inlineStr"/>
+      <c r="BI140" t="inlineStr"/>
+      <c r="BJ140" t="inlineStr"/>
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="inlineStr"/>
+      <c r="BM140" t="inlineStr"/>
+      <c r="BN140" t="inlineStr"/>
+      <c r="BO140" t="inlineStr"/>
+      <c r="BP140" t="inlineStr"/>
+      <c r="BQ140" t="inlineStr"/>
+      <c r="BR140" t="inlineStr"/>
+      <c r="BS140" t="inlineStr"/>
+      <c r="BT140" t="inlineStr"/>
+      <c r="BU140" t="inlineStr"/>
+      <c r="BV140" t="inlineStr"/>
+      <c r="BW140" t="inlineStr"/>
+      <c r="BX140" t="inlineStr"/>
+      <c r="BY140" t="inlineStr"/>
+      <c r="BZ140" t="inlineStr"/>
+      <c r="CA140" t="inlineStr"/>
+      <c r="CB140" t="inlineStr"/>
+      <c r="CC140" t="inlineStr"/>
+      <c r="CD140" t="inlineStr"/>
+      <c r="CE140" t="inlineStr"/>
+      <c r="CF140" t="inlineStr"/>
+      <c r="CG140" t="inlineStr"/>
+      <c r="CH140" t="inlineStr"/>
+      <c r="CI140" t="inlineStr"/>
+      <c r="CJ140" t="inlineStr"/>
+      <c r="CK140" t="inlineStr"/>
+      <c r="CL140" t="inlineStr"/>
+      <c r="CM140" t="inlineStr"/>
+      <c r="CN140" t="inlineStr"/>
+      <c r="CO140" t="inlineStr"/>
+      <c r="CP140" t="inlineStr"/>
+      <c r="CQ140" t="inlineStr"/>
+      <c r="CR140" t="inlineStr"/>
+      <c r="CS140" t="inlineStr"/>
+      <c r="CT140" t="inlineStr"/>
+      <c r="CU140" t="inlineStr"/>
+      <c r="CV140" t="inlineStr"/>
+      <c r="CW140" t="inlineStr"/>
+      <c r="CX140" t="inlineStr"/>
+      <c r="CY140" t="inlineStr"/>
+      <c r="CZ140" t="inlineStr"/>
+      <c r="DA140" t="inlineStr"/>
+      <c r="DB140" t="inlineStr"/>
+      <c r="DC140" t="inlineStr"/>
+      <c r="DD140" t="inlineStr"/>
+      <c r="DE140" t="inlineStr"/>
+      <c r="DF140" t="inlineStr"/>
+      <c r="DG140" t="inlineStr"/>
+      <c r="DH140" t="inlineStr"/>
+      <c r="DI140" t="inlineStr"/>
+      <c r="DJ140" t="inlineStr"/>
+      <c r="DK140" t="inlineStr"/>
+      <c r="DL140" t="inlineStr"/>
+      <c r="DM140" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM140"/>
+  <dimension ref="A1:DM161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46407,55 +46407,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H134" t="n">
+        <v>2021</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>162.2</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J134" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>75</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M134" t="n">
+        <v>225</v>
+      </c>
+      <c r="N134" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O134" t="n">
+        <v>720</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>269</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
@@ -46467,20 +46449,14 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>5150</t>
-        </is>
+      <c r="T134" t="n">
+        <v>16</v>
+      </c>
+      <c r="U134" t="n">
+        <v>8</v>
+      </c>
+      <c r="V134" t="n">
+        <v>5150</v>
       </c>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
@@ -46754,55 +46730,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H135" t="n">
+        <v>2021</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>169.7</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>82.1</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J135" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M135" t="n">
+        <v>285</v>
+      </c>
+      <c r="N135" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O135" t="n">
+        <v>720</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>269</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
@@ -46814,20 +46772,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>6150</t>
-        </is>
+      <c r="T135" t="n">
+        <v>20</v>
+      </c>
+      <c r="U135" t="n">
+        <v>8</v>
+      </c>
+      <c r="V135" t="n">
+        <v>6150</v>
       </c>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
@@ -47117,55 +47069,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H136" t="n">
+        <v>2021</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>169.7</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>82.1</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J136" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="K136" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="L136" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M136" t="n">
+        <v>282</v>
+      </c>
+      <c r="N136" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O136" t="n">
+        <v>720</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>269</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
@@ -47177,20 +47111,14 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>6150</t>
-        </is>
+      <c r="T136" t="n">
+        <v>20</v>
+      </c>
+      <c r="U136" t="n">
+        <v>8</v>
+      </c>
+      <c r="V136" t="n">
+        <v>6150</v>
       </c>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
@@ -47480,55 +47408,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H137" t="n">
+        <v>2021</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>167.8</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>2460</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
+      <c r="J137" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="K137" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="L137" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M137" t="n">
+        <v>225</v>
+      </c>
+      <c r="N137" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P137" t="n">
+        <v>2460</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>395</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
@@ -47540,20 +47450,14 @@
           <t>4GB | 8GB</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>5150</t>
-        </is>
+      <c r="T137" t="n">
+        <v>48</v>
+      </c>
+      <c r="U137" t="n">
+        <v>24</v>
+      </c>
+      <c r="V137" t="n">
+        <v>5150</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
@@ -47843,55 +47747,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H138" t="n">
+        <v>2021</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J138" t="n">
+        <v>164</v>
+      </c>
+      <c r="K138" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L138" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M138" t="n">
+        <v>265</v>
+      </c>
+      <c r="N138" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P138" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>409</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
@@ -47903,20 +47789,14 @@
           <t>4GB | 8GB</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T138" t="n">
+        <v>48</v>
+      </c>
+      <c r="U138" t="n">
+        <v>24</v>
+      </c>
+      <c r="V138" t="n">
+        <v>5000</v>
       </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
@@ -48206,55 +48086,37 @@
           <t>2021. Released 2021</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H139" t="n">
+        <v>2021</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>164.8</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>76.9</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J139" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="K139" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M139" t="n">
+        <v>211</v>
+      </c>
+      <c r="N139" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O139" t="n">
+        <v>720</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>269</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
@@ -48266,20 +48128,14 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>6150</t>
-        </is>
+      <c r="T139" t="n">
+        <v>16</v>
+      </c>
+      <c r="U139" t="n">
+        <v>8</v>
+      </c>
+      <c r="V139" t="n">
+        <v>6150</v>
       </c>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
@@ -48660,6 +48516,8085 @@
       <c r="DL140" t="inlineStr"/>
       <c r="DM140" t="inlineStr"/>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9AT</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9at-10591.php</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2020, September 09. Released 2020, September 09</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>164.9 x 77 x 9 mm (6.49 x 3.03 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr"/>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>194 g (6.84 oz)</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr"/>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>2020, September 09. Released 2020, September 09</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BE141" t="inlineStr">
+        <is>
+          <t>Carbon Gray, Sky Blue, Ocean Green</t>
+        </is>
+      </c>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG141" t="inlineStr">
+        <is>
+          <t>0.78 W/kg (head)     1.03 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH141" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI141" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ141" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK141" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL141" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A53 &amp; 4x1.5 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM141" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO141" t="inlineStr"/>
+      <c r="BP141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ141" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR141" t="inlineStr"/>
+      <c r="BS141" t="inlineStr"/>
+      <c r="BT141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU141" t="inlineStr"/>
+      <c r="BV141" t="inlineStr"/>
+      <c r="BW141" t="inlineStr"/>
+      <c r="BX141" t="inlineStr"/>
+      <c r="BY141" t="inlineStr"/>
+      <c r="BZ141" t="inlineStr"/>
+      <c r="CA141" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB141" t="inlineStr"/>
+      <c r="CC141" t="inlineStr"/>
+      <c r="CD141" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE141" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF141" t="inlineStr">
+        <is>
+          <t>M2006C3LVG</t>
+        </is>
+      </c>
+      <c r="CG141" t="inlineStr">
+        <is>
+          <t>0.87 W/kg (head)     1.01 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH141" t="inlineStr"/>
+      <c r="CI141" t="inlineStr"/>
+      <c r="CJ141" t="inlineStr"/>
+      <c r="CK141" t="inlineStr"/>
+      <c r="CL141" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM141" t="inlineStr"/>
+      <c r="CN141" t="inlineStr"/>
+      <c r="CO141" t="inlineStr"/>
+      <c r="CP141" t="inlineStr"/>
+      <c r="CQ141" t="inlineStr"/>
+      <c r="CR141" t="inlineStr">
+        <is>
+          <t>Mediatek MT6762G Helio G25 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS141" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT141" t="inlineStr"/>
+      <c r="CU141" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV141" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW141" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX141" t="inlineStr"/>
+      <c r="CY141" t="inlineStr"/>
+      <c r="CZ141" t="inlineStr"/>
+      <c r="DA141" t="inlineStr"/>
+      <c r="DB141" t="inlineStr"/>
+      <c r="DC141" t="inlineStr"/>
+      <c r="DD141" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1.0µm, PDAF</t>
+        </is>
+      </c>
+      <c r="DE141" t="inlineStr"/>
+      <c r="DF141" t="inlineStr"/>
+      <c r="DG141" t="inlineStr"/>
+      <c r="DH141" t="inlineStr"/>
+      <c r="DI141" t="inlineStr"/>
+      <c r="DJ141" t="inlineStr"/>
+      <c r="DK141" t="inlineStr"/>
+      <c r="DL141" t="inlineStr"/>
+      <c r="DM141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9i</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9i-10399.php</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2020, September 15. Released 2020, September 18</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>164.9 x 77.1 x 9 mm (6.49 x 3.04 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr"/>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>194 g (6.84 oz)</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr"/>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>IPS LCD, 270 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>2020, September 15. Released 2020, September 18</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE142" t="inlineStr">
+        <is>
+          <t>Midnight Black, Sea Blue, Nature Green</t>
+        </is>
+      </c>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr"/>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI142" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ142" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK142" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL142" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A53 &amp; 4x1.5 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM142" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO142" t="inlineStr"/>
+      <c r="BP142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ142" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR142" t="inlineStr"/>
+      <c r="BS142" t="inlineStr"/>
+      <c r="BT142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU142" t="inlineStr"/>
+      <c r="BV142" t="inlineStr"/>
+      <c r="BW142" t="inlineStr"/>
+      <c r="BX142" t="inlineStr"/>
+      <c r="BY142" t="inlineStr"/>
+      <c r="BZ142" t="inlineStr"/>
+      <c r="CA142" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB142" t="inlineStr"/>
+      <c r="CC142" t="inlineStr"/>
+      <c r="CD142" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE142" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF142" t="inlineStr">
+        <is>
+          <t>M2006C3LII</t>
+        </is>
+      </c>
+      <c r="CG142" t="inlineStr"/>
+      <c r="CH142" t="inlineStr"/>
+      <c r="CI142" t="inlineStr"/>
+      <c r="CJ142" t="inlineStr"/>
+      <c r="CK142" t="inlineStr"/>
+      <c r="CL142" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM142" t="inlineStr"/>
+      <c r="CN142" t="inlineStr"/>
+      <c r="CO142" t="inlineStr"/>
+      <c r="CP142" t="inlineStr"/>
+      <c r="CQ142" t="inlineStr"/>
+      <c r="CR142" t="inlineStr">
+        <is>
+          <t>Mediatek MT6762G Helio G25 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS142" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT142" t="inlineStr"/>
+      <c r="CU142" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV142" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW142" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX142" t="inlineStr"/>
+      <c r="CY142" t="inlineStr"/>
+      <c r="CZ142" t="inlineStr"/>
+      <c r="DA142" t="inlineStr"/>
+      <c r="DB142" t="inlineStr"/>
+      <c r="DC142" t="inlineStr"/>
+      <c r="DD142" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1.0µm, PDAF</t>
+        </is>
+      </c>
+      <c r="DE142" t="inlineStr"/>
+      <c r="DF142" t="inlineStr"/>
+      <c r="DG142" t="inlineStr"/>
+      <c r="DH142" t="inlineStr"/>
+      <c r="DI142" t="inlineStr"/>
+      <c r="DJ142" t="inlineStr"/>
+      <c r="DK142" t="inlineStr"/>
+      <c r="DL142" t="inlineStr"/>
+      <c r="DM142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Xiaomi Poco M2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_poco_m2-10434.php</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2020, September 08</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 15</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>163.3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>6GB</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>163.3 x 77 x 9.1 mm (6.43 x 3.03 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>198 g (6.98 oz)</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>Wireless FM radio (no wired headphones required)</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>6.53 inches, 104.7 cm 2 (~83.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr"/>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>2020, September 08</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 15</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>Brick Red, Pitch Black, Slate Blue</t>
+        </is>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI143" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ143" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK143" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL143" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM143" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO143" t="inlineStr"/>
+      <c r="BP143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ143" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR143" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS143" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 3), plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU143" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="BV143" t="inlineStr"/>
+      <c r="BW143" t="inlineStr"/>
+      <c r="BX143" t="inlineStr"/>
+      <c r="BY143" t="inlineStr"/>
+      <c r="BZ143" t="inlineStr"/>
+      <c r="CA143" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB143" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1/3.1", 1.12µm, PDAF 8 MP, f/2.2, 118˚ (ultrawide), 1/4.0", 1.12µm 5 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC143" t="inlineStr"/>
+      <c r="CD143" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE143" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF143" t="inlineStr">
+        <is>
+          <t>MZB9919IN, M2004J19PI</t>
+        </is>
+      </c>
+      <c r="CG143" t="inlineStr">
+        <is>
+          <t>0.85 W/kg (head)     0.42 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH143" t="inlineStr"/>
+      <c r="CI143" t="inlineStr"/>
+      <c r="CJ143" t="inlineStr"/>
+      <c r="CK143" t="inlineStr"/>
+      <c r="CL143" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM143" t="inlineStr"/>
+      <c r="CN143" t="inlineStr"/>
+      <c r="CO143" t="inlineStr"/>
+      <c r="CP143" t="inlineStr"/>
+      <c r="CQ143" t="inlineStr"/>
+      <c r="CR143" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769V/CU Helio G80 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS143" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT143" t="inlineStr"/>
+      <c r="CU143" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV143" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 27mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW143" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX143" t="inlineStr"/>
+      <c r="CY143" t="inlineStr"/>
+      <c r="CZ143" t="inlineStr"/>
+      <c r="DA143" t="inlineStr"/>
+      <c r="DB143" t="inlineStr"/>
+      <c r="DC143" t="inlineStr"/>
+      <c r="DD143" t="inlineStr"/>
+      <c r="DE143" t="inlineStr"/>
+      <c r="DF143" t="inlineStr"/>
+      <c r="DG143" t="inlineStr"/>
+      <c r="DH143" t="inlineStr"/>
+      <c r="DI143" t="inlineStr"/>
+      <c r="DJ143" t="inlineStr"/>
+      <c r="DK143" t="inlineStr"/>
+      <c r="DL143" t="inlineStr"/>
+      <c r="DM143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Xiaomi Poco X3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_poco_x3-10461.php</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2020, September 22</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 29</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>165.3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>About 230 EUR</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Li-Po 6000 mAh</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>165.3 x 76.8 x 10.1 mm (6.51 x 3.02 x 0.40 in)</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr"/>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>225 g (7.94 oz)</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>FM radio, recording</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~84.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>IPS LCD, 120Hz, HDR10, 450 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr"/>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>2020, September 22</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 29</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>Cobalt Blue, Shadow Gray</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>About 230 EUR</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL144" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.3 GHz Kryo 470 Gold &amp; 6x1.8 GHz Kryo 470 Silver)</t>
+        </is>
+      </c>
+      <c r="BM144" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO144" t="inlineStr"/>
+      <c r="BP144" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ144" t="inlineStr">
+        <is>
+          <t>33W wired</t>
+        </is>
+      </c>
+      <c r="BR144" t="inlineStr">
+        <is>
+          <t>IP53 dust protected and water resistant (vertical water sprays)</t>
+        </is>
+      </c>
+      <c r="BS144" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU144" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV144" t="inlineStr"/>
+      <c r="BW144" t="inlineStr"/>
+      <c r="BX144" t="inlineStr"/>
+      <c r="BY144" t="inlineStr"/>
+      <c r="BZ144" t="inlineStr"/>
+      <c r="CA144" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB144" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.9, (wide), 1/1.73", 0.8µm, PDAF 13 MP, f/2.2, 119˚ (ultrawide), 1.0µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC144" t="inlineStr"/>
+      <c r="CD144" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/120fps, 720p@960fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE144" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF144" t="inlineStr">
+        <is>
+          <t>MZB07Z0IN, MZB07Z1IN, MZB07Z2IN, MZB07Z3IN, MZB07Z4IN, MZB9965IN, M2007J20CI</t>
+        </is>
+      </c>
+      <c r="CG144" t="inlineStr">
+        <is>
+          <t>0.75 W/kg (head)     0.61 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH144" t="inlineStr"/>
+      <c r="CI144" t="inlineStr"/>
+      <c r="CJ144" t="inlineStr"/>
+      <c r="CK144" t="inlineStr"/>
+      <c r="CL144" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM144" t="inlineStr"/>
+      <c r="CN144" t="inlineStr"/>
+      <c r="CO144" t="inlineStr"/>
+      <c r="CP144" t="inlineStr"/>
+      <c r="CQ144" t="inlineStr"/>
+      <c r="CR144" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7150-AC Snapdragon 732G (8 nm)</t>
+        </is>
+      </c>
+      <c r="CS144" t="inlineStr">
+        <is>
+          <t>Adreno 618</t>
+        </is>
+      </c>
+      <c r="CT144" t="inlineStr"/>
+      <c r="CU144" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV144" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.2, (wide), 1/3.4", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CW144" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX144" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY144" t="inlineStr"/>
+      <c r="CZ144" t="inlineStr"/>
+      <c r="DA144" t="inlineStr"/>
+      <c r="DB144" t="inlineStr"/>
+      <c r="DC144" t="inlineStr"/>
+      <c r="DD144" t="inlineStr"/>
+      <c r="DE144" t="inlineStr"/>
+      <c r="DF144" t="inlineStr"/>
+      <c r="DG144" t="inlineStr"/>
+      <c r="DH144" t="inlineStr"/>
+      <c r="DI144" t="inlineStr"/>
+      <c r="DJ144" t="inlineStr"/>
+      <c r="DK144" t="inlineStr"/>
+      <c r="DL144" t="inlineStr"/>
+      <c r="DM144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Xiaomi Poco X3 NFC</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_poco_x3_nfc-10415.php</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2020, September 07</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 08</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>165.3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Li-Po 5160 mAh</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>165.3 x 76.8 x 9.4 mm (6.51 x 3.02 x 0.37 in)</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr"/>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>215 g (7.58 oz)</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>FM radio, recording</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~84.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>IPS LCD, 120Hz, HDR10, 450 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>2020, September 07</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, September 08</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>Cobalt Blue, Shadow Gray</t>
+        </is>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG145" t="inlineStr">
+        <is>
+          <t>0.56 W/kg (head)     0.99 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH145" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI145" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ145" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK145" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL145" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.3 GHz Kryo 470 Gold &amp; 6x1.8 GHz Kryo 470 Silver)</t>
+        </is>
+      </c>
+      <c r="BM145" t="inlineStr">
+        <is>
+          <t>Android 10, upgradable to Android 12, MIUI 14</t>
+        </is>
+      </c>
+      <c r="BN145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO145" t="inlineStr"/>
+      <c r="BP145" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ145" t="inlineStr">
+        <is>
+          <t>33W wired, 62% in 30 min, 100% in 65 min</t>
+        </is>
+      </c>
+      <c r="BR145" t="inlineStr">
+        <is>
+          <t>IP53 dust protected and water resistant (vertical water sprays)</t>
+        </is>
+      </c>
+      <c r="BS145" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), aluminum frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU145" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV145" t="inlineStr"/>
+      <c r="BW145" t="inlineStr"/>
+      <c r="BX145" t="inlineStr"/>
+      <c r="BY145" t="inlineStr"/>
+      <c r="BZ145" t="inlineStr"/>
+      <c r="CA145" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB145" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.9, (wide), 1/1.73", 0.8µm, PDAF 13 MP, f/2.2, 119˚ (ultrawide), 1.0µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC145" t="inlineStr"/>
+      <c r="CD145" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/120fps, 720p@960fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE145" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF145" t="inlineStr">
+        <is>
+          <t>M2007J20CG, M2007J20CT</t>
+        </is>
+      </c>
+      <c r="CG145" t="inlineStr">
+        <is>
+          <t>0.77 W/kg (head)     0.61 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH145" t="inlineStr"/>
+      <c r="CI145" t="inlineStr"/>
+      <c r="CJ145" t="inlineStr"/>
+      <c r="CK145" t="inlineStr"/>
+      <c r="CL145" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM145" t="inlineStr"/>
+      <c r="CN145" t="inlineStr"/>
+      <c r="CO145" t="inlineStr">
+        <is>
+          <t>Contrast ratio: 1299:1 (nominal)</t>
+        </is>
+      </c>
+      <c r="CP145" t="inlineStr">
+        <is>
+          <t>-25.3 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ145" t="inlineStr">
+        <is>
+          <t>AnTuTu: 283750 (v8) GeekBench: 1777 (v5.1) GFXBench: 16fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR145" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7150-AC Snapdragon 732G (8 nm)</t>
+        </is>
+      </c>
+      <c r="CS145" t="inlineStr">
+        <is>
+          <t>Adreno 618</t>
+        </is>
+      </c>
+      <c r="CT145" t="inlineStr"/>
+      <c r="CU145" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV145" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.2, (wide), 1/3.4", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CW145" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX145" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY145" t="inlineStr"/>
+      <c r="CZ145" t="inlineStr"/>
+      <c r="DA145" t="inlineStr"/>
+      <c r="DB145" t="inlineStr"/>
+      <c r="DC145" t="inlineStr"/>
+      <c r="DD145" t="inlineStr"/>
+      <c r="DE145" t="inlineStr"/>
+      <c r="DF145" t="inlineStr"/>
+      <c r="DG145" t="inlineStr"/>
+      <c r="DH145" t="inlineStr"/>
+      <c r="DI145" t="inlineStr"/>
+      <c r="DJ145" t="inlineStr"/>
+      <c r="DK145" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL145" t="inlineStr"/>
+      <c r="DM145" t="inlineStr">
+        <is>
+          <t>Endurance rating 125h</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9 (India)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Not to be confused with Xiaomi Redmi 9 for Global market</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9_(india)-10398.php</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2020, August 27. Released 2020, August 31</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>164.9 x 77.1 x 9 mm (6.49 x 3.04 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr"/>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>194 g (6.84 oz)</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr"/>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>2020, August 27. Released 2020, August 31</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>Black, Sky Blue, Sporty Orange</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI146" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ146" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK146" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL146" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM146" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO146" t="inlineStr"/>
+      <c r="BP146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ146" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR146" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS146" t="inlineStr"/>
+      <c r="BT146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU146" t="inlineStr"/>
+      <c r="BV146" t="inlineStr"/>
+      <c r="BW146" t="inlineStr"/>
+      <c r="BX146" t="inlineStr"/>
+      <c r="BY146" t="inlineStr"/>
+      <c r="BZ146" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, (wide), PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA146" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB146" t="inlineStr"/>
+      <c r="CC146" t="inlineStr"/>
+      <c r="CD146" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE146" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF146" t="inlineStr">
+        <is>
+          <t>M2004C3MI</t>
+        </is>
+      </c>
+      <c r="CG146" t="inlineStr">
+        <is>
+          <t>0.51 W/kg (head)     0.83 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH146" t="inlineStr"/>
+      <c r="CI146" t="inlineStr"/>
+      <c r="CJ146" t="inlineStr"/>
+      <c r="CK146" t="inlineStr"/>
+      <c r="CL146" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM146" t="inlineStr"/>
+      <c r="CN146" t="inlineStr"/>
+      <c r="CO146" t="inlineStr"/>
+      <c r="CP146" t="inlineStr"/>
+      <c r="CQ146" t="inlineStr"/>
+      <c r="CR146" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS146" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT146" t="inlineStr"/>
+      <c r="CU146" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV146" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW146" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX146" t="inlineStr"/>
+      <c r="CY146" t="inlineStr"/>
+      <c r="CZ146" t="inlineStr"/>
+      <c r="DA146" t="inlineStr"/>
+      <c r="DB146" t="inlineStr"/>
+      <c r="DC146" t="inlineStr"/>
+      <c r="DD146" t="inlineStr"/>
+      <c r="DE146" t="inlineStr"/>
+      <c r="DF146" t="inlineStr"/>
+      <c r="DG146" t="inlineStr"/>
+      <c r="DH146" t="inlineStr"/>
+      <c r="DI146" t="inlineStr"/>
+      <c r="DJ146" t="inlineStr"/>
+      <c r="DK146" t="inlineStr"/>
+      <c r="DL146" t="inlineStr"/>
+      <c r="DM146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Xiaomi Mi 10 Ultra</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_mi_10_ultra-10361.php</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2020, August 11. Released 2020, August 16</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>162.4</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>221.8</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>12GB | 16GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>About 650 EUR</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Li-Ion 4500 mAh, graphene-enhanced</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>162.4 x 75.1 x 9.5 mm (6.39 x 2.96 x 0.37 in)</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>221.8 g (7.83 oz)</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS (G1), BDS (B1I+B2a), GALILEO (E1+E5a), QZSS (L1+L5)</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct, DLNA</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~386 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>6.67 inches, 109.2 cm 2 (~89.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>OLED, 1B colors, 120Hz, HDR10+, 800 nits (HBM), 1120 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>2020, August 11. Released 2020, August 16</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM, 256GB 12GB RAM, 512GB 16GB RAM</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>Obsidian Black, Mercury Silver, Transparent Edition</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>About 650 EUR</t>
+        </is>
+      </c>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI147" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ147" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK147" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL147" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Cortex-A77 &amp; 3x2.42 GHz Cortex-A77 &amp; 4x1.80 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM147" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12.5</t>
+        </is>
+      </c>
+      <c r="BN147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO147" t="inlineStr"/>
+      <c r="BP147" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ147" t="inlineStr">
+        <is>
+          <t>120W wired, PD3.0, QC5, 41% in 5 min, 100% in 23 min 50W wireless, 100% in 40 min 10W reverse wireless</t>
+        </is>
+      </c>
+      <c r="BR147" t="inlineStr"/>
+      <c r="BS147" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 6), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU147" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV147" t="inlineStr"/>
+      <c r="BW147" t="inlineStr"/>
+      <c r="BX147" t="inlineStr"/>
+      <c r="BY147" t="inlineStr"/>
+      <c r="BZ147" t="inlineStr"/>
+      <c r="CA147" t="inlineStr">
+        <is>
+          <t>Laser AF, color spectrum sensor, Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB147" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.9, 25mm (wide), 1/1.32", 1.2µm, PDAF, OIS 48 MP, f/4.1, 120mm (periscope telephoto), 1/2.0", 0.8µm, PDAF, OIS, 5x optical zoom 12 MP, f/2.0, 50mm (telephoto), 1/2.55", 1.4µm, dual pixel PDAF, 2x optical zoom 20 MP, f/2.2, 128˚, 12mm (ultrawide), 1/2.8", 1.0µm, PDAF</t>
+        </is>
+      </c>
+      <c r="CC147" t="inlineStr"/>
+      <c r="CD147" t="inlineStr">
+        <is>
+          <t>8K@24fps, 4K@30/60fps, 1080p@30/60/120/240/960fps, gyro-EIS, HDR10 rec.</t>
+        </is>
+      </c>
+      <c r="CE147" t="inlineStr">
+        <is>
+          <t>UFS 3.1</t>
+        </is>
+      </c>
+      <c r="CF147" t="inlineStr">
+        <is>
+          <t>M2007J1SC</t>
+        </is>
+      </c>
+      <c r="CG147" t="inlineStr"/>
+      <c r="CH147" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI147" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ147" t="inlineStr"/>
+      <c r="CK147" t="inlineStr"/>
+      <c r="CL147" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM147" t="inlineStr">
+        <is>
+          <t>1, 3, 41, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN147" t="inlineStr"/>
+      <c r="CO147" t="inlineStr">
+        <is>
+          <t>Contrast ratio: Infinite (nominal)</t>
+        </is>
+      </c>
+      <c r="CP147" t="inlineStr">
+        <is>
+          <t>-24.6 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ147" t="inlineStr">
+        <is>
+          <t>AnTuTu: 638497 (v8) GeekBench: 3248 (v5.1) GFXBench: 46fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR147" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8250 Snapdragon 865 5G (7 nm+)</t>
+        </is>
+      </c>
+      <c r="CS147" t="inlineStr">
+        <is>
+          <t>Adreno 650</t>
+        </is>
+      </c>
+      <c r="CT147" t="inlineStr"/>
+      <c r="CU147" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV147" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.3, (wide), 1/3.4", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CW147" t="inlineStr">
+        <is>
+          <t>1080p@30fps, 720p@120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX147" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY147" t="inlineStr"/>
+      <c r="CZ147" t="inlineStr"/>
+      <c r="DA147" t="inlineStr"/>
+      <c r="DB147" t="inlineStr"/>
+      <c r="DC147" t="inlineStr"/>
+      <c r="DD147" t="inlineStr"/>
+      <c r="DE147" t="inlineStr"/>
+      <c r="DF147" t="inlineStr"/>
+      <c r="DG147" t="inlineStr"/>
+      <c r="DH147" t="inlineStr"/>
+      <c r="DI147" t="inlineStr"/>
+      <c r="DJ147" t="inlineStr"/>
+      <c r="DK147" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL147" t="inlineStr"/>
+      <c r="DM147" t="inlineStr">
+        <is>
+          <t>Endurance rating 85h</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi K30 Ultra</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_k30_ultra-10349.php</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2020, August 11. Released 2020, August 14</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>163.3</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Li-Po 4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>163.3 x 75.4 x 9.1 mm (6.43 x 2.97 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr"/>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>213 g (7.51 oz)</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS (G1), BDS (B1I+B2a), GALILEO (E1+E5a), QZSS (L1+L5)</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~87.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>AMOLED, 120Hz, HDR10+, 500 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr"/>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>2020, August 11. Released 2020, August 14</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM, 512GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>Moonlight White, Midnight Black, Mint Green</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI148" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ148" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK148" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL148" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.6 GHz Cortex-A77 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM148" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO148" t="inlineStr"/>
+      <c r="BP148" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ148" t="inlineStr">
+        <is>
+          <t>33W wired, PD, QC4, 100% in 58 min</t>
+        </is>
+      </c>
+      <c r="BR148" t="inlineStr"/>
+      <c r="BS148" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU148" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV148" t="inlineStr"/>
+      <c r="BW148" t="inlineStr"/>
+      <c r="BX148" t="inlineStr"/>
+      <c r="BY148" t="inlineStr"/>
+      <c r="BZ148" t="inlineStr"/>
+      <c r="CA148" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB148" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.9, 26mm (wide), 1/1.73", 0.8µm, PDAF 13 MP, f/2.4, 119˚ (ultrawide), 1.12µm 5 MP, f/2.2, 50mm (telephoto macro), AF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC148" t="inlineStr"/>
+      <c r="CD148" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120/240/960fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE148" t="inlineStr">
+        <is>
+          <t>UFS</t>
+        </is>
+      </c>
+      <c r="CF148" t="inlineStr">
+        <is>
+          <t>M2006J10C</t>
+        </is>
+      </c>
+      <c r="CG148" t="inlineStr"/>
+      <c r="CH148" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI148" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ148" t="inlineStr"/>
+      <c r="CK148" t="inlineStr"/>
+      <c r="CL148" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM148" t="inlineStr">
+        <is>
+          <t>1, 3, 41, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN148" t="inlineStr"/>
+      <c r="CO148" t="inlineStr"/>
+      <c r="CP148" t="inlineStr"/>
+      <c r="CQ148" t="inlineStr"/>
+      <c r="CR148" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 1000+ (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS148" t="inlineStr">
+        <is>
+          <t>Mali-G77 MC9</t>
+        </is>
+      </c>
+      <c r="CT148" t="inlineStr"/>
+      <c r="CU148" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV148" t="inlineStr">
+        <is>
+          <t>Motorized pop-up 20 MP, (wide)</t>
+        </is>
+      </c>
+      <c r="CW148" t="inlineStr">
+        <is>
+          <t>1080p@30fps, 720p@120fps</t>
+        </is>
+      </c>
+      <c r="CX148" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY148" t="inlineStr"/>
+      <c r="CZ148" t="inlineStr"/>
+      <c r="DA148" t="inlineStr"/>
+      <c r="DB148" t="inlineStr"/>
+      <c r="DC148" t="inlineStr"/>
+      <c r="DD148" t="inlineStr"/>
+      <c r="DE148" t="inlineStr"/>
+      <c r="DF148" t="inlineStr"/>
+      <c r="DG148" t="inlineStr"/>
+      <c r="DH148" t="inlineStr"/>
+      <c r="DI148" t="inlineStr"/>
+      <c r="DJ148" t="inlineStr"/>
+      <c r="DK148" t="inlineStr"/>
+      <c r="DL148" t="inlineStr"/>
+      <c r="DM148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9 Prime</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9_prime-10353.php</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2020, August 04</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, August 06</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>163.3</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>5020</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Li-Po 5020 mAh</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>163.3 x 77 x 9.1 mm (6.43 x 3.03 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr"/>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>198 g (6.98 oz)</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>Wireless FM radio (no wired headphones required)</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>6.53 inches, 104.7 cm 2 (~83.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>2020, August 04</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, August 06</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD149" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>Space Blue, Mint Green, Matte Black, Sunrise Flare</t>
+        </is>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI149" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ149" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK149" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL149" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM149" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 11</t>
+        </is>
+      </c>
+      <c r="BN149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO149" t="inlineStr"/>
+      <c r="BP149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ149" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR149" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS149" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 3), plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU149" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="BV149" t="inlineStr"/>
+      <c r="BW149" t="inlineStr"/>
+      <c r="BX149" t="inlineStr"/>
+      <c r="BY149" t="inlineStr"/>
+      <c r="BZ149" t="inlineStr"/>
+      <c r="CA149" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB149" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1/3.1", 1.12µm, PDAF 8 MP, f/2.2, 118˚ (ultrawide), 1/4.0", 1.12µm 5 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC149" t="inlineStr"/>
+      <c r="CD149" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE149" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF149" t="inlineStr">
+        <is>
+          <t>M2004J19PI</t>
+        </is>
+      </c>
+      <c r="CG149" t="inlineStr">
+        <is>
+          <t>0.85 W/kg (head)     0.42 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH149" t="inlineStr"/>
+      <c r="CI149" t="inlineStr"/>
+      <c r="CJ149" t="inlineStr"/>
+      <c r="CK149" t="inlineStr"/>
+      <c r="CL149" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM149" t="inlineStr"/>
+      <c r="CN149" t="inlineStr"/>
+      <c r="CO149" t="inlineStr"/>
+      <c r="CP149" t="inlineStr"/>
+      <c r="CQ149" t="inlineStr"/>
+      <c r="CR149" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769V/CU Helio G80 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS149" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT149" t="inlineStr"/>
+      <c r="CU149" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV149" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 27mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW149" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX149" t="inlineStr"/>
+      <c r="CY149" t="inlineStr"/>
+      <c r="CZ149" t="inlineStr"/>
+      <c r="DA149" t="inlineStr"/>
+      <c r="DB149" t="inlineStr"/>
+      <c r="DC149" t="inlineStr"/>
+      <c r="DD149" t="inlineStr"/>
+      <c r="DE149" t="inlineStr"/>
+      <c r="DF149" t="inlineStr"/>
+      <c r="DG149" t="inlineStr"/>
+      <c r="DH149" t="inlineStr"/>
+      <c r="DI149" t="inlineStr"/>
+      <c r="DJ149" t="inlineStr"/>
+      <c r="DK149" t="inlineStr"/>
+      <c r="DL149" t="inlineStr"/>
+      <c r="DM149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Xiaomi Black Shark 3S</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_black_shark_3s-10350.php</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2020, July 31. Released 2020, August 04</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>168.7</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>4729</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>About 600 EUR</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Li-Po 4729 mAh</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>168.7 x 77.3 x 10.4 mm (6.64 x 3.04 x 0.41 in)</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>222 g (7.83 oz)</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX HD, aptX Adaptive</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr"/>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, QZSS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~82.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>AMOLED, 120Hz, HDR10+, 500 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>2020, July 31. Released 2020, August 04</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>128GB 12GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>Sky Cloud Black, Crystal Blue</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>About 600 EUR</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ150" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK150" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL150" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Cortex-A77 &amp; 3x2.42 GHz Cortex-A77 &amp; 4x1.80 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM150" t="inlineStr">
+        <is>
+          <t>Android 10</t>
+        </is>
+      </c>
+      <c r="BN150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO150" t="inlineStr"/>
+      <c r="BP150" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ150" t="inlineStr">
+        <is>
+          <t>65W wired, 100% in 38 min 18W magnetic wireless</t>
+        </is>
+      </c>
+      <c r="BR150" t="inlineStr"/>
+      <c r="BS150" t="inlineStr">
+        <is>
+          <t>Glass front, aluminum back, aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU150" t="inlineStr"/>
+      <c r="BV150" t="inlineStr"/>
+      <c r="BW150" t="inlineStr"/>
+      <c r="BX150" t="inlineStr"/>
+      <c r="BY150" t="inlineStr"/>
+      <c r="BZ150" t="inlineStr"/>
+      <c r="CA150" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB150" t="inlineStr"/>
+      <c r="CC150" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/1.72", 0.8µm, PDAF 13 MP, f/2.3, 120˚ (ultrawide) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD150" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60/240fps, 720p@1920fps</t>
+        </is>
+      </c>
+      <c r="CE150" t="inlineStr">
+        <is>
+          <t>UFS 3.1</t>
+        </is>
+      </c>
+      <c r="CF150" t="inlineStr"/>
+      <c r="CG150" t="inlineStr"/>
+      <c r="CH150" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI150" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ150" t="inlineStr"/>
+      <c r="CK150" t="inlineStr"/>
+      <c r="CL150" t="inlineStr">
+        <is>
+          <t>1, 3, 4, 5, 7, 8, 12, 17, 20, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM150" t="inlineStr">
+        <is>
+          <t>41, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN150" t="inlineStr"/>
+      <c r="CO150" t="inlineStr"/>
+      <c r="CP150" t="inlineStr"/>
+      <c r="CQ150" t="inlineStr"/>
+      <c r="CR150" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8250 Snapdragon 865 5G (7 nm+)</t>
+        </is>
+      </c>
+      <c r="CS150" t="inlineStr">
+        <is>
+          <t>Adreno 650</t>
+        </is>
+      </c>
+      <c r="CT150" t="inlineStr"/>
+      <c r="CU150" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV150" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.0, (wide), 1/3", 0.9µm</t>
+        </is>
+      </c>
+      <c r="CW150" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX150" t="inlineStr"/>
+      <c r="CY150" t="inlineStr"/>
+      <c r="CZ150" t="inlineStr"/>
+      <c r="DA150" t="inlineStr"/>
+      <c r="DB150" t="inlineStr"/>
+      <c r="DC150" t="inlineStr"/>
+      <c r="DD150" t="inlineStr"/>
+      <c r="DE150" t="inlineStr"/>
+      <c r="DF150" t="inlineStr"/>
+      <c r="DG150" t="inlineStr"/>
+      <c r="DH150" t="inlineStr"/>
+      <c r="DI150" t="inlineStr"/>
+      <c r="DJ150" t="inlineStr"/>
+      <c r="DK150" t="inlineStr"/>
+      <c r="DL150" t="inlineStr"/>
+      <c r="DM150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Xiaomi Poco M2 Pro</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_poco_m2_pro-10318.php</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2020, July 07. Released 2020, July 14</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>165.8</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>165.8 x 76.7 x 8.8 mm (6.53 x 3.02 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>209 g (7.37 oz)</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>FM radio, recording</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~84.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>IPS LCD, HDR10, 450 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>2020, July 07. Released 2020, July 14</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 64GB 6GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>Out Of The Blue, Green and Greener, Two Shades of Black</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr">
+        <is>
+          <t>0.91 W/kg (head)     0.56 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH151" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI151" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ151" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK151" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL151" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.3 GHz Kryo 465 Gold &amp; 6x1.8 GHz Kryo 465 Silver)</t>
+        </is>
+      </c>
+      <c r="BM151" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO151" t="inlineStr"/>
+      <c r="BP151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ151" t="inlineStr">
+        <is>
+          <t>33W wired</t>
+        </is>
+      </c>
+      <c r="BR151" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS151" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5), plastic frame</t>
+        </is>
+      </c>
+      <c r="BT151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU151" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV151" t="inlineStr"/>
+      <c r="BW151" t="inlineStr"/>
+      <c r="BX151" t="inlineStr"/>
+      <c r="BY151" t="inlineStr"/>
+      <c r="BZ151" t="inlineStr"/>
+      <c r="CA151" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB151" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF 8 MP, f/2.2, 119˚ (ultrawide), 1/4.0", 1.12µm 5 MP (macro), AF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC151" t="inlineStr"/>
+      <c r="CD151" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120fps, 720p@960fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE151" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF151" t="inlineStr"/>
+      <c r="CG151" t="inlineStr"/>
+      <c r="CH151" t="inlineStr"/>
+      <c r="CI151" t="inlineStr"/>
+      <c r="CJ151" t="inlineStr"/>
+      <c r="CK151" t="inlineStr"/>
+      <c r="CL151" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM151" t="inlineStr"/>
+      <c r="CN151" t="inlineStr"/>
+      <c r="CO151" t="inlineStr"/>
+      <c r="CP151" t="inlineStr"/>
+      <c r="CQ151" t="inlineStr"/>
+      <c r="CR151" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7125 Snapdragon 720G (8 nm)</t>
+        </is>
+      </c>
+      <c r="CS151" t="inlineStr">
+        <is>
+          <t>Adreno 618</t>
+        </is>
+      </c>
+      <c r="CT151" t="inlineStr"/>
+      <c r="CU151" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV151" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, (wide), 1/3.06" 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW151" t="inlineStr">
+        <is>
+          <t>1080p@30/120fps</t>
+        </is>
+      </c>
+      <c r="CX151" t="inlineStr"/>
+      <c r="CY151" t="inlineStr"/>
+      <c r="CZ151" t="inlineStr"/>
+      <c r="DA151" t="inlineStr"/>
+      <c r="DB151" t="inlineStr"/>
+      <c r="DC151" t="inlineStr"/>
+      <c r="DD151" t="inlineStr"/>
+      <c r="DE151" t="inlineStr"/>
+      <c r="DF151" t="inlineStr"/>
+      <c r="DG151" t="inlineStr"/>
+      <c r="DH151" t="inlineStr"/>
+      <c r="DI151" t="inlineStr"/>
+      <c r="DJ151" t="inlineStr"/>
+      <c r="DK151" t="inlineStr"/>
+      <c r="DL151" t="inlineStr"/>
+      <c r="DM151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9A</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9a-10279.php</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2020, June 30. Released 2020, July 07</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>128GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>2GB | 3GB | 4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>164.9 x 77.1 x 9 mm (6.49 x 3.04 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>196 g (6.91 oz)</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr"/>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>2020, June 30. Released 2020, July 07</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD152" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM, 64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE152" t="inlineStr">
+        <is>
+          <t>Carbon Gray (Midnight Black), Sky Blue (Sea Blue), Ocean Green (Nature Green)</t>
+        </is>
+      </c>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG152" t="inlineStr">
+        <is>
+          <t>0.40 W/kg (head)     1.19 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH152" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI152" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - International</t>
+        </is>
+      </c>
+      <c r="BJ152" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK152" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL152" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A53 &amp; 4x1.5 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM152" t="inlineStr">
+        <is>
+          <t>Android 10, upgradable to Android 11, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO152" t="inlineStr"/>
+      <c r="BP152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ152" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR152" t="inlineStr"/>
+      <c r="BS152" t="inlineStr"/>
+      <c r="BT152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU152" t="inlineStr"/>
+      <c r="BV152" t="inlineStr"/>
+      <c r="BW152" t="inlineStr"/>
+      <c r="BX152" t="inlineStr"/>
+      <c r="BY152" t="inlineStr"/>
+      <c r="BZ152" t="inlineStr"/>
+      <c r="CA152" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB152" t="inlineStr"/>
+      <c r="CC152" t="inlineStr"/>
+      <c r="CD152" t="inlineStr">
+        <is>
+          <t>1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE152" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF152" t="inlineStr">
+        <is>
+          <t>M2006C3LG, M2006C3LI, M2006C3LC, M2004C3L</t>
+        </is>
+      </c>
+      <c r="CG152" t="inlineStr">
+        <is>
+          <t>0.90 W/kg (head)     0.65 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH152" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100 - India</t>
+        </is>
+      </c>
+      <c r="CI152" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41 - India</t>
+        </is>
+      </c>
+      <c r="CJ152" t="inlineStr"/>
+      <c r="CK152" t="inlineStr"/>
+      <c r="CL152" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41 - International</t>
+        </is>
+      </c>
+      <c r="CM152" t="inlineStr"/>
+      <c r="CN152" t="inlineStr"/>
+      <c r="CO152" t="inlineStr"/>
+      <c r="CP152" t="inlineStr"/>
+      <c r="CQ152" t="inlineStr"/>
+      <c r="CR152" t="inlineStr">
+        <is>
+          <t>Mediatek MT6762G Helio G25 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS152" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT152" t="inlineStr"/>
+      <c r="CU152" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV152" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW152" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX152" t="inlineStr"/>
+      <c r="CY152" t="inlineStr"/>
+      <c r="CZ152" t="inlineStr"/>
+      <c r="DA152" t="inlineStr"/>
+      <c r="DB152" t="inlineStr"/>
+      <c r="DC152" t="inlineStr"/>
+      <c r="DD152" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1.0µm, PDAF</t>
+        </is>
+      </c>
+      <c r="DE152" t="inlineStr"/>
+      <c r="DF152" t="inlineStr"/>
+      <c r="DG152" t="inlineStr"/>
+      <c r="DH152" t="inlineStr"/>
+      <c r="DI152" t="inlineStr"/>
+      <c r="DJ152" t="inlineStr"/>
+      <c r="DK152" t="inlineStr"/>
+      <c r="DL152" t="inlineStr"/>
+      <c r="DM152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9C NFC</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9c_nfc-10277.php</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2020, August 27. Released 2020, August 27</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>128GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>2GB | 3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>164.9 x 77.1 x 9 mm (6.49 x 3.04 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>196 g (6.91 oz)</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr"/>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr"/>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>2020, August 27. Released 2020, August 27</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD153" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM, 64GB 2GB RAM, 64GB 3GB RAM, 128GB 3GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE153" t="inlineStr">
+        <is>
+          <t>Midnight Gray, Sunshine Yellow, Twilight Blue</t>
+        </is>
+      </c>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>0.37 W/kg (head)     1.14 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI153" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ153" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK153" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL153" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM153" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO153" t="inlineStr"/>
+      <c r="BP153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ153" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR153" t="inlineStr"/>
+      <c r="BS153" t="inlineStr"/>
+      <c r="BT153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU153" t="inlineStr"/>
+      <c r="BV153" t="inlineStr"/>
+      <c r="BW153" t="inlineStr"/>
+      <c r="BX153" t="inlineStr"/>
+      <c r="BY153" t="inlineStr"/>
+      <c r="BZ153" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1.0µm, PDAF 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CA153" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB153" t="inlineStr"/>
+      <c r="CC153" t="inlineStr"/>
+      <c r="CD153" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE153" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF153" t="inlineStr">
+        <is>
+          <t>M2006C3MNG</t>
+        </is>
+      </c>
+      <c r="CG153" t="inlineStr">
+        <is>
+          <t>0.57 W/kg (head)     0.90 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH153" t="inlineStr"/>
+      <c r="CI153" t="inlineStr"/>
+      <c r="CJ153" t="inlineStr"/>
+      <c r="CK153" t="inlineStr"/>
+      <c r="CL153" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 38, 40</t>
+        </is>
+      </c>
+      <c r="CM153" t="inlineStr"/>
+      <c r="CN153" t="inlineStr"/>
+      <c r="CO153" t="inlineStr"/>
+      <c r="CP153" t="inlineStr"/>
+      <c r="CQ153" t="inlineStr"/>
+      <c r="CR153" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS153" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT153" t="inlineStr"/>
+      <c r="CU153" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV153" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW153" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX153" t="inlineStr"/>
+      <c r="CY153" t="inlineStr"/>
+      <c r="CZ153" t="inlineStr"/>
+      <c r="DA153" t="inlineStr"/>
+      <c r="DB153" t="inlineStr"/>
+      <c r="DC153" t="inlineStr"/>
+      <c r="DD153" t="inlineStr"/>
+      <c r="DE153" t="inlineStr"/>
+      <c r="DF153" t="inlineStr"/>
+      <c r="DG153" t="inlineStr"/>
+      <c r="DH153" t="inlineStr"/>
+      <c r="DI153" t="inlineStr"/>
+      <c r="DJ153" t="inlineStr"/>
+      <c r="DK153" t="inlineStr"/>
+      <c r="DL153" t="inlineStr"/>
+      <c r="DM153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9C</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9c-10278.php</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2020, June 30. Released 2020, August 12</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>164.9</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>128GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>2GB | 3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>164.9 x 77 x 9 mm (6.49 x 3.03 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>196 g (6.91 oz)</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr"/>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>6.53 inches, 102.9 cm 2 (~81.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr"/>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>2020, June 30. Released 2020, August 12</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD154" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM, 64GB 2GB RAM, 64GB 3GB RAM, 64GB 4GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE154" t="inlineStr">
+        <is>
+          <t>Midnight Gray, Sunrise Orange, Twilight Blue</t>
+        </is>
+      </c>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>0.35 W/kg (head)     0.78 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH154" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI154" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ154" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK154" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL154" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM154" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 12</t>
+        </is>
+      </c>
+      <c r="BN154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO154" t="inlineStr"/>
+      <c r="BP154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ154" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="BR154" t="inlineStr"/>
+      <c r="BS154" t="inlineStr"/>
+      <c r="BT154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU154" t="inlineStr"/>
+      <c r="BV154" t="inlineStr"/>
+      <c r="BW154" t="inlineStr"/>
+      <c r="BX154" t="inlineStr"/>
+      <c r="BY154" t="inlineStr"/>
+      <c r="BZ154" t="inlineStr"/>
+      <c r="CA154" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="CB154" t="inlineStr"/>
+      <c r="CC154" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1.0µm, PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD154" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE154" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF154" t="inlineStr">
+        <is>
+          <t>M2006C3MG, M2006C3MT</t>
+        </is>
+      </c>
+      <c r="CG154" t="inlineStr">
+        <is>
+          <t>0.73 W/kg (head)     0.52 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH154" t="inlineStr"/>
+      <c r="CI154" t="inlineStr"/>
+      <c r="CJ154" t="inlineStr"/>
+      <c r="CK154" t="inlineStr"/>
+      <c r="CL154" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM154" t="inlineStr"/>
+      <c r="CN154" t="inlineStr"/>
+      <c r="CO154" t="inlineStr"/>
+      <c r="CP154" t="inlineStr"/>
+      <c r="CQ154" t="inlineStr"/>
+      <c r="CR154" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS154" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT154" t="inlineStr"/>
+      <c r="CU154" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV154" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW154" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX154" t="inlineStr"/>
+      <c r="CY154" t="inlineStr"/>
+      <c r="CZ154" t="inlineStr"/>
+      <c r="DA154" t="inlineStr"/>
+      <c r="DB154" t="inlineStr"/>
+      <c r="DC154" t="inlineStr"/>
+      <c r="DD154" t="inlineStr"/>
+      <c r="DE154" t="inlineStr"/>
+      <c r="DF154" t="inlineStr"/>
+      <c r="DG154" t="inlineStr"/>
+      <c r="DH154" t="inlineStr"/>
+      <c r="DI154" t="inlineStr"/>
+      <c r="DJ154" t="inlineStr"/>
+      <c r="DK154" t="inlineStr"/>
+      <c r="DL154" t="inlineStr"/>
+      <c r="DM154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 9</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Not to be confused with Xiaomi Redmi 9 for Indian market</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_9-10233.php</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2020, June 10</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>163.3</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>128GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>3GB | 4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>5020</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Li-Po 5020 mAh</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>163.3 x 77 x 9.1 mm (6.43 x 3.03 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr"/>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>198 g (6.98 oz)</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr"/>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>Wireless FM radio (no wired headphones required)</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>6.53 inches, 104.7 cm 2 (~83.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr"/>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>2020, June 10</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 10</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD155" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM, 64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE155" t="inlineStr">
+        <is>
+          <t>Carbon Gray, Sunset Purple, Ocean Green, Pink/Blue</t>
+        </is>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr">
+        <is>
+          <t>0.71 W/kg (head)     1.06 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH155" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI155" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ155" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK155" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL155" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM155" t="inlineStr">
+        <is>
+          <t>Android 10, upgradable to Android 12, MIUI 13</t>
+        </is>
+      </c>
+      <c r="BN155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO155" t="inlineStr"/>
+      <c r="BP155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ155" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR155" t="inlineStr"/>
+      <c r="BS155" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 3), plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT155" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU155" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="BV155" t="inlineStr"/>
+      <c r="BW155" t="inlineStr"/>
+      <c r="BX155" t="inlineStr"/>
+      <c r="BY155" t="inlineStr"/>
+      <c r="BZ155" t="inlineStr"/>
+      <c r="CA155" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB155" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 28mm (wide), 1/3.1", 1.12µm, PDAF 8 MP, f/2.2, 118˚ (ultrawide), 1/4.0", 1.12µm 5 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC155" t="inlineStr"/>
+      <c r="CD155" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE155" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF155" t="inlineStr">
+        <is>
+          <t>M2004J19G, M2004J19C</t>
+        </is>
+      </c>
+      <c r="CG155" t="inlineStr">
+        <is>
+          <t>0.91 W/kg (head)     1.00 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH155" t="inlineStr"/>
+      <c r="CI155" t="inlineStr"/>
+      <c r="CJ155" t="inlineStr"/>
+      <c r="CK155" t="inlineStr"/>
+      <c r="CL155" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM155" t="inlineStr"/>
+      <c r="CN155" t="inlineStr"/>
+      <c r="CO155" t="inlineStr">
+        <is>
+          <t>1624:1 contrast ratio, 328 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP155" t="inlineStr">
+        <is>
+          <t>-26.9 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ155" t="inlineStr">
+        <is>
+          <t>AnTuTu: 201829 (v8) GeekBench: 1325 (v5.1)</t>
+        </is>
+      </c>
+      <c r="CR155" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769V/CU Helio G80 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS155" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT155" t="inlineStr"/>
+      <c r="CU155" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV155" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 27mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW155" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX155" t="inlineStr"/>
+      <c r="CY155" t="inlineStr"/>
+      <c r="CZ155" t="inlineStr"/>
+      <c r="DA155" t="inlineStr"/>
+      <c r="DB155" t="inlineStr"/>
+      <c r="DC155" t="inlineStr"/>
+      <c r="DD155" t="inlineStr"/>
+      <c r="DE155" t="inlineStr"/>
+      <c r="DF155" t="inlineStr"/>
+      <c r="DG155" t="inlineStr"/>
+      <c r="DH155" t="inlineStr"/>
+      <c r="DI155" t="inlineStr"/>
+      <c r="DJ155" t="inlineStr"/>
+      <c r="DK155" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL155" t="inlineStr"/>
+      <c r="DM155" t="inlineStr">
+        <is>
+          <t>Endurance rating 131h</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 10X Pro 5G</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_10x_pro_5g-10267.php</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 06</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>164.2</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>About 290 EUR</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Li-Po 4520 mAh</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>164.2 x 75.8 x 9 mm (6.46 x 2.98 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr"/>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>208 g (7.34 oz)</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr"/>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>FM radio; built-in antenna</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~401 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>6.57 inches, 104.2 cm 2 (~83.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>AMOLED, HDR10+, 600 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr"/>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 06</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD156" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE156" t="inlineStr">
+        <is>
+          <t>Blue, Gold, Pink/Blue</t>
+        </is>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>About 290 EUR</t>
+        </is>
+      </c>
+      <c r="BG156" t="inlineStr"/>
+      <c r="BH156" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI156" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ156" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK156" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL156" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.6 GHz Cortex-A76 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM156" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 11</t>
+        </is>
+      </c>
+      <c r="BN156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO156" t="inlineStr"/>
+      <c r="BP156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ156" t="inlineStr">
+        <is>
+          <t>33W wired, 58% in 30 min</t>
+        </is>
+      </c>
+      <c r="BR156" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS156" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5)</t>
+        </is>
+      </c>
+      <c r="BT156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU156" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV156" t="inlineStr"/>
+      <c r="BW156" t="inlineStr"/>
+      <c r="BX156" t="inlineStr"/>
+      <c r="BY156" t="inlineStr"/>
+      <c r="BZ156" t="inlineStr"/>
+      <c r="CA156" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB156" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF 8 MP, (telephoto), PDAF, OIS, 3x optical zoom 8 MP, f/2.2, 119˚ (ultrawide), 1/4.0", 1.12µm 5 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CC156" t="inlineStr"/>
+      <c r="CD156" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps, 720p@960fps</t>
+        </is>
+      </c>
+      <c r="CE156" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF156" t="inlineStr">
+        <is>
+          <t>M2004J7BC</t>
+        </is>
+      </c>
+      <c r="CG156" t="inlineStr"/>
+      <c r="CH156" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI156" t="inlineStr"/>
+      <c r="CJ156" t="inlineStr"/>
+      <c r="CK156" t="inlineStr"/>
+      <c r="CL156" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM156" t="inlineStr">
+        <is>
+          <t>1, 3, 41, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN156" t="inlineStr"/>
+      <c r="CO156" t="inlineStr"/>
+      <c r="CP156" t="inlineStr"/>
+      <c r="CQ156" t="inlineStr"/>
+      <c r="CR156" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 820 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS156" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC5</t>
+        </is>
+      </c>
+      <c r="CT156" t="inlineStr"/>
+      <c r="CU156" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV156" t="inlineStr">
+        <is>
+          <t>20 MP, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW156" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX156" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY156" t="inlineStr"/>
+      <c r="CZ156" t="inlineStr"/>
+      <c r="DA156" t="inlineStr"/>
+      <c r="DB156" t="inlineStr"/>
+      <c r="DC156" t="inlineStr"/>
+      <c r="DD156" t="inlineStr"/>
+      <c r="DE156" t="inlineStr"/>
+      <c r="DF156" t="inlineStr"/>
+      <c r="DG156" t="inlineStr"/>
+      <c r="DH156" t="inlineStr"/>
+      <c r="DI156" t="inlineStr"/>
+      <c r="DJ156" t="inlineStr"/>
+      <c r="DK156" t="inlineStr"/>
+      <c r="DL156" t="inlineStr"/>
+      <c r="DM156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 10X 5G</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Also available with 4G/LTE only</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_10x_5g-10266.php</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 01</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>164.2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Li-Po 4520 mAh</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>164.2 x 75.8 x 9 mm (6.46 x 2.98 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr"/>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>205 g (7.23 oz)</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr"/>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>FM radio; built-in antenna</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~401 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>6.57 inches, 104.2 cm 2 (~83.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>AMOLED, HDR10+, 600 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr"/>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, June 01</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD157" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE157" t="inlineStr">
+        <is>
+          <t>Blue, Gold, Pink/Blue</t>
+        </is>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI157" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ157" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK157" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL157" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.6 GHz Cortex-A76 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM157" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 11</t>
+        </is>
+      </c>
+      <c r="BN157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO157" t="inlineStr"/>
+      <c r="BP157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ157" t="inlineStr">
+        <is>
+          <t>22.5W wired</t>
+        </is>
+      </c>
+      <c r="BR157" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS157" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5)</t>
+        </is>
+      </c>
+      <c r="BT157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU157" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV157" t="inlineStr"/>
+      <c r="BW157" t="inlineStr"/>
+      <c r="BX157" t="inlineStr"/>
+      <c r="BY157" t="inlineStr"/>
+      <c r="BZ157" t="inlineStr"/>
+      <c r="CA157" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB157" t="inlineStr"/>
+      <c r="CC157" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF 8 MP, f/2.2, 119˚ (ultrawide), 1/4.0", 1.12µm Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD157" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps, 720p@960fps</t>
+        </is>
+      </c>
+      <c r="CE157" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF157" t="inlineStr"/>
+      <c r="CG157" t="inlineStr"/>
+      <c r="CH157" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI157" t="inlineStr"/>
+      <c r="CJ157" t="inlineStr"/>
+      <c r="CK157" t="inlineStr"/>
+      <c r="CL157" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM157" t="inlineStr">
+        <is>
+          <t>1, 3, 41, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN157" t="inlineStr"/>
+      <c r="CO157" t="inlineStr"/>
+      <c r="CP157" t="inlineStr"/>
+      <c r="CQ157" t="inlineStr"/>
+      <c r="CR157" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 820 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS157" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC5</t>
+        </is>
+      </c>
+      <c r="CT157" t="inlineStr"/>
+      <c r="CU157" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV157" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.3, (wide), 1/3.06", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW157" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX157" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY157" t="inlineStr"/>
+      <c r="CZ157" t="inlineStr"/>
+      <c r="DA157" t="inlineStr"/>
+      <c r="DB157" t="inlineStr"/>
+      <c r="DC157" t="inlineStr"/>
+      <c r="DD157" t="inlineStr"/>
+      <c r="DE157" t="inlineStr"/>
+      <c r="DF157" t="inlineStr"/>
+      <c r="DG157" t="inlineStr"/>
+      <c r="DH157" t="inlineStr"/>
+      <c r="DI157" t="inlineStr"/>
+      <c r="DJ157" t="inlineStr"/>
+      <c r="DK157" t="inlineStr"/>
+      <c r="DL157" t="inlineStr"/>
+      <c r="DM157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 10X 4G</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Also available with 5G</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_10x_4g-10202.php</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, May 26</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>162.3</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>5020</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Li-Po 5020 mAh</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>162.3 x 77.2 x 8.9 mm (6.39 x 3.04 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>199 g (7.02 oz)</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr"/>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>FM radio; built-in antenna</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>6.53 inches, 104.7 cm 2 (~83.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>IPS LCD, 450 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr"/>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>2020, May 26</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, May 26</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD158" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE158" t="inlineStr">
+        <is>
+          <t>Blue, Green, White</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI158" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ158" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK158" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL158" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM158" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 11</t>
+        </is>
+      </c>
+      <c r="BN158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO158" t="inlineStr"/>
+      <c r="BP158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ158" t="inlineStr">
+        <is>
+          <t>18W wired, QC3 9W reverse wired</t>
+        </is>
+      </c>
+      <c r="BR158" t="inlineStr">
+        <is>
+          <t>Water-repellent coating</t>
+        </is>
+      </c>
+      <c r="BS158" t="inlineStr"/>
+      <c r="BT158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU158" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV158" t="inlineStr"/>
+      <c r="BW158" t="inlineStr"/>
+      <c r="BX158" t="inlineStr"/>
+      <c r="BY158" t="inlineStr"/>
+      <c r="BZ158" t="inlineStr"/>
+      <c r="CA158" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB158" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF 8 MP, f/2.2, 118˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC158" t="inlineStr"/>
+      <c r="CD158" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE158" t="inlineStr"/>
+      <c r="CF158" t="inlineStr">
+        <is>
+          <t>M2003J15SC</t>
+        </is>
+      </c>
+      <c r="CG158" t="inlineStr"/>
+      <c r="CH158" t="inlineStr">
+        <is>
+          <t>CDMA 800 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI158" t="inlineStr"/>
+      <c r="CJ158" t="inlineStr"/>
+      <c r="CK158" t="inlineStr"/>
+      <c r="CL158" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM158" t="inlineStr"/>
+      <c r="CN158" t="inlineStr"/>
+      <c r="CO158" t="inlineStr"/>
+      <c r="CP158" t="inlineStr"/>
+      <c r="CQ158" t="inlineStr"/>
+      <c r="CR158" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769Z Helio G85 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS158" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT158" t="inlineStr"/>
+      <c r="CU158" t="inlineStr">
+        <is>
+          <t>Panorama</t>
+        </is>
+      </c>
+      <c r="CV158" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.3, (wide), 1/3.1", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW158" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX158" t="inlineStr"/>
+      <c r="CY158" t="inlineStr"/>
+      <c r="CZ158" t="inlineStr"/>
+      <c r="DA158" t="inlineStr"/>
+      <c r="DB158" t="inlineStr"/>
+      <c r="DC158" t="inlineStr"/>
+      <c r="DD158" t="inlineStr"/>
+      <c r="DE158" t="inlineStr"/>
+      <c r="DF158" t="inlineStr"/>
+      <c r="DG158" t="inlineStr"/>
+      <c r="DH158" t="inlineStr"/>
+      <c r="DI158" t="inlineStr"/>
+      <c r="DJ158" t="inlineStr"/>
+      <c r="DK158" t="inlineStr"/>
+      <c r="DL158" t="inlineStr"/>
+      <c r="DM158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi K30i 5G</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_k30i_5g-10200.php</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2020, May 25. Released 2020, June 07</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>165.3</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Li-Po 4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>165.3 x 76.6 x 8.8 mm (6.51 x 3.02 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>208 g (7.34 oz)</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr"/>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS (G1), BDS (B1I+B2a), GALILEO (E1+E5a), QZSS (L1+L5)</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~84.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>IPS LCD, 120Hz, HDR10</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr"/>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>2020, May 25. Released 2020, June 07</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>Blue, White, Red, Purple</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="BG159" t="inlineStr"/>
+      <c r="BH159" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI159" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ159" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G (2+ Gbps DL)</t>
+        </is>
+      </c>
+      <c r="BK159" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL159" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.4 GHz Kryo 475 Prime &amp; 1x2.2 GHz Kryo 475 Gold &amp; 6x1.8 GHz Kryo 475 Silver)</t>
+        </is>
+      </c>
+      <c r="BM159" t="inlineStr">
+        <is>
+          <t>Android 10, MIUI 11</t>
+        </is>
+      </c>
+      <c r="BN159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO159" t="inlineStr"/>
+      <c r="BP159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ159" t="inlineStr">
+        <is>
+          <t>30W wired</t>
+        </is>
+      </c>
+      <c r="BR159" t="inlineStr"/>
+      <c r="BS159" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU159" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV159" t="inlineStr"/>
+      <c r="BW159" t="inlineStr"/>
+      <c r="BX159" t="inlineStr"/>
+      <c r="BY159" t="inlineStr"/>
+      <c r="BZ159" t="inlineStr"/>
+      <c r="CA159" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB159" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.9, (wide), 1/2.0", 0.8µm, PDAF 8 MP, f/2.2, 120˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC159" t="inlineStr"/>
+      <c r="CD159" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE159" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF159" t="inlineStr"/>
+      <c r="CG159" t="inlineStr"/>
+      <c r="CH159" t="inlineStr"/>
+      <c r="CI159" t="inlineStr"/>
+      <c r="CJ159" t="inlineStr"/>
+      <c r="CK159" t="inlineStr"/>
+      <c r="CL159" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM159" t="inlineStr">
+        <is>
+          <t>41, 78 Sub6</t>
+        </is>
+      </c>
+      <c r="CN159" t="inlineStr"/>
+      <c r="CO159" t="inlineStr"/>
+      <c r="CP159" t="inlineStr"/>
+      <c r="CQ159" t="inlineStr"/>
+      <c r="CR159" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7250 Snapdragon 765G 5G (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS159" t="inlineStr">
+        <is>
+          <t>Adreno 620</t>
+        </is>
+      </c>
+      <c r="CT159" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.2, 27mm (wide), 1/3.4", 0.8µm 2 MP, f/2.4, 1/5.0", 1.75µm, depth sensor</t>
+        </is>
+      </c>
+      <c r="CU159" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV159" t="inlineStr"/>
+      <c r="CW159" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX159" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY159" t="inlineStr"/>
+      <c r="CZ159" t="inlineStr"/>
+      <c r="DA159" t="inlineStr"/>
+      <c r="DB159" t="inlineStr"/>
+      <c r="DC159" t="inlineStr"/>
+      <c r="DD159" t="inlineStr"/>
+      <c r="DE159" t="inlineStr"/>
+      <c r="DF159" t="inlineStr"/>
+      <c r="DG159" t="inlineStr"/>
+      <c r="DH159" t="inlineStr"/>
+      <c r="DI159" t="inlineStr"/>
+      <c r="DJ159" t="inlineStr"/>
+      <c r="DK159" t="inlineStr"/>
+      <c r="DL159" t="inlineStr"/>
+      <c r="DM159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Xiaomi Poco F2 Pro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_poco_f2_pro-10220.php</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2020, May 12</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, May 19</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>163.3</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Li-Po 4700 mAh</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>163.3 x 75.4 x 8.9 mm (6.43 x 2.97 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>219 g (7.72 oz)</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE, aptX HD, aptX Adaptive</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS (G1), BDS (B1), GALILEO (E1+E5a), QZSS (L1+L5)</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~87.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Super AMOLED, HDR10+, 500 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>2020, May 12</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>Available. Released 2020, May 19</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 6GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE160" t="inlineStr">
+        <is>
+          <t>Neon Blue, Phantom White, Electric Purple, Cyber Gray</t>
+        </is>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>0.79 W/kg (head)     1.03 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="BH160" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI160" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - International</t>
+        </is>
+      </c>
+      <c r="BJ160" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK160" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL160" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Cortex-A77 &amp; 3x2.42 GHz Cortex-A77 &amp; 4x1.80 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM160" t="inlineStr">
+        <is>
+          <t>Android 10, upgradable to Android 12, MIUI 14</t>
+        </is>
+      </c>
+      <c r="BN160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO160" t="inlineStr"/>
+      <c r="BP160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ160" t="inlineStr">
+        <is>
+          <t>30W wired, PD3.0, QC4, 100% in 63 min</t>
+        </is>
+      </c>
+      <c r="BR160" t="inlineStr"/>
+      <c r="BS160" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5), aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU160" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV160" t="inlineStr"/>
+      <c r="BW160" t="inlineStr"/>
+      <c r="BX160" t="inlineStr"/>
+      <c r="BY160" t="inlineStr"/>
+      <c r="BZ160" t="inlineStr"/>
+      <c r="CA160" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB160" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.9, 26mm (wide), 1/1.72", 0.8µm, PDAF 5 MP, f/2.2, 50mm (telephoto macro), AF 13 MP, f/2.4, 123˚ (ultrawide), 1.12µm Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC160" t="inlineStr"/>
+      <c r="CD160" t="inlineStr">
+        <is>
+          <t>8K@24/30fps, 4K@30/60fps, 1080p@30/60/120/240fps, 1080p@960fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE160" t="inlineStr">
+        <is>
+          <t>UFS 3.1 6GB RAM (LPDDR4X) 8GB RAM (LPDDR5)</t>
+        </is>
+      </c>
+      <c r="CF160" t="inlineStr">
+        <is>
+          <t>M2004J11G</t>
+        </is>
+      </c>
+      <c r="CG160" t="inlineStr">
+        <is>
+          <t>1.09 W/kg (head)     0.51 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH160" t="inlineStr"/>
+      <c r="CI160" t="inlineStr"/>
+      <c r="CJ160" t="inlineStr"/>
+      <c r="CK160" t="inlineStr"/>
+      <c r="CL160" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41 - International</t>
+        </is>
+      </c>
+      <c r="CM160" t="inlineStr">
+        <is>
+          <t>77, 78 Sub6</t>
+        </is>
+      </c>
+      <c r="CN160" t="inlineStr"/>
+      <c r="CO160" t="inlineStr">
+        <is>
+          <t>854 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP160" t="inlineStr">
+        <is>
+          <t>-25.6 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ160" t="inlineStr">
+        <is>
+          <t>AnTuTu: 538221 (v8) GeekBench: 3332 (v5.1) GFXBench: 40fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR160" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8250 Snapdragon 865 5G (7 nm+)</t>
+        </is>
+      </c>
+      <c r="CS160" t="inlineStr">
+        <is>
+          <t>Adreno 650</t>
+        </is>
+      </c>
+      <c r="CT160" t="inlineStr"/>
+      <c r="CU160" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV160" t="inlineStr">
+        <is>
+          <t>Motorized pop-up 20 MP, f/2.2, (wide), 1/3.4", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CW160" t="inlineStr">
+        <is>
+          <t>1080p@30fps, 720p@120fps</t>
+        </is>
+      </c>
+      <c r="CX160" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY160" t="inlineStr"/>
+      <c r="CZ160" t="inlineStr"/>
+      <c r="DA160" t="inlineStr"/>
+      <c r="DB160" t="inlineStr"/>
+      <c r="DC160" t="inlineStr"/>
+      <c r="DD160" t="inlineStr"/>
+      <c r="DE160" t="inlineStr"/>
+      <c r="DF160" t="inlineStr"/>
+      <c r="DG160" t="inlineStr"/>
+      <c r="DH160" t="inlineStr"/>
+      <c r="DI160" t="inlineStr"/>
+      <c r="DJ160" t="inlineStr"/>
+      <c r="DK160" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL160" t="inlineStr"/>
+      <c r="DM160" t="inlineStr">
+        <is>
+          <t>Endurance rating 120h</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Redmi K30 5G Racing</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/xiaomi_redmi_k30_5g_racing-10235.php</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="inlineStr"/>
+      <c r="AK161" t="inlineStr"/>
+      <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
+      <c r="AN161" t="inlineStr"/>
+      <c r="AO161" t="inlineStr"/>
+      <c r="AP161" t="inlineStr"/>
+      <c r="AQ161" t="inlineStr"/>
+      <c r="AR161" t="inlineStr"/>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AU161" t="inlineStr"/>
+      <c r="AV161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr"/>
+      <c r="AX161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr"/>
+      <c r="BA161" t="inlineStr"/>
+      <c r="BB161" t="inlineStr"/>
+      <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr"/>
+      <c r="BH161" t="inlineStr"/>
+      <c r="BI161" t="inlineStr"/>
+      <c r="BJ161" t="inlineStr"/>
+      <c r="BK161" t="inlineStr"/>
+      <c r="BL161" t="inlineStr"/>
+      <c r="BM161" t="inlineStr"/>
+      <c r="BN161" t="inlineStr"/>
+      <c r="BO161" t="inlineStr"/>
+      <c r="BP161" t="inlineStr"/>
+      <c r="BQ161" t="inlineStr"/>
+      <c r="BR161" t="inlineStr"/>
+      <c r="BS161" t="inlineStr"/>
+      <c r="BT161" t="inlineStr"/>
+      <c r="BU161" t="inlineStr"/>
+      <c r="BV161" t="inlineStr"/>
+      <c r="BW161" t="inlineStr"/>
+      <c r="BX161" t="inlineStr"/>
+      <c r="BY161" t="inlineStr"/>
+      <c r="BZ161" t="inlineStr"/>
+      <c r="CA161" t="inlineStr"/>
+      <c r="CB161" t="inlineStr"/>
+      <c r="CC161" t="inlineStr"/>
+      <c r="CD161" t="inlineStr"/>
+      <c r="CE161" t="inlineStr"/>
+      <c r="CF161" t="inlineStr"/>
+      <c r="CG161" t="inlineStr"/>
+      <c r="CH161" t="inlineStr"/>
+      <c r="CI161" t="inlineStr"/>
+      <c r="CJ161" t="inlineStr"/>
+      <c r="CK161" t="inlineStr"/>
+      <c r="CL161" t="inlineStr"/>
+      <c r="CM161" t="inlineStr"/>
+      <c r="CN161" t="inlineStr"/>
+      <c r="CO161" t="inlineStr"/>
+      <c r="CP161" t="inlineStr"/>
+      <c r="CQ161" t="inlineStr"/>
+      <c r="CR161" t="inlineStr"/>
+      <c r="CS161" t="inlineStr"/>
+      <c r="CT161" t="inlineStr"/>
+      <c r="CU161" t="inlineStr"/>
+      <c r="CV161" t="inlineStr"/>
+      <c r="CW161" t="inlineStr"/>
+      <c r="CX161" t="inlineStr"/>
+      <c r="CY161" t="inlineStr"/>
+      <c r="CZ161" t="inlineStr"/>
+      <c r="DA161" t="inlineStr"/>
+      <c r="DB161" t="inlineStr"/>
+      <c r="DC161" t="inlineStr"/>
+      <c r="DD161" t="inlineStr"/>
+      <c r="DE161" t="inlineStr"/>
+      <c r="DF161" t="inlineStr"/>
+      <c r="DG161" t="inlineStr"/>
+      <c r="DH161" t="inlineStr"/>
+      <c r="DI161" t="inlineStr"/>
+      <c r="DJ161" t="inlineStr"/>
+      <c r="DK161" t="inlineStr"/>
+      <c r="DL161" t="inlineStr"/>
+      <c r="DM161" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM183"/>
+  <dimension ref="A1:DM205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56075,55 +56075,37 @@
           <t>2022, January 04</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="H162" t="n">
+        <v>2022</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
           <t>Available. Released 2022, January 08</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>162.9</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>199.8</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>6.62</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
+      <c r="J162" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="K162" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L162" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M162" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="N162" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P162" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>398</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
@@ -56135,20 +56117,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T162" t="n">
+        <v>50</v>
+      </c>
+      <c r="U162" t="n">
+        <v>16</v>
+      </c>
+      <c r="V162" t="n">
+        <v>5000</v>
       </c>
       <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr"/>
@@ -56494,10 +56470,8 @@
           <t>2021, November 10</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H163" t="n">
+        <v>2021</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -56508,25 +56482,17 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="N163" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P163" t="n">
+        <v>2412</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>400</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
@@ -56538,20 +56504,14 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T163" t="n">
+        <v>48</v>
+      </c>
+      <c r="U163" t="n">
+        <v>16</v>
+      </c>
+      <c r="V163" t="n">
+        <v>5000</v>
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr"/>
@@ -56853,55 +56813,37 @@
           <t>2021, October 19</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H164" t="n">
+        <v>2021</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>Available. Released 2021, November 01</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J164" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K164" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L164" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M164" t="n">
+        <v>186</v>
+      </c>
+      <c r="N164" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P164" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>409</v>
       </c>
       <c r="R164" t="inlineStr">
         <is>
@@ -56913,20 +56855,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T164" t="n">
+        <v>64</v>
+      </c>
+      <c r="U164" t="n">
+        <v>16</v>
+      </c>
+      <c r="V164" t="n">
+        <v>4500</v>
       </c>
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr"/>
@@ -57240,55 +57176,37 @@
           <t>2021, October 19</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H165" t="n">
+        <v>2021</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
           <t>Available. Released 2021, November 01</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
+      <c r="J165" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="K165" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L165" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M165" t="n">
+        <v>199</v>
+      </c>
+      <c r="N165" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P165" t="n">
+        <v>2412</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>401</v>
       </c>
       <c r="R165" t="inlineStr">
         <is>
@@ -57300,20 +57218,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T165" t="n">
+        <v>48</v>
+      </c>
+      <c r="U165" t="n">
+        <v>16</v>
+      </c>
+      <c r="V165" t="n">
+        <v>5000</v>
       </c>
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr"/>
@@ -57615,60 +57527,42 @@
           <t>2021, October 19</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H166" t="n">
+        <v>2021</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>Available. Released 2021, November 01</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
+      <c r="J166" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K166" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L166" t="n">
+        <v>10.2</v>
       </c>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
+      <c r="N166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O166" t="n">
+        <v>416</v>
+      </c>
+      <c r="P166" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>453</v>
       </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="V166" t="n">
+        <v>228</v>
       </c>
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr"/>
@@ -57787,16 +57681,8 @@
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
-      <c r="BH166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="BI166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH166" t="inlineStr"/>
+      <c r="BI166" t="inlineStr"/>
       <c r="BJ166" t="inlineStr">
         <is>
           <t>No</t>
@@ -57857,11 +57743,7 @@
       <c r="CI166" t="inlineStr"/>
       <c r="CJ166" t="inlineStr"/>
       <c r="CK166" t="inlineStr"/>
-      <c r="CL166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CL166" t="inlineStr"/>
       <c r="CM166" t="inlineStr"/>
       <c r="CN166" t="inlineStr"/>
       <c r="CO166" t="inlineStr"/>
@@ -57930,55 +57812,37 @@
           <t>2021, September 24</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H167" t="n">
+        <v>2021</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
           <t>Available. Released 2021, October 07</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J167" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K167" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L167" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M167" t="n">
+        <v>207</v>
+      </c>
+      <c r="N167" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O167" t="n">
+        <v>720</v>
+      </c>
+      <c r="P167" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>270</v>
       </c>
       <c r="R167" t="inlineStr">
         <is>
@@ -57990,20 +57854,14 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T167" t="n">
+        <v>50</v>
+      </c>
+      <c r="U167" t="n">
+        <v>8</v>
+      </c>
+      <c r="V167" t="n">
+        <v>6000</v>
       </c>
       <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr"/>
@@ -58293,55 +58151,37 @@
           <t>2021, September 24</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H168" t="n">
+        <v>2021</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
           <t>Available. Released 2021, October 07</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>165.2</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J168" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="K168" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L168" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M168" t="n">
+        <v>195</v>
+      </c>
+      <c r="N168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O168" t="n">
+        <v>720</v>
+      </c>
+      <c r="P168" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>270</v>
       </c>
       <c r="R168" t="inlineStr">
         <is>
@@ -58353,20 +58193,14 @@
           <t>2GB | 4GB</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T168" t="n">
+        <v>8</v>
+      </c>
+      <c r="U168" t="n">
+        <v>5</v>
+      </c>
+      <c r="V168" t="n">
+        <v>5000</v>
       </c>
       <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr"/>
@@ -58656,10 +58490,8 @@
           <t>2021, September 24</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H169" t="n">
+        <v>2021</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -58669,30 +58501,20 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="M169" t="n">
+        <v>189</v>
+      </c>
+      <c r="N169" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O169" t="n">
+        <v>720</v>
+      </c>
+      <c r="P169" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>270</v>
       </c>
       <c r="R169" t="inlineStr">
         <is>
@@ -58704,20 +58526,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T169" t="n">
+        <v>13</v>
+      </c>
+      <c r="U169" t="n">
+        <v>8</v>
+      </c>
+      <c r="V169" t="n">
+        <v>5000</v>
       </c>
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr"/>
@@ -59019,55 +58835,37 @@
           <t>2021, September 22</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H170" t="n">
+        <v>2021</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
           <t>Available. Released 2021, September 28</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>162.9</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>199.8</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>6.62</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
+      <c r="J170" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="K170" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L170" t="n">
+        <v>9</v>
+      </c>
+      <c r="M170" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="N170" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P170" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>398</v>
       </c>
       <c r="R170" t="inlineStr">
         <is>
@@ -59079,20 +58877,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T170" t="n">
+        <v>64</v>
+      </c>
+      <c r="U170" t="n">
+        <v>16</v>
+      </c>
+      <c r="V170" t="n">
+        <v>5000</v>
       </c>
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr"/>
@@ -59430,55 +59222,37 @@
           <t>2021, September 16</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H171" t="n">
+        <v>2021</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>Available. Released 2021, September 30</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J171" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K171" t="n">
+        <v>76</v>
+      </c>
+      <c r="L171" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>200</v>
+      </c>
+      <c r="N171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O171" t="n">
+        <v>720</v>
+      </c>
+      <c r="P171" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>270</v>
       </c>
       <c r="R171" t="inlineStr">
         <is>
@@ -59490,20 +59264,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T171" t="n">
+        <v>50</v>
+      </c>
+      <c r="U171" t="n">
+        <v>8</v>
+      </c>
+      <c r="V171" t="n">
+        <v>5000</v>
       </c>
       <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr"/>
@@ -59801,55 +59569,37 @@
           <t>2021, September 09</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H172" t="n">
+        <v>2021</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
           <t>Available. Released 2021, September 13</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J172" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K172" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L172" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M172" t="n">
+        <v>191</v>
+      </c>
+      <c r="N172" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O172" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P172" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>405</v>
       </c>
       <c r="R172" t="inlineStr">
         <is>
@@ -59861,20 +59611,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T172" t="n">
+        <v>64</v>
+      </c>
+      <c r="U172" t="n">
+        <v>16</v>
+      </c>
+      <c r="V172" t="n">
+        <v>5000</v>
       </c>
       <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr"/>
@@ -60192,55 +59936,37 @@
           <t>2021, September 09</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H173" t="n">
+        <v>2021</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
           <t>Available. Released 2021, September 14</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>164.1</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="J173" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M173" t="n">
+        <v>194</v>
+      </c>
+      <c r="N173" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P173" t="n">
+        <v>2412</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>400</v>
       </c>
       <c r="R173" t="inlineStr">
         <is>
@@ -60252,20 +59978,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T173" t="n">
+        <v>50</v>
+      </c>
+      <c r="U173" t="n">
+        <v>16</v>
+      </c>
+      <c r="V173" t="n">
+        <v>5000</v>
       </c>
       <c r="W173" t="inlineStr"/>
       <c r="X173" t="inlineStr"/>
@@ -60583,55 +60303,37 @@
           <t>2021, September 09</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H174" t="n">
+        <v>2021</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
           <t>Available. Released 2021, September 16</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>246.1</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>155.9</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="J174" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="L174" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M174" t="n">
+        <v>440</v>
+      </c>
+      <c r="N174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P174" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>224</v>
       </c>
       <c r="R174" t="inlineStr">
         <is>
@@ -60643,20 +60345,14 @@
           <t>3GB | 4GB | 6GB</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>7100</t>
-        </is>
+      <c r="T174" t="n">
+        <v>8</v>
+      </c>
+      <c r="U174" t="n">
+        <v>8</v>
+      </c>
+      <c r="V174" t="n">
+        <v>7100</v>
       </c>
       <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr"/>
@@ -60962,10 +60658,8 @@
           <t>2021, July 21</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H175" t="n">
+        <v>2021</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -60975,30 +60669,20 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
+      <c r="M175" t="n">
+        <v>185</v>
+      </c>
+      <c r="N175" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P175" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>402</v>
       </c>
       <c r="R175" t="inlineStr">
         <is>
@@ -61010,20 +60694,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T175" t="n">
+        <v>50</v>
+      </c>
+      <c r="U175" t="n">
+        <v>32</v>
+      </c>
+      <c r="V175" t="n">
+        <v>4500</v>
       </c>
       <c r="W175" t="inlineStr"/>
       <c r="X175" t="inlineStr"/>
@@ -61365,10 +61043,8 @@
           <t>2021, July 21</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H176" t="n">
+        <v>2021</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -61378,30 +61054,20 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="M176" t="n">
+        <v>180</v>
+      </c>
+      <c r="N176" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O176" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P176" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>409</v>
       </c>
       <c r="R176" t="inlineStr">
         <is>
@@ -61413,20 +61079,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>4300</t>
-        </is>
+      <c r="T176" t="n">
+        <v>64</v>
+      </c>
+      <c r="U176" t="n">
+        <v>32</v>
+      </c>
+      <c r="V176" t="n">
+        <v>4300</v>
       </c>
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr"/>
@@ -61768,55 +61428,37 @@
           <t>2021, June 21</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H177" t="n">
+        <v>2021</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
           <t>Available. Released 2021, July 02</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J177" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K177" t="n">
+        <v>76</v>
+      </c>
+      <c r="L177" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>200</v>
+      </c>
+      <c r="N177" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O177" t="n">
+        <v>720</v>
+      </c>
+      <c r="P177" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>270</v>
       </c>
       <c r="R177" t="inlineStr">
         <is>
@@ -61828,20 +61470,14 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T177" t="n">
+        <v>13</v>
+      </c>
+      <c r="U177" t="n">
+        <v>5</v>
+      </c>
+      <c r="V177" t="n">
+        <v>5000</v>
       </c>
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr"/>
@@ -62139,55 +61775,37 @@
           <t>2021, June 28</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H178" t="n">
+        <v>2021</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>Available. Released 2021, June 28</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>165.2</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J178" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="K178" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L178" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M178" t="n">
+        <v>190</v>
+      </c>
+      <c r="N178" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="O178" t="n">
+        <v>720</v>
+      </c>
+      <c r="P178" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>269</v>
       </c>
       <c r="R178" t="inlineStr">
         <is>
@@ -62199,20 +61817,14 @@
           <t>2GB | 4GB</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T178" t="n">
+        <v>8</v>
+      </c>
+      <c r="U178" t="n">
+        <v>5</v>
+      </c>
+      <c r="V178" t="n">
+        <v>5000</v>
       </c>
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr"/>
@@ -62514,55 +62126,37 @@
           <t>2021, June 08</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H179" t="n">
+        <v>2021</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>Available. Released 2021, June 09</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J179" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K179" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L179" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M179" t="n">
+        <v>209</v>
+      </c>
+      <c r="N179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O179" t="n">
+        <v>720</v>
+      </c>
+      <c r="P179" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>270</v>
       </c>
       <c r="R179" t="inlineStr">
         <is>
@@ -62574,20 +62168,14 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T179" t="n">
+        <v>48</v>
+      </c>
+      <c r="U179" t="n">
+        <v>8</v>
+      </c>
+      <c r="V179" t="n">
+        <v>6000</v>
       </c>
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr"/>
@@ -62885,55 +62473,37 @@
           <t>2021, May 31</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H180" t="n">
+        <v>2021</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
           <t>Available. Released 2021, June 04</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J180" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K180" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L180" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M180" t="n">
+        <v>179</v>
+      </c>
+      <c r="N180" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O180" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P180" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>409</v>
       </c>
       <c r="R180" t="inlineStr">
         <is>
@@ -62945,20 +62515,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T180" t="n">
+        <v>64</v>
+      </c>
+      <c r="U180" t="n">
+        <v>16</v>
+      </c>
+      <c r="V180" t="n">
+        <v>4500</v>
       </c>
       <c r="W180" t="inlineStr"/>
       <c r="X180" t="inlineStr"/>
@@ -63288,55 +62852,37 @@
           <t>2021, May 26</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H181" t="n">
+        <v>2021</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>Available. Released 2021, June 11</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J181" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K181" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M181" t="n">
+        <v>185</v>
+      </c>
+      <c r="N181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P181" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>405</v>
       </c>
       <c r="R181" t="inlineStr">
         <is>
@@ -63348,20 +62894,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T181" t="n">
+        <v>48</v>
+      </c>
+      <c r="U181" t="n">
+        <v>16</v>
+      </c>
+      <c r="V181" t="n">
+        <v>5000</v>
       </c>
       <c r="W181" t="inlineStr"/>
       <c r="X181" t="inlineStr"/>
@@ -63909,6 +63449,7440 @@
       <c r="DL183" t="inlineStr"/>
       <c r="DM183" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Telit</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Telit GM 410</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/telit_gm_410-185.php</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>96 h</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>4 h</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 600 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>130 x 48 x 15 mm (5.12 x 1.89 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr"/>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>115 g (4.06 oz)</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr"/>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>Dynamic font size Fixed icons Softkeys</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>5 lines</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Monochrome graphic</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr"/>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr">
+        <is>
+          <t>GSM 900</t>
+        </is>
+      </c>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL184" t="inlineStr"/>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO184" t="inlineStr">
+        <is>
+          <t>Monophonic ringtones</t>
+        </is>
+      </c>
+      <c r="BP184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ184" t="inlineStr"/>
+      <c r="BR184" t="inlineStr"/>
+      <c r="BS184" t="inlineStr"/>
+      <c r="BT184" t="inlineStr"/>
+      <c r="BU184" t="inlineStr"/>
+      <c r="BV184" t="inlineStr"/>
+      <c r="BW184" t="inlineStr"/>
+      <c r="BX184" t="inlineStr"/>
+      <c r="BY184" t="inlineStr"/>
+      <c r="BZ184" t="inlineStr"/>
+      <c r="CA184" t="inlineStr"/>
+      <c r="CB184" t="inlineStr"/>
+      <c r="CC184" t="inlineStr"/>
+      <c r="CD184" t="inlineStr"/>
+      <c r="CE184" t="inlineStr">
+        <is>
+          <t>5 phonebook groups</t>
+        </is>
+      </c>
+      <c r="CF184" t="inlineStr"/>
+      <c r="CG184" t="inlineStr"/>
+      <c r="CH184" t="inlineStr"/>
+      <c r="CI184" t="inlineStr"/>
+      <c r="CJ184" t="inlineStr"/>
+      <c r="CK184" t="inlineStr"/>
+      <c r="CL184" t="inlineStr"/>
+      <c r="CM184" t="inlineStr"/>
+      <c r="CN184" t="inlineStr"/>
+      <c r="CO184" t="inlineStr"/>
+      <c r="CP184" t="inlineStr"/>
+      <c r="CQ184" t="inlineStr"/>
+      <c r="CR184" t="inlineStr"/>
+      <c r="CS184" t="inlineStr"/>
+      <c r="CT184" t="inlineStr"/>
+      <c r="CU184" t="inlineStr"/>
+      <c r="CV184" t="inlineStr"/>
+      <c r="CW184" t="inlineStr"/>
+      <c r="CX184" t="inlineStr"/>
+      <c r="CY184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CZ184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DA184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC184" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="DD184" t="inlineStr"/>
+      <c r="DE184" t="inlineStr"/>
+      <c r="DF184" t="inlineStr"/>
+      <c r="DG184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI184" t="inlineStr"/>
+      <c r="DJ184" t="inlineStr"/>
+      <c r="DK184" t="inlineStr"/>
+      <c r="DL184" t="inlineStr"/>
+      <c r="DM184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Thuraya</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Thuraya One</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>A mobile phone with dedicated satellite connectivity and services (370+ roaming partners worldwide)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/thuraya_one-13660.php</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2025, January</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, January</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>6GB</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>About 1200 EUR</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Li-Po 3500 mAh</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>167 x 76.5 x 11.6 mm (6.57 x 3.01 x 0.46 in)</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>230 g (8.11 oz)</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t>5.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr"/>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>GPS, GALILEO, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~395 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>6.67 inches, 107.4 cm 2 (~84.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>AMOLED, 90Hz, 700 nits</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass, gyro</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>2025, January</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>Available. Released 2025, January</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>About 1200 EUR</t>
+        </is>
+      </c>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI185" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ185" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK185" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL185" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A78 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM185" t="inlineStr">
+        <is>
+          <t>Android 14</t>
+        </is>
+      </c>
+      <c r="BN185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO185" t="inlineStr"/>
+      <c r="BP185" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ185" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR185" t="inlineStr">
+        <is>
+          <t>IP67 dust/water resistant (up to 1m for 30 min)</t>
+        </is>
+      </c>
+      <c r="BS185" t="inlineStr">
+        <is>
+          <t>Glass front (Corning Gorilla glass 5), plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU185" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV185" t="inlineStr"/>
+      <c r="BW185" t="inlineStr"/>
+      <c r="BX185" t="inlineStr"/>
+      <c r="BY185" t="inlineStr"/>
+      <c r="BZ185" t="inlineStr"/>
+      <c r="CA185" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB185" t="inlineStr"/>
+      <c r="CC185" t="inlineStr">
+        <is>
+          <t>50 MP, f/1.8, (wide), 1/2.76", PDAF 8 MP, f/2.2, (ultrawide), 1/4.0" 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD185" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE185" t="inlineStr">
+        <is>
+          <t>UMCP</t>
+        </is>
+      </c>
+      <c r="CF185" t="inlineStr"/>
+      <c r="CG185" t="inlineStr"/>
+      <c r="CH185" t="inlineStr"/>
+      <c r="CI185" t="inlineStr"/>
+      <c r="CJ185" t="inlineStr"/>
+      <c r="CK185" t="inlineStr"/>
+      <c r="CL185" t="inlineStr">
+        <is>
+          <t>LTE</t>
+        </is>
+      </c>
+      <c r="CM185" t="inlineStr">
+        <is>
+          <t>SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN185" t="inlineStr"/>
+      <c r="CO185" t="inlineStr"/>
+      <c r="CP185" t="inlineStr"/>
+      <c r="CQ185" t="inlineStr"/>
+      <c r="CR185" t="inlineStr">
+        <is>
+          <t>Qualcomm QCM4490  (4 nm)</t>
+        </is>
+      </c>
+      <c r="CS185" t="inlineStr">
+        <is>
+          <t>Adreno 613</t>
+        </is>
+      </c>
+      <c r="CT185" t="inlineStr"/>
+      <c r="CU185" t="inlineStr"/>
+      <c r="CV185" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.2, (wide), 1/3.0"</t>
+        </is>
+      </c>
+      <c r="CW185" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX185" t="inlineStr"/>
+      <c r="CY185" t="inlineStr"/>
+      <c r="CZ185" t="inlineStr"/>
+      <c r="DA185" t="inlineStr"/>
+      <c r="DB185" t="inlineStr"/>
+      <c r="DC185" t="inlineStr"/>
+      <c r="DD185" t="inlineStr"/>
+      <c r="DE185" t="inlineStr"/>
+      <c r="DF185" t="inlineStr"/>
+      <c r="DG185" t="inlineStr"/>
+      <c r="DH185" t="inlineStr"/>
+      <c r="DI185" t="inlineStr"/>
+      <c r="DJ185" t="inlineStr"/>
+      <c r="DK185" t="inlineStr"/>
+      <c r="DL185" t="inlineStr"/>
+      <c r="DM185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Thuraya</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Thuraya SG-2520</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/thuraya_sg_2520-1925.php</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2007, March</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>128MB</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>Up to 75 h</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1280 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>138.5 x 53 x 18.8 mm (5.45 x 2.09 x 0.74 in)</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr"/>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>170 g (6.00 oz)</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>Wallpapers, screensavers</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels (~148 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>1.9 inches, 11.4 cm 2 (~15.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>MP3/AAC/MP4/AMR player eZi Text Input Organizer Voice memo File browser</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>WAP 2.0/HTML</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr"/>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>2007, March</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>SD ( 128 MB included )</t>
+        </is>
+      </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>128MB</t>
+        </is>
+      </c>
+      <c r="BE186" t="inlineStr">
+        <is>
+          <t>Light Silver, Dark Gray</t>
+        </is>
+      </c>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="BL186" t="inlineStr"/>
+      <c r="BM186" t="inlineStr">
+        <is>
+          <t>WinCE 4.2</t>
+        </is>
+      </c>
+      <c r="BN186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO186" t="inlineStr">
+        <is>
+          <t>Downloadable polyphonic, MP3, WAV, MIDI ringtones</t>
+        </is>
+      </c>
+      <c r="BP186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ186" t="inlineStr"/>
+      <c r="BR186" t="inlineStr"/>
+      <c r="BS186" t="inlineStr"/>
+      <c r="BT186" t="inlineStr"/>
+      <c r="BU186" t="inlineStr"/>
+      <c r="BV186" t="inlineStr"/>
+      <c r="BW186" t="inlineStr"/>
+      <c r="BX186" t="inlineStr"/>
+      <c r="BY186" t="inlineStr"/>
+      <c r="BZ186" t="inlineStr"/>
+      <c r="CA186" t="inlineStr"/>
+      <c r="CB186" t="inlineStr"/>
+      <c r="CC186" t="inlineStr"/>
+      <c r="CD186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE186" t="inlineStr"/>
+      <c r="CF186" t="inlineStr"/>
+      <c r="CG186" t="inlineStr"/>
+      <c r="CH186" t="inlineStr">
+        <is>
+          <t>SATELLITE</t>
+        </is>
+      </c>
+      <c r="CI186" t="inlineStr"/>
+      <c r="CJ186" t="inlineStr"/>
+      <c r="CK186" t="inlineStr"/>
+      <c r="CL186" t="inlineStr"/>
+      <c r="CM186" t="inlineStr"/>
+      <c r="CN186" t="inlineStr"/>
+      <c r="CO186" t="inlineStr"/>
+      <c r="CP186" t="inlineStr"/>
+      <c r="CQ186" t="inlineStr"/>
+      <c r="CR186" t="inlineStr"/>
+      <c r="CS186" t="inlineStr"/>
+      <c r="CT186" t="inlineStr"/>
+      <c r="CU186" t="inlineStr"/>
+      <c r="CV186" t="inlineStr"/>
+      <c r="CW186" t="inlineStr"/>
+      <c r="CX186" t="inlineStr"/>
+      <c r="CY186" t="inlineStr"/>
+      <c r="CZ186" t="inlineStr"/>
+      <c r="DA186" t="inlineStr"/>
+      <c r="DB186" t="inlineStr"/>
+      <c r="DC186" t="inlineStr"/>
+      <c r="DD186" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="DE186" t="inlineStr"/>
+      <c r="DF186" t="inlineStr"/>
+      <c r="DG186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH186" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="DI186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ186" t="inlineStr"/>
+      <c r="DK186" t="inlineStr"/>
+      <c r="DL186" t="inlineStr"/>
+      <c r="DM186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Toshiba Excite Go</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Also known as Toshiba Excite Go AT7-C8</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_go-6466.php</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2014, May. Released 2014, July</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>119.8</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>354.4</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Up to 7 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>Li-Po 3500 mAh, non-removable (13 Wh)</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>199 x 119.8 x 10.9 mm (7.83 x 4.72 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>354.4 g (12.49 oz)</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr"/>
+      <c r="AP187" t="inlineStr"/>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>600 x 1024 pixels, 16:9 ratio (~170 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>7.0 inches, 137.9 cm 2 (~57.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>2014, May. Released 2014, July</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>8GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>Black/Silver, Black/White</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL187" t="inlineStr">
+        <is>
+          <t>Quad-core 1.33 GHz</t>
+        </is>
+      </c>
+      <c r="BM187" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="BN187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO187" t="inlineStr"/>
+      <c r="BP187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ187" t="inlineStr"/>
+      <c r="BR187" t="inlineStr"/>
+      <c r="BS187" t="inlineStr"/>
+      <c r="BT187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU187" t="inlineStr"/>
+      <c r="BV187" t="inlineStr"/>
+      <c r="BW187" t="inlineStr"/>
+      <c r="BX187" t="inlineStr"/>
+      <c r="BY187" t="inlineStr"/>
+      <c r="BZ187" t="inlineStr"/>
+      <c r="CA187" t="inlineStr"/>
+      <c r="CB187" t="inlineStr"/>
+      <c r="CC187" t="inlineStr"/>
+      <c r="CD187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE187" t="inlineStr"/>
+      <c r="CF187" t="inlineStr"/>
+      <c r="CG187" t="inlineStr"/>
+      <c r="CH187" t="inlineStr"/>
+      <c r="CI187" t="inlineStr"/>
+      <c r="CJ187" t="inlineStr"/>
+      <c r="CK187" t="inlineStr"/>
+      <c r="CL187" t="inlineStr"/>
+      <c r="CM187" t="inlineStr"/>
+      <c r="CN187" t="inlineStr"/>
+      <c r="CO187" t="inlineStr"/>
+      <c r="CP187" t="inlineStr"/>
+      <c r="CQ187" t="inlineStr"/>
+      <c r="CR187" t="inlineStr">
+        <is>
+          <t>Intel Atom Z3735G</t>
+        </is>
+      </c>
+      <c r="CS187" t="inlineStr"/>
+      <c r="CT187" t="inlineStr"/>
+      <c r="CU187" t="inlineStr"/>
+      <c r="CV187" t="inlineStr"/>
+      <c r="CW187" t="inlineStr"/>
+      <c r="CX187" t="inlineStr"/>
+      <c r="CY187" t="inlineStr"/>
+      <c r="CZ187" t="inlineStr"/>
+      <c r="DA187" t="inlineStr"/>
+      <c r="DB187" t="inlineStr"/>
+      <c r="DC187" t="inlineStr"/>
+      <c r="DD187" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE187" t="inlineStr"/>
+      <c r="DF187" t="inlineStr"/>
+      <c r="DG187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ187" t="inlineStr"/>
+      <c r="DK187" t="inlineStr"/>
+      <c r="DL187" t="inlineStr"/>
+      <c r="DM187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Toshiba Excite 7c AT7-B8</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_7c_at7_b8-6467.php</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2014, February. Released 2014, February</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>119.8</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>354.4</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>About 70 EUR</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Up to 11 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>Li-Po 3500 mAh, non-removable (13 Wh)</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>199 x 119.8 x 10.9 mm (7.83 x 4.72 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>354.4 g (12.49 oz)</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr"/>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>600 x 1024 pixels, 16:9 ratio (~170 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>7.0 inches, 137.9 cm 2 (~57.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>2014, February. Released 2014, February</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD188" t="inlineStr">
+        <is>
+          <t>8GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE188" t="inlineStr">
+        <is>
+          <t>Black/Silver</t>
+        </is>
+      </c>
+      <c r="BF188" t="inlineStr">
+        <is>
+          <t>About 70 EUR</t>
+        </is>
+      </c>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL188" t="inlineStr">
+        <is>
+          <t>Dual-core 1.5 GHz Cortex-A9</t>
+        </is>
+      </c>
+      <c r="BM188" t="inlineStr">
+        <is>
+          <t>Android 4.2.2 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="BN188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO188" t="inlineStr"/>
+      <c r="BP188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ188" t="inlineStr"/>
+      <c r="BR188" t="inlineStr"/>
+      <c r="BS188" t="inlineStr"/>
+      <c r="BT188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU188" t="inlineStr"/>
+      <c r="BV188" t="inlineStr"/>
+      <c r="BW188" t="inlineStr"/>
+      <c r="BX188" t="inlineStr"/>
+      <c r="BY188" t="inlineStr"/>
+      <c r="BZ188" t="inlineStr"/>
+      <c r="CA188" t="inlineStr"/>
+      <c r="CB188" t="inlineStr"/>
+      <c r="CC188" t="inlineStr"/>
+      <c r="CD188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE188" t="inlineStr"/>
+      <c r="CF188" t="inlineStr"/>
+      <c r="CG188" t="inlineStr"/>
+      <c r="CH188" t="inlineStr"/>
+      <c r="CI188" t="inlineStr"/>
+      <c r="CJ188" t="inlineStr"/>
+      <c r="CK188" t="inlineStr"/>
+      <c r="CL188" t="inlineStr"/>
+      <c r="CM188" t="inlineStr"/>
+      <c r="CN188" t="inlineStr"/>
+      <c r="CO188" t="inlineStr"/>
+      <c r="CP188" t="inlineStr"/>
+      <c r="CQ188" t="inlineStr"/>
+      <c r="CR188" t="inlineStr">
+        <is>
+          <t>Rockchip RK3168</t>
+        </is>
+      </c>
+      <c r="CS188" t="inlineStr"/>
+      <c r="CT188" t="inlineStr"/>
+      <c r="CU188" t="inlineStr"/>
+      <c r="CV188" t="inlineStr"/>
+      <c r="CW188" t="inlineStr"/>
+      <c r="CX188" t="inlineStr"/>
+      <c r="CY188" t="inlineStr"/>
+      <c r="CZ188" t="inlineStr"/>
+      <c r="DA188" t="inlineStr"/>
+      <c r="DB188" t="inlineStr"/>
+      <c r="DC188" t="inlineStr"/>
+      <c r="DD188" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="DE188" t="inlineStr"/>
+      <c r="DF188" t="inlineStr"/>
+      <c r="DG188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ188" t="inlineStr"/>
+      <c r="DK188" t="inlineStr"/>
+      <c r="DL188" t="inlineStr"/>
+      <c r="DM188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Toshiba Excite Pro</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_pro-5500.php</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>261.6</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>177.8</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>630.5</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Up to 11 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Li-Po (33 Wh)</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>261.6 x 177.8 x 10.2 mm (10.30 x 7.00 x 0.40 in)</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>630.5 g (1.39 lb)</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr"/>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>2560 x 1600 pixels, 16:10 ratio (~299 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~63.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>LED-backlit IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>HDMI port</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD189" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t>Quad-core Cortex-A15</t>
+        </is>
+      </c>
+      <c r="BM189" t="inlineStr">
+        <is>
+          <t>Android 4.2.1 (Jelly Bean), upgradаble to 4.3 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="BN189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO189" t="inlineStr"/>
+      <c r="BP189" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ189" t="inlineStr"/>
+      <c r="BR189" t="inlineStr"/>
+      <c r="BS189" t="inlineStr"/>
+      <c r="BT189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU189" t="inlineStr"/>
+      <c r="BV189" t="inlineStr"/>
+      <c r="BW189" t="inlineStr"/>
+      <c r="BX189" t="inlineStr"/>
+      <c r="BY189" t="inlineStr"/>
+      <c r="BZ189" t="inlineStr"/>
+      <c r="CA189" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB189" t="inlineStr"/>
+      <c r="CC189" t="inlineStr"/>
+      <c r="CD189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE189" t="inlineStr"/>
+      <c r="CF189" t="inlineStr"/>
+      <c r="CG189" t="inlineStr"/>
+      <c r="CH189" t="inlineStr"/>
+      <c r="CI189" t="inlineStr"/>
+      <c r="CJ189" t="inlineStr"/>
+      <c r="CK189" t="inlineStr"/>
+      <c r="CL189" t="inlineStr"/>
+      <c r="CM189" t="inlineStr"/>
+      <c r="CN189" t="inlineStr"/>
+      <c r="CO189" t="inlineStr"/>
+      <c r="CP189" t="inlineStr"/>
+      <c r="CQ189" t="inlineStr"/>
+      <c r="CR189" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 4</t>
+        </is>
+      </c>
+      <c r="CS189" t="inlineStr">
+        <is>
+          <t>ULP GeForce</t>
+        </is>
+      </c>
+      <c r="CT189" t="inlineStr"/>
+      <c r="CU189" t="inlineStr"/>
+      <c r="CV189" t="inlineStr">
+        <is>
+          <t>1.2 MP</t>
+        </is>
+      </c>
+      <c r="CW189" t="inlineStr"/>
+      <c r="CX189" t="inlineStr"/>
+      <c r="CY189" t="inlineStr"/>
+      <c r="CZ189" t="inlineStr"/>
+      <c r="DA189" t="inlineStr"/>
+      <c r="DB189" t="inlineStr"/>
+      <c r="DC189" t="inlineStr"/>
+      <c r="DD189" t="inlineStr">
+        <is>
+          <t>8 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE189" t="inlineStr"/>
+      <c r="DF189" t="inlineStr"/>
+      <c r="DG189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI189" t="inlineStr"/>
+      <c r="DJ189" t="inlineStr"/>
+      <c r="DK189" t="inlineStr"/>
+      <c r="DL189" t="inlineStr"/>
+      <c r="DM189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Toshiba Excite Write</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_write-5501.php</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>261.6</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>177.8</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>671.3</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>About 440 EUR</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Up to 11 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Li-Po (33 Wh)</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>261.6 x 177.8 x 10.2 mm (10.30 x 7.00 x 0.40 in)</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr"/>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>671.3 g (1.48 lb)</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr"/>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>2560 x 1600 pixels, 16:10 ratio (~299 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~63.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>LED-backlit IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>HDMI port</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>About 440 EUR</t>
+        </is>
+      </c>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t>Quad-core Cortex-A15</t>
+        </is>
+      </c>
+      <c r="BM190" t="inlineStr">
+        <is>
+          <t>Android 4.2.1 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="BN190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO190" t="inlineStr"/>
+      <c r="BP190" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ190" t="inlineStr"/>
+      <c r="BR190" t="inlineStr">
+        <is>
+          <t>Stylus</t>
+        </is>
+      </c>
+      <c r="BS190" t="inlineStr"/>
+      <c r="BT190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU190" t="inlineStr"/>
+      <c r="BV190" t="inlineStr"/>
+      <c r="BW190" t="inlineStr"/>
+      <c r="BX190" t="inlineStr"/>
+      <c r="BY190" t="inlineStr"/>
+      <c r="BZ190" t="inlineStr"/>
+      <c r="CA190" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB190" t="inlineStr"/>
+      <c r="CC190" t="inlineStr"/>
+      <c r="CD190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE190" t="inlineStr"/>
+      <c r="CF190" t="inlineStr"/>
+      <c r="CG190" t="inlineStr"/>
+      <c r="CH190" t="inlineStr"/>
+      <c r="CI190" t="inlineStr"/>
+      <c r="CJ190" t="inlineStr"/>
+      <c r="CK190" t="inlineStr"/>
+      <c r="CL190" t="inlineStr"/>
+      <c r="CM190" t="inlineStr"/>
+      <c r="CN190" t="inlineStr"/>
+      <c r="CO190" t="inlineStr"/>
+      <c r="CP190" t="inlineStr"/>
+      <c r="CQ190" t="inlineStr"/>
+      <c r="CR190" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 4</t>
+        </is>
+      </c>
+      <c r="CS190" t="inlineStr">
+        <is>
+          <t>ULP GeForce</t>
+        </is>
+      </c>
+      <c r="CT190" t="inlineStr"/>
+      <c r="CU190" t="inlineStr"/>
+      <c r="CV190" t="inlineStr">
+        <is>
+          <t>1.2 MP</t>
+        </is>
+      </c>
+      <c r="CW190" t="inlineStr"/>
+      <c r="CX190" t="inlineStr"/>
+      <c r="CY190" t="inlineStr"/>
+      <c r="CZ190" t="inlineStr"/>
+      <c r="DA190" t="inlineStr"/>
+      <c r="DB190" t="inlineStr"/>
+      <c r="DC190" t="inlineStr"/>
+      <c r="DD190" t="inlineStr">
+        <is>
+          <t>8 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE190" t="inlineStr"/>
+      <c r="DF190" t="inlineStr"/>
+      <c r="DG190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI190" t="inlineStr"/>
+      <c r="DJ190" t="inlineStr"/>
+      <c r="DK190" t="inlineStr"/>
+      <c r="DL190" t="inlineStr"/>
+      <c r="DM190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Toshiba Excite Pure</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_pure-5502.php</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>261.6</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>177.8</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>598.7</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>About 230 EUR</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Up to 13 h 30 min (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Li-Po (25 Wh)</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>261.6 x 177.8 x 10.2 mm (10.30 x 7.00 x 0.40 in)</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>598.7 g (1.32 lb)</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr"/>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~149 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~63.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>LED-backlit IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>HDMI port</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>2013, June. Released 2013, July</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD191" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE191" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>About 230 EUR</t>
+        </is>
+      </c>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
+        <is>
+          <t>Quad-core</t>
+        </is>
+      </c>
+      <c r="BM191" t="inlineStr">
+        <is>
+          <t>Android 4.2.1 (Jelly Bean), upgradаble to 4.3 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="BN191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO191" t="inlineStr"/>
+      <c r="BP191" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ191" t="inlineStr"/>
+      <c r="BR191" t="inlineStr"/>
+      <c r="BS191" t="inlineStr"/>
+      <c r="BT191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU191" t="inlineStr"/>
+      <c r="BV191" t="inlineStr"/>
+      <c r="BW191" t="inlineStr"/>
+      <c r="BX191" t="inlineStr"/>
+      <c r="BY191" t="inlineStr"/>
+      <c r="BZ191" t="inlineStr"/>
+      <c r="CA191" t="inlineStr"/>
+      <c r="CB191" t="inlineStr"/>
+      <c r="CC191" t="inlineStr"/>
+      <c r="CD191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE191" t="inlineStr"/>
+      <c r="CF191" t="inlineStr"/>
+      <c r="CG191" t="inlineStr"/>
+      <c r="CH191" t="inlineStr"/>
+      <c r="CI191" t="inlineStr"/>
+      <c r="CJ191" t="inlineStr"/>
+      <c r="CK191" t="inlineStr"/>
+      <c r="CL191" t="inlineStr"/>
+      <c r="CM191" t="inlineStr"/>
+      <c r="CN191" t="inlineStr"/>
+      <c r="CO191" t="inlineStr"/>
+      <c r="CP191" t="inlineStr"/>
+      <c r="CQ191" t="inlineStr"/>
+      <c r="CR191" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 3</t>
+        </is>
+      </c>
+      <c r="CS191" t="inlineStr"/>
+      <c r="CT191" t="inlineStr"/>
+      <c r="CU191" t="inlineStr"/>
+      <c r="CV191" t="inlineStr"/>
+      <c r="CW191" t="inlineStr"/>
+      <c r="CX191" t="inlineStr"/>
+      <c r="CY191" t="inlineStr"/>
+      <c r="CZ191" t="inlineStr"/>
+      <c r="DA191" t="inlineStr"/>
+      <c r="DB191" t="inlineStr"/>
+      <c r="DC191" t="inlineStr"/>
+      <c r="DD191" t="inlineStr">
+        <is>
+          <t>1.2 MP</t>
+        </is>
+      </c>
+      <c r="DE191" t="inlineStr"/>
+      <c r="DF191" t="inlineStr"/>
+      <c r="DG191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ191" t="inlineStr"/>
+      <c r="DK191" t="inlineStr"/>
+      <c r="DL191" t="inlineStr"/>
+      <c r="DM191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Toshiba Excite 10 SE</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tablet with no support for GSM voice communicationAvailable as Toshiba AT300SE in UK</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_10_se-5154.php</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2012, December. Released 2012, December</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>261.6</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>180.3</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>639.6</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Up to 12 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Li-Po (25 Wh)</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>261.6 x 180.3 x 10.2 mm (10.30 x 7.10 x 0.40 in)</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr"/>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>639.6 g (1.41 lb)</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr"/>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~149 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~62.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>LED-backlit IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr"/>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>2012, December. Released 2012, December</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD192" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE192" t="inlineStr">
+        <is>
+          <t>Black/Silver</t>
+        </is>
+      </c>
+      <c r="BF192" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL192" t="inlineStr">
+        <is>
+          <t>Quad-core 1.5 GHz</t>
+        </is>
+      </c>
+      <c r="BM192" t="inlineStr">
+        <is>
+          <t>Android 4.1 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="BN192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO192" t="inlineStr"/>
+      <c r="BP192" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ192" t="inlineStr"/>
+      <c r="BR192" t="inlineStr"/>
+      <c r="BS192" t="inlineStr"/>
+      <c r="BT192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU192" t="inlineStr"/>
+      <c r="BV192" t="inlineStr"/>
+      <c r="BW192" t="inlineStr"/>
+      <c r="BX192" t="inlineStr"/>
+      <c r="BY192" t="inlineStr"/>
+      <c r="BZ192" t="inlineStr"/>
+      <c r="CA192" t="inlineStr"/>
+      <c r="CB192" t="inlineStr"/>
+      <c r="CC192" t="inlineStr"/>
+      <c r="CD192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE192" t="inlineStr"/>
+      <c r="CF192" t="inlineStr"/>
+      <c r="CG192" t="inlineStr"/>
+      <c r="CH192" t="inlineStr"/>
+      <c r="CI192" t="inlineStr"/>
+      <c r="CJ192" t="inlineStr"/>
+      <c r="CK192" t="inlineStr"/>
+      <c r="CL192" t="inlineStr"/>
+      <c r="CM192" t="inlineStr"/>
+      <c r="CN192" t="inlineStr"/>
+      <c r="CO192" t="inlineStr"/>
+      <c r="CP192" t="inlineStr"/>
+      <c r="CQ192" t="inlineStr"/>
+      <c r="CR192" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 3</t>
+        </is>
+      </c>
+      <c r="CS192" t="inlineStr">
+        <is>
+          <t>ULP GeForce 2</t>
+        </is>
+      </c>
+      <c r="CT192" t="inlineStr"/>
+      <c r="CU192" t="inlineStr"/>
+      <c r="CV192" t="inlineStr">
+        <is>
+          <t>1.2 MP</t>
+        </is>
+      </c>
+      <c r="CW192" t="inlineStr"/>
+      <c r="CX192" t="inlineStr">
+        <is>
+          <t>SRS audio</t>
+        </is>
+      </c>
+      <c r="CY192" t="inlineStr"/>
+      <c r="CZ192" t="inlineStr"/>
+      <c r="DA192" t="inlineStr"/>
+      <c r="DB192" t="inlineStr"/>
+      <c r="DC192" t="inlineStr"/>
+      <c r="DD192" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE192" t="inlineStr"/>
+      <c r="DF192" t="inlineStr"/>
+      <c r="DG192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI192" t="inlineStr"/>
+      <c r="DJ192" t="inlineStr"/>
+      <c r="DK192" t="inlineStr"/>
+      <c r="DL192" t="inlineStr"/>
+      <c r="DM192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Toshiba Excite 13 AT335</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_13_at335-4691.php</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, July</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>343.8</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>211.2</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>About 540 EUR</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>Up to 168 h</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Up to 13 h</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Po battery (38 Wh)</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>343.8 x 211.2 x 9.8 mm (13.54 x 8.31 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr"/>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>998 g (2.20 lb)</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr"/>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>miniUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>1600 x 900 pixels, 16:9 ratio (~120 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>13.3 inches, 644.9 cm 2 (~88.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>LED-backlit IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>HDMI port MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, July</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>SD/microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD193" t="inlineStr">
+        <is>
+          <t>32GB 1GB RAM, 64GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE193" t="inlineStr">
+        <is>
+          <t>Dark gray metallic</t>
+        </is>
+      </c>
+      <c r="BF193" t="inlineStr">
+        <is>
+          <t>About 540 EUR</t>
+        </is>
+      </c>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI193" t="inlineStr">
+        <is>
+          <t>HSDPA</t>
+        </is>
+      </c>
+      <c r="BJ193" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL193" t="inlineStr">
+        <is>
+          <t>Quad-core 1.5 GHz</t>
+        </is>
+      </c>
+      <c r="BM193" t="inlineStr">
+        <is>
+          <t>Android 4.0 (Ice Cream Sandwich)</t>
+        </is>
+      </c>
+      <c r="BN193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO193" t="inlineStr"/>
+      <c r="BP193" t="inlineStr">
+        <is>
+          <t>Yes, with four speakers</t>
+        </is>
+      </c>
+      <c r="BQ193" t="inlineStr"/>
+      <c r="BR193" t="inlineStr"/>
+      <c r="BS193" t="inlineStr"/>
+      <c r="BT193" t="inlineStr"/>
+      <c r="BU193" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV193" t="inlineStr"/>
+      <c r="BW193" t="inlineStr"/>
+      <c r="BX193" t="inlineStr"/>
+      <c r="BY193" t="inlineStr"/>
+      <c r="BZ193" t="inlineStr"/>
+      <c r="CA193" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB193" t="inlineStr"/>
+      <c r="CC193" t="inlineStr"/>
+      <c r="CD193" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE193" t="inlineStr"/>
+      <c r="CF193" t="inlineStr"/>
+      <c r="CG193" t="inlineStr"/>
+      <c r="CH193" t="inlineStr"/>
+      <c r="CI193" t="inlineStr"/>
+      <c r="CJ193" t="inlineStr"/>
+      <c r="CK193" t="inlineStr"/>
+      <c r="CL193" t="inlineStr"/>
+      <c r="CM193" t="inlineStr"/>
+      <c r="CN193" t="inlineStr"/>
+      <c r="CO193" t="inlineStr"/>
+      <c r="CP193" t="inlineStr"/>
+      <c r="CQ193" t="inlineStr"/>
+      <c r="CR193" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 3</t>
+        </is>
+      </c>
+      <c r="CS193" t="inlineStr">
+        <is>
+          <t>ULP GeForce 2</t>
+        </is>
+      </c>
+      <c r="CT193" t="inlineStr"/>
+      <c r="CU193" t="inlineStr"/>
+      <c r="CV193" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW193" t="inlineStr"/>
+      <c r="CX193" t="inlineStr">
+        <is>
+          <t>SRS audio</t>
+        </is>
+      </c>
+      <c r="CY193" t="inlineStr"/>
+      <c r="CZ193" t="inlineStr"/>
+      <c r="DA193" t="inlineStr"/>
+      <c r="DB193" t="inlineStr"/>
+      <c r="DC193" t="inlineStr"/>
+      <c r="DD193" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE193" t="inlineStr"/>
+      <c r="DF193" t="inlineStr"/>
+      <c r="DG193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DH193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DI193" t="inlineStr"/>
+      <c r="DJ193" t="inlineStr"/>
+      <c r="DK193" t="inlineStr"/>
+      <c r="DL193" t="inlineStr"/>
+      <c r="DM193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Toshiba Excite 10 AT305</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tablet with no support for GSM voice communication</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_10_at305-4692.php</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, May</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>16GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>About 290 EUR</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>Up to 168 h</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Up to 10 h</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Po battery (25 Wh)</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>262 x 178 x 9 mm (10.31 x 7.01 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>599 g (1.32 lb)</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr"/>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~149 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~63.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>LED-backlit LCD,</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>HDMI port MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, May</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>SD/microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD194" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM, 32GB 1GB RAM, 64GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE194" t="inlineStr">
+        <is>
+          <t>Black/Silver</t>
+        </is>
+      </c>
+      <c r="BF194" t="inlineStr">
+        <is>
+          <t>About 290 EUR</t>
+        </is>
+      </c>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL194" t="inlineStr">
+        <is>
+          <t>Quad-core 1.5 GHz</t>
+        </is>
+      </c>
+      <c r="BM194" t="inlineStr">
+        <is>
+          <t>Android 4.0 (Ice Cream Sandwich)</t>
+        </is>
+      </c>
+      <c r="BN194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO194" t="inlineStr"/>
+      <c r="BP194" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ194" t="inlineStr"/>
+      <c r="BR194" t="inlineStr"/>
+      <c r="BS194" t="inlineStr"/>
+      <c r="BT194" t="inlineStr"/>
+      <c r="BU194" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV194" t="inlineStr"/>
+      <c r="BW194" t="inlineStr"/>
+      <c r="BX194" t="inlineStr"/>
+      <c r="BY194" t="inlineStr"/>
+      <c r="BZ194" t="inlineStr"/>
+      <c r="CA194" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB194" t="inlineStr"/>
+      <c r="CC194" t="inlineStr"/>
+      <c r="CD194" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE194" t="inlineStr"/>
+      <c r="CF194" t="inlineStr"/>
+      <c r="CG194" t="inlineStr"/>
+      <c r="CH194" t="inlineStr"/>
+      <c r="CI194" t="inlineStr"/>
+      <c r="CJ194" t="inlineStr"/>
+      <c r="CK194" t="inlineStr"/>
+      <c r="CL194" t="inlineStr"/>
+      <c r="CM194" t="inlineStr"/>
+      <c r="CN194" t="inlineStr"/>
+      <c r="CO194" t="inlineStr"/>
+      <c r="CP194" t="inlineStr"/>
+      <c r="CQ194" t="inlineStr"/>
+      <c r="CR194" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 3</t>
+        </is>
+      </c>
+      <c r="CS194" t="inlineStr">
+        <is>
+          <t>ULP GeForce 2</t>
+        </is>
+      </c>
+      <c r="CT194" t="inlineStr"/>
+      <c r="CU194" t="inlineStr"/>
+      <c r="CV194" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW194" t="inlineStr"/>
+      <c r="CX194" t="inlineStr">
+        <is>
+          <t>SRS audio</t>
+        </is>
+      </c>
+      <c r="CY194" t="inlineStr"/>
+      <c r="CZ194" t="inlineStr"/>
+      <c r="DA194" t="inlineStr"/>
+      <c r="DB194" t="inlineStr"/>
+      <c r="DC194" t="inlineStr"/>
+      <c r="DD194" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE194" t="inlineStr"/>
+      <c r="DF194" t="inlineStr"/>
+      <c r="DG194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI194" t="inlineStr"/>
+      <c r="DJ194" t="inlineStr"/>
+      <c r="DK194" t="inlineStr"/>
+      <c r="DL194" t="inlineStr"/>
+      <c r="DM194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Toshiba Excite 7.7 AT275</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_7_7_at275-4693.php</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, July</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>204.5</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>135.2</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>16GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>About 410 EUR</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Po battery (15 Wh)</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>204.5 x 135.2 x 7.8 mm (8.05 x 5.32 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr"/>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>332 g (11.71 oz)</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr"/>
+      <c r="AN195" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr"/>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>miniUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~196 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>7.7 inches, 171.9 cm 2 (~62.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>2012, April. Released 2012, July</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD195" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM, 32GB 1GB RAM, 64GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE195" t="inlineStr">
+        <is>
+          <t>Dark gray metallic</t>
+        </is>
+      </c>
+      <c r="BF195" t="inlineStr">
+        <is>
+          <t>About 410 EUR</t>
+        </is>
+      </c>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI195" t="inlineStr">
+        <is>
+          <t>HSDPA</t>
+        </is>
+      </c>
+      <c r="BJ195" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="BK195" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL195" t="inlineStr">
+        <is>
+          <t>Quad-core 1.5 GHz</t>
+        </is>
+      </c>
+      <c r="BM195" t="inlineStr">
+        <is>
+          <t>Android 4.0 (Ice Cream Sandwich)</t>
+        </is>
+      </c>
+      <c r="BN195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO195" t="inlineStr"/>
+      <c r="BP195" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ195" t="inlineStr"/>
+      <c r="BR195" t="inlineStr"/>
+      <c r="BS195" t="inlineStr"/>
+      <c r="BT195" t="inlineStr"/>
+      <c r="BU195" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="BV195" t="inlineStr"/>
+      <c r="BW195" t="inlineStr"/>
+      <c r="BX195" t="inlineStr"/>
+      <c r="BY195" t="inlineStr"/>
+      <c r="BZ195" t="inlineStr"/>
+      <c r="CA195" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB195" t="inlineStr"/>
+      <c r="CC195" t="inlineStr"/>
+      <c r="CD195" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE195" t="inlineStr"/>
+      <c r="CF195" t="inlineStr"/>
+      <c r="CG195" t="inlineStr"/>
+      <c r="CH195" t="inlineStr"/>
+      <c r="CI195" t="inlineStr"/>
+      <c r="CJ195" t="inlineStr"/>
+      <c r="CK195" t="inlineStr"/>
+      <c r="CL195" t="inlineStr"/>
+      <c r="CM195" t="inlineStr"/>
+      <c r="CN195" t="inlineStr"/>
+      <c r="CO195" t="inlineStr"/>
+      <c r="CP195" t="inlineStr"/>
+      <c r="CQ195" t="inlineStr"/>
+      <c r="CR195" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 3</t>
+        </is>
+      </c>
+      <c r="CS195" t="inlineStr">
+        <is>
+          <t>ULP GeForce 2</t>
+        </is>
+      </c>
+      <c r="CT195" t="inlineStr"/>
+      <c r="CU195" t="inlineStr"/>
+      <c r="CV195" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW195" t="inlineStr"/>
+      <c r="CX195" t="inlineStr">
+        <is>
+          <t>SRS audio</t>
+        </is>
+      </c>
+      <c r="CY195" t="inlineStr"/>
+      <c r="CZ195" t="inlineStr"/>
+      <c r="DA195" t="inlineStr"/>
+      <c r="DB195" t="inlineStr"/>
+      <c r="DC195" t="inlineStr"/>
+      <c r="DD195" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE195" t="inlineStr"/>
+      <c r="DF195" t="inlineStr"/>
+      <c r="DG195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DH195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DI195" t="inlineStr"/>
+      <c r="DJ195" t="inlineStr"/>
+      <c r="DK195" t="inlineStr"/>
+      <c r="DL195" t="inlineStr"/>
+      <c r="DM195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Toshiba Excite AT200</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_excite_at200-4400.php</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2011, September. Released 2012, January</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>16GB | 32GB</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>About 530 EUR</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Up to 8 h (multimedia)</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>256 x 176 x 7.7 mm (10.08 x 6.93 x 0.30 in)</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>558 g (1.23 lb)</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr">
+        <is>
+          <t>2.1, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr"/>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>miniUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~149 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~65.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>LED-backlit LCD,</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>HDMI port MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>2011, September. Released 2012, January</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM, 32GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>About 530 EUR</t>
+        </is>
+      </c>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL196" t="inlineStr">
+        <is>
+          <t>1.2 GHz</t>
+        </is>
+      </c>
+      <c r="BM196" t="inlineStr">
+        <is>
+          <t>Android 3.2 (Honeycomb)</t>
+        </is>
+      </c>
+      <c r="BN196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO196" t="inlineStr"/>
+      <c r="BP196" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ196" t="inlineStr"/>
+      <c r="BR196" t="inlineStr"/>
+      <c r="BS196" t="inlineStr"/>
+      <c r="BT196" t="inlineStr"/>
+      <c r="BU196" t="inlineStr"/>
+      <c r="BV196" t="inlineStr"/>
+      <c r="BW196" t="inlineStr"/>
+      <c r="BX196" t="inlineStr"/>
+      <c r="BY196" t="inlineStr"/>
+      <c r="BZ196" t="inlineStr"/>
+      <c r="CA196" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB196" t="inlineStr"/>
+      <c r="CC196" t="inlineStr"/>
+      <c r="CD196" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE196" t="inlineStr"/>
+      <c r="CF196" t="inlineStr"/>
+      <c r="CG196" t="inlineStr"/>
+      <c r="CH196" t="inlineStr"/>
+      <c r="CI196" t="inlineStr"/>
+      <c r="CJ196" t="inlineStr"/>
+      <c r="CK196" t="inlineStr"/>
+      <c r="CL196" t="inlineStr"/>
+      <c r="CM196" t="inlineStr"/>
+      <c r="CN196" t="inlineStr"/>
+      <c r="CO196" t="inlineStr"/>
+      <c r="CP196" t="inlineStr"/>
+      <c r="CQ196" t="inlineStr"/>
+      <c r="CR196" t="inlineStr">
+        <is>
+          <t>TI OMAP 4430</t>
+        </is>
+      </c>
+      <c r="CS196" t="inlineStr">
+        <is>
+          <t>PowerVR SGX540</t>
+        </is>
+      </c>
+      <c r="CT196" t="inlineStr"/>
+      <c r="CU196" t="inlineStr"/>
+      <c r="CV196" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW196" t="inlineStr"/>
+      <c r="CX196" t="inlineStr"/>
+      <c r="CY196" t="inlineStr"/>
+      <c r="CZ196" t="inlineStr"/>
+      <c r="DA196" t="inlineStr"/>
+      <c r="DB196" t="inlineStr"/>
+      <c r="DC196" t="inlineStr"/>
+      <c r="DD196" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE196" t="inlineStr"/>
+      <c r="DF196" t="inlineStr"/>
+      <c r="DG196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI196" t="inlineStr"/>
+      <c r="DJ196" t="inlineStr"/>
+      <c r="DK196" t="inlineStr"/>
+      <c r="DL196" t="inlineStr"/>
+      <c r="DM196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Toshiba Thrive 7</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Also known as Toshiba Thrive 7 inch, Toshiba Thrive 7" tablet</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_thrive_7-4203.php</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2011, September. Released 2011, December</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>128.1</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>16GB | 32GB</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Ion battery (15 Wh)</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>189 x 128.1 x 11.9 mm (7.44 x 5.04 x 0.47 in)</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>400 g (14.11 oz)</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr"/>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr"/>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>miniUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~216 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>7.0 inches, 142.1 cm 2 (~58.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>LED-backlit LCD,</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>HDMI port MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input (Swype)</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>2011, September. Released 2011, December</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD197" t="inlineStr">
+        <is>
+          <t>16GB 1GB RAM, 32GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE197" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF197" t="inlineStr">
+        <is>
+          <t>About 250 EUR</t>
+        </is>
+      </c>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL197" t="inlineStr">
+        <is>
+          <t>Dual-core 1.0 GHz Cortex-A9</t>
+        </is>
+      </c>
+      <c r="BM197" t="inlineStr">
+        <is>
+          <t>Android 3.2 (Honeycomb)</t>
+        </is>
+      </c>
+      <c r="BN197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO197" t="inlineStr"/>
+      <c r="BP197" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ197" t="inlineStr"/>
+      <c r="BR197" t="inlineStr"/>
+      <c r="BS197" t="inlineStr"/>
+      <c r="BT197" t="inlineStr"/>
+      <c r="BU197" t="inlineStr"/>
+      <c r="BV197" t="inlineStr"/>
+      <c r="BW197" t="inlineStr"/>
+      <c r="BX197" t="inlineStr"/>
+      <c r="BY197" t="inlineStr"/>
+      <c r="BZ197" t="inlineStr"/>
+      <c r="CA197" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB197" t="inlineStr"/>
+      <c r="CC197" t="inlineStr"/>
+      <c r="CD197" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="CE197" t="inlineStr"/>
+      <c r="CF197" t="inlineStr"/>
+      <c r="CG197" t="inlineStr"/>
+      <c r="CH197" t="inlineStr"/>
+      <c r="CI197" t="inlineStr"/>
+      <c r="CJ197" t="inlineStr"/>
+      <c r="CK197" t="inlineStr"/>
+      <c r="CL197" t="inlineStr"/>
+      <c r="CM197" t="inlineStr"/>
+      <c r="CN197" t="inlineStr"/>
+      <c r="CO197" t="inlineStr"/>
+      <c r="CP197" t="inlineStr"/>
+      <c r="CQ197" t="inlineStr"/>
+      <c r="CR197" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 2 T20</t>
+        </is>
+      </c>
+      <c r="CS197" t="inlineStr">
+        <is>
+          <t>ULP GeForce</t>
+        </is>
+      </c>
+      <c r="CT197" t="inlineStr"/>
+      <c r="CU197" t="inlineStr"/>
+      <c r="CV197" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW197" t="inlineStr"/>
+      <c r="CX197" t="inlineStr"/>
+      <c r="CY197" t="inlineStr"/>
+      <c r="CZ197" t="inlineStr"/>
+      <c r="DA197" t="inlineStr"/>
+      <c r="DB197" t="inlineStr"/>
+      <c r="DC197" t="inlineStr"/>
+      <c r="DD197" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE197" t="inlineStr"/>
+      <c r="DF197" t="inlineStr"/>
+      <c r="DG197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI197" t="inlineStr"/>
+      <c r="DJ197" t="inlineStr"/>
+      <c r="DK197" t="inlineStr"/>
+      <c r="DL197" t="inlineStr"/>
+      <c r="DM197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Toshiba Windows Phone IS12T</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>For KDDI</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_windows_phone_is12t-4076.php</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2011, July. Released 2011, Q3</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>About 590 EUR</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>Up to 280 h</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Up to 6 h 40 min</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1460 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>118 x 59 x 10.6 mm (4.65 x 2.32 x 0.42 in)</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr"/>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>113 g (3.99 oz)</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr"/>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t>2.1, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr"/>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g/n</t>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~252 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>3.7 inches, 39.0 cm 2 (~56.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>MP3/AAC+/WAV/WMA9 player MP4/WMV9 player Document viewer/editor Facebook integration</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>2011, July. Released 2011, Q3</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD198" t="inlineStr">
+        <is>
+          <t>32GB (28GB user available)</t>
+        </is>
+      </c>
+      <c r="BE198" t="inlineStr">
+        <is>
+          <t>Citrus, Magenta, Black</t>
+        </is>
+      </c>
+      <c r="BF198" t="inlineStr">
+        <is>
+          <t>About 590 EUR</t>
+        </is>
+      </c>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI198" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BJ198" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.A 3.1 Mbps</t>
+        </is>
+      </c>
+      <c r="BK198" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="BL198" t="inlineStr">
+        <is>
+          <t>1.0 GHz Scorpion</t>
+        </is>
+      </c>
+      <c r="BM198" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Phone 7.5 Mango</t>
+        </is>
+      </c>
+      <c r="BN198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO198" t="inlineStr"/>
+      <c r="BP198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ198" t="inlineStr"/>
+      <c r="BR198" t="inlineStr">
+        <is>
+          <t>IPX8 water resistant</t>
+        </is>
+      </c>
+      <c r="BS198" t="inlineStr"/>
+      <c r="BT198" t="inlineStr"/>
+      <c r="BU198" t="inlineStr"/>
+      <c r="BV198" t="inlineStr"/>
+      <c r="BW198" t="inlineStr"/>
+      <c r="BX198" t="inlineStr"/>
+      <c r="BY198" t="inlineStr"/>
+      <c r="BZ198" t="inlineStr"/>
+      <c r="CA198" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="CB198" t="inlineStr"/>
+      <c r="CC198" t="inlineStr"/>
+      <c r="CD198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE198" t="inlineStr"/>
+      <c r="CF198" t="inlineStr"/>
+      <c r="CG198" t="inlineStr"/>
+      <c r="CH198" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI198" t="inlineStr"/>
+      <c r="CJ198" t="inlineStr"/>
+      <c r="CK198" t="inlineStr"/>
+      <c r="CL198" t="inlineStr"/>
+      <c r="CM198" t="inlineStr"/>
+      <c r="CN198" t="inlineStr"/>
+      <c r="CO198" t="inlineStr"/>
+      <c r="CP198" t="inlineStr"/>
+      <c r="CQ198" t="inlineStr"/>
+      <c r="CR198" t="inlineStr">
+        <is>
+          <t>Qualcomm MSM8655 Snapdragon S2</t>
+        </is>
+      </c>
+      <c r="CS198" t="inlineStr">
+        <is>
+          <t>Adreno 205</t>
+        </is>
+      </c>
+      <c r="CT198" t="inlineStr"/>
+      <c r="CU198" t="inlineStr"/>
+      <c r="CV198" t="inlineStr"/>
+      <c r="CW198" t="inlineStr"/>
+      <c r="CX198" t="inlineStr"/>
+      <c r="CY198" t="inlineStr"/>
+      <c r="CZ198" t="inlineStr"/>
+      <c r="DA198" t="inlineStr"/>
+      <c r="DB198" t="inlineStr"/>
+      <c r="DC198" t="inlineStr"/>
+      <c r="DD198" t="inlineStr">
+        <is>
+          <t>13.2 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE198" t="inlineStr"/>
+      <c r="DF198" t="inlineStr"/>
+      <c r="DG198" t="inlineStr"/>
+      <c r="DH198" t="inlineStr"/>
+      <c r="DI198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ198" t="inlineStr"/>
+      <c r="DK198" t="inlineStr"/>
+      <c r="DL198" t="inlineStr"/>
+      <c r="DM198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Toshiba Thrive</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Also known as Toshiba Regza AT300, Toshiba Tablet.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_thrive-3970.php</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2011, July</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>16GB | 32GB | 8GB</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>About 300 EUR</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Up to 7 h</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Non-removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>273 x 177 x 16 mm (10.75 x 6.97 x 0.63 in)</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr"/>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>725 g (1.60 lb)</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr"/>
+      <c r="AN199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr"/>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>miniUSB 2.0, USB 2.0</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>1280 x 800 pixels, 16:10 ratio (~149 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~61.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>HDMI port MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Document viewer Photo editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>HTML5, Adobe Flash</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, compass</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2011, July</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>SD, up to 32 GB</t>
+        </is>
+      </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>8GB 1GB RAM, 16GB 1GB RAM, 32GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>About 300 EUR</t>
+        </is>
+      </c>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI199" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ199" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/2 Mbps</t>
+        </is>
+      </c>
+      <c r="BK199" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL199" t="inlineStr">
+        <is>
+          <t>Dual-core 1.0 GHz Cortex-A9</t>
+        </is>
+      </c>
+      <c r="BM199" t="inlineStr">
+        <is>
+          <t>Android 3.0 (Honeycomb), upgradable to 3.2 (Honeycomb)</t>
+        </is>
+      </c>
+      <c r="BN199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO199" t="inlineStr"/>
+      <c r="BP199" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ199" t="inlineStr"/>
+      <c r="BR199" t="inlineStr"/>
+      <c r="BS199" t="inlineStr"/>
+      <c r="BT199" t="inlineStr"/>
+      <c r="BU199" t="inlineStr"/>
+      <c r="BV199" t="inlineStr"/>
+      <c r="BW199" t="inlineStr"/>
+      <c r="BX199" t="inlineStr"/>
+      <c r="BY199" t="inlineStr"/>
+      <c r="BZ199" t="inlineStr"/>
+      <c r="CA199" t="inlineStr"/>
+      <c r="CB199" t="inlineStr"/>
+      <c r="CC199" t="inlineStr"/>
+      <c r="CD199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE199" t="inlineStr"/>
+      <c r="CF199" t="inlineStr"/>
+      <c r="CG199" t="inlineStr"/>
+      <c r="CH199" t="inlineStr"/>
+      <c r="CI199" t="inlineStr"/>
+      <c r="CJ199" t="inlineStr"/>
+      <c r="CK199" t="inlineStr"/>
+      <c r="CL199" t="inlineStr"/>
+      <c r="CM199" t="inlineStr"/>
+      <c r="CN199" t="inlineStr"/>
+      <c r="CO199" t="inlineStr"/>
+      <c r="CP199" t="inlineStr"/>
+      <c r="CQ199" t="inlineStr"/>
+      <c r="CR199" t="inlineStr">
+        <is>
+          <t>Nvidia Tegra 2 T20</t>
+        </is>
+      </c>
+      <c r="CS199" t="inlineStr">
+        <is>
+          <t>ULP GeForce</t>
+        </is>
+      </c>
+      <c r="CT199" t="inlineStr"/>
+      <c r="CU199" t="inlineStr"/>
+      <c r="CV199" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CW199" t="inlineStr"/>
+      <c r="CX199" t="inlineStr"/>
+      <c r="CY199" t="inlineStr"/>
+      <c r="CZ199" t="inlineStr"/>
+      <c r="DA199" t="inlineStr"/>
+      <c r="DB199" t="inlineStr"/>
+      <c r="DC199" t="inlineStr"/>
+      <c r="DD199" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE199" t="inlineStr"/>
+      <c r="DF199" t="inlineStr"/>
+      <c r="DG199" t="inlineStr"/>
+      <c r="DH199" t="inlineStr"/>
+      <c r="DI199" t="inlineStr"/>
+      <c r="DJ199" t="inlineStr"/>
+      <c r="DK199" t="inlineStr"/>
+      <c r="DL199" t="inlineStr"/>
+      <c r="DM199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Toshiba K01</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Also known as Toshiba IS02</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_k01-3161.php</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2010, February. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>256MB | 512MB</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>122 x 65 x 12.9 mm (4.80 x 2.56 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>158 g (5.57 oz)</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr"/>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t>2.0, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr"/>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g</t>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>3D UI Shake control</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~228 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>4.1 inches, 47.8 cm 2 (~60.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>AMOLED, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Pocket Office MP3/WAV/WMA/eAAC+ player MP4/H.264/WMV player Organizer Facebook and YouTube apps Photo editor Voice memo/dial/commands Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (IE)</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>2010, February. Released 2010, April</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD200" t="inlineStr">
+        <is>
+          <t>256MB RAM, 512MB ROM</t>
+        </is>
+      </c>
+      <c r="BE200" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI200" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="BJ200" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/2 Mbps</t>
+        </is>
+      </c>
+      <c r="BK200" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL200" t="inlineStr">
+        <is>
+          <t>1.0 GHz Scorpion</t>
+        </is>
+      </c>
+      <c r="BM200" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.5 Professional, upgradable to Windows Mobile 6.5.3</t>
+        </is>
+      </c>
+      <c r="BN200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO200" t="inlineStr"/>
+      <c r="BP200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ200" t="inlineStr"/>
+      <c r="BR200" t="inlineStr"/>
+      <c r="BS200" t="inlineStr"/>
+      <c r="BT200" t="inlineStr"/>
+      <c r="BU200" t="inlineStr"/>
+      <c r="BV200" t="inlineStr"/>
+      <c r="BW200" t="inlineStr"/>
+      <c r="BX200" t="inlineStr"/>
+      <c r="BY200" t="inlineStr"/>
+      <c r="BZ200" t="inlineStr"/>
+      <c r="CA200" t="inlineStr"/>
+      <c r="CB200" t="inlineStr"/>
+      <c r="CC200" t="inlineStr"/>
+      <c r="CD200" t="inlineStr">
+        <is>
+          <t>480p@30fps</t>
+        </is>
+      </c>
+      <c r="CE200" t="inlineStr"/>
+      <c r="CF200" t="inlineStr"/>
+      <c r="CG200" t="inlineStr">
+        <is>
+          <t>0.37 W/kg (head)     0.36 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH200" t="inlineStr"/>
+      <c r="CI200" t="inlineStr"/>
+      <c r="CJ200" t="inlineStr"/>
+      <c r="CK200" t="inlineStr"/>
+      <c r="CL200" t="inlineStr"/>
+      <c r="CM200" t="inlineStr"/>
+      <c r="CN200" t="inlineStr"/>
+      <c r="CO200" t="inlineStr"/>
+      <c r="CP200" t="inlineStr"/>
+      <c r="CQ200" t="inlineStr"/>
+      <c r="CR200" t="inlineStr">
+        <is>
+          <t>Qualcomm QSD8250 Snapdragon S1</t>
+        </is>
+      </c>
+      <c r="CS200" t="inlineStr">
+        <is>
+          <t>Adreno 200</t>
+        </is>
+      </c>
+      <c r="CT200" t="inlineStr"/>
+      <c r="CU200" t="inlineStr"/>
+      <c r="CV200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW200" t="inlineStr"/>
+      <c r="CX200" t="inlineStr"/>
+      <c r="CY200" t="inlineStr"/>
+      <c r="CZ200" t="inlineStr"/>
+      <c r="DA200" t="inlineStr"/>
+      <c r="DB200" t="inlineStr"/>
+      <c r="DC200" t="inlineStr"/>
+      <c r="DD200" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE200" t="inlineStr"/>
+      <c r="DF200" t="inlineStr"/>
+      <c r="DG200" t="inlineStr"/>
+      <c r="DH200" t="inlineStr"/>
+      <c r="DI200" t="inlineStr"/>
+      <c r="DJ200" t="inlineStr"/>
+      <c r="DK200" t="inlineStr"/>
+      <c r="DL200" t="inlineStr"/>
+      <c r="DM200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Toshiba TG02</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_tg02-3159.php</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2010, February</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>256MB | 512MB</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>Up to 275 h (2G) / Up to 220 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Up to 5 h (2G) / Up to 4 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>126 x 66 x 9.9 mm (4.96 x 2.60 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr"/>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>119 g (4.20 oz)</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr"/>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>2.0, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr"/>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g</t>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>3D UI Shake control</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~228 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>4.1 inches, 47.8 cm 2 (~57.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Pocket Office Organizer MP3/eAAC+/WMA player MP4/H.264/WMV player Facebook and YouTube apps Photo editor Voice memo/dial/commands Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (IE)</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>2010, February</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD201" t="inlineStr">
+        <is>
+          <t>256MB RAM, 512MB ROM</t>
+        </is>
+      </c>
+      <c r="BE201" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF201" t="inlineStr"/>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI201" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ201" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/2 Mbps</t>
+        </is>
+      </c>
+      <c r="BK201" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL201" t="inlineStr">
+        <is>
+          <t>1.0 GHz Scorpion</t>
+        </is>
+      </c>
+      <c r="BM201" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.5 Professional</t>
+        </is>
+      </c>
+      <c r="BN201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO201" t="inlineStr"/>
+      <c r="BP201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ201" t="inlineStr"/>
+      <c r="BR201" t="inlineStr"/>
+      <c r="BS201" t="inlineStr"/>
+      <c r="BT201" t="inlineStr"/>
+      <c r="BU201" t="inlineStr"/>
+      <c r="BV201" t="inlineStr"/>
+      <c r="BW201" t="inlineStr"/>
+      <c r="BX201" t="inlineStr"/>
+      <c r="BY201" t="inlineStr"/>
+      <c r="BZ201" t="inlineStr"/>
+      <c r="CA201" t="inlineStr"/>
+      <c r="CB201" t="inlineStr"/>
+      <c r="CC201" t="inlineStr"/>
+      <c r="CD201" t="inlineStr">
+        <is>
+          <t>480p@30fps</t>
+        </is>
+      </c>
+      <c r="CE201" t="inlineStr"/>
+      <c r="CF201" t="inlineStr"/>
+      <c r="CG201" t="inlineStr">
+        <is>
+          <t>0.20 W/kg (head)     0.30 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH201" t="inlineStr"/>
+      <c r="CI201" t="inlineStr"/>
+      <c r="CJ201" t="inlineStr"/>
+      <c r="CK201" t="inlineStr"/>
+      <c r="CL201" t="inlineStr"/>
+      <c r="CM201" t="inlineStr"/>
+      <c r="CN201" t="inlineStr"/>
+      <c r="CO201" t="inlineStr"/>
+      <c r="CP201" t="inlineStr"/>
+      <c r="CQ201" t="inlineStr"/>
+      <c r="CR201" t="inlineStr">
+        <is>
+          <t>Qualcomm QSD8250 Snapdragon S1</t>
+        </is>
+      </c>
+      <c r="CS201" t="inlineStr">
+        <is>
+          <t>Adreno 200</t>
+        </is>
+      </c>
+      <c r="CT201" t="inlineStr"/>
+      <c r="CU201" t="inlineStr"/>
+      <c r="CV201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW201" t="inlineStr"/>
+      <c r="CX201" t="inlineStr"/>
+      <c r="CY201" t="inlineStr"/>
+      <c r="CZ201" t="inlineStr"/>
+      <c r="DA201" t="inlineStr"/>
+      <c r="DB201" t="inlineStr"/>
+      <c r="DC201" t="inlineStr"/>
+      <c r="DD201" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE201" t="inlineStr"/>
+      <c r="DF201" t="inlineStr"/>
+      <c r="DG201" t="inlineStr"/>
+      <c r="DH201" t="inlineStr"/>
+      <c r="DI201" t="inlineStr"/>
+      <c r="DJ201" t="inlineStr"/>
+      <c r="DK201" t="inlineStr"/>
+      <c r="DL201" t="inlineStr"/>
+      <c r="DM201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Toshiba TG01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_tg01-2662.php</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2009, January. Released 2009, June</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>256MB | 512MB</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>About 500 EUR</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>Up to 276 h (2G) / Up to 220 h (3G)</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Up to 5 h (2G) / Up to 4 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>130 x 70 x 9.9 mm (5.12 x 2.76 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr"/>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>129 g (4.55 oz)</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr"/>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr"/>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>3D UI Shake control</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~228 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>4.1 inches, 47.8 cm 2 (~52.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 256K colors (65K effective)</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Pocket Office MP3/eAAC+/WMA player MP4/H.264/WMV player Facebook and YouTube apps Photo editor Voice memo/dial Organizer Predictive text input</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (IE)</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>2009, January. Released 2009, June</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD202" t="inlineStr">
+        <is>
+          <t>256MB RAM, 512MB ROM</t>
+        </is>
+      </c>
+      <c r="BE202" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BF202" t="inlineStr">
+        <is>
+          <t>About 500 EUR</t>
+        </is>
+      </c>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI202" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="BJ202" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/2 Mbps</t>
+        </is>
+      </c>
+      <c r="BK202" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL202" t="inlineStr">
+        <is>
+          <t>1.0 GHz Scorpion</t>
+        </is>
+      </c>
+      <c r="BM202" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.1 Professional, upgradable to Windows Mobile 6.5</t>
+        </is>
+      </c>
+      <c r="BN202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO202" t="inlineStr"/>
+      <c r="BP202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ202" t="inlineStr"/>
+      <c r="BR202" t="inlineStr"/>
+      <c r="BS202" t="inlineStr"/>
+      <c r="BT202" t="inlineStr"/>
+      <c r="BU202" t="inlineStr"/>
+      <c r="BV202" t="inlineStr"/>
+      <c r="BW202" t="inlineStr"/>
+      <c r="BX202" t="inlineStr"/>
+      <c r="BY202" t="inlineStr"/>
+      <c r="BZ202" t="inlineStr"/>
+      <c r="CA202" t="inlineStr"/>
+      <c r="CB202" t="inlineStr"/>
+      <c r="CC202" t="inlineStr"/>
+      <c r="CD202" t="inlineStr">
+        <is>
+          <t>480p@30fps</t>
+        </is>
+      </c>
+      <c r="CE202" t="inlineStr"/>
+      <c r="CF202" t="inlineStr"/>
+      <c r="CG202" t="inlineStr">
+        <is>
+          <t>0.37 W/kg (head)     0.44 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH202" t="inlineStr"/>
+      <c r="CI202" t="inlineStr"/>
+      <c r="CJ202" t="inlineStr"/>
+      <c r="CK202" t="inlineStr"/>
+      <c r="CL202" t="inlineStr"/>
+      <c r="CM202" t="inlineStr"/>
+      <c r="CN202" t="inlineStr"/>
+      <c r="CO202" t="inlineStr"/>
+      <c r="CP202" t="inlineStr"/>
+      <c r="CQ202" t="inlineStr"/>
+      <c r="CR202" t="inlineStr">
+        <is>
+          <t>Qualcomm QSD8250 Snapdragon S1</t>
+        </is>
+      </c>
+      <c r="CS202" t="inlineStr">
+        <is>
+          <t>Adreno 200</t>
+        </is>
+      </c>
+      <c r="CT202" t="inlineStr"/>
+      <c r="CU202" t="inlineStr"/>
+      <c r="CV202" t="inlineStr"/>
+      <c r="CW202" t="inlineStr"/>
+      <c r="CX202" t="inlineStr"/>
+      <c r="CY202" t="inlineStr"/>
+      <c r="CZ202" t="inlineStr"/>
+      <c r="DA202" t="inlineStr"/>
+      <c r="DB202" t="inlineStr"/>
+      <c r="DC202" t="inlineStr"/>
+      <c r="DD202" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE202" t="inlineStr"/>
+      <c r="DF202" t="inlineStr"/>
+      <c r="DG202" t="inlineStr"/>
+      <c r="DH202" t="inlineStr"/>
+      <c r="DI202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DJ202" t="inlineStr"/>
+      <c r="DK202" t="inlineStr"/>
+      <c r="DL202" t="inlineStr"/>
+      <c r="DM202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Toshiba G810</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_g810-2273.php</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, September</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>128MB | 256MB</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>128MB</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1530 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>110 x 58 x 14 mm (4.33 x 2.28 x 0.55 in)</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr"/>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>120 g (4.23 oz)</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr"/>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr"/>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g</t>
+        </is>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>320 x 240 pixels, 4:3 ratio (~141 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>2.83 inches, 24.8 cm 2 (~38.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Pocket Office MP3/ACC+ player Photo editor Voice memo Organizer</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (IE)</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr"/>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, September</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD203" t="inlineStr">
+        <is>
+          <t>128MB RAM, 256MB ROM</t>
+        </is>
+      </c>
+      <c r="BE203" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF203" t="inlineStr">
+        <is>
+          <t>About 220 EUR</t>
+        </is>
+      </c>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI203" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ203" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/2 Mbps</t>
+        </is>
+      </c>
+      <c r="BK203" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL203" t="inlineStr">
+        <is>
+          <t>400 MHz ARM 11</t>
+        </is>
+      </c>
+      <c r="BM203" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.0 Professional</t>
+        </is>
+      </c>
+      <c r="BN203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO203" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="BP203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ203" t="inlineStr"/>
+      <c r="BR203" t="inlineStr"/>
+      <c r="BS203" t="inlineStr"/>
+      <c r="BT203" t="inlineStr"/>
+      <c r="BU203" t="inlineStr"/>
+      <c r="BV203" t="inlineStr"/>
+      <c r="BW203" t="inlineStr"/>
+      <c r="BX203" t="inlineStr"/>
+      <c r="BY203" t="inlineStr"/>
+      <c r="BZ203" t="inlineStr"/>
+      <c r="CA203" t="inlineStr"/>
+      <c r="CB203" t="inlineStr"/>
+      <c r="CC203" t="inlineStr"/>
+      <c r="CD203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE203" t="inlineStr"/>
+      <c r="CF203" t="inlineStr"/>
+      <c r="CG203" t="inlineStr"/>
+      <c r="CH203" t="inlineStr"/>
+      <c r="CI203" t="inlineStr"/>
+      <c r="CJ203" t="inlineStr"/>
+      <c r="CK203" t="inlineStr"/>
+      <c r="CL203" t="inlineStr"/>
+      <c r="CM203" t="inlineStr"/>
+      <c r="CN203" t="inlineStr"/>
+      <c r="CO203" t="inlineStr"/>
+      <c r="CP203" t="inlineStr"/>
+      <c r="CQ203" t="inlineStr"/>
+      <c r="CR203" t="inlineStr">
+        <is>
+          <t>Qualcomm MSM7200</t>
+        </is>
+      </c>
+      <c r="CS203" t="inlineStr"/>
+      <c r="CT203" t="inlineStr"/>
+      <c r="CU203" t="inlineStr"/>
+      <c r="CV203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW203" t="inlineStr"/>
+      <c r="CX203" t="inlineStr"/>
+      <c r="CY203" t="inlineStr"/>
+      <c r="CZ203" t="inlineStr"/>
+      <c r="DA203" t="inlineStr"/>
+      <c r="DB203" t="inlineStr"/>
+      <c r="DC203" t="inlineStr"/>
+      <c r="DD203" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE203" t="inlineStr"/>
+      <c r="DF203" t="inlineStr"/>
+      <c r="DG203" t="inlineStr"/>
+      <c r="DH203" t="inlineStr"/>
+      <c r="DI203" t="inlineStr"/>
+      <c r="DJ203" t="inlineStr"/>
+      <c r="DK203" t="inlineStr"/>
+      <c r="DL203" t="inlineStr"/>
+      <c r="DM203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Toshiba G910 / G920</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_g910___g920-2231.php</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2008, January. Released 2008, June</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>128MB | 256MB</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>128MB</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>About 190 EUR</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>Up to 330 h</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Up to 4 h 25 min</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1320 mAh battery</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>117 x 64 x 19.8 mm, 145 cc (4.61 x 2.52 x 0.78 in)</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>183 g (6.46 oz)</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr"/>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11b/g, VoIP over WLAN</t>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>800 x 480 pixels (Wide-VGA), 5:3 ratio (~311 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>3.0 inches, 25.6 cm 2 (~34.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 65K colors</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Pocket Office MP3/ACC+ player Photo editor Voice memo Organizer</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (Opera 8.6)</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr"/>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>2008, January. Released 2008, June</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD204" t="inlineStr">
+        <is>
+          <t>128MB RAM, 256MB ROM</t>
+        </is>
+      </c>
+      <c r="BE204" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF204" t="inlineStr">
+        <is>
+          <t>About 190 EUR</t>
+        </is>
+      </c>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI204" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="BJ204" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="BK204" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="BL204" t="inlineStr">
+        <is>
+          <t>400 MHz ARM 11</t>
+        </is>
+      </c>
+      <c r="BM204" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6 Professional</t>
+        </is>
+      </c>
+      <c r="BN204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO204" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="BP204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ204" t="inlineStr"/>
+      <c r="BR204" t="inlineStr"/>
+      <c r="BS204" t="inlineStr"/>
+      <c r="BT204" t="inlineStr"/>
+      <c r="BU204" t="inlineStr"/>
+      <c r="BV204" t="inlineStr"/>
+      <c r="BW204" t="inlineStr"/>
+      <c r="BX204" t="inlineStr"/>
+      <c r="BY204" t="inlineStr"/>
+      <c r="BZ204" t="inlineStr"/>
+      <c r="CA204" t="inlineStr"/>
+      <c r="CB204" t="inlineStr"/>
+      <c r="CC204" t="inlineStr"/>
+      <c r="CD204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CE204" t="inlineStr"/>
+      <c r="CF204" t="inlineStr"/>
+      <c r="CG204" t="inlineStr">
+        <is>
+          <t>0.33 W/kg (head)     0.66 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH204" t="inlineStr"/>
+      <c r="CI204" t="inlineStr"/>
+      <c r="CJ204" t="inlineStr"/>
+      <c r="CK204" t="inlineStr"/>
+      <c r="CL204" t="inlineStr"/>
+      <c r="CM204" t="inlineStr"/>
+      <c r="CN204" t="inlineStr"/>
+      <c r="CO204" t="inlineStr"/>
+      <c r="CP204" t="inlineStr"/>
+      <c r="CQ204" t="inlineStr"/>
+      <c r="CR204" t="inlineStr">
+        <is>
+          <t>Qualcomm MSM7200</t>
+        </is>
+      </c>
+      <c r="CS204" t="inlineStr">
+        <is>
+          <t>Adreno 130</t>
+        </is>
+      </c>
+      <c r="CT204" t="inlineStr"/>
+      <c r="CU204" t="inlineStr"/>
+      <c r="CV204" t="inlineStr">
+        <is>
+          <t>VGA videocall camera</t>
+        </is>
+      </c>
+      <c r="CW204" t="inlineStr"/>
+      <c r="CX204" t="inlineStr"/>
+      <c r="CY204" t="inlineStr"/>
+      <c r="CZ204" t="inlineStr"/>
+      <c r="DA204" t="inlineStr"/>
+      <c r="DB204" t="inlineStr"/>
+      <c r="DC204" t="inlineStr"/>
+      <c r="DD204" t="inlineStr">
+        <is>
+          <t>2 MP, AF</t>
+        </is>
+      </c>
+      <c r="DE204" t="inlineStr"/>
+      <c r="DF204" t="inlineStr"/>
+      <c r="DG204" t="inlineStr"/>
+      <c r="DH204" t="inlineStr"/>
+      <c r="DI204" t="inlineStr"/>
+      <c r="DJ204" t="inlineStr"/>
+      <c r="DK204" t="inlineStr"/>
+      <c r="DL204" t="inlineStr"/>
+      <c r="DM204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Toshiba</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>G450</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/toshiba_g450-2237.php</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:07 UTC</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="inlineStr"/>
+      <c r="AL205" t="inlineStr"/>
+      <c r="AM205" t="inlineStr"/>
+      <c r="AN205" t="inlineStr"/>
+      <c r="AO205" t="inlineStr"/>
+      <c r="AP205" t="inlineStr"/>
+      <c r="AQ205" t="inlineStr"/>
+      <c r="AR205" t="inlineStr"/>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AU205" t="inlineStr"/>
+      <c r="AV205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr"/>
+      <c r="AX205" t="inlineStr"/>
+      <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr"/>
+      <c r="BA205" t="inlineStr"/>
+      <c r="BB205" t="inlineStr"/>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
+      <c r="BM205" t="inlineStr"/>
+      <c r="BN205" t="inlineStr"/>
+      <c r="BO205" t="inlineStr"/>
+      <c r="BP205" t="inlineStr"/>
+      <c r="BQ205" t="inlineStr"/>
+      <c r="BR205" t="inlineStr"/>
+      <c r="BS205" t="inlineStr"/>
+      <c r="BT205" t="inlineStr"/>
+      <c r="BU205" t="inlineStr"/>
+      <c r="BV205" t="inlineStr"/>
+      <c r="BW205" t="inlineStr"/>
+      <c r="BX205" t="inlineStr"/>
+      <c r="BY205" t="inlineStr"/>
+      <c r="BZ205" t="inlineStr"/>
+      <c r="CA205" t="inlineStr"/>
+      <c r="CB205" t="inlineStr"/>
+      <c r="CC205" t="inlineStr"/>
+      <c r="CD205" t="inlineStr"/>
+      <c r="CE205" t="inlineStr"/>
+      <c r="CF205" t="inlineStr"/>
+      <c r="CG205" t="inlineStr"/>
+      <c r="CH205" t="inlineStr"/>
+      <c r="CI205" t="inlineStr"/>
+      <c r="CJ205" t="inlineStr"/>
+      <c r="CK205" t="inlineStr"/>
+      <c r="CL205" t="inlineStr"/>
+      <c r="CM205" t="inlineStr"/>
+      <c r="CN205" t="inlineStr"/>
+      <c r="CO205" t="inlineStr"/>
+      <c r="CP205" t="inlineStr"/>
+      <c r="CQ205" t="inlineStr"/>
+      <c r="CR205" t="inlineStr"/>
+      <c r="CS205" t="inlineStr"/>
+      <c r="CT205" t="inlineStr"/>
+      <c r="CU205" t="inlineStr"/>
+      <c r="CV205" t="inlineStr"/>
+      <c r="CW205" t="inlineStr"/>
+      <c r="CX205" t="inlineStr"/>
+      <c r="CY205" t="inlineStr"/>
+      <c r="CZ205" t="inlineStr"/>
+      <c r="DA205" t="inlineStr"/>
+      <c r="DB205" t="inlineStr"/>
+      <c r="DC205" t="inlineStr"/>
+      <c r="DD205" t="inlineStr"/>
+      <c r="DE205" t="inlineStr"/>
+      <c r="DF205" t="inlineStr"/>
+      <c r="DG205" t="inlineStr"/>
+      <c r="DH205" t="inlineStr"/>
+      <c r="DI205" t="inlineStr"/>
+      <c r="DJ205" t="inlineStr"/>
+      <c r="DK205" t="inlineStr"/>
+      <c r="DL205" t="inlineStr"/>
+      <c r="DM205" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM205"/>
+  <dimension ref="A1:DM226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63487,25 +63487,17 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="J184" t="n">
+        <v>130</v>
+      </c>
+      <c r="K184" t="n">
+        <v>48</v>
+      </c>
+      <c r="L184" t="n">
+        <v>15</v>
+      </c>
+      <c r="M184" t="n">
+        <v>115</v>
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
@@ -63515,10 +63507,8 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="V184" t="n">
+        <v>600</v>
       </c>
       <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr"/>
@@ -63776,55 +63766,37 @@
           <t>2025, January</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H185" t="n">
+        <v>2025</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
           <t>Available. Released 2025, January</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
+      <c r="J185" t="n">
+        <v>167</v>
+      </c>
+      <c r="K185" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L185" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M185" t="n">
+        <v>230</v>
+      </c>
+      <c r="N185" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P185" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>395</v>
       </c>
       <c r="R185" t="inlineStr">
         <is>
@@ -63836,20 +63808,14 @@
           <t>6GB</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="T185" t="n">
+        <v>50</v>
+      </c>
+      <c r="U185" t="n">
+        <v>16</v>
+      </c>
+      <c r="V185" t="n">
+        <v>3500</v>
       </c>
       <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr"/>
@@ -64151,55 +64117,37 @@
           <t>2007, March</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+      <c r="H186" t="n">
+        <v>2007</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>138.5</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="J186" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="K186" t="n">
+        <v>53</v>
+      </c>
+      <c r="L186" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M186" t="n">
+        <v>170</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O186" t="n">
+        <v>176</v>
+      </c>
+      <c r="P186" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>148</v>
       </c>
       <c r="R186" t="inlineStr">
         <is>
@@ -64207,16 +64155,12 @@
         </is>
       </c>
       <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="T186" t="n">
+        <v>3</v>
       </c>
       <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
+      <c r="V186" t="n">
+        <v>1280</v>
       </c>
       <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr"/>
@@ -64490,55 +64434,37 @@
           <t>2014, May. Released 2014, July</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H187" t="n">
+        <v>2014</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>119.8</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>354.4</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="J187" t="n">
+        <v>199</v>
+      </c>
+      <c r="K187" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="L187" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M187" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="N187" t="n">
+        <v>7</v>
+      </c>
+      <c r="O187" t="n">
+        <v>600</v>
+      </c>
+      <c r="P187" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>170</v>
       </c>
       <c r="R187" t="inlineStr">
         <is>
@@ -64552,10 +64478,8 @@
       </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="V187" t="n">
+        <v>3500</v>
       </c>
       <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr"/>
@@ -64674,11 +64598,7 @@
         </is>
       </c>
       <c r="BG187" t="inlineStr"/>
-      <c r="BH187" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr"/>
       <c r="BJ187" t="inlineStr"/>
       <c r="BK187" t="inlineStr">
@@ -64817,55 +64737,37 @@
           <t>2014, February. Released 2014, February</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H188" t="n">
+        <v>2014</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>119.8</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>354.4</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="J188" t="n">
+        <v>199</v>
+      </c>
+      <c r="K188" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="L188" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M188" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="N188" t="n">
+        <v>7</v>
+      </c>
+      <c r="O188" t="n">
+        <v>600</v>
+      </c>
+      <c r="P188" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>170</v>
       </c>
       <c r="R188" t="inlineStr">
         <is>
@@ -64879,10 +64781,8 @@
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="V188" t="n">
+        <v>3500</v>
       </c>
       <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr"/>
@@ -65005,11 +64905,7 @@
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
-      <c r="BH188" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr"/>
       <c r="BJ188" t="inlineStr"/>
       <c r="BK188" t="inlineStr">
@@ -65148,55 +65044,37 @@
           <t>2013, June. Released 2013, July</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="H189" t="n">
+        <v>2013</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>261.6</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>177.8</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>630.5</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="J189" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="K189" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="L189" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M189" t="n">
+        <v>630.5</v>
+      </c>
+      <c r="N189" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O189" t="n">
+        <v>2560</v>
+      </c>
+      <c r="P189" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>299</v>
       </c>
       <c r="R189" t="inlineStr">
         <is>
@@ -65208,15 +65086,11 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T189" t="n">
+        <v>8</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2</v>
       </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="inlineStr"/>
@@ -65344,11 +65218,7 @@
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
-      <c r="BH189" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr"/>
       <c r="BJ189" t="inlineStr"/>
       <c r="BK189" t="inlineStr">
@@ -65495,55 +65365,37 @@
           <t>2013, June. Released 2013, July</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="H190" t="n">
+        <v>2013</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>261.6</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>177.8</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>671.3</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="J190" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="K190" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="L190" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M190" t="n">
+        <v>671.3</v>
+      </c>
+      <c r="N190" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O190" t="n">
+        <v>2560</v>
+      </c>
+      <c r="P190" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>299</v>
       </c>
       <c r="R190" t="inlineStr">
         <is>
@@ -65555,15 +65407,11 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T190" t="n">
+        <v>8</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2</v>
       </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" t="inlineStr"/>
@@ -65691,11 +65539,7 @@
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
-      <c r="BH190" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr"/>
       <c r="BJ190" t="inlineStr"/>
       <c r="BK190" t="inlineStr">
@@ -65846,55 +65690,37 @@
           <t>2013, June. Released 2013, July</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="H191" t="n">
+        <v>2013</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>261.6</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>177.8</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>598.7</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="J191" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="K191" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="L191" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M191" t="n">
+        <v>598.7</v>
+      </c>
+      <c r="N191" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O191" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P191" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>149</v>
       </c>
       <c r="R191" t="inlineStr">
         <is>
@@ -65906,10 +65732,8 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T191" t="n">
+        <v>2</v>
       </c>
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
@@ -66038,11 +65862,7 @@
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
-      <c r="BH191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr"/>
       <c r="BJ191" t="inlineStr"/>
       <c r="BK191" t="inlineStr">
@@ -66185,55 +66005,37 @@
           <t>2012, December. Released 2012, December</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H192" t="n">
+        <v>2012</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>261.6</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>180.3</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>639.6</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="J192" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="K192" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="L192" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M192" t="n">
+        <v>639.6</v>
+      </c>
+      <c r="N192" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O192" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P192" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>149</v>
       </c>
       <c r="R192" t="inlineStr">
         <is>
@@ -66245,15 +66047,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T192" t="n">
+        <v>15</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2</v>
       </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr"/>
@@ -66377,11 +66175,7 @@
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
-      <c r="BH192" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr"/>
       <c r="BJ192" t="inlineStr"/>
       <c r="BK192" t="inlineStr">
@@ -66528,55 +66322,37 @@
           <t>2012, April. Released 2012, July</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H193" t="n">
+        <v>2012</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>343.8</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>211.2</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="J193" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="K193" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="L193" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M193" t="n">
+        <v>998</v>
+      </c>
+      <c r="N193" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P193" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>120</v>
       </c>
       <c r="R193" t="inlineStr">
         <is>
@@ -66588,15 +66364,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T193" t="n">
+        <v>5</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2</v>
       </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr"/>
@@ -66895,55 +66667,37 @@
           <t>2012, April. Released 2012, May</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H194" t="n">
+        <v>2012</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="J194" t="n">
+        <v>262</v>
+      </c>
+      <c r="K194" t="n">
+        <v>178</v>
+      </c>
+      <c r="L194" t="n">
+        <v>9</v>
+      </c>
+      <c r="M194" t="n">
+        <v>599</v>
+      </c>
+      <c r="N194" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P194" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>149</v>
       </c>
       <c r="R194" t="inlineStr">
         <is>
@@ -66955,15 +66709,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T194" t="n">
+        <v>5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2</v>
       </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr"/>
@@ -67095,11 +66845,7 @@
         </is>
       </c>
       <c r="BG194" t="inlineStr"/>
-      <c r="BH194" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH194" t="inlineStr"/>
       <c r="BI194" t="inlineStr"/>
       <c r="BJ194" t="inlineStr"/>
       <c r="BK194" t="inlineStr">
@@ -67250,55 +66996,37 @@
           <t>2012, April. Released 2012, July</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H195" t="n">
+        <v>2012</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>204.5</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>135.2</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+      <c r="J195" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="K195" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="L195" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M195" t="n">
+        <v>332</v>
+      </c>
+      <c r="N195" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O195" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P195" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>196</v>
       </c>
       <c r="R195" t="inlineStr">
         <is>
@@ -67310,15 +67038,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T195" t="n">
+        <v>5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2</v>
       </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr"/>
@@ -67605,55 +67329,37 @@
           <t>2011, September. Released 2012, January</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H196" t="n">
+        <v>2011</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="J196" t="n">
+        <v>256</v>
+      </c>
+      <c r="K196" t="n">
+        <v>176</v>
+      </c>
+      <c r="L196" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M196" t="n">
+        <v>558</v>
+      </c>
+      <c r="N196" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O196" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P196" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>149</v>
       </c>
       <c r="R196" t="inlineStr">
         <is>
@@ -67665,15 +67371,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T196" t="n">
+        <v>5</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2</v>
       </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" t="inlineStr"/>
@@ -67801,11 +67503,7 @@
         </is>
       </c>
       <c r="BG196" t="inlineStr"/>
-      <c r="BH196" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH196" t="inlineStr"/>
       <c r="BI196" t="inlineStr"/>
       <c r="BJ196" t="inlineStr"/>
       <c r="BK196" t="inlineStr">
@@ -67952,55 +67650,37 @@
           <t>2011, September. Released 2011, December</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H197" t="n">
+        <v>2011</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
+      <c r="J197" t="n">
+        <v>189</v>
+      </c>
+      <c r="K197" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="L197" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M197" t="n">
+        <v>400</v>
+      </c>
+      <c r="N197" t="n">
+        <v>7</v>
+      </c>
+      <c r="O197" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P197" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>216</v>
       </c>
       <c r="R197" t="inlineStr">
         <is>
@@ -68012,15 +67692,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T197" t="n">
+        <v>5</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2</v>
       </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" t="inlineStr"/>
@@ -68148,11 +67824,7 @@
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
-      <c r="BH197" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH197" t="inlineStr"/>
       <c r="BI197" t="inlineStr"/>
       <c r="BJ197" t="inlineStr"/>
       <c r="BK197" t="inlineStr">
@@ -68299,55 +67971,37 @@
           <t>2011, July. Released 2011, Q3</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H198" t="n">
+        <v>2011</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
+      <c r="J198" t="n">
+        <v>118</v>
+      </c>
+      <c r="K198" t="n">
+        <v>59</v>
+      </c>
+      <c r="L198" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M198" t="n">
+        <v>113</v>
+      </c>
+      <c r="N198" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O198" t="n">
+        <v>480</v>
+      </c>
+      <c r="P198" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>252</v>
       </c>
       <c r="R198" t="inlineStr">
         <is>
@@ -68355,16 +68009,12 @@
         </is>
       </c>
       <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T198" t="n">
+        <v>2</v>
       </c>
       <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
+      <c r="V198" t="n">
+        <v>1460</v>
       </c>
       <c r="W198" t="inlineStr"/>
       <c r="X198" t="inlineStr"/>
@@ -68654,55 +68304,37 @@
           <t>2010, June. Released 2011, July</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="H199" t="n">
+        <v>2010</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="J199" t="n">
+        <v>273</v>
+      </c>
+      <c r="K199" t="n">
+        <v>177</v>
+      </c>
+      <c r="L199" t="n">
+        <v>16</v>
+      </c>
+      <c r="M199" t="n">
+        <v>725</v>
+      </c>
+      <c r="N199" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O199" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P199" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>149</v>
       </c>
       <c r="R199" t="inlineStr">
         <is>
@@ -68714,15 +68346,11 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T199" t="n">
+        <v>5</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2</v>
       </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" t="inlineStr"/>
@@ -69001,55 +68629,37 @@
           <t>2010, February. Released 2010, April</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="H200" t="n">
+        <v>2010</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="J200" t="n">
+        <v>122</v>
+      </c>
+      <c r="K200" t="n">
+        <v>65</v>
+      </c>
+      <c r="L200" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M200" t="n">
+        <v>158</v>
+      </c>
+      <c r="N200" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O200" t="n">
+        <v>480</v>
+      </c>
+      <c r="P200" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>228</v>
       </c>
       <c r="R200" t="inlineStr">
         <is>
@@ -69061,26 +68671,18 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T200" t="n">
+        <v>15</v>
       </c>
       <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
+      <c r="V200" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W200" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="X200" t="n">
+        <v>0.36</v>
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="inlineStr"/>
@@ -69352,55 +68954,37 @@
           <t>2010, February</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="H201" t="n">
+        <v>2010</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="J201" t="n">
+        <v>126</v>
+      </c>
+      <c r="K201" t="n">
+        <v>66</v>
+      </c>
+      <c r="L201" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M201" t="n">
+        <v>119</v>
+      </c>
+      <c r="N201" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O201" t="n">
+        <v>480</v>
+      </c>
+      <c r="P201" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>228</v>
       </c>
       <c r="R201" t="inlineStr">
         <is>
@@ -69412,26 +68996,18 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T201" t="n">
+        <v>15</v>
       </c>
       <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+      <c r="V201" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X201" t="n">
+        <v>0.3</v>
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="inlineStr"/>
@@ -69707,55 +69283,37 @@
           <t>2009, January. Released 2009, June</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+      <c r="H202" t="n">
+        <v>2009</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="J202" t="n">
+        <v>130</v>
+      </c>
+      <c r="K202" t="n">
+        <v>70</v>
+      </c>
+      <c r="L202" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M202" t="n">
+        <v>129</v>
+      </c>
+      <c r="N202" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>480</v>
+      </c>
+      <c r="P202" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>228</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -69767,26 +69325,18 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T202" t="n">
+        <v>15</v>
       </c>
       <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
+      <c r="V202" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W202" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="X202" t="n">
+        <v>0.44</v>
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="inlineStr"/>
@@ -70070,55 +69620,37 @@
           <t>2008, February. Released 2008, September</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="H203" t="n">
+        <v>2008</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="J203" t="n">
+        <v>110</v>
+      </c>
+      <c r="K203" t="n">
+        <v>58</v>
+      </c>
+      <c r="L203" t="n">
+        <v>14</v>
+      </c>
+      <c r="M203" t="n">
+        <v>120</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O203" t="n">
+        <v>320</v>
+      </c>
+      <c r="P203" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>141</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -70130,16 +69662,12 @@
           <t>128MB</t>
         </is>
       </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T203" t="n">
+        <v>15</v>
       </c>
       <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
+      <c r="V203" t="n">
+        <v>1530</v>
       </c>
       <c r="W203" t="inlineStr"/>
       <c r="X203" t="inlineStr"/>
@@ -70413,55 +69941,37 @@
           <t>2008, January. Released 2008, June</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="H204" t="n">
+        <v>2008</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
+      <c r="J204" t="n">
+        <v>117</v>
+      </c>
+      <c r="K204" t="n">
+        <v>64</v>
+      </c>
+      <c r="L204" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M204" t="n">
+        <v>183</v>
+      </c>
+      <c r="N204" t="n">
+        <v>3</v>
+      </c>
+      <c r="O204" t="n">
+        <v>800</v>
+      </c>
+      <c r="P204" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>311</v>
       </c>
       <c r="R204" t="inlineStr">
         <is>
@@ -70473,26 +69983,18 @@
           <t>128MB</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T204" t="n">
+        <v>2</v>
       </c>
       <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="V204" t="n">
+        <v>1320</v>
+      </c>
+      <c r="W204" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X204" t="n">
+        <v>0.66</v>
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="inlineStr"/>
@@ -70883,6 +70385,7709 @@
       <c r="DL205" t="inlineStr"/>
       <c r="DM205" t="inlineStr"/>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Realme Narzo 30</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_narzo_30-10911.php</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2021, May 18</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 20</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>162.3</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>About 460 EUR</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>162.3 x 75.4 x 9.4 mm (6.39 x 2.97 x 0.37 in)</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr"/>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>192 g (6.77 oz)</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr"/>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr"/>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>IPS LCD, 90Hz, 580 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>2021, May 18</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 20</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD206" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 64GB 6GB RAM, 128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE206" t="inlineStr">
+        <is>
+          <t>Racing Blue, Racing Silver</t>
+        </is>
+      </c>
+      <c r="BF206" t="inlineStr">
+        <is>
+          <t>About 460 EUR</t>
+        </is>
+      </c>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI206" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ206" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK206" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL206" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.05 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM206" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO206" t="inlineStr"/>
+      <c r="BP206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ206" t="inlineStr">
+        <is>
+          <t>30W wired, 100% in 65 min</t>
+        </is>
+      </c>
+      <c r="BR206" t="inlineStr"/>
+      <c r="BS206" t="inlineStr"/>
+      <c r="BT206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU206" t="inlineStr"/>
+      <c r="BV206" t="inlineStr"/>
+      <c r="BW206" t="inlineStr"/>
+      <c r="BX206" t="inlineStr"/>
+      <c r="BY206" t="inlineStr"/>
+      <c r="BZ206" t="inlineStr"/>
+      <c r="CA206" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB206" t="inlineStr"/>
+      <c r="CC206" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD206" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE206" t="inlineStr"/>
+      <c r="CF206" t="inlineStr">
+        <is>
+          <t>RMX2156</t>
+        </is>
+      </c>
+      <c r="CG206" t="inlineStr"/>
+      <c r="CH206" t="inlineStr"/>
+      <c r="CI206" t="inlineStr"/>
+      <c r="CJ206" t="inlineStr"/>
+      <c r="CK206" t="inlineStr"/>
+      <c r="CL206" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM206" t="inlineStr"/>
+      <c r="CN206" t="inlineStr"/>
+      <c r="CO206" t="inlineStr"/>
+      <c r="CP206" t="inlineStr"/>
+      <c r="CQ206" t="inlineStr"/>
+      <c r="CR206" t="inlineStr">
+        <is>
+          <t>Mediatek MT6785V/CD Helio G95 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS206" t="inlineStr">
+        <is>
+          <t>Mali-G76 MC4</t>
+        </is>
+      </c>
+      <c r="CT206" t="inlineStr"/>
+      <c r="CU206" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV206" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.1, (wide), 1/3.06", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW206" t="inlineStr">
+        <is>
+          <t>1080p@30/120fps</t>
+        </is>
+      </c>
+      <c r="CX206" t="inlineStr"/>
+      <c r="CY206" t="inlineStr"/>
+      <c r="CZ206" t="inlineStr"/>
+      <c r="DA206" t="inlineStr"/>
+      <c r="DB206" t="inlineStr"/>
+      <c r="DC206" t="inlineStr"/>
+      <c r="DD206" t="inlineStr"/>
+      <c r="DE206" t="inlineStr"/>
+      <c r="DF206" t="inlineStr"/>
+      <c r="DG206" t="inlineStr"/>
+      <c r="DH206" t="inlineStr"/>
+      <c r="DI206" t="inlineStr"/>
+      <c r="DJ206" t="inlineStr"/>
+      <c r="DK206" t="inlineStr"/>
+      <c r="DL206" t="inlineStr"/>
+      <c r="DM206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Realme C20A</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_c20a-10901.php</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2021, May 11</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 11</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>165.2</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>165.2 x 76.4 x 8.9 mm (6.50 x 3.01 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr"/>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>190 g (6.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr"/>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>5.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr"/>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~80.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>2021, May 11</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 11</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD207" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BE207" t="inlineStr">
+        <is>
+          <t>Iron Grey, Lake Blue</t>
+        </is>
+      </c>
+      <c r="BF207" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI207" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ207" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK207" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL207" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM207" t="inlineStr">
+        <is>
+          <t>Android 10, Realme UI</t>
+        </is>
+      </c>
+      <c r="BN207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO207" t="inlineStr"/>
+      <c r="BP207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ207" t="inlineStr">
+        <is>
+          <t>Reverse wired</t>
+        </is>
+      </c>
+      <c r="BR207" t="inlineStr">
+        <is>
+          <t>Splash-resistant design</t>
+        </is>
+      </c>
+      <c r="BS207" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU207" t="inlineStr"/>
+      <c r="BV207" t="inlineStr"/>
+      <c r="BW207" t="inlineStr"/>
+      <c r="BX207" t="inlineStr"/>
+      <c r="BY207" t="inlineStr"/>
+      <c r="BZ207" t="inlineStr"/>
+      <c r="CA207" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB207" t="inlineStr"/>
+      <c r="CC207" t="inlineStr"/>
+      <c r="CD207" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE207" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF207" t="inlineStr"/>
+      <c r="CG207" t="inlineStr"/>
+      <c r="CH207" t="inlineStr"/>
+      <c r="CI207" t="inlineStr"/>
+      <c r="CJ207" t="inlineStr"/>
+      <c r="CK207" t="inlineStr"/>
+      <c r="CL207" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM207" t="inlineStr"/>
+      <c r="CN207" t="inlineStr"/>
+      <c r="CO207" t="inlineStr"/>
+      <c r="CP207" t="inlineStr"/>
+      <c r="CQ207" t="inlineStr"/>
+      <c r="CR207" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS207" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT207" t="inlineStr"/>
+      <c r="CU207" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV207" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1/5.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW207" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX207" t="inlineStr"/>
+      <c r="CY207" t="inlineStr"/>
+      <c r="CZ207" t="inlineStr"/>
+      <c r="DA207" t="inlineStr"/>
+      <c r="DB207" t="inlineStr"/>
+      <c r="DC207" t="inlineStr"/>
+      <c r="DD207" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, (wide), 1/4.0", 1.12µm, AF</t>
+        </is>
+      </c>
+      <c r="DE207" t="inlineStr"/>
+      <c r="DF207" t="inlineStr"/>
+      <c r="DG207" t="inlineStr"/>
+      <c r="DH207" t="inlineStr"/>
+      <c r="DI207" t="inlineStr"/>
+      <c r="DJ207" t="inlineStr"/>
+      <c r="DK207" t="inlineStr"/>
+      <c r="DL207" t="inlineStr"/>
+      <c r="DM207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Realme Watch 2 Pro</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_watch_2_pro-10917.php</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2021, May 20</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 29</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Li-Ion 390 mAh</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>38.9 x 25.2 x 12.7 mm (1.53 x 0.99 x 0.5 in)</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>40 g (1.41 oz)</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr"/>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5)</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>320 x 385 pixels (~286 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>1.75 inches</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>IPS LCD, 600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>Accelerometer, heart rate, SpO2</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>2021, May 20</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 29</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr">
+        <is>
+          <t>Space Grey, Metallic Silver</t>
+        </is>
+      </c>
+      <c r="BF208" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BJ208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BK208" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr">
+        <is>
+          <t>Proprietary OS</t>
+        </is>
+      </c>
+      <c r="BN208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO208" t="inlineStr"/>
+      <c r="BP208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ208" t="inlineStr"/>
+      <c r="BR208" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m) Not swim proof Compatible with standard 22mm straps</t>
+        </is>
+      </c>
+      <c r="BS208" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU208" t="inlineStr"/>
+      <c r="BV208" t="inlineStr"/>
+      <c r="BW208" t="inlineStr"/>
+      <c r="BX208" t="inlineStr"/>
+      <c r="BY208" t="inlineStr"/>
+      <c r="BZ208" t="inlineStr"/>
+      <c r="CA208" t="inlineStr"/>
+      <c r="CB208" t="inlineStr"/>
+      <c r="CC208" t="inlineStr"/>
+      <c r="CD208" t="inlineStr"/>
+      <c r="CE208" t="inlineStr">
+        <is>
+          <t>eMMC 4.5</t>
+        </is>
+      </c>
+      <c r="CF208" t="inlineStr"/>
+      <c r="CG208" t="inlineStr"/>
+      <c r="CH208" t="inlineStr"/>
+      <c r="CI208" t="inlineStr"/>
+      <c r="CJ208" t="inlineStr"/>
+      <c r="CK208" t="inlineStr"/>
+      <c r="CL208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="CM208" t="inlineStr"/>
+      <c r="CN208" t="inlineStr"/>
+      <c r="CO208" t="inlineStr"/>
+      <c r="CP208" t="inlineStr"/>
+      <c r="CQ208" t="inlineStr"/>
+      <c r="CR208" t="inlineStr"/>
+      <c r="CS208" t="inlineStr"/>
+      <c r="CT208" t="inlineStr"/>
+      <c r="CU208" t="inlineStr"/>
+      <c r="CV208" t="inlineStr"/>
+      <c r="CW208" t="inlineStr"/>
+      <c r="CX208" t="inlineStr"/>
+      <c r="CY208" t="inlineStr"/>
+      <c r="CZ208" t="inlineStr"/>
+      <c r="DA208" t="inlineStr"/>
+      <c r="DB208" t="inlineStr"/>
+      <c r="DC208" t="inlineStr"/>
+      <c r="DD208" t="inlineStr"/>
+      <c r="DE208" t="inlineStr"/>
+      <c r="DF208" t="inlineStr"/>
+      <c r="DG208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI208" t="inlineStr"/>
+      <c r="DJ208" t="inlineStr"/>
+      <c r="DK208" t="inlineStr"/>
+      <c r="DL208" t="inlineStr"/>
+      <c r="DM208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Realme Watch 2</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_watch_2-10888.php</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2021, April 30</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 20</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>35.7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Li-Ion 315 mAh</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>35.7 x 25.8 x 12.2 mm (1.41 x 1.02 x 0.48 in)</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr"/>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>38 g (1.34 oz)</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr"/>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>320 x 320 pixels (~323 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>1.4 inches</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>IPS LCD, 600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>Accelerometer, heart rate, SpO2</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>2021, April 30</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 20</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF209" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI209" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BJ209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BK209" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr">
+        <is>
+          <t>Proprietary OS</t>
+        </is>
+      </c>
+      <c r="BN209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO209" t="inlineStr"/>
+      <c r="BP209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ209" t="inlineStr"/>
+      <c r="BR209" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m) Not swim proof Compatible with standard 22mm straps</t>
+        </is>
+      </c>
+      <c r="BS209" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU209" t="inlineStr"/>
+      <c r="BV209" t="inlineStr"/>
+      <c r="BW209" t="inlineStr"/>
+      <c r="BX209" t="inlineStr"/>
+      <c r="BY209" t="inlineStr"/>
+      <c r="BZ209" t="inlineStr"/>
+      <c r="CA209" t="inlineStr"/>
+      <c r="CB209" t="inlineStr"/>
+      <c r="CC209" t="inlineStr"/>
+      <c r="CD209" t="inlineStr"/>
+      <c r="CE209" t="inlineStr">
+        <is>
+          <t>eMMC 4.5</t>
+        </is>
+      </c>
+      <c r="CF209" t="inlineStr">
+        <is>
+          <t>RMW2008</t>
+        </is>
+      </c>
+      <c r="CG209" t="inlineStr"/>
+      <c r="CH209" t="inlineStr"/>
+      <c r="CI209" t="inlineStr"/>
+      <c r="CJ209" t="inlineStr"/>
+      <c r="CK209" t="inlineStr"/>
+      <c r="CL209" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="CM209" t="inlineStr"/>
+      <c r="CN209" t="inlineStr"/>
+      <c r="CO209" t="inlineStr"/>
+      <c r="CP209" t="inlineStr"/>
+      <c r="CQ209" t="inlineStr"/>
+      <c r="CR209" t="inlineStr"/>
+      <c r="CS209" t="inlineStr"/>
+      <c r="CT209" t="inlineStr"/>
+      <c r="CU209" t="inlineStr"/>
+      <c r="CV209" t="inlineStr"/>
+      <c r="CW209" t="inlineStr"/>
+      <c r="CX209" t="inlineStr"/>
+      <c r="CY209" t="inlineStr"/>
+      <c r="CZ209" t="inlineStr"/>
+      <c r="DA209" t="inlineStr"/>
+      <c r="DB209" t="inlineStr"/>
+      <c r="DC209" t="inlineStr"/>
+      <c r="DD209" t="inlineStr"/>
+      <c r="DE209" t="inlineStr"/>
+      <c r="DF209" t="inlineStr"/>
+      <c r="DG209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DH209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI209" t="inlineStr"/>
+      <c r="DJ209" t="inlineStr"/>
+      <c r="DK209" t="inlineStr"/>
+      <c r="DL209" t="inlineStr"/>
+      <c r="DM209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Realme Q3 Pro 5G</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_q3_pro_5g-10871.php</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 29</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>158.5</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>158.5 x 73.3 x 8.4 mm (6.24 x 2.89 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr"/>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>179 g (6.31 oz)</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr"/>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>6.43 inches, 99.8 cm 2 (~85.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 120Hz</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 29</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD210" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE210" t="inlineStr">
+        <is>
+          <t>Black, Blue, Electric Yellow</t>
+        </is>
+      </c>
+      <c r="BF210" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI210" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ210" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK210" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / CDMA2000 / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL210" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.6 GHz Cortex-A78 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM210" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO210" t="inlineStr"/>
+      <c r="BP210" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers (Dolby Atmos)</t>
+        </is>
+      </c>
+      <c r="BQ210" t="inlineStr">
+        <is>
+          <t>30W wired, 100% in 59 min</t>
+        </is>
+      </c>
+      <c r="BR210" t="inlineStr"/>
+      <c r="BS210" t="inlineStr"/>
+      <c r="BT210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU210" t="inlineStr"/>
+      <c r="BV210" t="inlineStr"/>
+      <c r="BW210" t="inlineStr"/>
+      <c r="BX210" t="inlineStr"/>
+      <c r="BY210" t="inlineStr"/>
+      <c r="BZ210" t="inlineStr"/>
+      <c r="CA210" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB210" t="inlineStr"/>
+      <c r="CC210" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/1.73", 0.8µm, PDAF 8 MP, f/2.3, 16mm, 119˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD210" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE210" t="inlineStr">
+        <is>
+          <t>UFS 3.1</t>
+        </is>
+      </c>
+      <c r="CF210" t="inlineStr">
+        <is>
+          <t>RMX2205</t>
+        </is>
+      </c>
+      <c r="CG210" t="inlineStr"/>
+      <c r="CH210" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI210" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CJ210" t="inlineStr"/>
+      <c r="CK210" t="inlineStr"/>
+      <c r="CL210" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 28, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM210" t="inlineStr">
+        <is>
+          <t>1, 28, 40, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN210" t="inlineStr"/>
+      <c r="CO210" t="inlineStr"/>
+      <c r="CP210" t="inlineStr"/>
+      <c r="CQ210" t="inlineStr"/>
+      <c r="CR210" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 1100 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS210" t="inlineStr">
+        <is>
+          <t>Mali-G77 MC9</t>
+        </is>
+      </c>
+      <c r="CT210" t="inlineStr"/>
+      <c r="CU210" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV210" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW210" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX210" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY210" t="inlineStr"/>
+      <c r="CZ210" t="inlineStr"/>
+      <c r="DA210" t="inlineStr"/>
+      <c r="DB210" t="inlineStr"/>
+      <c r="DC210" t="inlineStr"/>
+      <c r="DD210" t="inlineStr"/>
+      <c r="DE210" t="inlineStr"/>
+      <c r="DF210" t="inlineStr"/>
+      <c r="DG210" t="inlineStr"/>
+      <c r="DH210" t="inlineStr"/>
+      <c r="DI210" t="inlineStr"/>
+      <c r="DJ210" t="inlineStr"/>
+      <c r="DK210" t="inlineStr"/>
+      <c r="DL210" t="inlineStr"/>
+      <c r="DM210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Realme Q3 5G</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_q3_5g-10870.php</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 29</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>162.5 x 74.8 x 8.8 mm (6.40 x 2.94 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr"/>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>189 g (6.67 oz)</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr"/>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>IPS LCD, 120Hz, 480 nits (typ), 600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 29</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD211" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE211" t="inlineStr">
+        <is>
+          <t>Black, Silver</t>
+        </is>
+      </c>
+      <c r="BF211" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI211" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ211" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK211" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / CDMA2000 / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL211" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Kryo 570 &amp; 6x1.8 GHz Kryo 570)</t>
+        </is>
+      </c>
+      <c r="BM211" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO211" t="inlineStr"/>
+      <c r="BP211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ211" t="inlineStr">
+        <is>
+          <t>30W wired, 100% in 63 min</t>
+        </is>
+      </c>
+      <c r="BR211" t="inlineStr"/>
+      <c r="BS211" t="inlineStr"/>
+      <c r="BT211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU211" t="inlineStr"/>
+      <c r="BV211" t="inlineStr"/>
+      <c r="BW211" t="inlineStr"/>
+      <c r="BX211" t="inlineStr"/>
+      <c r="BY211" t="inlineStr"/>
+      <c r="BZ211" t="inlineStr"/>
+      <c r="CA211" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB211" t="inlineStr"/>
+      <c r="CC211" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF 8 MP, f/2.3, 16mm, 119˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD211" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60fps; gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE211" t="inlineStr"/>
+      <c r="CF211" t="inlineStr">
+        <is>
+          <t>RMX3161</t>
+        </is>
+      </c>
+      <c r="CG211" t="inlineStr"/>
+      <c r="CH211" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI211" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CJ211" t="inlineStr"/>
+      <c r="CK211" t="inlineStr"/>
+      <c r="CL211" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM211" t="inlineStr">
+        <is>
+          <t>1, 28, 41, 78 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN211" t="inlineStr"/>
+      <c r="CO211" t="inlineStr"/>
+      <c r="CP211" t="inlineStr"/>
+      <c r="CQ211" t="inlineStr"/>
+      <c r="CR211" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7225 Snapdragon 750G 5G (8 nm)</t>
+        </is>
+      </c>
+      <c r="CS211" t="inlineStr">
+        <is>
+          <t>Adreno 619</t>
+        </is>
+      </c>
+      <c r="CT211" t="inlineStr"/>
+      <c r="CU211" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV211" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.1, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW211" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX211" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY211" t="inlineStr"/>
+      <c r="CZ211" t="inlineStr"/>
+      <c r="DA211" t="inlineStr"/>
+      <c r="DB211" t="inlineStr"/>
+      <c r="DC211" t="inlineStr"/>
+      <c r="DD211" t="inlineStr"/>
+      <c r="DE211" t="inlineStr"/>
+      <c r="DF211" t="inlineStr"/>
+      <c r="DG211" t="inlineStr"/>
+      <c r="DH211" t="inlineStr"/>
+      <c r="DI211" t="inlineStr"/>
+      <c r="DJ211" t="inlineStr"/>
+      <c r="DK211" t="inlineStr"/>
+      <c r="DL211" t="inlineStr"/>
+      <c r="DM211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Realme Q3i 5G</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_q3i_5g-10872.php</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 22</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>162.5 x 74.8 x 8.5 mm (6.40 x 2.94 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>185 g (6.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr"/>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>IPS LCD, 90Hz, 480 nits (typ), 600 nits</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr"/>
+      <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>2021, April 22</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 22</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD212" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE212" t="inlineStr">
+        <is>
+          <t>Supersonic Blue, Supersonic Black</t>
+        </is>
+      </c>
+      <c r="BF212" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="BG212" t="inlineStr"/>
+      <c r="BH212" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI212" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ212" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK212" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / CDMA2000 / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL212" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM212" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO212" t="inlineStr"/>
+      <c r="BP212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ212" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR212" t="inlineStr"/>
+      <c r="BS212" t="inlineStr"/>
+      <c r="BT212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU212" t="inlineStr"/>
+      <c r="BV212" t="inlineStr"/>
+      <c r="BW212" t="inlineStr"/>
+      <c r="BX212" t="inlineStr"/>
+      <c r="BY212" t="inlineStr"/>
+      <c r="BZ212" t="inlineStr"/>
+      <c r="CA212" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB212" t="inlineStr"/>
+      <c r="CC212" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD212" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE212" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF212" t="inlineStr">
+        <is>
+          <t>RMX3042</t>
+        </is>
+      </c>
+      <c r="CG212" t="inlineStr"/>
+      <c r="CH212" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI212" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CJ212" t="inlineStr"/>
+      <c r="CK212" t="inlineStr"/>
+      <c r="CL212" t="inlineStr">
+        <is>
+          <t>LTE</t>
+        </is>
+      </c>
+      <c r="CM212" t="inlineStr">
+        <is>
+          <t>SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN212" t="inlineStr"/>
+      <c r="CO212" t="inlineStr"/>
+      <c r="CP212" t="inlineStr"/>
+      <c r="CQ212" t="inlineStr"/>
+      <c r="CR212" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 700 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS212" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT212" t="inlineStr"/>
+      <c r="CU212" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV212" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.1, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW212" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX212" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY212" t="inlineStr"/>
+      <c r="CZ212" t="inlineStr"/>
+      <c r="DA212" t="inlineStr"/>
+      <c r="DB212" t="inlineStr"/>
+      <c r="DC212" t="inlineStr"/>
+      <c r="DD212" t="inlineStr"/>
+      <c r="DE212" t="inlineStr"/>
+      <c r="DF212" t="inlineStr"/>
+      <c r="DG212" t="inlineStr"/>
+      <c r="DH212" t="inlineStr"/>
+      <c r="DI212" t="inlineStr"/>
+      <c r="DJ212" t="inlineStr"/>
+      <c r="DK212" t="inlineStr"/>
+      <c r="DL212" t="inlineStr"/>
+      <c r="DM212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Realme 8 5G</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_8_5g-10846.php</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2021, April 21</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 28</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>162.5 x 74.8 x 8.5 mm (6.40 x 2.94 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>185 g (6.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr"/>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>IPS LCD, 90Hz, 480 nits (typ), 600 nits</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>2021, April 21</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 28</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD213" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE213" t="inlineStr">
+        <is>
+          <t>Supersonic Blue, Supersonic Black</t>
+        </is>
+      </c>
+      <c r="BF213" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI213" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ213" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK213" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL213" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM213" t="inlineStr">
+        <is>
+          <t>Android 11, upgradable to Android 13, Realme UI 4.0</t>
+        </is>
+      </c>
+      <c r="BN213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO213" t="inlineStr"/>
+      <c r="BP213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ213" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR213" t="inlineStr"/>
+      <c r="BS213" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU213" t="inlineStr"/>
+      <c r="BV213" t="inlineStr"/>
+      <c r="BW213" t="inlineStr"/>
+      <c r="BX213" t="inlineStr"/>
+      <c r="BY213" t="inlineStr"/>
+      <c r="BZ213" t="inlineStr"/>
+      <c r="CA213" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB213" t="inlineStr"/>
+      <c r="CC213" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD213" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE213" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF213" t="inlineStr">
+        <is>
+          <t>RMX3241</t>
+        </is>
+      </c>
+      <c r="CG213" t="inlineStr"/>
+      <c r="CH213" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 28, 34, 38, 39, 40, 41 - India</t>
+        </is>
+      </c>
+      <c r="CI213" t="inlineStr">
+        <is>
+          <t>1, 28, 41, 77, 78 SA/NSA - India</t>
+        </is>
+      </c>
+      <c r="CJ213" t="inlineStr"/>
+      <c r="CK213" t="inlineStr"/>
+      <c r="CL213" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 18, 19, 20, 26, 28, 38, 39, 40, 41, 66 - International</t>
+        </is>
+      </c>
+      <c r="CM213" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41, 77, 78 SA/NSA - International</t>
+        </is>
+      </c>
+      <c r="CN213" t="inlineStr"/>
+      <c r="CO213" t="inlineStr">
+        <is>
+          <t>Contrast ratio: 1413:1 (nominal)</t>
+        </is>
+      </c>
+      <c r="CP213" t="inlineStr">
+        <is>
+          <t>-27.8 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CQ213" t="inlineStr">
+        <is>
+          <t>AnTuTu: 302059 (v8), 361505 (v9) GeekBench: 1784 (v5.1) GFXBench: 13fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR213" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 700 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS213" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT213" t="inlineStr"/>
+      <c r="CU213" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV213" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.1, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW213" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX213" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY213" t="inlineStr"/>
+      <c r="CZ213" t="inlineStr"/>
+      <c r="DA213" t="inlineStr"/>
+      <c r="DB213" t="inlineStr"/>
+      <c r="DC213" t="inlineStr"/>
+      <c r="DD213" t="inlineStr"/>
+      <c r="DE213" t="inlineStr"/>
+      <c r="DF213" t="inlineStr"/>
+      <c r="DG213" t="inlineStr"/>
+      <c r="DH213" t="inlineStr"/>
+      <c r="DI213" t="inlineStr"/>
+      <c r="DJ213" t="inlineStr"/>
+      <c r="DK213" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL213" t="inlineStr"/>
+      <c r="DM213" t="inlineStr">
+        <is>
+          <t>Endurance rating 118h</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Realme X7 Pro Ultra</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Also known as Realme X7 Pro Extreme</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_x7_pro_ultra-10826.php</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2021, April 02</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 02</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>159.9</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>12GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>About 310 EUR</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>159.9 x 73.4 x 7.8 mm (6.30 x 2.89 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr"/>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>170 g (6.00 oz)</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~402 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>6.55 inches, 103.6 cm 2 (~88.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 90Hz, 1200 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr"/>
+      <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>2021, April 02</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 02</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD214" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE214" t="inlineStr">
+        <is>
+          <t>Black, Aurora</t>
+        </is>
+      </c>
+      <c r="BF214" t="inlineStr">
+        <is>
+          <t>About 310 EUR</t>
+        </is>
+      </c>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI214" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ214" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK214" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL214" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.6 GHz Cortex-A77 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM214" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO214" t="inlineStr"/>
+      <c r="BP214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ214" t="inlineStr">
+        <is>
+          <t>65W wired, 100% in 35 min</t>
+        </is>
+      </c>
+      <c r="BR214" t="inlineStr"/>
+      <c r="BS214" t="inlineStr"/>
+      <c r="BT214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU214" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="BV214" t="inlineStr"/>
+      <c r="BW214" t="inlineStr"/>
+      <c r="BX214" t="inlineStr"/>
+      <c r="BY214" t="inlineStr"/>
+      <c r="BZ214" t="inlineStr"/>
+      <c r="CA214" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB214" t="inlineStr"/>
+      <c r="CC214" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/2.0", 0.7µm, PDAF 8 MP, f/2.3, 119˚, 16mm (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD214" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE214" t="inlineStr"/>
+      <c r="CF214" t="inlineStr">
+        <is>
+          <t>RMX3115</t>
+        </is>
+      </c>
+      <c r="CG214" t="inlineStr"/>
+      <c r="CH214" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI214" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ214" t="inlineStr"/>
+      <c r="CK214" t="inlineStr"/>
+      <c r="CL214" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 18, 19, 26, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM214" t="inlineStr">
+        <is>
+          <t>1, 3, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN214" t="inlineStr"/>
+      <c r="CO214" t="inlineStr"/>
+      <c r="CP214" t="inlineStr"/>
+      <c r="CQ214" t="inlineStr"/>
+      <c r="CR214" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 1000+ (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS214" t="inlineStr">
+        <is>
+          <t>Mali-G77 MC9</t>
+        </is>
+      </c>
+      <c r="CT214" t="inlineStr"/>
+      <c r="CU214" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV214" t="inlineStr">
+        <is>
+          <t>32 MP, f/2.5, 26mm (wide), 1/2.8", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CW214" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX214" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY214" t="inlineStr"/>
+      <c r="CZ214" t="inlineStr"/>
+      <c r="DA214" t="inlineStr"/>
+      <c r="DB214" t="inlineStr"/>
+      <c r="DC214" t="inlineStr"/>
+      <c r="DD214" t="inlineStr"/>
+      <c r="DE214" t="inlineStr"/>
+      <c r="DF214" t="inlineStr"/>
+      <c r="DG214" t="inlineStr"/>
+      <c r="DH214" t="inlineStr"/>
+      <c r="DI214" t="inlineStr"/>
+      <c r="DJ214" t="inlineStr"/>
+      <c r="DK214" t="inlineStr"/>
+      <c r="DL214" t="inlineStr"/>
+      <c r="DM214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Realme GT Neo</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_gt_neo-10812.php</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2021, March 31</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 08</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>158.5</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>12GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>158.5 x 73.3 x 8.4 mm (6.24 x 2.89 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>179 g (6.31 oz)</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>6.43 inches, 99.8 cm 2 (~85.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 120Hz</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>2021, March 31</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 08</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>Black, Silver, Aurora</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI215" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ215" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK215" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL215" t="inlineStr">
+        <is>
+          <t>Octa-core (1x3.0 GHz Cortex-A78 &amp; 3x2.6 GHz Cortex-A78 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM215" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO215" t="inlineStr"/>
+      <c r="BP215" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ215" t="inlineStr">
+        <is>
+          <t>50W wired, 50% in 16 min</t>
+        </is>
+      </c>
+      <c r="BR215" t="inlineStr"/>
+      <c r="BS215" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU215" t="inlineStr"/>
+      <c r="BV215" t="inlineStr"/>
+      <c r="BW215" t="inlineStr"/>
+      <c r="BX215" t="inlineStr"/>
+      <c r="BY215" t="inlineStr"/>
+      <c r="BZ215" t="inlineStr"/>
+      <c r="CA215" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB215" t="inlineStr"/>
+      <c r="CC215" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/1.73", 0.8µm, PDAF 8 MP, f/2.3, 16mm, 119˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD215" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60/480fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE215" t="inlineStr">
+        <is>
+          <t>UFS 3.1</t>
+        </is>
+      </c>
+      <c r="CF215" t="inlineStr">
+        <is>
+          <t>RMX3031</t>
+        </is>
+      </c>
+      <c r="CG215" t="inlineStr"/>
+      <c r="CH215" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI215" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ215" t="inlineStr"/>
+      <c r="CK215" t="inlineStr"/>
+      <c r="CL215" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 28, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM215" t="inlineStr">
+        <is>
+          <t>1, 28, 40, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN215" t="inlineStr"/>
+      <c r="CO215" t="inlineStr"/>
+      <c r="CP215" t="inlineStr"/>
+      <c r="CQ215" t="inlineStr"/>
+      <c r="CR215" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 1200 (6 nm)</t>
+        </is>
+      </c>
+      <c r="CS215" t="inlineStr">
+        <is>
+          <t>Mali-G77 MC9</t>
+        </is>
+      </c>
+      <c r="CT215" t="inlineStr"/>
+      <c r="CU215" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV215" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, 26mm (wide), 1/3.0", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW215" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX215" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY215" t="inlineStr"/>
+      <c r="CZ215" t="inlineStr"/>
+      <c r="DA215" t="inlineStr"/>
+      <c r="DB215" t="inlineStr"/>
+      <c r="DC215" t="inlineStr"/>
+      <c r="DD215" t="inlineStr"/>
+      <c r="DE215" t="inlineStr"/>
+      <c r="DF215" t="inlineStr"/>
+      <c r="DG215" t="inlineStr"/>
+      <c r="DH215" t="inlineStr"/>
+      <c r="DI215" t="inlineStr"/>
+      <c r="DJ215" t="inlineStr"/>
+      <c r="DK215" t="inlineStr"/>
+      <c r="DL215" t="inlineStr"/>
+      <c r="DM215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Realme V13 5G</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_v13_5g-10822.php</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2021, March 31</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 02</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>162.5 x 74.8 x 8.5 mm (6.40 x 2.94 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr"/>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>185 g (6.53 oz)</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr"/>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>IPS LCD, 90Hz, 480 nits (typ), 600 nits</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr"/>
+      <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>2021, March 31</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 02</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>Blue, Gray</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI216" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ216" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK216" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL216" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM216" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO216" t="inlineStr"/>
+      <c r="BP216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ216" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR216" t="inlineStr"/>
+      <c r="BS216" t="inlineStr"/>
+      <c r="BT216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU216" t="inlineStr"/>
+      <c r="BV216" t="inlineStr"/>
+      <c r="BW216" t="inlineStr"/>
+      <c r="BX216" t="inlineStr"/>
+      <c r="BY216" t="inlineStr"/>
+      <c r="BZ216" t="inlineStr"/>
+      <c r="CA216" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB216" t="inlineStr"/>
+      <c r="CC216" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD216" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE216" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF216" t="inlineStr"/>
+      <c r="CG216" t="inlineStr"/>
+      <c r="CH216" t="inlineStr"/>
+      <c r="CI216" t="inlineStr"/>
+      <c r="CJ216" t="inlineStr"/>
+      <c r="CK216" t="inlineStr"/>
+      <c r="CL216" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 28, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM216" t="inlineStr">
+        <is>
+          <t>1, 28, 41, 77, 78 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN216" t="inlineStr"/>
+      <c r="CO216" t="inlineStr"/>
+      <c r="CP216" t="inlineStr"/>
+      <c r="CQ216" t="inlineStr"/>
+      <c r="CR216" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 700 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS216" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT216" t="inlineStr"/>
+      <c r="CU216" t="inlineStr"/>
+      <c r="CV216" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW216" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX216" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY216" t="inlineStr"/>
+      <c r="CZ216" t="inlineStr"/>
+      <c r="DA216" t="inlineStr"/>
+      <c r="DB216" t="inlineStr"/>
+      <c r="DC216" t="inlineStr"/>
+      <c r="DD216" t="inlineStr"/>
+      <c r="DE216" t="inlineStr"/>
+      <c r="DF216" t="inlineStr"/>
+      <c r="DG216" t="inlineStr"/>
+      <c r="DH216" t="inlineStr"/>
+      <c r="DI216" t="inlineStr"/>
+      <c r="DJ216" t="inlineStr"/>
+      <c r="DK216" t="inlineStr"/>
+      <c r="DL216" t="inlineStr"/>
+      <c r="DM216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Realme 8 Pro</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_8_pro-10809.php</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2021, March 24</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 25</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>160.6</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>About 550 EUR</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>160.6 x 73.9 x 8.1 mm (6.32 x 2.91 x 0.32 in)</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr"/>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>176 g (6.21 oz)</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr"/>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~411 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>6.4 inches, 98.9 cm 2 (~83.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 430 nits (typ), 1000 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr"/>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>2021, March 24</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 25</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>Infinite Blue, Infinite Black, Punk Black, Illuminating Yellow</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>About 550 EUR</t>
+        </is>
+      </c>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI217" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ217" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK217" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL217" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.3 GHz Kryo 465 Gold &amp; 6x1.8 GHz Kryo 465 Silver)</t>
+        </is>
+      </c>
+      <c r="BM217" t="inlineStr">
+        <is>
+          <t>Android 11, upgradable to Android 12, Realme UI 3.0</t>
+        </is>
+      </c>
+      <c r="BN217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO217" t="inlineStr"/>
+      <c r="BP217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ217" t="inlineStr">
+        <is>
+          <t>50W wired, 50% in 17 min, 100% in 47 min</t>
+        </is>
+      </c>
+      <c r="BR217" t="inlineStr"/>
+      <c r="BS217" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT217" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU217" t="inlineStr"/>
+      <c r="BV217" t="inlineStr"/>
+      <c r="BW217" t="inlineStr"/>
+      <c r="BX217" t="inlineStr"/>
+      <c r="BY217" t="inlineStr"/>
+      <c r="BZ217" t="inlineStr"/>
+      <c r="CA217" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB217" t="inlineStr">
+        <is>
+          <t>108 MP, f/1.9, 26mm (wide), 1/1.52", 0.7µm, PDAF 8 MP, f/2.3, 119˚, 16mm (ultrawide), 1/4.0", 1.12µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC217" t="inlineStr"/>
+      <c r="CD217" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120/480fps, 720p@960fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE217" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF217" t="inlineStr">
+        <is>
+          <t>RMX3081</t>
+        </is>
+      </c>
+      <c r="CG217" t="inlineStr">
+        <is>
+          <t>1.10 W/kg (head)     0.53 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH217" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41 - Asia</t>
+        </is>
+      </c>
+      <c r="CI217" t="inlineStr"/>
+      <c r="CJ217" t="inlineStr"/>
+      <c r="CK217" t="inlineStr"/>
+      <c r="CL217" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41 - International</t>
+        </is>
+      </c>
+      <c r="CM217" t="inlineStr"/>
+      <c r="CN217" t="inlineStr"/>
+      <c r="CO217" t="inlineStr">
+        <is>
+          <t>Contrast ratio: Infinite (nominal)</t>
+        </is>
+      </c>
+      <c r="CP217" t="inlineStr">
+        <is>
+          <t>-28.2 LUFS (Average)</t>
+        </is>
+      </c>
+      <c r="CQ217" t="inlineStr">
+        <is>
+          <t>AnTuTu: 286666 (v8) GeekBench: 1678 (v5.1) GFXBench: 16fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR217" t="inlineStr">
+        <is>
+          <t>Qualcomm SM7125 Snapdragon 720G (8 nm)</t>
+        </is>
+      </c>
+      <c r="CS217" t="inlineStr">
+        <is>
+          <t>Adreno 618</t>
+        </is>
+      </c>
+      <c r="CT217" t="inlineStr"/>
+      <c r="CU217" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV217" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, (wide), 1/3.0", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW217" t="inlineStr">
+        <is>
+          <t>1080p@30/120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX217" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY217" t="inlineStr"/>
+      <c r="CZ217" t="inlineStr"/>
+      <c r="DA217" t="inlineStr"/>
+      <c r="DB217" t="inlineStr"/>
+      <c r="DC217" t="inlineStr"/>
+      <c r="DD217" t="inlineStr"/>
+      <c r="DE217" t="inlineStr"/>
+      <c r="DF217" t="inlineStr"/>
+      <c r="DG217" t="inlineStr"/>
+      <c r="DH217" t="inlineStr"/>
+      <c r="DI217" t="inlineStr"/>
+      <c r="DJ217" t="inlineStr"/>
+      <c r="DK217" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL217" t="inlineStr"/>
+      <c r="DM217" t="inlineStr">
+        <is>
+          <t>Endurance rating 116h</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Realme 8</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_8-10810.php</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2021, March 24</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 25</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>160.6</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>234.38</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>163.15</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>£ 163.15 / € 234.38</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>160.6 x 73.9 x 8 mm (6.32 x 2.91 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr"/>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>177 g (6.24 oz)</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr"/>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~411 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>6.4 inches, 98.9 cm 2 (~83.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Super AMOLED, HDR10, 1000 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr"/>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>2021, March 24</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 25</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM, 128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>Cyber Silver, Cyber Black</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>£ 163.15 / € 234.38</t>
+        </is>
+      </c>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI218" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ218" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK218" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL218" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.05 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM218" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO218" t="inlineStr"/>
+      <c r="BP218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ218" t="inlineStr">
+        <is>
+          <t>30W wired, 50% in 26 min, 100% in 65 min</t>
+        </is>
+      </c>
+      <c r="BR218" t="inlineStr"/>
+      <c r="BS218" t="inlineStr">
+        <is>
+          <t>Glass front, plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT218" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="BU218" t="inlineStr"/>
+      <c r="BV218" t="inlineStr"/>
+      <c r="BW218" t="inlineStr"/>
+      <c r="BX218" t="inlineStr"/>
+      <c r="BY218" t="inlineStr"/>
+      <c r="BZ218" t="inlineStr"/>
+      <c r="CA218" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB218" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/1.73", 0.8µm, PDAF 8 MP, f/2.3, 119˚, 16mm (ultrawide), 1/4.0", 1.12µm 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CC218" t="inlineStr"/>
+      <c r="CD218" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE218" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF218" t="inlineStr">
+        <is>
+          <t>RMX3085</t>
+        </is>
+      </c>
+      <c r="CG218" t="inlineStr"/>
+      <c r="CH218" t="inlineStr"/>
+      <c r="CI218" t="inlineStr"/>
+      <c r="CJ218" t="inlineStr"/>
+      <c r="CK218" t="inlineStr"/>
+      <c r="CL218" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM218" t="inlineStr"/>
+      <c r="CN218" t="inlineStr"/>
+      <c r="CO218" t="inlineStr">
+        <is>
+          <t>657 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP218" t="inlineStr">
+        <is>
+          <t>-28.6 LUFS (Average)</t>
+        </is>
+      </c>
+      <c r="CQ218" t="inlineStr">
+        <is>
+          <t>AnTuTu: 298328 (v8) GeekBench: 6779 (v4.4), 1690 (v5.1) GFXBench: 18fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR218" t="inlineStr">
+        <is>
+          <t>Mediatek MT6785V/CD Helio G95 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS218" t="inlineStr">
+        <is>
+          <t>Mali-G76 MC4</t>
+        </is>
+      </c>
+      <c r="CT218" t="inlineStr"/>
+      <c r="CU218" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV218" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, (wide), 1/3.0", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW218" t="inlineStr">
+        <is>
+          <t>1080p@30/120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX218" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY218" t="inlineStr"/>
+      <c r="CZ218" t="inlineStr"/>
+      <c r="DA218" t="inlineStr"/>
+      <c r="DB218" t="inlineStr"/>
+      <c r="DC218" t="inlineStr"/>
+      <c r="DD218" t="inlineStr"/>
+      <c r="DE218" t="inlineStr"/>
+      <c r="DF218" t="inlineStr"/>
+      <c r="DG218" t="inlineStr"/>
+      <c r="DH218" t="inlineStr"/>
+      <c r="DI218" t="inlineStr"/>
+      <c r="DJ218" t="inlineStr"/>
+      <c r="DK218" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL218" t="inlineStr"/>
+      <c r="DM218" t="inlineStr">
+        <is>
+          <t>Endurance rating 127h</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Realme C25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_c25-10793.php</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2021, March 23</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 27</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>6000 mAh</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>164.5 x 75.9 x 9.6 mm (6.48 x 2.99 x 0.38 in)</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr"/>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>209 g (7.37 oz)</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr"/>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr"/>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~81.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>IPS LCD, 480 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr"/>
+      <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>2021, March 23</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 27</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr">
+        <is>
+          <t>Water Blue, Water Gray</t>
+        </is>
+      </c>
+      <c r="BF219" t="inlineStr">
+        <is>
+          <t>About 140 EUR</t>
+        </is>
+      </c>
+      <c r="BG219" t="inlineStr"/>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI219" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ219" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK219" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL219" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.7 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM219" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO219" t="inlineStr"/>
+      <c r="BP219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ219" t="inlineStr">
+        <is>
+          <t>18W wired 5W reverse wired</t>
+        </is>
+      </c>
+      <c r="BR219" t="inlineStr"/>
+      <c r="BS219" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU219" t="inlineStr"/>
+      <c r="BV219" t="inlineStr"/>
+      <c r="BW219" t="inlineStr"/>
+      <c r="BX219" t="inlineStr"/>
+      <c r="BY219" t="inlineStr"/>
+      <c r="BZ219" t="inlineStr"/>
+      <c r="CA219" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB219" t="inlineStr"/>
+      <c r="CC219" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), PDAF (International model) or 13 MP, f/2.2, 26mm (wide), 1/3.06", 1.12µm, PDAF (India model) 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CD219" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE219" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF219" t="inlineStr">
+        <is>
+          <t>RMX3193, RMX3191</t>
+        </is>
+      </c>
+      <c r="CG219" t="inlineStr">
+        <is>
+          <t>0.82 W/kg (head)     0.81 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH219" t="inlineStr"/>
+      <c r="CI219" t="inlineStr"/>
+      <c r="CJ219" t="inlineStr"/>
+      <c r="CK219" t="inlineStr"/>
+      <c r="CL219" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM219" t="inlineStr"/>
+      <c r="CN219" t="inlineStr"/>
+      <c r="CO219" t="inlineStr"/>
+      <c r="CP219" t="inlineStr"/>
+      <c r="CQ219" t="inlineStr"/>
+      <c r="CR219" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769V/CB Helio G70 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS219" t="inlineStr">
+        <is>
+          <t>Mali-G52 2EEMC2</t>
+        </is>
+      </c>
+      <c r="CT219" t="inlineStr"/>
+      <c r="CU219" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV219" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW219" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX219" t="inlineStr"/>
+      <c r="CY219" t="inlineStr"/>
+      <c r="CZ219" t="inlineStr"/>
+      <c r="DA219" t="inlineStr"/>
+      <c r="DB219" t="inlineStr"/>
+      <c r="DC219" t="inlineStr"/>
+      <c r="DD219" t="inlineStr"/>
+      <c r="DE219" t="inlineStr"/>
+      <c r="DF219" t="inlineStr"/>
+      <c r="DG219" t="inlineStr"/>
+      <c r="DH219" t="inlineStr"/>
+      <c r="DI219" t="inlineStr"/>
+      <c r="DJ219" t="inlineStr"/>
+      <c r="DK219" t="inlineStr"/>
+      <c r="DL219" t="inlineStr"/>
+      <c r="DM219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Realme C21</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_c21-10759.php</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2021, March 05</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 05</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>165.2</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr"/>
+      <c r="Z220" t="inlineStr"/>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>About 410 EUR</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>165.2 x 76.4 x 8.9 mm (6.50 x 3.01 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr"/>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>190 g (6.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr"/>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr"/>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~80.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr"/>
+      <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>2021, March 05</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 05</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD220" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM, 64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE220" t="inlineStr">
+        <is>
+          <t>Cross Black, Cross Blue</t>
+        </is>
+      </c>
+      <c r="BF220" t="inlineStr">
+        <is>
+          <t>About 410 EUR</t>
+        </is>
+      </c>
+      <c r="BG220" t="inlineStr"/>
+      <c r="BH220" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI220" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ220" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK220" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL220" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM220" t="inlineStr">
+        <is>
+          <t>Android 10, Realme UI</t>
+        </is>
+      </c>
+      <c r="BN220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO220" t="inlineStr"/>
+      <c r="BP220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ220" t="inlineStr">
+        <is>
+          <t>10W wired Reverse wired</t>
+        </is>
+      </c>
+      <c r="BR220" t="inlineStr"/>
+      <c r="BS220" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU220" t="inlineStr"/>
+      <c r="BV220" t="inlineStr"/>
+      <c r="BW220" t="inlineStr"/>
+      <c r="BX220" t="inlineStr"/>
+      <c r="BY220" t="inlineStr"/>
+      <c r="BZ220" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 26mm (wide), 1/3.06", 1.12µm, PDAF 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA220" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB220" t="inlineStr"/>
+      <c r="CC220" t="inlineStr"/>
+      <c r="CD220" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE220" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF220" t="inlineStr">
+        <is>
+          <t>RMX3201</t>
+        </is>
+      </c>
+      <c r="CG220" t="inlineStr"/>
+      <c r="CH220" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41 - India</t>
+        </is>
+      </c>
+      <c r="CI220" t="inlineStr"/>
+      <c r="CJ220" t="inlineStr"/>
+      <c r="CK220" t="inlineStr"/>
+      <c r="CL220" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40, 41 - International</t>
+        </is>
+      </c>
+      <c r="CM220" t="inlineStr"/>
+      <c r="CN220" t="inlineStr"/>
+      <c r="CO220" t="inlineStr"/>
+      <c r="CP220" t="inlineStr"/>
+      <c r="CQ220" t="inlineStr"/>
+      <c r="CR220" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS220" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT220" t="inlineStr"/>
+      <c r="CU220" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV220" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1/5.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW220" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX220" t="inlineStr"/>
+      <c r="CY220" t="inlineStr"/>
+      <c r="CZ220" t="inlineStr"/>
+      <c r="DA220" t="inlineStr"/>
+      <c r="DB220" t="inlineStr"/>
+      <c r="DC220" t="inlineStr"/>
+      <c r="DD220" t="inlineStr"/>
+      <c r="DE220" t="inlineStr"/>
+      <c r="DF220" t="inlineStr"/>
+      <c r="DG220" t="inlineStr"/>
+      <c r="DH220" t="inlineStr"/>
+      <c r="DI220" t="inlineStr"/>
+      <c r="DJ220" t="inlineStr"/>
+      <c r="DK220" t="inlineStr"/>
+      <c r="DL220" t="inlineStr"/>
+      <c r="DM220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Realme GT 5G</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_gt_5g-10689.php</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2021, March 04</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 10</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>158.5</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>12GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr"/>
+      <c r="Z221" t="inlineStr"/>
+      <c r="AA221" t="inlineStr"/>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>About 330 EUR</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>4500 mAh</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>158.5 x 73.3 x 8.4 mm (Glass) / 9.1 mm (Leather)</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr"/>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>186 g (6.56 oz)</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr"/>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t>5.2, A2DP, LE, aptX HD</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr"/>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>GPS (L1+L5), GLONASS, BDS, GALILEO, QZSS</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>6.43 inches, 99.8 cm 2 (~85.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Super AMOLED, 120Hz, HDR10+</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr"/>
+      <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>2021, March 04</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 10</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD221" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE221" t="inlineStr">
+        <is>
+          <t>Gold/Black, Blue, Silver</t>
+        </is>
+      </c>
+      <c r="BF221" t="inlineStr">
+        <is>
+          <t>About 330 EUR</t>
+        </is>
+      </c>
+      <c r="BG221" t="inlineStr"/>
+      <c r="BH221" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI221" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ221" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK221" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL221" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Cortex-X1 &amp; 3x2.42 GHz Cortex-A78 &amp; 4x1.80 GHz Cortex-A55</t>
+        </is>
+      </c>
+      <c r="BM221" t="inlineStr">
+        <is>
+          <t>Android 11, upgradable to Android 14, Realme UI 5.0</t>
+        </is>
+      </c>
+      <c r="BN221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO221" t="inlineStr"/>
+      <c r="BP221" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ221" t="inlineStr">
+        <is>
+          <t>65W wired, 100% in 35 min</t>
+        </is>
+      </c>
+      <c r="BR221" t="inlineStr"/>
+      <c r="BS221" t="inlineStr">
+        <is>
+          <t>Glass front, glass back or eco leather back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU221" t="inlineStr"/>
+      <c r="BV221" t="inlineStr"/>
+      <c r="BW221" t="inlineStr"/>
+      <c r="BX221" t="inlineStr"/>
+      <c r="BY221" t="inlineStr"/>
+      <c r="BZ221" t="inlineStr"/>
+      <c r="CA221" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB221" t="inlineStr"/>
+      <c r="CC221" t="inlineStr">
+        <is>
+          <t>64 MP, f/1.8, 26mm (wide), 1/1.73", 0.8µm, PDAF 8 MP, f/2.3, 16mm, 119˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD221" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60/240fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE221" t="inlineStr">
+        <is>
+          <t>UFS 3.1</t>
+        </is>
+      </c>
+      <c r="CF221" t="inlineStr">
+        <is>
+          <t>RMX2202</t>
+        </is>
+      </c>
+      <c r="CG221" t="inlineStr"/>
+      <c r="CH221" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI221" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ221" t="inlineStr"/>
+      <c r="CK221" t="inlineStr"/>
+      <c r="CL221" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 18, 19, 20, 26, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM221" t="inlineStr">
+        <is>
+          <t>1, 3, 28, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN221" t="inlineStr"/>
+      <c r="CO221" t="inlineStr">
+        <is>
+          <t>650 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="CP221" t="inlineStr">
+        <is>
+          <t>-24.5 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CQ221" t="inlineStr">
+        <is>
+          <t>AnTuTu: 703986 (v8), 810433 (v9) GeekBench: 3555 (v5.1) GFXBench: 55fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="CR221" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8350 Snapdragon 888 5G (5 nm)</t>
+        </is>
+      </c>
+      <c r="CS221" t="inlineStr">
+        <is>
+          <t>Adreno 660</t>
+        </is>
+      </c>
+      <c r="CT221" t="inlineStr"/>
+      <c r="CU221" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV221" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.5, 26mm (wide), 1/3.0", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW221" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX221" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY221" t="inlineStr"/>
+      <c r="CZ221" t="inlineStr"/>
+      <c r="DA221" t="inlineStr"/>
+      <c r="DB221" t="inlineStr"/>
+      <c r="DC221" t="inlineStr"/>
+      <c r="DD221" t="inlineStr"/>
+      <c r="DE221" t="inlineStr"/>
+      <c r="DF221" t="inlineStr"/>
+      <c r="DG221" t="inlineStr"/>
+      <c r="DH221" t="inlineStr"/>
+      <c r="DI221" t="inlineStr"/>
+      <c r="DJ221" t="inlineStr"/>
+      <c r="DK221" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DL221" t="inlineStr"/>
+      <c r="DM221" t="inlineStr">
+        <is>
+          <t>Endurance rating 98h</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Realme Narzo 30 Pro 5G</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_narzo_30_pro_5g-10736.php</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2021, February 24</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 04</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>162.2</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="inlineStr"/>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>162.2 x 75.1 x 9.1 mm (6.39 x 2.96 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr"/>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>196 g (6.91 oz)</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr"/>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr"/>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>1080 x 2400 pixels, 20:9 ratio (~405 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~83.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>IPS LCD, 120Hz , 480 nits (typ), 600 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr"/>
+      <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>2021, February 24</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 04</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>Sword Black, Blade Silver</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="BG222" t="inlineStr"/>
+      <c r="BH222" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI222" t="inlineStr">
+        <is>
+          <t>HSDPA 800 / 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ222" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK222" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL222" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.4 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM222" t="inlineStr">
+        <is>
+          <t>Android 10, Realme UI</t>
+        </is>
+      </c>
+      <c r="BN222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO222" t="inlineStr"/>
+      <c r="BP222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ222" t="inlineStr">
+        <is>
+          <t>30W wired, PD, 50% in 25 min, 100% in 65 min</t>
+        </is>
+      </c>
+      <c r="BR222" t="inlineStr"/>
+      <c r="BS222" t="inlineStr"/>
+      <c r="BT222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU222" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="BV222" t="inlineStr"/>
+      <c r="BW222" t="inlineStr"/>
+      <c r="BX222" t="inlineStr"/>
+      <c r="BY222" t="inlineStr"/>
+      <c r="BZ222" t="inlineStr"/>
+      <c r="CA222" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB222" t="inlineStr"/>
+      <c r="CC222" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF 8 MP, f/2.3, 119˚ (ultrawide), 1/4.0", 1.12µm 2 MP (macro)</t>
+        </is>
+      </c>
+      <c r="CD222" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30/60/120fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CE222" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="CF222" t="inlineStr">
+        <is>
+          <t>RMX2117</t>
+        </is>
+      </c>
+      <c r="CG222" t="inlineStr"/>
+      <c r="CH222" t="inlineStr"/>
+      <c r="CI222" t="inlineStr"/>
+      <c r="CJ222" t="inlineStr"/>
+      <c r="CK222" t="inlineStr"/>
+      <c r="CL222" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM222" t="inlineStr">
+        <is>
+          <t>1, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN222" t="inlineStr"/>
+      <c r="CO222" t="inlineStr"/>
+      <c r="CP222" t="inlineStr"/>
+      <c r="CQ222" t="inlineStr"/>
+      <c r="CR222" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 800U (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS222" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC3</t>
+        </is>
+      </c>
+      <c r="CT222" t="inlineStr"/>
+      <c r="CU222" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV222" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.1, 26mm (wide), 1/3.09", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW222" t="inlineStr">
+        <is>
+          <t>1080p@30fps, gyro-EIS</t>
+        </is>
+      </c>
+      <c r="CX222" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY222" t="inlineStr"/>
+      <c r="CZ222" t="inlineStr"/>
+      <c r="DA222" t="inlineStr"/>
+      <c r="DB222" t="inlineStr"/>
+      <c r="DC222" t="inlineStr"/>
+      <c r="DD222" t="inlineStr"/>
+      <c r="DE222" t="inlineStr"/>
+      <c r="DF222" t="inlineStr"/>
+      <c r="DG222" t="inlineStr"/>
+      <c r="DH222" t="inlineStr"/>
+      <c r="DI222" t="inlineStr"/>
+      <c r="DJ222" t="inlineStr"/>
+      <c r="DK222" t="inlineStr"/>
+      <c r="DL222" t="inlineStr"/>
+      <c r="DM222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Realme Narzo 30A</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_narzo_30a-10748.php</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2021, February 24</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 05</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr"/>
+      <c r="Z223" t="inlineStr"/>
+      <c r="AA223" t="inlineStr"/>
+      <c r="AB223" t="inlineStr"/>
+      <c r="AC223" t="inlineStr"/>
+      <c r="AD223" t="inlineStr"/>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>About 450 EUR</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>6000 mAh</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>164.5 x 75.9 x 9.8 mm (6.48 x 2.99 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr"/>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>205 g (7.23 oz)</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr"/>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~81.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>IPS LCD, 470 nits (typ), 570 nits (peak)</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr"/>
+      <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>2021, February 24</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, March 05</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD223" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM, 64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE223" t="inlineStr">
+        <is>
+          <t>Laser Black, Laser Blue</t>
+        </is>
+      </c>
+      <c r="BF223" t="inlineStr">
+        <is>
+          <t>About 450 EUR</t>
+        </is>
+      </c>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI223" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ223" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK223" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL223" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Cortex-A75 &amp; 6x1.8 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM223" t="inlineStr">
+        <is>
+          <t>Android 10, Realme UI</t>
+        </is>
+      </c>
+      <c r="BN223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO223" t="inlineStr"/>
+      <c r="BP223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ223" t="inlineStr">
+        <is>
+          <t>18W wired 5W reverse wired</t>
+        </is>
+      </c>
+      <c r="BR223" t="inlineStr"/>
+      <c r="BS223" t="inlineStr"/>
+      <c r="BT223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU223" t="inlineStr"/>
+      <c r="BV223" t="inlineStr"/>
+      <c r="BW223" t="inlineStr"/>
+      <c r="BX223" t="inlineStr"/>
+      <c r="BY223" t="inlineStr"/>
+      <c r="BZ223" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 26mm (wide), 1/3.06", 1.12µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA223" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB223" t="inlineStr"/>
+      <c r="CC223" t="inlineStr"/>
+      <c r="CD223" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE223" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF223" t="inlineStr">
+        <is>
+          <t>RMX3171</t>
+        </is>
+      </c>
+      <c r="CG223" t="inlineStr">
+        <is>
+          <t>1.37 W/kg (head)     1.10 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH223" t="inlineStr"/>
+      <c r="CI223" t="inlineStr"/>
+      <c r="CJ223" t="inlineStr"/>
+      <c r="CK223" t="inlineStr"/>
+      <c r="CL223" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM223" t="inlineStr"/>
+      <c r="CN223" t="inlineStr"/>
+      <c r="CO223" t="inlineStr"/>
+      <c r="CP223" t="inlineStr"/>
+      <c r="CQ223" t="inlineStr"/>
+      <c r="CR223" t="inlineStr">
+        <is>
+          <t>Mediatek MT6769Z Helio G85 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS223" t="inlineStr">
+        <is>
+          <t>Mali-G52 MC2</t>
+        </is>
+      </c>
+      <c r="CT223" t="inlineStr"/>
+      <c r="CU223" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CV223" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW223" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX223" t="inlineStr"/>
+      <c r="CY223" t="inlineStr"/>
+      <c r="CZ223" t="inlineStr"/>
+      <c r="DA223" t="inlineStr"/>
+      <c r="DB223" t="inlineStr"/>
+      <c r="DC223" t="inlineStr"/>
+      <c r="DD223" t="inlineStr"/>
+      <c r="DE223" t="inlineStr"/>
+      <c r="DF223" t="inlineStr"/>
+      <c r="DG223" t="inlineStr"/>
+      <c r="DH223" t="inlineStr"/>
+      <c r="DI223" t="inlineStr"/>
+      <c r="DJ223" t="inlineStr"/>
+      <c r="DK223" t="inlineStr"/>
+      <c r="DL223" t="inlineStr"/>
+      <c r="DM223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Realme V11 5G</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_v11_5g-10722.php</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2021, February 05</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, February 05</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr"/>
+      <c r="Z224" t="inlineStr"/>
+      <c r="AA224" t="inlineStr"/>
+      <c r="AB224" t="inlineStr"/>
+      <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>About 160 EUR</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>8.4 mm thickness</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr"/>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>186 g (6.56 oz)</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr"/>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr"/>
+      <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>2021, February 05</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, February 05</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD224" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BE224" t="inlineStr">
+        <is>
+          <t>Black, Blue</t>
+        </is>
+      </c>
+      <c r="BF224" t="inlineStr">
+        <is>
+          <t>About 160 EUR</t>
+        </is>
+      </c>
+      <c r="BG224" t="inlineStr"/>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI224" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ224" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="BK224" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL224" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.2 GHz Cortex-A76 &amp; 6x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM224" t="inlineStr">
+        <is>
+          <t>Android 11, Realme UI 2.0</t>
+        </is>
+      </c>
+      <c r="BN224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO224" t="inlineStr"/>
+      <c r="BP224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ224" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR224" t="inlineStr"/>
+      <c r="BS224" t="inlineStr"/>
+      <c r="BT224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU224" t="inlineStr"/>
+      <c r="BV224" t="inlineStr"/>
+      <c r="BW224" t="inlineStr"/>
+      <c r="BX224" t="inlineStr"/>
+      <c r="BY224" t="inlineStr"/>
+      <c r="BZ224" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.2, 26mm (wide), PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA224" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB224" t="inlineStr"/>
+      <c r="CC224" t="inlineStr"/>
+      <c r="CD224" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60fps</t>
+        </is>
+      </c>
+      <c r="CE224" t="inlineStr"/>
+      <c r="CF224" t="inlineStr">
+        <is>
+          <t>RMX3121, RMX3122</t>
+        </is>
+      </c>
+      <c r="CG224" t="inlineStr"/>
+      <c r="CH224" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI224" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ224" t="inlineStr"/>
+      <c r="CK224" t="inlineStr"/>
+      <c r="CL224" t="inlineStr">
+        <is>
+          <t>1, 3, 4, 5, 7, 8, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM224" t="inlineStr">
+        <is>
+          <t>1, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN224" t="inlineStr"/>
+      <c r="CO224" t="inlineStr"/>
+      <c r="CP224" t="inlineStr"/>
+      <c r="CQ224" t="inlineStr"/>
+      <c r="CR224" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 700 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CS224" t="inlineStr">
+        <is>
+          <t>Mali-G57 MC2</t>
+        </is>
+      </c>
+      <c r="CT224" t="inlineStr"/>
+      <c r="CU224" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV224" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide)</t>
+        </is>
+      </c>
+      <c r="CW224" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX224" t="inlineStr"/>
+      <c r="CY224" t="inlineStr"/>
+      <c r="CZ224" t="inlineStr"/>
+      <c r="DA224" t="inlineStr"/>
+      <c r="DB224" t="inlineStr"/>
+      <c r="DC224" t="inlineStr"/>
+      <c r="DD224" t="inlineStr"/>
+      <c r="DE224" t="inlineStr"/>
+      <c r="DF224" t="inlineStr"/>
+      <c r="DG224" t="inlineStr"/>
+      <c r="DH224" t="inlineStr"/>
+      <c r="DI224" t="inlineStr"/>
+      <c r="DJ224" t="inlineStr"/>
+      <c r="DK224" t="inlineStr"/>
+      <c r="DL224" t="inlineStr"/>
+      <c r="DM224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Realme C20</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_c20-10690.php</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2021, January 19</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, January 19</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>165.2</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="inlineStr"/>
+      <c r="AA225" t="inlineStr"/>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>165.2 x 76.4 x 8.9 mm (6.50 x 3.01 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr"/>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>190 g (6.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr"/>
+      <c r="AN225" t="inlineStr">
+        <is>
+          <t>5.1, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr"/>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~270 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>6.5 inches, 102.0 cm 2 (~80.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>IPS LCD, 400 nits (typ)</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr"/>
+      <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>2021, January 19</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, January 19</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD225" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BE225" t="inlineStr">
+        <is>
+          <t>Cool Gray, Cool Blue</t>
+        </is>
+      </c>
+      <c r="BF225" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG225" t="inlineStr"/>
+      <c r="BH225" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI225" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ225" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK225" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL225" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.3 GHz Cortex-A53 &amp; 4x1.8 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM225" t="inlineStr">
+        <is>
+          <t>Android 10, Realme UI</t>
+        </is>
+      </c>
+      <c r="BN225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO225" t="inlineStr"/>
+      <c r="BP225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ225" t="inlineStr">
+        <is>
+          <t>10W wired Reverse wired</t>
+        </is>
+      </c>
+      <c r="BR225" t="inlineStr">
+        <is>
+          <t>Splash-resistant design</t>
+        </is>
+      </c>
+      <c r="BS225" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 3), plastic frame, plastic back</t>
+        </is>
+      </c>
+      <c r="BT225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU225" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="BV225" t="inlineStr"/>
+      <c r="BW225" t="inlineStr"/>
+      <c r="BX225" t="inlineStr"/>
+      <c r="BY225" t="inlineStr"/>
+      <c r="BZ225" t="inlineStr"/>
+      <c r="CA225" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB225" t="inlineStr"/>
+      <c r="CC225" t="inlineStr"/>
+      <c r="CD225" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE225" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF225" t="inlineStr">
+        <is>
+          <t>RMX3063, RMX3061</t>
+        </is>
+      </c>
+      <c r="CG225" t="inlineStr">
+        <is>
+          <t>0.98 W/kg (head)     0.50 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CH225" t="inlineStr"/>
+      <c r="CI225" t="inlineStr"/>
+      <c r="CJ225" t="inlineStr"/>
+      <c r="CK225" t="inlineStr"/>
+      <c r="CL225" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM225" t="inlineStr"/>
+      <c r="CN225" t="inlineStr"/>
+      <c r="CO225" t="inlineStr"/>
+      <c r="CP225" t="inlineStr"/>
+      <c r="CQ225" t="inlineStr"/>
+      <c r="CR225" t="inlineStr">
+        <is>
+          <t>Mediatek MT6765G Helio G35 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS225" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT225" t="inlineStr"/>
+      <c r="CU225" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV225" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2, (wide), 1/5.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CW225" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX225" t="inlineStr"/>
+      <c r="CY225" t="inlineStr"/>
+      <c r="CZ225" t="inlineStr"/>
+      <c r="DA225" t="inlineStr"/>
+      <c r="DB225" t="inlineStr"/>
+      <c r="DC225" t="inlineStr"/>
+      <c r="DD225" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, (wide), 1/4.0", 1.12µm, AF</t>
+        </is>
+      </c>
+      <c r="DE225" t="inlineStr"/>
+      <c r="DF225" t="inlineStr"/>
+      <c r="DG225" t="inlineStr"/>
+      <c r="DH225" t="inlineStr"/>
+      <c r="DI225" t="inlineStr"/>
+      <c r="DJ225" t="inlineStr"/>
+      <c r="DK225" t="inlineStr"/>
+      <c r="DL225" t="inlineStr"/>
+      <c r="DM225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>X7 (India)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/realme_x7_(india)-10717.php</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:08 UTC</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+      <c r="W226" t="inlineStr"/>
+      <c r="X226" t="inlineStr"/>
+      <c r="Y226" t="inlineStr"/>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr"/>
+      <c r="AD226" t="inlineStr"/>
+      <c r="AE226" t="inlineStr"/>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr"/>
+      <c r="AI226" t="inlineStr"/>
+      <c r="AJ226" t="inlineStr"/>
+      <c r="AK226" t="inlineStr"/>
+      <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
+      <c r="AN226" t="inlineStr"/>
+      <c r="AO226" t="inlineStr"/>
+      <c r="AP226" t="inlineStr"/>
+      <c r="AQ226" t="inlineStr"/>
+      <c r="AR226" t="inlineStr"/>
+      <c r="AS226" t="inlineStr"/>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AU226" t="inlineStr"/>
+      <c r="AV226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr"/>
+      <c r="AX226" t="inlineStr"/>
+      <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr"/>
+      <c r="BA226" t="inlineStr"/>
+      <c r="BB226" t="inlineStr"/>
+      <c r="BC226" t="inlineStr"/>
+      <c r="BD226" t="inlineStr"/>
+      <c r="BE226" t="inlineStr"/>
+      <c r="BF226" t="inlineStr"/>
+      <c r="BG226" t="inlineStr"/>
+      <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="inlineStr"/>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="inlineStr"/>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
+      <c r="BO226" t="inlineStr"/>
+      <c r="BP226" t="inlineStr"/>
+      <c r="BQ226" t="inlineStr"/>
+      <c r="BR226" t="inlineStr"/>
+      <c r="BS226" t="inlineStr"/>
+      <c r="BT226" t="inlineStr"/>
+      <c r="BU226" t="inlineStr"/>
+      <c r="BV226" t="inlineStr"/>
+      <c r="BW226" t="inlineStr"/>
+      <c r="BX226" t="inlineStr"/>
+      <c r="BY226" t="inlineStr"/>
+      <c r="BZ226" t="inlineStr"/>
+      <c r="CA226" t="inlineStr"/>
+      <c r="CB226" t="inlineStr"/>
+      <c r="CC226" t="inlineStr"/>
+      <c r="CD226" t="inlineStr"/>
+      <c r="CE226" t="inlineStr"/>
+      <c r="CF226" t="inlineStr"/>
+      <c r="CG226" t="inlineStr"/>
+      <c r="CH226" t="inlineStr"/>
+      <c r="CI226" t="inlineStr"/>
+      <c r="CJ226" t="inlineStr"/>
+      <c r="CK226" t="inlineStr"/>
+      <c r="CL226" t="inlineStr"/>
+      <c r="CM226" t="inlineStr"/>
+      <c r="CN226" t="inlineStr"/>
+      <c r="CO226" t="inlineStr"/>
+      <c r="CP226" t="inlineStr"/>
+      <c r="CQ226" t="inlineStr"/>
+      <c r="CR226" t="inlineStr"/>
+      <c r="CS226" t="inlineStr"/>
+      <c r="CT226" t="inlineStr"/>
+      <c r="CU226" t="inlineStr"/>
+      <c r="CV226" t="inlineStr"/>
+      <c r="CW226" t="inlineStr"/>
+      <c r="CX226" t="inlineStr"/>
+      <c r="CY226" t="inlineStr"/>
+      <c r="CZ226" t="inlineStr"/>
+      <c r="DA226" t="inlineStr"/>
+      <c r="DB226" t="inlineStr"/>
+      <c r="DC226" t="inlineStr"/>
+      <c r="DD226" t="inlineStr"/>
+      <c r="DE226" t="inlineStr"/>
+      <c r="DF226" t="inlineStr"/>
+      <c r="DG226" t="inlineStr"/>
+      <c r="DH226" t="inlineStr"/>
+      <c r="DI226" t="inlineStr"/>
+      <c r="DJ226" t="inlineStr"/>
+      <c r="DK226" t="inlineStr"/>
+      <c r="DL226" t="inlineStr"/>
+      <c r="DM226" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-01.xlsx
+++ b/gsmarena_new_2026-06-01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM226"/>
+  <dimension ref="A1:DM237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70417,55 +70417,37 @@
           <t>2021, May 18</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H206" t="n">
+        <v>2021</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>Available. Released 2021, May 20</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>162.3</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J206" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="K206" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="L206" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M206" t="n">
+        <v>192</v>
+      </c>
+      <c r="N206" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O206" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P206" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>405</v>
       </c>
       <c r="R206" t="inlineStr">
         <is>
@@ -70477,20 +70459,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T206" t="n">
+        <v>48</v>
+      </c>
+      <c r="U206" t="n">
+        <v>16</v>
+      </c>
+      <c r="V206" t="n">
+        <v>5000</v>
       </c>
       <c r="W206" t="inlineStr"/>
       <c r="X206" t="inlineStr"/>
@@ -70780,55 +70756,37 @@
           <t>2021, May 11</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H207" t="n">
+        <v>2021</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
           <t>Available. Released 2021, May 11</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>165.2</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J207" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="K207" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L207" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M207" t="n">
+        <v>190</v>
+      </c>
+      <c r="N207" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O207" t="n">
+        <v>720</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>270</v>
       </c>
       <c r="R207" t="inlineStr">
         <is>
@@ -70840,20 +70798,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T207" t="n">
+        <v>8</v>
+      </c>
+      <c r="U207" t="n">
+        <v>5</v>
+      </c>
+      <c r="V207" t="n">
+        <v>5000</v>
       </c>
       <c r="W207" t="inlineStr"/>
       <c r="X207" t="inlineStr"/>
@@ -71151,64 +71103,44 @@
           <t>2021, May 20</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H208" t="n">
+        <v>2021</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>Available. Released 2021, May 29</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+      <c r="J208" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K208" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="L208" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M208" t="n">
+        <v>40</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O208" t="n">
+        <v>320</v>
+      </c>
+      <c r="P208" t="n">
+        <v>385</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>286</v>
       </c>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="V208" t="n">
+        <v>390</v>
       </c>
       <c r="W208" t="inlineStr"/>
       <c r="X208" t="inlineStr"/>
@@ -71327,16 +71259,8 @@
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
-      <c r="BH208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="BI208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
       <c r="BJ208" t="inlineStr">
         <is>
           <t>No</t>
@@ -71401,11 +71325,7 @@
       <c r="CI208" t="inlineStr"/>
       <c r="CJ208" t="inlineStr"/>
       <c r="CK208" t="inlineStr"/>
-      <c r="CL208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CL208" t="inlineStr"/>
       <c r="CM208" t="inlineStr"/>
       <c r="CN208" t="inlineStr"/>
       <c r="CO208" t="inlineStr"/>
@@ -71474,64 +71394,44 @@
           <t>2021, April 30</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H209" t="n">
+        <v>2021</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
           <t>Available. Released 2021, May 20</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>35.7</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>25.8</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
+      <c r="J209" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K209" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L209" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>38</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O209" t="n">
+        <v>320</v>
+      </c>
+      <c r="P209" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>323</v>
       </c>
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
+      <c r="V209" t="n">
+        <v>315</v>
       </c>
       <c r="W209" t="inlineStr"/>
       <c r="X209" t="inlineStr"/>
@@ -71650,16 +71550,8 @@
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
-      <c r="BH209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="BI209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
       <c r="BJ209" t="inlineStr">
         <is>
           <t>No</t>
@@ -71728,11 +71620,7 @@
       <c r="CI209" t="inlineStr"/>
       <c r="CJ209" t="inlineStr"/>
       <c r="CK209" t="inlineStr"/>
-      <c r="CL209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CL209" t="inlineStr"/>
       <c r="CM209" t="inlineStr"/>
       <c r="CN209" t="inlineStr"/>
       <c r="CO209" t="inlineStr"/>
@@ -71801,55 +71689,37 @@
           <t>2021, April 22</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H210" t="n">
+        <v>2021</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 29</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J210" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K210" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L210" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M210" t="n">
+        <v>179</v>
+      </c>
+      <c r="N210" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P210" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>409</v>
       </c>
       <c r="R210" t="inlineStr">
         <is>
@@ -71861,20 +71731,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T210" t="n">
+        <v>64</v>
+      </c>
+      <c r="U210" t="n">
+        <v>16</v>
+      </c>
+      <c r="V210" t="n">
+        <v>4500</v>
       </c>
       <c r="W210" t="inlineStr"/>
       <c r="X210" t="inlineStr"/>
@@ -72184,55 +72048,37 @@
           <t>2021, April 22</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H211" t="n">
+        <v>2021</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 29</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J211" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K211" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L211" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M211" t="n">
+        <v>189</v>
+      </c>
+      <c r="N211" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O211" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P211" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>405</v>
       </c>
       <c r="R211" t="inlineStr">
         <is>
@@ -72244,20 +72090,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T211" t="n">
+        <v>48</v>
+      </c>
+      <c r="U211" t="n">
+        <v>16</v>
+      </c>
+      <c r="V211" t="n">
+        <v>5000</v>
       </c>
       <c r="W211" t="inlineStr"/>
       <c r="X211" t="inlineStr"/>
@@ -72559,55 +72399,37 @@
           <t>2021, April 22</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H212" t="n">
+        <v>2021</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 22</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J212" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K212" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L212" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M212" t="n">
+        <v>185</v>
+      </c>
+      <c r="N212" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O212" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P212" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>405</v>
       </c>
       <c r="R212" t="inlineStr">
         <is>
@@ -72619,20 +72441,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T212" t="n">
+        <v>48</v>
+      </c>
+      <c r="U212" t="n">
+        <v>16</v>
+      </c>
+      <c r="V212" t="n">
+        <v>5000</v>
       </c>
       <c r="W212" t="inlineStr"/>
       <c r="X212" t="inlineStr"/>
@@ -72942,55 +72758,37 @@
           <t>2021, April 21</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H213" t="n">
+        <v>2021</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 28</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J213" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K213" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L213" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M213" t="n">
+        <v>185</v>
+      </c>
+      <c r="N213" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O213" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P213" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>405</v>
       </c>
       <c r="R213" t="inlineStr">
         <is>
@@ -73002,20 +72800,14 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T213" t="n">
+        <v>48</v>
+      </c>
+      <c r="U213" t="n">
+        <v>16</v>
+      </c>
+      <c r="V213" t="n">
+        <v>5000</v>
       </c>
       <c r="W213" t="inlineStr"/>
       <c r="X213" t="inlineStr"/>
@@ -73353,55 +73145,37 @@
           <t>2021, April 02</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H214" t="n">
+        <v>2021</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 02</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>159.9</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
+      <c r="J214" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="K214" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="L214" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M214" t="n">
+        <v>170</v>
+      </c>
+      <c r="N214" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P214" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>402</v>
       </c>
       <c r="R214" t="inlineStr">
         <is>
@@ -73413,20 +73187,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T214" t="n">
+        <v>64</v>
+      </c>
+      <c r="U214" t="n">
+        <v>32</v>
+      </c>
+      <c r="V214" t="n">
+        <v>4500</v>
       </c>
       <c r="W214" t="inlineStr"/>
       <c r="X214" t="inlineStr"/>
@@ -73736,55 +73504,37 @@
           <t>2021, March 31</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H215" t="n">
+        <v>2021</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 08</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J215" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K215" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L215" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M215" t="n">
+        <v>179</v>
+      </c>
+      <c r="N215" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O215" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P215" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>409</v>
       </c>
       <c r="R215" t="inlineStr">
         <is>
@@ -73796,20 +73546,14 @@
           <t>12GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T215" t="n">
+        <v>64</v>
+      </c>
+      <c r="U215" t="n">
+        <v>16</v>
+      </c>
+      <c r="V215" t="n">
+        <v>4500</v>
       </c>
       <c r="W215" t="inlineStr"/>
       <c r="X215" t="inlineStr"/>
@@ -74123,55 +73867,37 @@
           <t>2021, March 31</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H216" t="n">
+        <v>2021</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>Available. Released 2021, April 02</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J216" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="K216" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L216" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M216" t="n">
+        <v>185</v>
+      </c>
+      <c r="N216" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O216" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P216" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>405</v>
       </c>
       <c r="R216" t="inlineStr">
         <is>
@@ -74183,20 +73909,14 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T216" t="n">
+        <v>48</v>
+      </c>
+      <c r="U216" t="n">
+        <v>8</v>
+      </c>
+      <c r="V216" t="n">
+        <v>5000</v>
       </c>
       <c r="W216" t="inlineStr"/>
       <c r="X216" t="inlineStr"/>
@@ -74490,55 +74210,37 @@
           <t>2021, March 24</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H217" t="n">
+        <v>2021</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 25</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>160.6</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+      <c r="J217" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="K217" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="L217" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>176</v>
+      </c>
+      <c r="N217" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O217" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P217" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>411</v>
       </c>
       <c r="R217" t="inlineStr">
         <is>
@@ -74550,30 +74252,20 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+      <c r="T217" t="n">
+        <v>108</v>
+      </c>
+      <c r="U217" t="n">
+        <v>16</v>
+      </c>
+      <c r="V217" t="n">
+        <v>4500</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X217" t="n">
+        <v>0.53</v>
       </c>
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
@@ -74901,55 +74593,37 @@
           <t>2021, March 24</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H218" t="n">
+        <v>2021</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 25</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>160.6</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+      <c r="J218" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="K218" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="L218" t="n">
+        <v>8</v>
+      </c>
+      <c r="M218" t="n">
+        <v>177</v>
+      </c>
+      <c r="N218" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P218" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>411</v>
       </c>
       <c r="R218" t="inlineStr">
         <is>
@@ -74961,35 +74635,25 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T218" t="n">
+        <v>64</v>
+      </c>
+      <c r="U218" t="n">
+        <v>16</v>
+      </c>
+      <c r="V218" t="n">
+        <v>5000</v>
       </c>
       <c r="W218" t="inlineStr"/>
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="inlineStr"/>
       <c r="AA218" t="inlineStr"/>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>234.38</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>163.15</t>
-        </is>
+      <c r="AB218" t="n">
+        <v>234.38</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>163.15</v>
       </c>
       <c r="AD218" t="inlineStr"/>
       <c r="AE218" t="inlineStr">
@@ -75304,55 +74968,37 @@
           <t>2021, March 23</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H219" t="n">
+        <v>2021</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 27</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J219" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K219" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L219" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M219" t="n">
+        <v>209</v>
+      </c>
+      <c r="N219" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O219" t="n">
+        <v>720</v>
+      </c>
+      <c r="P219" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>270</v>
       </c>
       <c r="R219" t="inlineStr">
         <is>
@@ -75364,30 +75010,20 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T219" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
+      <c r="T219" t="n">
+        <v>48</v>
+      </c>
+      <c r="U219" t="n">
+        <v>8</v>
+      </c>
+      <c r="V219" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="X219" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="inlineStr"/>
@@ -75687,55 +75323,37 @@
           <t>2021, March 05</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H220" t="n">
+        <v>2021</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 05</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>165.2</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J220" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="K220" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L220" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M220" t="n">
+        <v>190</v>
+      </c>
+      <c r="N220" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O220" t="n">
+        <v>720</v>
+      </c>
+      <c r="P220" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>270</v>
       </c>
       <c r="R220" t="inlineStr">
         <is>
@@ -75747,20 +75365,14 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T220" t="n">
+        <v>13</v>
+      </c>
+      <c r="U220" t="n">
+        <v>5</v>
+      </c>
+      <c r="V220" t="n">
+        <v>5000</v>
       </c>
       <c r="W220" t="inlineStr"/>
       <c r="X220" t="inlineStr"/>
@@ -76062,55 +75674,37 @@
           <t>2021, March 04</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H221" t="n">
+        <v>2021</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 10</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J221" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="K221" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L221" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M221" t="n">
+        <v>186</v>
+      </c>
+      <c r="N221" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P221" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>409</v>
       </c>
       <c r="R221" t="inlineStr">
         <is>
@@ -76122,20 +75716,14 @@
           <t>12GB | 8GB</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
+      <c r="T221" t="n">
+        <v>64</v>
+      </c>
+      <c r="U221" t="n">
+        <v>16</v>
+      </c>
+      <c r="V221" t="n">
+        <v>4500</v>
       </c>
       <c r="W221" t="inlineStr"/>
       <c r="X221" t="inlineStr"/>
@@ -76469,55 +76057,37 @@
           <t>2021, February 24</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H222" t="n">
+        <v>2021</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 04</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>162.2</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P222" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="J222" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="K222" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L222" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>196</v>
+      </c>
+      <c r="N222" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O222" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P222" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>405</v>
       </c>
       <c r="R222" t="inlineStr">
         <is>
@@ -76529,20 +76099,14 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T222" t="n">
+        <v>48</v>
+      </c>
+      <c r="U222" t="n">
+        <v>16</v>
+      </c>
+      <c r="V222" t="n">
+        <v>5000</v>
       </c>
       <c r="W222" t="inlineStr"/>
       <c r="X222" t="inlineStr"/>
@@ -76848,55 +76412,37 @@
           <t>2021, February 24</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H223" t="n">
+        <v>2021</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>Available. Released 2021, March 05</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J223" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K223" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L223" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M223" t="n">
+        <v>205</v>
+      </c>
+      <c r="N223" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O223" t="n">
+        <v>720</v>
+      </c>
+      <c r="P223" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>270</v>
       </c>
       <c r="R223" t="inlineStr">
         <is>
@@ -76908,30 +76454,20 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
+      <c r="T223" t="n">
+        <v>13</v>
+      </c>
+      <c r="U223" t="n">
+        <v>8</v>
+      </c>
+      <c r="V223" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X223" t="n">
+        <v>1.1</v>
       </c>
       <c r="Y223" t="inlineStr"/>
       <c r="Z223" t="inlineStr"/>
@@ -77227,10 +76763,8 @@
           <t>2021, February 05</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H224" t="n">
+        <v>2021</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -77240,30 +76774,20 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="M224" t="n">
+        <v>186</v>
+      </c>
+      <c r="N224" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O224" t="n">
+        <v>720</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>270</v>
       </c>
       <c r="R224" t="inlineStr">
         <is>
@@ -77275,20 +76799,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T224" t="n">
+        <v>13</v>
+      </c>
+      <c r="U224" t="n">
+        <v>8</v>
+      </c>
+      <c r="V224" t="n">
+        <v>5000</v>
       </c>
       <c r="W224" t="inlineStr"/>
       <c r="X224" t="inlineStr"/>
@@ -77590,55 +77108,37 @@
           <t>2021, January 19</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H225" t="n">
+        <v>2021</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
           <t>Available. Released 2021, January 19</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>165.2</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="J225" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="K225" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L225" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M225" t="n">
+        <v>190</v>
+      </c>
+      <c r="N225" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O225" t="n">
+        <v>720</v>
+      </c>
+      <c r="P225" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>270</v>
       </c>
       <c r="R225" t="inlineStr">
         <is>
@@ -77650,30 +77150,20 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="T225" t="n">
+        <v>8</v>
+      </c>
+      <c r="U225" t="n">
+        <v>5</v>
+      </c>
+      <c r="V225" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W225" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X225" t="n">
+        <v>0.5</v>
       </c>
       <c r="Y225" t="inlineStr"/>
       <c r="Z225" t="inlineStr"/>
@@ -78088,6 +77578,2875 @@
       <c r="DL226" t="inlineStr"/>
       <c r="DM226" t="inlineStr"/>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ZTE Axon 10s Pro 5G</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_axon_10s_pro_5g-9998.php</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2020, February 06</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>159.2</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>12GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr"/>
+      <c r="X227" t="inlineStr"/>
+      <c r="Y227" t="inlineStr"/>
+      <c r="Z227" t="inlineStr"/>
+      <c r="AA227" t="inlineStr"/>
+      <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
+      <c r="AE227" t="inlineStr"/>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>Li-Ion 4000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>159.2 x 73.4 x 7.9 mm (6.27 x 2.89 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr"/>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>175 g (6.17 oz)</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr"/>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr"/>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~398 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>6.47 inches, 102.8 cm 2 (~87.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>AMOLED, HDR10</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr"/>
+      <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>2020, February 06</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD227" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 256GB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BE227" t="inlineStr">
+        <is>
+          <t>Blue, Black</t>
+        </is>
+      </c>
+      <c r="BF227" t="inlineStr"/>
+      <c r="BG227" t="inlineStr"/>
+      <c r="BH227" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI227" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ227" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G (2+ Gbps DL)</t>
+        </is>
+      </c>
+      <c r="BK227" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="BL227" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Cortex-A77 &amp; 3x2.42 GHz Cortex-A77 &amp; 4x1.80 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="BM227" t="inlineStr">
+        <is>
+          <t>Android 10, MiFavor 10</t>
+        </is>
+      </c>
+      <c r="BN227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO227" t="inlineStr"/>
+      <c r="BP227" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="BQ227" t="inlineStr">
+        <is>
+          <t>18W wired, QC4 Wireless (Qi)</t>
+        </is>
+      </c>
+      <c r="BR227" t="inlineStr"/>
+      <c r="BS227" t="inlineStr">
+        <is>
+          <t>Glass front, glass back, aluminum frame</t>
+        </is>
+      </c>
+      <c r="BT227" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU227" t="inlineStr"/>
+      <c r="BV227" t="inlineStr"/>
+      <c r="BW227" t="inlineStr"/>
+      <c r="BX227" t="inlineStr"/>
+      <c r="BY227" t="inlineStr"/>
+      <c r="BZ227" t="inlineStr"/>
+      <c r="CA227" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB227" t="inlineStr"/>
+      <c r="CC227" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.7, 28mm (wide), 1/2.0", 0.8µm, PDAF, OIS 8 MP, f/2.4, 80mm (telephoto), PDAF, OIS, 3x optical zoom 20 MP, f/2.2, 125˚, 16mm (ultrawide)</t>
+        </is>
+      </c>
+      <c r="CD227" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE227" t="inlineStr">
+        <is>
+          <t>UFS 3.0</t>
+        </is>
+      </c>
+      <c r="CF227" t="inlineStr"/>
+      <c r="CG227" t="inlineStr"/>
+      <c r="CH227" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CI227" t="inlineStr"/>
+      <c r="CJ227" t="inlineStr"/>
+      <c r="CK227" t="inlineStr"/>
+      <c r="CL227" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 26, 28, 34, 38, 39, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM227" t="inlineStr">
+        <is>
+          <t>41, 78 SA/NSA</t>
+        </is>
+      </c>
+      <c r="CN227" t="inlineStr"/>
+      <c r="CO227" t="inlineStr"/>
+      <c r="CP227" t="inlineStr"/>
+      <c r="CQ227" t="inlineStr"/>
+      <c r="CR227" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8250 Snapdragon 865 5G (7 nm+)</t>
+        </is>
+      </c>
+      <c r="CS227" t="inlineStr">
+        <is>
+          <t>Adreno 650</t>
+        </is>
+      </c>
+      <c r="CT227" t="inlineStr"/>
+      <c r="CU227" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="CV227" t="inlineStr">
+        <is>
+          <t>20 MP, f/2.0, (wide), 1/2.8", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW227" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX227" t="inlineStr">
+        <is>
+          <t>24-bit/192kHz Hi-Res audio</t>
+        </is>
+      </c>
+      <c r="CY227" t="inlineStr"/>
+      <c r="CZ227" t="inlineStr"/>
+      <c r="DA227" t="inlineStr"/>
+      <c r="DB227" t="inlineStr"/>
+      <c r="DC227" t="inlineStr"/>
+      <c r="DD227" t="inlineStr"/>
+      <c r="DE227" t="inlineStr"/>
+      <c r="DF227" t="inlineStr"/>
+      <c r="DG227" t="inlineStr"/>
+      <c r="DH227" t="inlineStr"/>
+      <c r="DI227" t="inlineStr"/>
+      <c r="DJ227" t="inlineStr"/>
+      <c r="DK227" t="inlineStr"/>
+      <c r="DL227" t="inlineStr"/>
+      <c r="DM227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ZTE Cymbal 2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_cymbal_2-11705.php</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2020, January. Released 2020, January</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr"/>
+      <c r="X228" t="inlineStr"/>
+      <c r="Y228" t="inlineStr"/>
+      <c r="Z228" t="inlineStr"/>
+      <c r="AA228" t="inlineStr"/>
+      <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr"/>
+      <c r="AD228" t="inlineStr"/>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>Li-Ion 1600 mAh, removable</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>109 x 56 x 19.5 mm (4.29 x 2.20 x 0.77 in)</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr"/>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>135 g (4.76 oz)</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr"/>
+      <c r="AN228" t="inlineStr">
+        <is>
+          <t>4.2, A2DP</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr"/>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr">
+        <is>
+          <t>Cover display: TFT LCD, 1.77 inches</t>
+        </is>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~143 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>2.8 inches, 24.3 cm 2 (~39.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>TFT LCD</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr"/>
+      <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>2020, January. Released 2020, January</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BD228" t="inlineStr">
+        <is>
+          <t>8GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BE228" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF228" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="BG228" t="inlineStr"/>
+      <c r="BH228" t="inlineStr">
+        <is>
+          <t>GSM 850 / 1900</t>
+        </is>
+      </c>
+      <c r="BI228" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900</t>
+        </is>
+      </c>
+      <c r="BJ228" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK228" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL228" t="inlineStr">
+        <is>
+          <t>Quad-core 1.3 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="BM228" t="inlineStr">
+        <is>
+          <t>Linux 3.18.71</t>
+        </is>
+      </c>
+      <c r="BN228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO228" t="inlineStr"/>
+      <c r="BP228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ228" t="inlineStr"/>
+      <c r="BR228" t="inlineStr"/>
+      <c r="BS228" t="inlineStr"/>
+      <c r="BT228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU228" t="inlineStr"/>
+      <c r="BV228" t="inlineStr"/>
+      <c r="BW228" t="inlineStr"/>
+      <c r="BX228" t="inlineStr"/>
+      <c r="BY228" t="inlineStr"/>
+      <c r="BZ228" t="inlineStr"/>
+      <c r="CA228" t="inlineStr"/>
+      <c r="CB228" t="inlineStr"/>
+      <c r="CC228" t="inlineStr"/>
+      <c r="CD228" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="CE228" t="inlineStr"/>
+      <c r="CF228" t="inlineStr"/>
+      <c r="CG228" t="inlineStr"/>
+      <c r="CH228" t="inlineStr"/>
+      <c r="CI228" t="inlineStr"/>
+      <c r="CJ228" t="inlineStr"/>
+      <c r="CK228" t="inlineStr"/>
+      <c r="CL228" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 7, 12, 13, 66</t>
+        </is>
+      </c>
+      <c r="CM228" t="inlineStr"/>
+      <c r="CN228" t="inlineStr"/>
+      <c r="CO228" t="inlineStr"/>
+      <c r="CP228" t="inlineStr"/>
+      <c r="CQ228" t="inlineStr"/>
+      <c r="CR228" t="inlineStr">
+        <is>
+          <t>Qualcomm QM215 Snapdragon 215 (28 nm)</t>
+        </is>
+      </c>
+      <c r="CS228" t="inlineStr">
+        <is>
+          <t>Adreno 308</t>
+        </is>
+      </c>
+      <c r="CT228" t="inlineStr"/>
+      <c r="CU228" t="inlineStr"/>
+      <c r="CV228" t="inlineStr"/>
+      <c r="CW228" t="inlineStr"/>
+      <c r="CX228" t="inlineStr"/>
+      <c r="CY228" t="inlineStr"/>
+      <c r="CZ228" t="inlineStr"/>
+      <c r="DA228" t="inlineStr"/>
+      <c r="DB228" t="inlineStr"/>
+      <c r="DC228" t="inlineStr"/>
+      <c r="DD228" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="DE228" t="inlineStr"/>
+      <c r="DF228" t="inlineStr"/>
+      <c r="DG228" t="inlineStr"/>
+      <c r="DH228" t="inlineStr"/>
+      <c r="DI228" t="inlineStr"/>
+      <c r="DJ228" t="inlineStr"/>
+      <c r="DK228" t="inlineStr"/>
+      <c r="DL228" t="inlineStr"/>
+      <c r="DM228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ZTE Blade Max View</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_max_view-10070.php</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2019. Released 2019</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>163.1</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>3GB</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>Li-Po 4000 mAh</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>163.1 x 74.9 x 8.1 mm (6.42 x 2.95 x 0.32 in)</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr"/>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>160 g (5.64 oz)</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr"/>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr"/>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>1080 x 2160 pixels, 18:9 ratio (~402 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>6.0 inches, 92.9 cm 2 (~76.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr"/>
+      <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>2019. Released 2019</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>microSDXC</t>
+        </is>
+      </c>
+      <c r="BD229" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BE229" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF229" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG229" t="inlineStr"/>
+      <c r="BH229" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI229" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1700(AWS) / 1900</t>
+        </is>
+      </c>
+      <c r="BJ229" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (2CA) Cat6 300/50 Mbps</t>
+        </is>
+      </c>
+      <c r="BK229" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="BL229" t="inlineStr">
+        <is>
+          <t>Octa-core 1.4 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="BM229" t="inlineStr">
+        <is>
+          <t>Android 7.1.1 (Nougat), upgradable to Android 8.1 (Oreo)</t>
+        </is>
+      </c>
+      <c r="BN229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO229" t="inlineStr"/>
+      <c r="BP229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ229" t="inlineStr"/>
+      <c r="BR229" t="inlineStr"/>
+      <c r="BS229" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU229" t="inlineStr"/>
+      <c r="BV229" t="inlineStr"/>
+      <c r="BW229" t="inlineStr"/>
+      <c r="BX229" t="inlineStr"/>
+      <c r="BY229" t="inlineStr"/>
+      <c r="BZ229" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, 25mm (wide), 1/3.1", 1.0µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA229" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB229" t="inlineStr"/>
+      <c r="CC229" t="inlineStr"/>
+      <c r="CD229" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE229" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF229" t="inlineStr">
+        <is>
+          <t>Z610DL</t>
+        </is>
+      </c>
+      <c r="CG229" t="inlineStr"/>
+      <c r="CH229" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CI229" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ229" t="inlineStr"/>
+      <c r="CK229" t="inlineStr"/>
+      <c r="CL229" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 13, 66</t>
+        </is>
+      </c>
+      <c r="CM229" t="inlineStr"/>
+      <c r="CN229" t="inlineStr"/>
+      <c r="CO229" t="inlineStr"/>
+      <c r="CP229" t="inlineStr"/>
+      <c r="CQ229" t="inlineStr"/>
+      <c r="CR229" t="inlineStr">
+        <is>
+          <t>Qualcomm MSM8940 Snapdragon 435 (28 nm)</t>
+        </is>
+      </c>
+      <c r="CS229" t="inlineStr">
+        <is>
+          <t>Adreno 505</t>
+        </is>
+      </c>
+      <c r="CT229" t="inlineStr"/>
+      <c r="CU229" t="inlineStr"/>
+      <c r="CV229" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="CW229" t="inlineStr"/>
+      <c r="CX229" t="inlineStr"/>
+      <c r="CY229" t="inlineStr"/>
+      <c r="CZ229" t="inlineStr"/>
+      <c r="DA229" t="inlineStr"/>
+      <c r="DB229" t="inlineStr"/>
+      <c r="DC229" t="inlineStr"/>
+      <c r="DD229" t="inlineStr"/>
+      <c r="DE229" t="inlineStr"/>
+      <c r="DF229" t="inlineStr"/>
+      <c r="DG229" t="inlineStr"/>
+      <c r="DH229" t="inlineStr"/>
+      <c r="DI229" t="inlineStr"/>
+      <c r="DJ229" t="inlineStr"/>
+      <c r="DK229" t="inlineStr"/>
+      <c r="DL229" t="inlineStr"/>
+      <c r="DM229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ZTE Blade A7 Prime</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_a7_prime-9955.php</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2019, November. Released 2019, November</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>156.7</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>3GB</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
+      <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>Li-Po 3200 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>156.7 x 72.9 x 8.1 mm (6.17 x 2.87 x 0.32 in)</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr"/>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>165 g (5.82 oz)</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr"/>
+      <c r="AN230" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr"/>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>720 x 1560 pixels, 19.5:9 ratio (~282 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>6.09 inches, 91.0 cm 2 (~79.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr"/>
+      <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>2019, November. Released 2019, November</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD230" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BE230" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="BF230" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="BG230" t="inlineStr"/>
+      <c r="BH230" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI230" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ230" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="BK230" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL230" t="inlineStr">
+        <is>
+          <t>Quad-core 2.0 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="BM230" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie)</t>
+        </is>
+      </c>
+      <c r="BN230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO230" t="inlineStr"/>
+      <c r="BP230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ230" t="inlineStr"/>
+      <c r="BR230" t="inlineStr"/>
+      <c r="BS230" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU230" t="inlineStr"/>
+      <c r="BV230" t="inlineStr"/>
+      <c r="BW230" t="inlineStr"/>
+      <c r="BX230" t="inlineStr"/>
+      <c r="BY230" t="inlineStr"/>
+      <c r="BZ230" t="inlineStr"/>
+      <c r="CA230" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB230" t="inlineStr"/>
+      <c r="CC230" t="inlineStr"/>
+      <c r="CD230" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE230" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF230" t="inlineStr"/>
+      <c r="CG230" t="inlineStr"/>
+      <c r="CH230" t="inlineStr"/>
+      <c r="CI230" t="inlineStr"/>
+      <c r="CJ230" t="inlineStr"/>
+      <c r="CK230" t="inlineStr"/>
+      <c r="CL230" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 13</t>
+        </is>
+      </c>
+      <c r="CM230" t="inlineStr"/>
+      <c r="CN230" t="inlineStr"/>
+      <c r="CO230" t="inlineStr"/>
+      <c r="CP230" t="inlineStr"/>
+      <c r="CQ230" t="inlineStr"/>
+      <c r="CR230" t="inlineStr">
+        <is>
+          <t>Mediatek MT6761 Helio A22 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS230" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CT230" t="inlineStr"/>
+      <c r="CU230" t="inlineStr"/>
+      <c r="CV230" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2</t>
+        </is>
+      </c>
+      <c r="CW230" t="inlineStr"/>
+      <c r="CX230" t="inlineStr"/>
+      <c r="CY230" t="inlineStr"/>
+      <c r="CZ230" t="inlineStr"/>
+      <c r="DA230" t="inlineStr"/>
+      <c r="DB230" t="inlineStr"/>
+      <c r="DC230" t="inlineStr"/>
+      <c r="DD230" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, PDAF</t>
+        </is>
+      </c>
+      <c r="DE230" t="inlineStr"/>
+      <c r="DF230" t="inlineStr"/>
+      <c r="DG230" t="inlineStr"/>
+      <c r="DH230" t="inlineStr"/>
+      <c r="DI230" t="inlineStr"/>
+      <c r="DJ230" t="inlineStr"/>
+      <c r="DK230" t="inlineStr"/>
+      <c r="DL230" t="inlineStr"/>
+      <c r="DM230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ZTE Blade 10 Prime</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_10_prime-9954.php</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2019, November. Released 2019, November</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>3GB</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="inlineStr"/>
+      <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>About 160 EUR</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>Li-Po 3200 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>158 x 75.2 x 7.9 mm (6.22 x 2.96 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr"/>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>165 g (5.82 oz)</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr"/>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr"/>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>1080 x 2280 pixels, 19:9 ratio (~400 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>6.3 inches, 99.1 cm 2 (~83.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr"/>
+      <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>2019, November. Released 2019, November</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD231" t="inlineStr">
+        <is>
+          <t>64GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BE231" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BF231" t="inlineStr">
+        <is>
+          <t>About 160 EUR</t>
+        </is>
+      </c>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI231" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ231" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (2CA) Cat6 300/50 Mbps</t>
+        </is>
+      </c>
+      <c r="BK231" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="BL231" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A73 &amp; 4x2.0 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM231" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie)</t>
+        </is>
+      </c>
+      <c r="BN231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO231" t="inlineStr"/>
+      <c r="BP231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ231" t="inlineStr">
+        <is>
+          <t>18W wired, PD2.0</t>
+        </is>
+      </c>
+      <c r="BR231" t="inlineStr"/>
+      <c r="BS231" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU231" t="inlineStr"/>
+      <c r="BV231" t="inlineStr"/>
+      <c r="BW231" t="inlineStr"/>
+      <c r="BX231" t="inlineStr"/>
+      <c r="BY231" t="inlineStr"/>
+      <c r="BZ231" t="inlineStr">
+        <is>
+          <t>16 MP, f/1.8, 1/2.8", 1.12µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA231" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB231" t="inlineStr"/>
+      <c r="CC231" t="inlineStr"/>
+      <c r="CD231" t="inlineStr">
+        <is>
+          <t>1080p@30fps (gyro-EIS)</t>
+        </is>
+      </c>
+      <c r="CE231" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF231" t="inlineStr">
+        <is>
+          <t>Z6530, Z6530M, Z6530V</t>
+        </is>
+      </c>
+      <c r="CG231" t="inlineStr"/>
+      <c r="CH231" t="inlineStr"/>
+      <c r="CI231" t="inlineStr"/>
+      <c r="CJ231" t="inlineStr"/>
+      <c r="CK231" t="inlineStr"/>
+      <c r="CL231" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 13, 66</t>
+        </is>
+      </c>
+      <c r="CM231" t="inlineStr"/>
+      <c r="CN231" t="inlineStr"/>
+      <c r="CO231" t="inlineStr"/>
+      <c r="CP231" t="inlineStr"/>
+      <c r="CQ231" t="inlineStr"/>
+      <c r="CR231" t="inlineStr">
+        <is>
+          <t>Mediatek MT6771 Helio P60 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS231" t="inlineStr">
+        <is>
+          <t>Mali-G72 MP3</t>
+        </is>
+      </c>
+      <c r="CT231" t="inlineStr"/>
+      <c r="CU231" t="inlineStr"/>
+      <c r="CV231" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, 26mm (wide), 1/3.06", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CW231" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX231" t="inlineStr"/>
+      <c r="CY231" t="inlineStr"/>
+      <c r="CZ231" t="inlineStr"/>
+      <c r="DA231" t="inlineStr"/>
+      <c r="DB231" t="inlineStr"/>
+      <c r="DC231" t="inlineStr"/>
+      <c r="DD231" t="inlineStr"/>
+      <c r="DE231" t="inlineStr"/>
+      <c r="DF231" t="inlineStr"/>
+      <c r="DG231" t="inlineStr"/>
+      <c r="DH231" t="inlineStr"/>
+      <c r="DI231" t="inlineStr"/>
+      <c r="DJ231" t="inlineStr"/>
+      <c r="DK231" t="inlineStr"/>
+      <c r="DL231" t="inlineStr"/>
+      <c r="DM231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Blade Vantage 2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_vantage_2-11731.php</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="inlineStr"/>
+      <c r="Y232" t="inlineStr"/>
+      <c r="Z232" t="inlineStr"/>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
+      <c r="AE232" t="inlineStr"/>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr"/>
+      <c r="AJ232" t="inlineStr"/>
+      <c r="AK232" t="inlineStr"/>
+      <c r="AL232" t="inlineStr"/>
+      <c r="AM232" t="inlineStr"/>
+      <c r="AN232" t="inlineStr"/>
+      <c r="AO232" t="inlineStr"/>
+      <c r="AP232" t="inlineStr"/>
+      <c r="AQ232" t="inlineStr"/>
+      <c r="AR232" t="inlineStr"/>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AU232" t="inlineStr"/>
+      <c r="AV232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr"/>
+      <c r="AX232" t="inlineStr"/>
+      <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr"/>
+      <c r="BA232" t="inlineStr"/>
+      <c r="BB232" t="inlineStr"/>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
+      <c r="BO232" t="inlineStr"/>
+      <c r="BP232" t="inlineStr"/>
+      <c r="BQ232" t="inlineStr"/>
+      <c r="BR232" t="inlineStr"/>
+      <c r="BS232" t="inlineStr"/>
+      <c r="BT232" t="inlineStr"/>
+      <c r="BU232" t="inlineStr"/>
+      <c r="BV232" t="inlineStr"/>
+      <c r="BW232" t="inlineStr"/>
+      <c r="BX232" t="inlineStr"/>
+      <c r="BY232" t="inlineStr"/>
+      <c r="BZ232" t="inlineStr"/>
+      <c r="CA232" t="inlineStr"/>
+      <c r="CB232" t="inlineStr"/>
+      <c r="CC232" t="inlineStr"/>
+      <c r="CD232" t="inlineStr"/>
+      <c r="CE232" t="inlineStr"/>
+      <c r="CF232" t="inlineStr"/>
+      <c r="CG232" t="inlineStr"/>
+      <c r="CH232" t="inlineStr"/>
+      <c r="CI232" t="inlineStr"/>
+      <c r="CJ232" t="inlineStr"/>
+      <c r="CK232" t="inlineStr"/>
+      <c r="CL232" t="inlineStr"/>
+      <c r="CM232" t="inlineStr"/>
+      <c r="CN232" t="inlineStr"/>
+      <c r="CO232" t="inlineStr"/>
+      <c r="CP232" t="inlineStr"/>
+      <c r="CQ232" t="inlineStr"/>
+      <c r="CR232" t="inlineStr"/>
+      <c r="CS232" t="inlineStr"/>
+      <c r="CT232" t="inlineStr"/>
+      <c r="CU232" t="inlineStr"/>
+      <c r="CV232" t="inlineStr"/>
+      <c r="CW232" t="inlineStr"/>
+      <c r="CX232" t="inlineStr"/>
+      <c r="CY232" t="inlineStr"/>
+      <c r="CZ232" t="inlineStr"/>
+      <c r="DA232" t="inlineStr"/>
+      <c r="DB232" t="inlineStr"/>
+      <c r="DC232" t="inlineStr"/>
+      <c r="DD232" t="inlineStr"/>
+      <c r="DE232" t="inlineStr"/>
+      <c r="DF232" t="inlineStr"/>
+      <c r="DG232" t="inlineStr"/>
+      <c r="DH232" t="inlineStr"/>
+      <c r="DI232" t="inlineStr"/>
+      <c r="DJ232" t="inlineStr"/>
+      <c r="DK232" t="inlineStr"/>
+      <c r="DL232" t="inlineStr"/>
+      <c r="DM232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ZTE Blade 20</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_20-9921.php</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2019, October. Released 2019, October</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>162.9</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>6.49</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>128GB</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr"/>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr"/>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>162.9 x 76.6 x 9 mm (6.41 x 3.02 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr"/>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>190 g (6.70 oz)</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr"/>
+      <c r="AN233" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr"/>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>FM radio, recording</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>720 x 1560 pixels, 19.5:9 ratio (~265 ppi density)</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>6.49 inches, 103.4 cm 2 (~82.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr"/>
+      <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>2019, October. Released 2019, October</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BD233" t="inlineStr">
+        <is>
+          <t>128GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BE233" t="inlineStr">
+        <is>
+          <t>Turquoise, Magic red</t>
+        </is>
+      </c>
+      <c r="BF233" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="BI233" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="BJ233" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="BK233" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="BL233" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A73 &amp; 4x2.0 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="BM233" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie)</t>
+        </is>
+      </c>
+      <c r="BN233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO233" t="inlineStr"/>
+      <c r="BP233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BQ233" t="inlineStr">
+        <is>
+          <t>18W wired</t>
+        </is>
+      </c>
+      <c r="BR233" t="inlineStr"/>
+      <c r="BS233" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="BT233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BU233" t="inlineStr"/>
+      <c r="BV233" t="inlineStr"/>
+      <c r="BW233" t="inlineStr"/>
+      <c r="BX233" t="inlineStr"/>
+      <c r="BY233" t="inlineStr"/>
+      <c r="BZ233" t="inlineStr">
+        <is>
+          <t>16 MP, f/1.8, (wide), PDAF 8 MP, f/2.2, 12mm (ultrawide) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="CA233" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="CB233" t="inlineStr"/>
+      <c r="CC233" t="inlineStr"/>
+      <c r="CD233" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CE233" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="CF233" t="inlineStr">
+        <is>
+          <t>V1050</t>
+        </is>
+      </c>
+      <c r="CG233" t="inlineStr"/>
+      <c r="CH233" t="inlineStr">
+        <is>
+          <t>CDMA 800</t>
+        </is>
+      </c>
+      <c r="CI233" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CJ233" t="inlineStr"/>
+      <c r="CK233" t="inlineStr"/>
+      <c r="CL233" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CM233" t="inlineStr"/>
+      <c r="CN233" t="inlineStr"/>
+      <c r="CO233" t="inlineStr"/>
+      <c r="CP233" t="inlineStr"/>
+      <c r="CQ233" t="inlineStr"/>
+      <c r="CR233" t="inlineStr">
+        <is>
+          <t>Mediatek MT6771 Helio P60 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CS233" t="inlineStr">
+        <is>
+          <t>Mali-G72 MP3</t>
+        </is>
+      </c>
+      <c r="CT233" t="inlineStr"/>
+      <c r="CU233" t="inlineStr"/>
+      <c r="CV233" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0</t>
+        </is>
+      </c>
+      <c r="CW233" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CX233" t="inlineStr"/>
+      <c r="CY233" t="inlineStr"/>
+      <c r="CZ233" t="inlineStr"/>
+      <c r="DA233" t="inlineStr"/>
+      <c r="DB233" t="inlineStr"/>
+      <c r="DC233" t="inlineStr"/>
+      <c r="DD233" t="inlineStr"/>
+      <c r="DE233" t="inlineStr"/>
+      <c r="DF233" t="inlineStr"/>
+      <c r="DG233" t="inlineStr"/>
+      <c r="DH233" t="inlineStr"/>
+      <c r="DI233" t="inlineStr"/>
+      <c r="DJ233" t="inlineStr"/>
+      <c r="DK233" t="inlineStr"/>
+      <c r="DL233" t="inlineStr"/>
+      <c r="DM233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>nubia RedMagic 3S</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_nubia_red_magic_3s-9839.php</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr"/>
+      <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr"/>
+      <c r="AD234" t="inlineStr"/>
+      <c r="AE234" t="inlineStr"/>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr"/>
+      <c r="AI234" t="inlineStr"/>
+      <c r="AJ234" t="inlineStr"/>
+      <c r="AK234" t="inlineStr"/>
+      <c r="AL234" t="inlineStr"/>
+      <c r="AM234" t="inlineStr"/>
+      <c r="AN234" t="inlineStr"/>
+      <c r="AO234" t="inlineStr"/>
+      <c r="AP234" t="inlineStr"/>
+      <c r="AQ234" t="inlineStr"/>
+      <c r="AR234" t="inlineStr"/>
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AU234" t="inlineStr"/>
+      <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr"/>
+      <c r="AX234" t="inlineStr"/>
+      <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr"/>
+      <c r="BA234" t="inlineStr"/>
+      <c r="BB234" t="inlineStr"/>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="inlineStr"/>
+      <c r="BM234" t="inlineStr"/>
+      <c r="BN234" t="inlineStr"/>
+      <c r="BO234" t="inlineStr"/>
+      <c r="BP234" t="inlineStr"/>
+      <c r="BQ234" t="inlineStr"/>
+      <c r="BR234" t="inlineStr"/>
+      <c r="BS234" t="inlineStr"/>
+      <c r="BT234" t="inlineStr"/>
+      <c r="BU234" t="inlineStr"/>
+      <c r="BV234" t="inlineStr"/>
+      <c r="BW234" t="inlineStr"/>
+      <c r="BX234" t="inlineStr"/>
+      <c r="BY234" t="inlineStr"/>
+      <c r="BZ234" t="inlineStr"/>
+      <c r="CA234" t="inlineStr"/>
+      <c r="CB234" t="inlineStr"/>
+      <c r="CC234" t="inlineStr"/>
+      <c r="CD234" t="inlineStr"/>
+      <c r="CE234" t="inlineStr"/>
+      <c r="CF234" t="inlineStr"/>
+      <c r="CG234" t="inlineStr"/>
+      <c r="CH234" t="inlineStr"/>
+      <c r="CI234" t="inlineStr"/>
+      <c r="CJ234" t="inlineStr"/>
+      <c r="CK234" t="inlineStr"/>
+      <c r="CL234" t="inlineStr"/>
+      <c r="CM234" t="inlineStr"/>
+      <c r="CN234" t="inlineStr"/>
+      <c r="CO234" t="inlineStr"/>
+      <c r="CP234" t="inlineStr"/>
+      <c r="CQ234" t="inlineStr"/>
+      <c r="CR234" t="inlineStr"/>
+      <c r="CS234" t="inlineStr"/>
+      <c r="CT234" t="inlineStr"/>
+      <c r="CU234" t="inlineStr"/>
+      <c r="CV234" t="inlineStr"/>
+      <c r="CW234" t="inlineStr"/>
+      <c r="CX234" t="inlineStr"/>
+      <c r="CY234" t="inlineStr"/>
+      <c r="CZ234" t="inlineStr"/>
+      <c r="DA234" t="inlineStr"/>
+      <c r="DB234" t="inlineStr"/>
+      <c r="DC234" t="inlineStr"/>
+      <c r="DD234" t="inlineStr"/>
+      <c r="DE234" t="inlineStr"/>
+      <c r="DF234" t="inlineStr"/>
+      <c r="DG234" t="inlineStr"/>
+      <c r="DH234" t="inlineStr"/>
+      <c r="DI234" t="inlineStr"/>
+      <c r="DJ234" t="inlineStr"/>
+      <c r="DK234" t="inlineStr"/>
+      <c r="DL234" t="inlineStr"/>
+      <c r="DM234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>nubia Z20</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_nubia_z20-9780.php</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
+      <c r="W235" t="inlineStr"/>
+      <c r="X235" t="inlineStr"/>
+      <c r="Y235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr"/>
+      <c r="AA235" t="inlineStr"/>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr"/>
+      <c r="AD235" t="inlineStr"/>
+      <c r="AE235" t="inlineStr"/>
+      <c r="AF235" t="inlineStr"/>
+      <c r="AG235" t="inlineStr"/>
+      <c r="AH235" t="inlineStr"/>
+      <c r="AI235" t="inlineStr"/>
+      <c r="AJ235" t="inlineStr"/>
+      <c r="AK235" t="inlineStr"/>
+      <c r="AL235" t="inlineStr"/>
+      <c r="AM235" t="inlineStr"/>
+      <c r="AN235" t="inlineStr"/>
+      <c r="AO235" t="inlineStr"/>
+      <c r="AP235" t="inlineStr"/>
+      <c r="AQ235" t="inlineStr"/>
+      <c r="AR235" t="inlineStr"/>
+      <c r="AS235" t="inlineStr"/>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AU235" t="inlineStr"/>
+      <c r="AV235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr"/>
+      <c r="AX235" t="inlineStr"/>
+      <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr"/>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
+      <c r="BO235" t="inlineStr"/>
+      <c r="BP235" t="inlineStr"/>
+      <c r="BQ235" t="inlineStr"/>
+      <c r="BR235" t="inlineStr"/>
+      <c r="BS235" t="inlineStr"/>
+      <c r="BT235" t="inlineStr"/>
+      <c r="BU235" t="inlineStr"/>
+      <c r="BV235" t="inlineStr"/>
+      <c r="BW235" t="inlineStr"/>
+      <c r="BX235" t="inlineStr"/>
+      <c r="BY235" t="inlineStr"/>
+      <c r="BZ235" t="inlineStr"/>
+      <c r="CA235" t="inlineStr"/>
+      <c r="CB235" t="inlineStr"/>
+      <c r="CC235" t="inlineStr"/>
+      <c r="CD235" t="inlineStr"/>
+      <c r="CE235" t="inlineStr"/>
+      <c r="CF235" t="inlineStr"/>
+      <c r="CG235" t="inlineStr"/>
+      <c r="CH235" t="inlineStr"/>
+      <c r="CI235" t="inlineStr"/>
+      <c r="CJ235" t="inlineStr"/>
+      <c r="CK235" t="inlineStr"/>
+      <c r="CL235" t="inlineStr"/>
+      <c r="CM235" t="inlineStr"/>
+      <c r="CN235" t="inlineStr"/>
+      <c r="CO235" t="inlineStr"/>
+      <c r="CP235" t="inlineStr"/>
+      <c r="CQ235" t="inlineStr"/>
+      <c r="CR235" t="inlineStr"/>
+      <c r="CS235" t="inlineStr"/>
+      <c r="CT235" t="inlineStr"/>
+      <c r="CU235" t="inlineStr"/>
+      <c r="CV235" t="inlineStr"/>
+      <c r="CW235" t="inlineStr"/>
+      <c r="CX235" t="inlineStr"/>
+      <c r="CY235" t="inlineStr"/>
+      <c r="CZ235" t="inlineStr"/>
+      <c r="DA235" t="inlineStr"/>
+      <c r="DB235" t="inlineStr"/>
+      <c r="DC235" t="inlineStr"/>
+      <c r="DD235" t="inlineStr"/>
+      <c r="DE235" t="inlineStr"/>
+      <c r="DF235" t="inlineStr"/>
+      <c r="DG235" t="inlineStr"/>
+      <c r="DH235" t="inlineStr"/>
+      <c r="DI235" t="inlineStr"/>
+      <c r="DJ235" t="inlineStr"/>
+      <c r="DK235" t="inlineStr"/>
+      <c r="DL235" t="inlineStr"/>
+      <c r="DM235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Blade A5 (2019)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_a5_(2019)-9712.php</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr"/>
+      <c r="W236" t="inlineStr"/>
+      <c r="X236" t="inlineStr"/>
+      <c r="Y236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="inlineStr"/>
+      <c r="AB236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
+      <c r="AE236" t="inlineStr"/>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="inlineStr"/>
+      <c r="AJ236" t="inlineStr"/>
+      <c r="AK236" t="inlineStr"/>
+      <c r="AL236" t="inlineStr"/>
+      <c r="AM236" t="inlineStr"/>
+      <c r="AN236" t="inlineStr"/>
+      <c r="AO236" t="inlineStr"/>
+      <c r="AP236" t="inlineStr"/>
+      <c r="AQ236" t="inlineStr"/>
+      <c r="AR236" t="inlineStr"/>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AU236" t="inlineStr"/>
+      <c r="AV236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr"/>
+      <c r="AX236" t="inlineStr"/>
+      <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr"/>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="inlineStr"/>
+      <c r="BD236" t="inlineStr"/>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+      <c r="BO236" t="inlineStr"/>
+      <c r="BP236" t="inlineStr"/>
+      <c r="BQ236" t="inlineStr"/>
+      <c r="BR236" t="inlineStr"/>
+      <c r="BS236" t="inlineStr"/>
+      <c r="BT236" t="inlineStr"/>
+      <c r="BU236" t="inlineStr"/>
+      <c r="BV236" t="inlineStr"/>
+      <c r="BW236" t="inlineStr"/>
+      <c r="BX236" t="inlineStr"/>
+      <c r="BY236" t="inlineStr"/>
+      <c r="BZ236" t="inlineStr"/>
+      <c r="CA236" t="inlineStr"/>
+      <c r="CB236" t="inlineStr"/>
+      <c r="CC236" t="inlineStr"/>
+      <c r="CD236" t="inlineStr"/>
+      <c r="CE236" t="inlineStr"/>
+      <c r="CF236" t="inlineStr"/>
+      <c r="CG236" t="inlineStr"/>
+      <c r="CH236" t="inlineStr"/>
+      <c r="CI236" t="inlineStr"/>
+      <c r="CJ236" t="inlineStr"/>
+      <c r="CK236" t="inlineStr"/>
+      <c r="CL236" t="inlineStr"/>
+      <c r="CM236" t="inlineStr"/>
+      <c r="CN236" t="inlineStr"/>
+      <c r="CO236" t="inlineStr"/>
+      <c r="CP236" t="inlineStr"/>
+      <c r="CQ236" t="inlineStr"/>
+      <c r="CR236" t="inlineStr"/>
+      <c r="CS236" t="inlineStr"/>
+      <c r="CT236" t="inlineStr"/>
+      <c r="CU236" t="inlineStr"/>
+      <c r="CV236" t="inlineStr"/>
+      <c r="CW236" t="inlineStr"/>
+      <c r="CX236" t="inlineStr"/>
+      <c r="CY236" t="inlineStr"/>
+      <c r="CZ236" t="inlineStr"/>
+      <c r="DA236" t="inlineStr"/>
+      <c r="DB236" t="inlineStr"/>
+      <c r="DC236" t="inlineStr"/>
+      <c r="DD236" t="inlineStr"/>
+      <c r="DE236" t="inlineStr"/>
+      <c r="DF236" t="inlineStr"/>
+      <c r="DG236" t="inlineStr"/>
+      <c r="DH236" t="inlineStr"/>
+      <c r="DI236" t="inlineStr"/>
+      <c r="DJ236" t="inlineStr"/>
+      <c r="DK236" t="inlineStr"/>
+      <c r="DL236" t="inlineStr"/>
+      <c r="DM236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Blade A3 (2019)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/zte_blade_a3_(2019)-9713.php</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:09 UTC</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr"/>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="inlineStr"/>
+      <c r="Y237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
+      <c r="AE237" t="inlineStr"/>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr"/>
+      <c r="AJ237" t="inlineStr"/>
+      <c r="AK237" t="inlineStr"/>
+      <c r="AL237" t="inlineStr"/>
+      <c r="AM237" t="inlineStr"/>
+      <c r="AN237" t="inlineStr"/>
+      <c r="AO237" t="inlineStr"/>
+      <c r="AP237" t="inlineStr"/>
+      <c r="AQ237" t="inlineStr"/>
+      <c r="AR237" t="inlineStr"/>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AU237" t="inlineStr"/>
+      <c r="AV237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr"/>
+      <c r="AX237" t="inlineStr"/>
+      <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr"/>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="inlineStr"/>
+      <c r="BD237" t="inlineStr"/>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="inlineStr"/>
+      <c r="BM237" t="inlineStr"/>
+      <c r="BN237" t="inlineStr"/>
+      <c r="BO237" t="inlineStr"/>
+      <c r="BP237" t="inlineStr"/>
+      <c r="BQ237" t="inlineStr"/>
+      <c r="BR237" t="inlineStr"/>
+      <c r="BS237" t="inlineStr"/>
+      <c r="BT237" t="inlineStr"/>
+      <c r="BU237" t="inlineStr"/>
+      <c r="BV237" t="inlineStr"/>
+      <c r="BW237" t="inlineStr"/>
+      <c r="BX237" t="inlineStr"/>
+      <c r="BY237" t="inlineStr"/>
+      <c r="BZ237" t="inlineStr"/>
+      <c r="CA237" t="inlineStr"/>
+      <c r="CB237" t="inlineStr"/>
+      <c r="CC237" t="inlineStr"/>
+      <c r="CD237" t="inlineStr"/>
+      <c r="CE237" t="inlineStr"/>
+      <c r="CF237" t="inlineStr"/>
+      <c r="CG237" t="inlineStr"/>
+      <c r="CH237" t="inlineStr"/>
+      <c r="CI237" t="inlineStr"/>
+      <c r="CJ237" t="inlineStr"/>
+      <c r="CK237" t="inlineStr"/>
+      <c r="CL237" t="inlineStr"/>
+      <c r="CM237" t="inlineStr"/>
+      <c r="CN237" t="inlineStr"/>
+      <c r="CO237" t="inlineStr"/>
+      <c r="CP237" t="inlineStr"/>
+      <c r="CQ237" t="inlineStr"/>
+      <c r="CR237" t="inlineStr"/>
+      <c r="CS237" t="inlineStr"/>
+      <c r="CT237" t="inlineStr"/>
+      <c r="CU237" t="inlineStr"/>
+      <c r="CV237" t="inlineStr"/>
+      <c r="CW237" t="inlineStr"/>
+      <c r="CX237" t="inlineStr"/>
+      <c r="CY237" t="inlineStr"/>
+      <c r="CZ237" t="inlineStr"/>
+      <c r="DA237" t="inlineStr"/>
+      <c r="DB237" t="inlineStr"/>
+      <c r="DC237" t="inlineStr"/>
+      <c r="DD237" t="inlineStr"/>
+      <c r="DE237" t="inlineStr"/>
+      <c r="DF237" t="inlineStr"/>
+      <c r="DG237" t="inlineStr"/>
+      <c r="DH237" t="inlineStr"/>
+      <c r="DI237" t="inlineStr"/>
+      <c r="DJ237" t="inlineStr"/>
+      <c r="DK237" t="inlineStr"/>
+      <c r="DL237" t="inlineStr"/>
+      <c r="DM237" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
